--- a/results/scraped_Cape_Town_Senior_Care.xlsx
+++ b/results/scraped_Cape_Town_Senior_Care.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="333">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -52,112 +52,112 @@
     <t>OLDDefinition &amp; Meaning - Merriam-Webster</t>
   </si>
   <si>
+    <t>Old-Official Trailer[HD] - YouTube</t>
+  </si>
+  <si>
+    <t>Old| Rotten Tomatoes</t>
+  </si>
+  <si>
     <t>Old- YouTube</t>
   </si>
   <si>
-    <t>Old| Rotten Tomatoes</t>
-  </si>
-  <si>
-    <t>Old-Official Trailer[HD] - YouTube</t>
-  </si>
-  <si>
     <t>OLD| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>Old(2021) - Full cast &amp; crew - IMDb</t>
-  </si>
-  <si>
     <t>WatchOld| Netflix</t>
   </si>
   <si>
+    <t>Old| Universal Pictures At Home</t>
+  </si>
+  <si>
     <t>Retirement benefits| SSA</t>
   </si>
   <si>
+    <t>Retirement- News, Advice &amp; Resources fromAARP</t>
+  </si>
+  <si>
     <t>RetirementCalculator - NerdWallet</t>
   </si>
   <si>
-    <t>Retirement- News, Advice &amp; Resources fromAARP</t>
-  </si>
-  <si>
     <t>Retirement- Wikipedia</t>
   </si>
   <si>
+    <t>Legacy Village - Premier Senior Living in St. George, Utah</t>
+  </si>
+  <si>
     <t>Retirement Calculator</t>
   </si>
   <si>
+    <t>10 Steps to Take as You Get Ready to Retire - AARP</t>
+  </si>
+  <si>
     <t>Plan forRetirement| SSA</t>
   </si>
   <si>
-    <t>10 Steps to Take as You Get Ready to Retire - AARP</t>
-  </si>
-  <si>
     <t>Retirementplanning tools - USAGov</t>
   </si>
   <si>
-    <t>Retirement Calculator- Ramsey</t>
-  </si>
-  <si>
-    <t>Retirementplanning guide: How to plan forretirementat any age</t>
-  </si>
-  <si>
-    <t>IllinoisDepartment on Aging</t>
-  </si>
-  <si>
-    <t>SeniorServices of CentralIllinois</t>
-  </si>
-  <si>
-    <t>55+ Communities &amp;SeniorLiving inSpringfield,Illinois| After55</t>
-  </si>
-  <si>
-    <t>Senior Services Of Central Illinois At The Springfield SeniorCenter</t>
-  </si>
-  <si>
-    <t>SeniorHelpLine -Illinois</t>
-  </si>
-  <si>
-    <t>Illinois SeniorGames |Springfield IL- Facebook</t>
-  </si>
-  <si>
-    <t>10 Best Independent Living Communities inSpringfield,IL</t>
-  </si>
-  <si>
-    <t>SeniorServices of CentralIllinois-Transportation</t>
-  </si>
-  <si>
-    <t>55+ Active Living CommunitySpringfield IL| 55+ Housing</t>
-  </si>
-  <si>
-    <t>Senior Springfield Apartments for Rent|Springfield,IL</t>
-  </si>
-  <si>
-    <t>ELDERLYDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Old age -Wikipedia</t>
-  </si>
-  <si>
-    <t>What Age Is ConsideredElderly? - MedicareAdvantage.com</t>
-  </si>
-  <si>
-    <t>THEELDERLYDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Elderly Instruments| New, Used &amp; Vintage Musical Instruments</t>
-  </si>
-  <si>
-    <t>ELDERLY| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>At What Age Are You Officially ConsideredElderly?</t>
-  </si>
-  <si>
-    <t>What IsElderly? Understanding the Age Group</t>
-  </si>
-  <si>
-    <t>What Age Is Legally Considered Elderly? - Informed Senior Living</t>
-  </si>
-  <si>
-    <t>ELDERLY| definition in the Cambridge English Dictionary</t>
+    <t>Log Into Your Account |Transamerica</t>
+  </si>
+  <si>
+    <t>-San DiegoSeniors Community Foundation</t>
+  </si>
+  <si>
+    <t>Home | Serving Seniors</t>
+  </si>
+  <si>
+    <t>SeniorResources -San DiegoSeniors Community Foundation</t>
+  </si>
+  <si>
+    <t>Aging and Independence Services- SanDiegoCounty.gov</t>
+  </si>
+  <si>
+    <t>Property Tax Relief for Seniors - sdarcc.gov</t>
+  </si>
+  <si>
+    <t>135SeniorLiving Communities inSan Diego,California</t>
+  </si>
+  <si>
+    <t>Older Adults- SanDiegoCounty.gov</t>
+  </si>
+  <si>
+    <t>Senior Food Program-San DiegoFood Bank</t>
+  </si>
+  <si>
+    <t>Serving SeniorsHousing Program</t>
+  </si>
+  <si>
+    <t>SeniorLiving inSan Diego,CA: 33 Communities From $7,965/mo (2026)</t>
+  </si>
+  <si>
+    <t>83-Year-Old Air Force Veteran Dies After Illegal Alien Shoves Him …</t>
+  </si>
+  <si>
+    <t>Abandoned Subway (Rochester, Irondequoit, Sodus: living in, cost, …</t>
+  </si>
+  <si>
+    <t>America's Most Wanted Fans - amwfans.com</t>
+  </si>
+  <si>
+    <t>What are some movies that feature the L.A. subway? (construction, …</t>
+  </si>
+  <si>
+    <t>Subway, 6910 Fayetteville Rd, Durham, NC - Restaurant inspection ...</t>
+  </si>
+  <si>
+    <t>SUBWAY #34195, 955 Catalina Blvd, San Diego, CA 92106</t>
+  </si>
+  <si>
+    <t>3x12 vs 3x6 Subway tile backsplash (granite countertops, stove, color ...</t>
+  </si>
+  <si>
+    <t>Just Posted Vid on Montreal Metro (Subway). Compare to NYC …</t>
+  </si>
+  <si>
+    <t>Subway balance questions (living in, bus, safest) - New York City</t>
+  </si>
+  <si>
+    <t>Subway locations in Lynnwood, WA - City-Data.com</t>
   </si>
   <si>
     <t>FRAILDefinition &amp; Meaning -Merriam-Webster</t>
@@ -187,7 +187,7 @@
     <t>FRAIL definitionand meaning | Collins English Dictionary</t>
   </si>
   <si>
-    <t>What DoesfrailMean? Definition &amp; Examples | Dictionary.net</t>
+    <t>frailadjective - Definition, pictures, pronunciation and usage notes ...</t>
   </si>
   <si>
     <t>AGEDDefinition &amp; Meaning -Merriam-Webster</t>
@@ -196,30 +196,30 @@
     <t>AGED| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
+    <t>Agedvs. Age - Which is Correct?</t>
+  </si>
+  <si>
     <t>AGEDDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
+    <t>THEAGEDDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>AGED| definition in the Cambridge English Dictionary</t>
+  </si>
+  <si>
+    <t>Aged(2023) - IMDb</t>
+  </si>
+  <si>
     <t>Aged- definition ofagedby The Free Dictionary</t>
   </si>
   <si>
-    <t>Aged(2023) - IMDb</t>
+    <t>aged- Wiktionary, the free dictionary</t>
   </si>
   <si>
     <t>AGEDTrust Home -AgedTrust | Non-Profit</t>
   </si>
   <si>
-    <t>aged- Wiktionary, the free dictionary</t>
-  </si>
-  <si>
-    <t>AGED| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>Agedvs. Age - Which is Correct?</t>
-  </si>
-  <si>
-    <t>agèd - Wiktionary, the free dictionary</t>
-  </si>
-  <si>
     <t>67Easy Dinner IdeasWe Love - Taste of Home</t>
   </si>
   <si>
@@ -232,82 +232,286 @@
     <t>92 Dinner Ideas You Can Make in a Flash | Taste of Home</t>
   </si>
   <si>
+    <t>104 Quick Dinner Ideas in 30 Minutes or Less | Food Network</t>
+  </si>
+  <si>
     <t>70 Easy Dinner Ideas</t>
   </si>
   <si>
-    <t>104 Quick Dinner Ideas in 30 Minutes or Less | Food Network</t>
-  </si>
-  <si>
     <t>100Easy DinnerRecipes for Busy Weeknights - The Pioneer Woman</t>
   </si>
   <si>
-    <t>22 Easy Dinner Recipes to Make With 5 Ingredients (Or Fewer!)</t>
-  </si>
-  <si>
-    <t>Recipes, Dinners and Easy Meal Ideas | Food Network</t>
+    <t>Mealson Wheels Santa Maria Valley</t>
+  </si>
+  <si>
+    <t>52Easy Dinner Recipes&amp; Ideas | Food Network</t>
   </si>
   <si>
     <t>HelloFresh® Meal Kits | Free Breakfast for Life + 10 FreeMeals</t>
   </si>
   <si>
-    <t>“Golden” Official Music Video | KPop Demon Hunters | Sony Animation</t>
-  </si>
-  <si>
-    <t>“Golden” Official Lyric Video | KPop Demon Hunters | Sony Animation</t>
-  </si>
-  <si>
-    <t>Westopolis: ExploreSt. Louis Park&amp;GoldenValley,MN</t>
-  </si>
-  <si>
-    <t>Gold (color) -Wikipedia</t>
-  </si>
-  <si>
-    <t>Smart Home &amp; Entertainment inSt. Louis Park|Golden</t>
-  </si>
-  <si>
-    <t>Golden(Huntrix song) - Wikipedia</t>
-  </si>
-  <si>
-    <t>Golden- definition ofgoldenby The Free Dictionary</t>
-  </si>
-  <si>
-    <t>Golden Corral| Endless Buffet | America's #1 Buffet Restaurant</t>
-  </si>
-  <si>
-    <t>GOLDENDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>GoldenValley,MN| Official Website</t>
-  </si>
-  <si>
-    <t>PENSIONERDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Pensioner-Wikipedia</t>
-  </si>
-  <si>
-    <t>PENSIONER| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>Pensioner- definition ofpensionerby The Free Dictionary</t>
-  </si>
-  <si>
-    <t>PENSIONERDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
-    <t>PENSIONER| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>pensioner, n. meanings, etymology and more | Oxford English Dictionary</t>
-  </si>
-  <si>
-    <t>Pensioner - Definition, Meaning &amp; Synonyms| Vocabulary.com</t>
-  </si>
-  <si>
-    <t>What doespensionermean? -Definitions.net</t>
-  </si>
-  <si>
-    <t>PensionerDefinition &amp; Meaning | Britannica Dictionary</t>
+    <t>Online Stopwatch - easy to use - timeanddate.com</t>
+  </si>
+  <si>
+    <t>Online Timer - timeanddate.com</t>
+  </si>
+  <si>
+    <t>Date Calculator: Add to or Subtract From a Date</t>
+  </si>
+  <si>
+    <t>timeanddate.com</t>
+  </si>
+  <si>
+    <t>Countdown Timer to Any Date</t>
+  </si>
+  <si>
+    <t>Calendar 2026 - timeanddate.com</t>
+  </si>
+  <si>
+    <t>Business Days Calculator – Count Workdays - timeanddate.com</t>
+  </si>
+  <si>
+    <t>Sunrise and Sunset Calculator</t>
+  </si>
+  <si>
+    <t>Free Clocks for Your Website - timeanddate.com</t>
+  </si>
+  <si>
+    <t>FAQ: Online Stopwatch - timeanddate.com</t>
+  </si>
+  <si>
+    <t>Bank of AmericaTravel Insurance Benefits for 2026 - WalletHub</t>
+  </si>
+  <si>
+    <t>Bank of America® Premium Rewards® credit card - WalletHub</t>
+  </si>
+  <si>
+    <t>Bank of America locations in Albany, GA - City-Data.com</t>
+  </si>
+  <si>
+    <t>How Bank of America Rental Car Insurance Works - WalletHub</t>
+  </si>
+  <si>
+    <t>Bank of America Travel Rewards Business Card Reviews for</t>
+  </si>
+  <si>
+    <t>Bank of America Customized Cash Rewards credit card for Students</t>
+  </si>
+  <si>
+    <t>VentureOne vs. Bank of America Travel Rewards - WalletHub</t>
+  </si>
+  <si>
+    <t>Bank of America® Customized Cash Rewards Secured Credit Card</t>
+  </si>
+  <si>
+    <t>How to Redeem Bank of America Travel Rewards Credit Card</t>
+  </si>
+  <si>
+    <t>Best Bank of America Credit Cards for International Students (2026)</t>
+  </si>
+  <si>
+    <t>Microsoft– AI, Cloud, Productivity, Computing, Gaming &amp; Apps</t>
+  </si>
+  <si>
+    <t>Microsoftaccount | Sign In or Create Your Account Today –Microsoft</t>
+  </si>
+  <si>
+    <t>Sign in to your account</t>
+  </si>
+  <si>
+    <t>Microsoft365 for Individuals: Subscription for Productivity Apps</t>
+  </si>
+  <si>
+    <t>Microsoft- Wikipedia</t>
+  </si>
+  <si>
+    <t>Create yourMicrosoftaccount</t>
+  </si>
+  <si>
+    <t>Sign in to your account - myaccount.microsoft.com</t>
+  </si>
+  <si>
+    <t>Microsoft365 - Sign into Copilot</t>
+  </si>
+  <si>
+    <t>Outlook</t>
+  </si>
+  <si>
+    <t>Sign in - account.microsoft.com</t>
+  </si>
+  <si>
+    <t>Contact Us - Microsoft Support</t>
+  </si>
+  <si>
+    <t>Anmelden bei Hotmail | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Microsoft Copilot Blog | Microsoft Community Hub</t>
+  </si>
+  <si>
+    <t>Exchange Online EWS, Your Time is Almost Up | Microsoft …</t>
+  </si>
+  <si>
+    <t>Getting ready for the Windows 11 upgrade | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Mettre à jour les pilotes via Gestionnaire de périphériques dans ...</t>
+  </si>
+  <si>
+    <t>Aktualisieren von Treibern über Geräte-Manager in Windows</t>
+  </si>
+  <si>
+    <t>Getting the latest Microsoft Edge update just got easier</t>
+  </si>
+  <si>
+    <t>Share your calendar in Outlook | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Sign in to Microsoft Forms</t>
+  </si>
+  <si>
+    <t>7-Day Forecast 37.77N 122.44W -National Weather Service</t>
+  </si>
+  <si>
+    <t>7-Day Forecast 37.78N 122.5W - National Weather Service</t>
+  </si>
+  <si>
+    <t>National Weather Service</t>
+  </si>
+  <si>
+    <t>Zone Area Forecast forSan FranciscoCounty</t>
+  </si>
+  <si>
+    <t>San Francisco, CA WeatherTomorrowwith 5-Day Forecast ...</t>
+  </si>
+  <si>
+    <t>Rain Probability Checker — Free Online Tool | KiranIntl</t>
+  </si>
+  <si>
+    <t>WeatherTomorrowforSan Francisco, CA |AccuWeather</t>
+  </si>
+  <si>
+    <t>Tomorrow's Weatherin San Francisco- Hourly Forecast and Conditions</t>
+  </si>
+  <si>
+    <t>Ex-Secret Service agent reveals newJFKassassination detail -BBC</t>
+  </si>
+  <si>
+    <t>The Most Convincing Theories About WhoKilled JFK</t>
+  </si>
+  <si>
+    <t>Assassination ofJohn F. Kennedy-Wikipedia</t>
+  </si>
+  <si>
+    <t>The Assassination ofJohn F. Kennedy– Official Story vs Persistent ...</t>
+  </si>
+  <si>
+    <t>Who Really Killed JFK? Inside The Mystery With History Uncovered</t>
+  </si>
+  <si>
+    <t>assassination of John F. Kennedy-Encyclopedia Britannica</t>
+  </si>
+  <si>
+    <t>JFK Assassination— FBI</t>
+  </si>
+  <si>
+    <t>Lee Harvey Oswald-Wikipedia</t>
+  </si>
+  <si>
+    <t>Did the Mobkill JFK? New evidence suggests they did</t>
+  </si>
+  <si>
+    <t>Assassination ofJohn F. Kennedy- Facts, Investigation, Photos |HISTORY</t>
+  </si>
+  <si>
+    <t>Sign in to Gmail - Computer - Gmail Help - Google Help</t>
+  </si>
+  <si>
+    <t>Facebook Login. Please. No More. : r/webdev - Reddit</t>
+  </si>
+  <si>
+    <t>Facebook: How do you get past the "See more of..." login popup</t>
+  </si>
+  <si>
+    <t>How Sign in with Google works - Google Account Help</t>
+  </si>
+  <si>
+    <t>Disable facebook login popup. : r/uBlockOrigin - Reddit</t>
+  </si>
+  <si>
+    <t>Did anyone else get prompted to “Sign In” again to their Facebook app ...</t>
+  </si>
+  <si>
+    <t>How to browse Facebook without logging in? : r/privacytoolsIO</t>
+  </si>
+  <si>
+    <t>Facebook login no longer possible, little help? : r/lineapp - Reddit</t>
+  </si>
+  <si>
+    <t>Unexpected error occurred when I tried logging in on the Facebook ...</t>
+  </si>
+  <si>
+    <t>Facebook - 2FA (two factor authentication) login issue - Lost phone</t>
+  </si>
+  <si>
+    <t>University of Mississippi | Ole Miss</t>
+  </si>
+  <si>
+    <t>University of Mississippi - Admissions | Ole Miss</t>
+  </si>
+  <si>
+    <t>University of Mississippi - Recruiting | Ole Miss</t>
+  </si>
+  <si>
+    <t>UM Libraries | Ole Miss</t>
+  </si>
+  <si>
+    <t>Faculty Staff Directory | Ole Miss - University of Mississippi</t>
+  </si>
+  <si>
+    <t>Campus Map | University of Mississippi</t>
+  </si>
+  <si>
+    <t>University of Mississippi - SAP NetWeaver Portal</t>
+  </si>
+  <si>
+    <t>Sign In - University of Mississippi</t>
+  </si>
+  <si>
+    <t>Admission Application</t>
+  </si>
+  <si>
+    <t>2026 Commencement Convocation - University of Mississippi</t>
+  </si>
+  <si>
+    <t>Store Details at Menards®</t>
+  </si>
+  <si>
+    <t>Sitemap at Menards®</t>
+  </si>
+  <si>
+    <t>Menards® Careers at Menards®</t>
+  </si>
+  <si>
+    <t>Shop All at Menards®</t>
+  </si>
+  <si>
+    <t>Weekly Flyer at Menards®</t>
+  </si>
+  <si>
+    <t>Sign In at Menards®</t>
+  </si>
+  <si>
+    <t>Home at Menards®</t>
+  </si>
+  <si>
+    <t>Store Careers at Menards®</t>
+  </si>
+  <si>
+    <t>Indoor Lighting at Menards®</t>
+  </si>
+  <si>
+    <t>Decking &amp; Deck Materials at Menards®</t>
   </si>
   <si>
     <t>Senior Care</t>
@@ -316,277 +520,496 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=195ae987cf4c70b11317cf9a29f4a7e183789443c319b4380569dfe86e1b8832JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d7031b5-9c58-6875-042e-26549de96913&amp;u=a1aHR0cHM6Ly9vbGRuYXZ5LmdhcC5jb20vP21zb2NraWQ9MWQ3MDMxYjU5YzU4Njg3NTA0MmUyNjU0OWRlOTY5MTM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a70d81c9401b11cb00013866c3e190464733023e44f3050a26f5c99b74c22576JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d7031b5-9c58-6875-042e-26549de96913&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9PbGRfKGZpbG0p&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=200786fbd7a3712eb4d91fa57f78fd9994335a2c9d6a8562b78a8c01351943b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d7031b5-9c58-6875-042e-26549de96913&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTA5NTQ2NTIv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c645610dbf64635e4033f12156f6249d5766c5aa5db61f5c5ea3b443372fd3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d7031b5-9c58-6875-042e-26549de96913&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L29sZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6fa79bb207af4e863c76221614f14b018d3859888c15983da51e78f50aeeb88JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d7031b5-9c58-6875-042e-26549de96913&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9ODR4QUQ0ci05a0U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bb92acef6290164c39869118127d38d59dce4f0295ae01adf4e2cb34178eb612JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d7031b5-9c58-6875-042e-26549de96913&amp;u=a1aHR0cHM6Ly93d3cucm90dGVudG9tYXRvZXMuY29tL20vb2xk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=44023c93d99a1ede77b5e37facff1f81896c9950e6e12ee5e36c31ca848892feJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d7031b5-9c58-6875-042e-26549de96913&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9QTRVMnBNUlY5X2s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee6f2db86044b77e4e527ed341ee043b11b5d4ae47271942e3b5459a8918f681JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d7031b5-9c58-6875-042e-26549de96913&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL29sZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ec282b47805f6a52580c7b6e9cabbf6cdb521d44e0d87ebc98c23e61bd9616cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d7031b5-9c58-6875-042e-26549de96913&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTA5NTQ2NTIvZnVsbGNyZWRpdHMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c4b62e90e15a521dad485585bf659d050c4b64c05c71879932c303c42d4af551JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d7031b5-9c58-6875-042e-26549de96913&amp;u=a1aHR0cHM6Ly93d3cubmV0ZmxpeC5jb20vdGl0bGUvODE0MTAzODY&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d2ca5dce58bd8d4c920cc203c0a5f6e47c8e1fa6fdab4804c043e95ddd5e2dd3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bb78e4a-e1ba-67a0-1b19-99abe021666f&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cde460ccbf935ba15df839e17a02954c7c07cb8c85ee3cae3c548e830a587be2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bb78e4a-e1ba-67a0-1b19-99abe021666f&amp;u=a1aHR0cHM6Ly93d3cubmVyZHdhbGxldC5jb20vaW52ZXN0aW5nL2NhbGN1bGF0b3JzL3JldGlyZW1lbnQtY2FsY3VsYXRvcj9tc29ja2lkPTNiYjc4ZTRhZTFiYTY3YTAxYjE5OTlhYmUwMjE2NjZm&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e2c1a6fcc29cf792be3bad9d0761702deba1442b3d2e42ca9b05f2b7c1e91c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bb78e4a-e1ba-67a0-1b19-99abe021666f&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC8_bXNvY2tpZD0zYmI3OGU0YWUxYmE2N2EwMWIxOTk5YWJlMDIxNjY2Zg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98d7c9e80b59e6f82ceed77819c00628bfe71d1c941b4288e5a354b1c35f143eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bb78e4a-e1ba-67a0-1b19-99abe021666f&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUmV0aXJlbWVudA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=19842a64df7a7273869566d489355951cc19f92bfcf59fb3362dc4431115c2f0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bb78e4a-e1ba-67a0-1b19-99abe021666f&amp;u=a1aHR0cHM6Ly93d3cuY2FsY3VsYXRvci5uZXQvcmV0aXJlbWVudC1jYWxjdWxhdG9yLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=57732e7d211dd51beced4aa49290527340634f64d0611405c31be0e4a4ba8733JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bb78e4a-e1ba-67a0-1b19-99abe021666f&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50L3BsYW4tZm9yLXJldGlyZW1lbnQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=489ee41e410bce6bb467462835dff076675826889df8f465d3e04bc07bcb6193JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bb78e4a-e1ba-67a0-1b19-99abe021666f&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC9zdGVwcy10by10YWtlLWJlZm9yZS15b3UtcmV0aXJlLz9tc29ja2lkPTNiYjc4ZTRhZTFiYTY3YTAxYjE5OTlhYmUwMjE2NjZm&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=19c760ee5d46916fb1158456ed7a33ab31bca72f12a51e7d50814f1d2aadc9adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bb78e4a-e1ba-67a0-1b19-99abe021666f&amp;u=a1aHR0cHM6Ly93d3cudXNhLmdvdi9yZXRpcmVtZW50LXBsYW5uaW5nLXRvb2xz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40779f3b503087fe36db7a46dc2900dd055ae9f0aa85f76aa400696e83207f48JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bb78e4a-e1ba-67a0-1b19-99abe021666f&amp;u=a1aHR0cHM6Ly93d3cucmFtc2V5c29sdXRpb25zLmNvbS9yZXRpcmVtZW50L3JldGlyZW1lbnQtY2FsY3VsYXRvcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef537fcdcc3f334870137447b10164fbddfed1803ad5aeb6948b02293c5cded5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bb78e4a-e1ba-67a0-1b19-99abe021666f&amp;u=a1aHR0cHM6Ly93d3cuZmlkZWxpdHkuY29tL2xlYXJuaW5nLWNlbnRlci9wZXJzb25hbC1maW5hbmNlL3JldGlyZW1lbnQvaG93LXRvLXBsYW4tZm9yLXJldGlyZW1lbnQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=438a0c05f3695b462770a4b26477bab8a21f02ff9946d41ba3eaffb3726bb8f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d83bd64-f7ee-6916-05c5-aa85f6a168fa&amp;u=a1aHR0cHM6Ly9pbGFnaW5nLmlsbGlub2lzLmdvdi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1f81bca94c5164805a590aae0459a1d056876f8a0623daae45c4fea957a2fbcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d83bd64-f7ee-6916-05c5-aa85f6a168fa&amp;u=a1aHR0cHM6Ly93d3cuY2VudHJhbGlsc2VuaW9ycy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10da9159e13208651ad34174c9454e01e61450599c1840701dd75a83c6682948JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d83bd64-f7ee-6916-05c5-aa85f6a168fa&amp;u=a1aHR0cHM6Ly93d3cuYWZ0ZXI1NS5jb20vc2VhcmNoL2lsL3NwcmluZ2ZpZWxk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a2aae66d1849ea516f6679827a70ecac8a88f3a4672f631ca4744fe57af982aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d83bd64-f7ee-6916-05c5-aa85f6a168fa&amp;u=a1aHR0cHM6Ly9zZW5pb3JjZW50ZXIudXMvc2Mvc2VuaW9yX3NlcnZpY2VzX29mX2NlbnRyYWxfaWxsaW5vaXNfYXRfdGhlX3NwcmluZ2ZpZWxkX3Nlbmlvcl9jZW50ZXJfc3ByaW5nZmllbGRfaWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d6acf9cb046f7956c5fe6dd7095b9928424e3d21cf3bae7121da6314a35d4deeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d83bd64-f7ee-6916-05c5-aa85f6a168fa&amp;u=a1aHR0cHM6Ly9pbGFnaW5nLmlsbGlub2lzLmdvdi9yZXNvdXJjZXMvaGVscGxpbmUtbWFpbi5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6aeca87c8b78644f3c7656e5229bd3707d3e383d87a2c3bd8fed59124c8f2aeaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d83bd64-f7ee-6916-05c5-aa85f6a168fa&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2lsc2VuaW9yZ2FtZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=737498a4390b2e552ce448d1fbb4a9697332fd96891cbfd0c0e43aa74d826cedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d83bd64-f7ee-6916-05c5-aa85f6a168fa&amp;u=a1aHR0cHM6Ly93d3cuYXBsYWNlZm9ybW9tLmNvbS9pbmRlcGVuZGVudC1saXZpbmcvaWxsaW5vaXMvc3ByaW5nZmllbGQ_bXNvY2tpZD0yZDgzYmQ2NGY3ZWU2OTE2MDVjNWFhODVmNmExNjhmYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bf88c1c6798b47e728dcbadab7dee76258f5d15201ef6fb5d47ee89ef0528b23JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d83bd64-f7ee-6916-05c5-aa85f6a168fa&amp;u=a1aHR0cHM6Ly93d3cuY2VudHJhbGlsc2VuaW9ycy5vcmcvdHJhbnNwb3J0YXRpb24uaHRt&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f28c0d891304b15749d475f7bfd357f51b16a576ae5a8e41b901a5e8c9a0eff3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d83bd64-f7ee-6916-05c5-aa85f6a168fa&amp;u=a1aHR0cHM6Ly90aW1iZXJjcmVla2xpdmluZy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8dd94842f95628d99bba79516087d6c0917b45f993b5bcf3a3f381164c70367dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d83bd64-f7ee-6916-05c5-aa85f6a168fa&amp;u=a1aHR0cHM6Ly93d3cuYXBhcnRtZW50aG9tZWxpdmluZy5jb20vc3ByaW5nZmllbGQtaWwvYXBhcnRtZW50cy1mb3ItcmVudC9zZW5pb3I_bXNvY2tpZD0yZDgzYmQ2NGY3ZWU2OTE2MDVjNWFhODVmNmExNjhmYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60a8ac3c76fb1f6d35cba45a690865d627ab94eaed5c32a70f2ad5d7b29e60c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0045b3bc-8662-6a84-389a-a45d87ed6bae&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3466ab5fe6fd8482a097ed0ea7252ba31379ae1a4ab1c4026d0aff565b992c4dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0045b3bc-8662-6a84-389a-a45d87ed6bae&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT2xkX2FnZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df3f15e7326a301383785e80ee635256daedb8154033d3eed87e1b8941afceb6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0045b3bc-8662-6a84-389a-a45d87ed6bae&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhcmVhZHZhbnRhZ2UuY29tL2NvbW1vbi1xdWVzdGlvbnMvd2hhdC1hZ2UtaXMtY29uc2lkZXJlZC1lbGRlcmx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0b7cb250c58df46b90b6af6ff2d5db235be46455895cc8849feb0008980252cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0045b3bc-8662-6a84-389a-a45d87ed6bae&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3RoZSUyMGVsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b2d3e1fc9a0bfc38147198b461495d930ead75a718f33da33eb2974cbb933c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0045b3bc-8662-6a84-389a-a45d87ed6bae&amp;u=a1aHR0cHM6Ly93d3cuZWxkZXJseS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d9267a9c31fceeeb4e68ef79ff18b650015b54398a50d6bc58d0fe2fdf8a0ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0045b3bc-8662-6a84-389a-a45d87ed6bae&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc4c47b23baf4479f3208650d03ba63ffafd2ae113bdd8cb8a5646941adddacfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0045b3bc-8662-6a84-389a-a45d87ed6bae&amp;u=a1aHR0cHM6Ly93d3cuc2VuaW9yc3Ryb25nLm9yZy9hdC13aGF0LWFnZS1hcmUteW91LWNvbnNpZGVyZWQtZWxkZXJseS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe44e6a4b2ae5b78e4139652d7d6b707728b55f51a08f5df84101da5abb3c917JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0045b3bc-8662-6a84-389a-a45d87ed6bae&amp;u=a1aHR0cHM6Ly93d3cudGhlZWxkZXJseXdlbGxuZXNzLmNvbS9ibG9ncy93aGF0LWlzLWVsZGVybHkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=566537c472ec671a80e10e106b0cd4fe570d1fad801f65885fdf4465af414df4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0045b3bc-8662-6a84-389a-a45d87ed6bae&amp;u=a1aHR0cHM6Ly9pbmZvcm1lZHNlbmlvcmxpdmluZy5jb20vd2hhdC1hZ2UtaXMtbGVnYWxseS1jb25zaWRlcmVkLWVsZGVybHkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5bdc3fb8df5b43abc02003e95f186129508504565342f62cfca0eb205bbf2e85JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0045b3bc-8662-6a84-389a-a45d87ed6bae&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2VsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4b4a18b75abb44e2d63076c88b4ebff17c7d934dedaee4794a926547ed1f3de3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c97b101-1457-64d9-3899-a6e015c36514&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee8453298cf42c853b8735279556cdf565ab5943d8751d778d46ed8ed838f9a4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c97b101-1457-64d9-3899-a6e015c36514&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4f66923a3fad3c787b5206fdaaebfc9c1c92ecdd5e6acea8e707c99331b60b83JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c97b101-1457-64d9-3899-a6e015c36514&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvZnJhaWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=550054e1d9877415bf743d56018ed632bf3950177db370b240b8490529f1124bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c97b101-1457-64d9-3899-a6e015c36514&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c21eecfa44c61fd865234a56a350a19d9ed69b8fa6eb49cd48ebf9e28450fb31JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c97b101-1457-64d9-3899-a6e015c36514&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c88413d5465d40ee6d4d9d31c76f269c867fba2a92583989e81c8c410f542922JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c97b101-1457-64d9-3899-a6e015c36514&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2d0fc9265eecb115a8fabd44f58a7cb34fd13d439ea1301cd008c754be1e6a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c97b101-1457-64d9-3899-a6e015c36514&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5db782670afaae71da89a05fce84fe447af1de1c29042336dbefb9763607609JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c97b101-1457-64d9-3899-a6e015c36514&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9473de5bdaa8819d2f70e819b46812428d307eff72d594417d273852437d9ca5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c97b101-1457-64d9-3899-a6e015c36514&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL2RpY3Rpb25hcnkvZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4bbd9c7707519cff53ce1a034b83d10b3f89c8dc18cbe15f8f4ead7dabb094d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c97b101-1457-64d9-3899-a6e015c36514&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5uZXQvZGljdGlvbmFyeS9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b5ad5e4e8c0383ea5c092b75e21297a92aea42b801098f049cefdc3f11b64e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3490799e-87fc-60d9-0474-6e7f86aa6122&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4147129d9e942e3b2fda06bc17e02299564baa7e85eb2bbc8ad2ea118ade49e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3490799e-87fc-60d9-0474-6e7f86aa6122&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38a1c68c66cfde14f85fdbb7324a7fd9e8a233695c7d01e754a04b7c5cfafb7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3490799e-87fc-60d9-0474-6e7f86aa6122&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e5959b018ab416252f2cae077cb4428fe6237b404461536c944a9b63b846ff55JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3490799e-87fc-60d9-0474-6e7f86aa6122&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d2a5728734ed79c5f4bbdea78119b94336bc67499f30e8a7a7af0518bed3f4a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3490799e-87fc-60d9-0474-6e7f86aa6122&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTcwNDQwMjA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ad7c3779f8d710c80c33c1bdfa61567ec9a67feb185cf2195fdba4297fbefc8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3490799e-87fc-60d9-0474-6e7f86aa6122&amp;u=a1aHR0cHM6Ly90cnVzdGFnZWQub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4322475e03214ccdebc53dd1e69f7f825902581af874ae2f09773639b64b8067JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3490799e-87fc-60d9-0474-6e7f86aa6122&amp;u=a1aHR0cHM6Ly9lbi5tLndpa3Rpb25hcnkub3JnL3dpa2kvYWdlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1cbe78f9320aa14fe09677135d1629ed59feff5418c0f8cebf4a10e069491c49JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3490799e-87fc-60d9-0474-6e7f86aa6122&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d86d8b5cf498aeb594963ccd5ce04d2a1461b6c659b0cba38c20c2eda819cb9fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3490799e-87fc-60d9-0474-6e7f86aa6122&amp;u=a1aHR0cHM6Ly9jb3JyZWN0d29yZGluZy5jb20vYWdlZC1vci1hZ2Uv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d151a1e524411e3762c5c2b6c8b34cabd4f8213221384324ae2525b8466b4ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3490799e-87fc-60d9-0474-6e7f86aa6122&amp;u=a1aHR0cHM6Ly9lbi5tLndpa3Rpb25hcnkub3JnL3dpa2kvYWclQzMlQThk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a24539a9cb1abc579b9c1fdde6c9ef0139c3e16cdd52bdb50df8cd3a9c572f4fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34ad8d7d-e1d2-60f9-3812-9a9ce0c16136&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZWFzeS1kaW5uZXItaWRlYXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4b72bac865940a759047cd3f19b008d6d470661c136ee7645804c6fc7390a94JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34ad8d7d-e1d2-60f9-3812-9a9ce0c16136&amp;u=a1aHR0cHM6Ly93d3cuYWxscmVjaXBlcy5jb20vMTAwLWVhc3ktbWVhbHMtMTE2OTUyMjc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=46a6895761cc06584580476910663535bbc92a48f3adcbf41c9506fad6df41a1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34ad8d7d-e1d2-60f9-3812-9a9ce0c16136&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzY4OTA2OTk3L2Jlc3QtZWFzeS1kaW5uZXItcmVjaXBlcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3bf5d92f4b7bebdc0012a3f811893d2cb4a04009882310af7e9bcb5cba6c861fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34ad8d7d-e1d2-60f9-3812-9a9ce0c16136&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d651e1fced2e84401dca2faaa16f0233e939304c64a1946dbc3ffdd1040532aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34ad8d7d-e1d2-60f9-3812-9a9ce0c16136&amp;u=a1aHR0cHM6Ly90aGVyZWFsZm9vZGRpZXRpdGlhbnMuY29tL2Vhc3ktZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0070df9b4cf9bd80b71d7049af93422fa965f27095e1c4ed2f979e96c0539c27JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34ad8d7d-e1d2-60f9-3812-9a9ce0c16136&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zLzMwLW1pbnV0ZS1kaW5uZXItcmVjaXBlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1fff91109af0547ab4aa189174553b00630e9c268bb295fdb764fc9a2fbec0ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34ad8d7d-e1d2-60f9-3812-9a9ce0c16136&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzMyMjY0Mjg0L2Vhc3ktZGlubmVyLXJlY2lwZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9055142f50f06fdc648c56159f426e7c18cc9895dded897d1837a4dc1d629c3dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34ad8d7d-e1d2-60f9-3812-9a9ce0c16136&amp;u=a1aHR0cHM6Ly93d3cuYWxscmVjaXBlcy5jb20vNS1pbmdyZWRpZW50LWRpbm5lci1yZWNpcGVzLTExODQxODYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b00323dced45a0bf0d5eaf175207cbdd31e52eb5f51a4d469dd658cd274c7f45JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34ad8d7d-e1d2-60f9-3812-9a9ce0c16136&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=35db0818a867b50bd4b6e8611d20ef49193828015142a20800843bc563f0bf99JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34ad8d7d-e1d2-60f9-3812-9a9ce0c16136&amp;u=a1aHR0cHM6Ly93d3cuaGVsbG9mcmVzaC5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=759fb8bfe78c57c1a221e1b139b2d520e444e1a246a718051e449743f81cd440JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d6f408a-85f5-6550-0f8b-576b84f964d1&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9T0RBWnhXMmQ1cTQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b94179b6c5aef0c7efc28013863b6ffead54be2486902ec04ee8a9ea3a66ed30JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d6f408a-85f5-6550-0f8b-576b84f964d1&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9eWViTklIS0FDNEE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aa48653dd97e0611c5f7837a7e56ef032f4d5843c87fa72762bc5d75736240e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d6f408a-85f5-6550-0f8b-576b84f964d1&amp;u=a1aHR0cHM6Ly93ZXN0b3BvbGlzLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe0da756dafbe1002851ea63f369074756846dc24e0cafe8d545c0c7bf2b6f00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d6f408a-85f5-6550-0f8b-576b84f964d1&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Hb2xkXyhjb2xvcik&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3ad7e3cd2a7a12be205b03a87af5228138d5e60148a9366bd6ffdcb276f4a847JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d6f408a-85f5-6550-0f8b-576b84f964d1&amp;u=a1aHR0cHM6Ly9nb2xkZW5tbi5jb20vc3QtbG91aXMtcGFyaw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0888d687ed9265935e7150e83f1d6a0dcf6f0648e3abf76ae257dd68d26ddaffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d6f408a-85f5-6550-0f8b-576b84f964d1&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Hb2xkZW5fKEh1bnRyaXhfc29uZyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d552b815ac886fd2419643439f75ff7f1366c7bf5be62fbc612934d0285db7dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d6f408a-85f5-6550-0f8b-576b84f964d1&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2dvbGRlbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d6b11b83eaa21d85207943eaa2dd87acda09630c78d58033801299d32337a5d1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d6f408a-85f5-6550-0f8b-576b84f964d1&amp;u=a1aHR0cHM6Ly93d3cuZ29sZGVuY29ycmFsLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=62904a598d52ca79631e8b0192ecb8131f7c64b84b3ce527966bf9534914b8cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d6f408a-85f5-6550-0f8b-576b84f964d1&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2dvbGRlbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=28eb55688eddfb0a9aab13befb77a55b6cfc661662ec6aa55d4bd76b2067f8b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d6f408a-85f5-6550-0f8b-576b84f964d1&amp;u=a1aHR0cHM6Ly93d3cuZ29sZGVudmFsbGV5bW4uZ292Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=50899f4adaa1cdd028f27b016dfa0f9bf2307b4624b41c4bb5710a7f7dc2f487JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3557012f-fee6-61b9-32c5-16ceff1e60fc&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3BlbnNpb25lcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=189f652db295ecfd990f36ab87cac6e219320616ef63cd5473ae70b781d08af2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3557012f-fee6-61b9-32c5-16ceff1e60fc&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUGVuc2lvbmVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38f89f4560cfda97cf59b77d9e0d076854635106d5b02e9a7d990b1edde50b42JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3557012f-fee6-61b9-32c5-16ceff1e60fc&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3BlbnNpb25lcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9423da3cea706292bb549d23c93ca601adc0663c5e074f59c8e39e935fe7a71fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3557012f-fee6-61b9-32c5-16ceff1e60fc&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL3BlbnNpb25lcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4c334b9e07979b65a7bb32e31e37d158ae14d24ca0defeb7d99957e54bf56f19JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3557012f-fee6-61b9-32c5-16ceff1e60fc&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3BlbnNpb25lcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0953fafa9c408e38856266ed02e29f526ef9bd05c8e9818eaed8ceebbb13a81eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3557012f-fee6-61b9-32c5-16ceff1e60fc&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3BlbnNpb25lcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61b40a860e30767e878e31edd884403096010796a796d0ee40f8fab1a6f9bb87JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3557012f-fee6-61b9-32c5-16ceff1e60fc&amp;u=a1aHR0cHM6Ly93d3cub2VkLmNvbS9kaWN0aW9uYXJ5L3BlbnNpb25lcl9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00e76c55345e420ce8315fe3733eef8652f1e17bfd5c1b99b87e5adf8e382e4bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3557012f-fee6-61b9-32c5-16ceff1e60fc&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9wZW5zaW9uZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80c0312fab92596db4fd4be28e52072a76039c708852497655dbd1c90ba6b90cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3557012f-fee6-61b9-32c5-16ceff1e60fc&amp;u=a1aHR0cHM6Ly93d3cuZGVmaW5pdGlvbnMubmV0L2RlZmluaXRpb24vcGVuc2lvbmVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f9f8d6dd8666d87dc02a7492a8018e7c4a928b051994793f00d5abdeb3709f5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3557012f-fee6-61b9-32c5-16ceff1e60fc&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vZGljdGlvbmFyeS9wZW5zaW9uZXI&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0112a008b96f1520d2811fa3468646827b6104fa7a4a72a101c90ee8b3f70d9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c25b331-5f77-600a-2970-a4d05ed9617d&amp;u=a1aHR0cHM6Ly9vbGRuYXZ5LmdhcC5jb20vP21zb2NraWQ9MGMyNWIzMzE1Zjc3NjAwYTI5NzBhNGQwNWVkOTYxN2Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1163f1910630f8bbffd9f9b14602bf792af7b9230555eb8ddd46784b3edc30bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c25b331-5f77-600a-2970-a4d05ed9617d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT2xkXyhmaWxtKQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c221bb3900bba241a517e3f3797bbbad9cffb7c4441f1a477b2d0b4638701909JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c25b331-5f77-600a-2970-a4d05ed9617d&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxMDk1NDY1Mi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d66c82a65ccda35ba79671b66b36e11e2a22d004d00af9f36be9c2df57c0144fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c25b331-5f77-600a-2970-a4d05ed9617d&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L29sZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00f3173b91652e8ddf19eb61a0b300b6868849aa19ce08dd246ede532c19d3a1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c25b331-5f77-600a-2970-a4d05ed9617d&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1BNFUycE1SVjlfaw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c6a2accc3d77f3561b5705e7d23ce99714a1bc6f471a6582e987f3886d7e3efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c25b331-5f77-600a-2970-a4d05ed9617d&amp;u=a1aHR0cHM6Ly93d3cucm90dGVudG9tYXRvZXMuY29tL20vb2xk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54987163103076d9d85f391a213351593b5b0f4f9b8dd9d5186bdcce74662952JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c25b331-5f77-600a-2970-a4d05ed9617d&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj04NHhBRDRyLTlrRQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0dbaa480d022651339678fc80eb5d2dbd9e18866f79129b0d99acb623237014JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c25b331-5f77-600a-2970-a4d05ed9617d&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL29sZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0af534c882f4351f540f1ed80043ad67c1399fa89a74164f78a72b02de248a1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c25b331-5f77-600a-2970-a4d05ed9617d&amp;u=a1aHR0cHM6Ly93d3cubmV0ZmxpeC5jb20vdGl0bGUvODE0MTAzODY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9cc974bc96d0504098501897b839f0407b21561fa57e6de86ffd5063dca08870JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c25b331-5f77-600a-2970-a4d05ed9617d&amp;u=a1aHR0cHM6Ly93d3cudW5pdmVyc2FscGljdHVyZXNhdGhvbWUuY29tL21vdmllcy9vbGQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b5d697e67d81d5b950c115d3a61a94217e4d47000f3299916673094e573d7abJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1410d6c7-5d1c-6fd8-18dc-c1265c496e70&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=741501231b913239a8cf50469183cfceb2690a2554b03fd4629b827b3be24710JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1410d6c7-5d1c-6fd8-18dc-c1265c496e70&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC8_bXNvY2tpZD0xNDEwZDZjNzVkMWM2ZmQ4MThkY2MxMjY1YzQ5NmU3MA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1009d5f20e2588205c6db7438ebf1b52bf7aa183c78330eca84afcdfc2bc621cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1410d6c7-5d1c-6fd8-18dc-c1265c496e70&amp;u=a1aHR0cHM6Ly93d3cubmVyZHdhbGxldC5jb20vaW52ZXN0aW5nL2NhbGN1bGF0b3JzL3JldGlyZW1lbnQtY2FsY3VsYXRvcj9tc29ja2lkPTE0MTBkNmM3NWQxYzZmZDgxOGRjYzEyNjVjNDk2ZTcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=37a157c539582207d8a2ec2d530dabb146718c9a18847a86ed52f445f7c78732JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1410d6c7-5d1c-6fd8-18dc-c1265c496e70&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUmV0aXJlbWVudA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b82703f9f56f6e3faae2de35b90f684a919d578f50900d2d7e98f720482fb6bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1410d6c7-5d1c-6fd8-18dc-c1265c496e70&amp;u=a1aHR0cHM6Ly93d3cubGVnYWN5cmV0aXJlLmNvbS9jb21tdW5pdGllcy9sZWdhY3ktdmlsbGFnZS1vZi1zdC1nZW9yZ2Uv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e6ad9e58cca0ae8c463b8267c257b23edc26831b9603b1dd774ddf2da73b6e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1410d6c7-5d1c-6fd8-18dc-c1265c496e70&amp;u=a1aHR0cHM6Ly93d3cuY2FsY3VsYXRvci5uZXQvcmV0aXJlbWVudC1jYWxjdWxhdG9yLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f500e55a513ddbbd92ea16a68aa9aea78f6383eda935c37283b9a93a7af6f19aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1410d6c7-5d1c-6fd8-18dc-c1265c496e70&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC9zdGVwcy10by10YWtlLWJlZm9yZS15b3UtcmV0aXJlLz9tc29ja2lkPTE0MTBkNmM3NWQxYzZmZDgxOGRjYzEyNjVjNDk2ZTcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c76b245cf09dbde788825be0b142a4731b51ec02ee1295b4a23ae429a2d558aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1410d6c7-5d1c-6fd8-18dc-c1265c496e70&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50L3BsYW4tZm9yLXJldGlyZW1lbnQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2993937cb3f7f93c923fbdad21a472fa232bbaf86a108901c85472654c1ed4faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1410d6c7-5d1c-6fd8-18dc-c1265c496e70&amp;u=a1aHR0cHM6Ly93d3cudXNhLmdvdi9yZXRpcmVtZW50LXBsYW5uaW5nLXRvb2xz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3920b90a961651f7eefcb26bd9dd0328dcc7fcb3f9dc4ee41301d48263f69428JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1410d6c7-5d1c-6fd8-18dc-c1265c496e70&amp;u=a1aHR0cHM6Ly93d3cudHJhbnNhbWVyaWNhLmNvbS9sb2dpbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97dbb273818c4fcbfd598f0625ace7d8c351af6017146388f8e7f8a77920eb8bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c0e7bf8-02da-6615-103e-6c1903216730&amp;u=a1aHR0cHM6Ly9zZHNjZi5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cc5b0dd4c9d85eae80a707afbe776665dc335ed7a0a316b6a6744f4fef295237JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c0e7bf8-02da-6615-103e-6c1903216730&amp;u=a1aHR0cHM6Ly9zZXJ2aW5nc2VuaW9ycy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c9e378701a6f4bb1a02485f7b2701623e0d427c21873dc04edc5aebf81b36f6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c0e7bf8-02da-6615-103e-6c1903216730&amp;u=a1aHR0cHM6Ly9zZHNjZi5vcmcvc2VuaW9yLXJlc291cmNlcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=32aed60c93d687aea71748d633d8fdc8ea29ce61de82540364c8bb13e7187b83JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c0e7bf8-02da-6615-103e-6c1903216730&amp;u=a1aHR0cHM6Ly93d3cuc2FuZGllZ29jb3VudHkuZ292L2NvbnRlbnQvc2RjL2hoc2EvcHJvZ3JhbXMvYWlzLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7f44f93c1b699e7819b0fc50d5c77011364f22b9f0af712a32602e8ff14911aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c0e7bf8-02da-6615-103e-6c1903216730&amp;u=a1aHR0cHM6Ly93d3cuc2RhcmNjLmdvdi9jb250ZW50L2FyY2MvaG9tZS9kaXZpc2lvbnMvYXNzZXNzb3IvcHJvcGVydHktdGF4LXNhdmluZ3Mvc2VuaW9yLWRpc2FibGVkLWV4Y2x1c2lvbi5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=22fe82986fdfc931cdf01d013df72e5558e05b721e7996fa22764963164fdc69JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c0e7bf8-02da-6615-103e-6c1903216730&amp;u=a1aHR0cHM6Ly93d3cuYWZ0ZXI1NS5jb20vc2VhcmNoL2NhL3Nhbi1kaWVnbw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ea893d84e5becf4bde90db5ce956fe85c6fc5119cbf2d8b3e59abcb00a4d62b8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c0e7bf8-02da-6615-103e-6c1903216730&amp;u=a1aHR0cHM6Ly93d3cuc2FuZGllZ29jb3VudHkuZ292L2NvbnRlbnQvc2RjL2hoc2EvcHJvZ3JhbXMvYWlzL09sZGVyLUFkdWx0cy5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc5d983c41180d5bd083af43588f03a7804fbd1bd50082eb4d06d99abf7611acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c0e7bf8-02da-6615-103e-6c1903216730&amp;u=a1aHR0cHM6Ly93d3cuc2FuZGllZ29mb29kYmFuay5vcmcvcHJvZ3JhbXMvc2VuaW9yLWZvb2QtcHJvZ3JhbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6fbb144d2035ac58dbb0aa375b2502c3430e4215449c341594e6aa250c0c66eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c0e7bf8-02da-6615-103e-6c1903216730&amp;u=a1aHR0cHM6Ly9zZXJ2aW5nc2VuaW9ycy5vcmcvd2hhdC13ZS1kby9wcm9ncmFtcy1zZXJ2aWNlcy9ob3VzaW5nLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d939e52ffc11b0d4eb5326521de6abf56061ff1ec5e7afd2017242fff2856de3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c0e7bf8-02da-6615-103e-6c1903216730&amp;u=a1aHR0cHM6Ly91bHRpbWF0ZXNlbmlvcnJlc291cmNlLmNvbS9zdGF0ZXMvY2FsaWZvcm5pYS9zYW4tZGllZ28&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f75133fa68ce6eaed18e132e5f64996d4a83b9ee49a1fe769e96bb0236ab2dbfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05df75b2-ecec-6301-3574-6253ed7662b7&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9uZXcteW9yay1jaXR5LzM1MjgwNjctODMteWVhci1vbGQtYWlyLWZvcmNlLXZldGVyYW4tMi5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5e789bf72d29ce1d50bee1139b484a0f3031397e23d3c64cbe741289f7b54103JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05df75b2-ecec-6301-3574-6253ed7662b7&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9yb2NoZXN0ZXItYXJlYS8yNjAxOTU0LWFiYW5kb25lZC1zdWJ3YXkuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7331fc7252116bcc3e0f2b2ac834cf136ea6b2fb02f2eade630388fd3fc3e3e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05df75b2-ecec-6301-3574-6253ed7662b7&amp;u=a1aHR0cHM6Ly9hbXdmYW5zLmNvbS90aHJlYWQvNDU2L2xpdHRsZXRvbi1ib3dsaW5nLWFsbGV5LW11cmRlcnMtY29sb3JhZG8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=104c1e3259601cab15a6971e7f2c67c7d6080d9949d98d60de140d250947cbcdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05df75b2-ecec-6301-3574-6253ed7662b7&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9sb3MtYW5nZWxlcy8xODQ0NzYwLXdoYXQtc29tZS1tb3ZpZXMtZmVhdHVyZS1sLXN1YndheS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82a68ff5d64181407b1e98203607db9f59c4e2ba4409a1afc3cdf0a5b9451860JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05df75b2-ecec-6301-3574-6253ed7662b7&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9kdXJoYW0tY291bnR5LXJlc3RhdXJhbnRzL3N1YndheTE2Lmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80d9678f9dfde1d08785746c5b1fff69931f859cc1c7ab4d0725d59d85c8808dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05df75b2-ecec-6301-3574-6253ed7662b7&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9zYW4tZGllZ28tY291bnR5LXJlc3RhdXJhbnRzL3N1YndheS0zNDE5NS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d5673a6e41bbf99132f698c040376705cb80de311f06b4078a965db0e1a4ed54JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05df75b2-ecec-6301-3574-6253ed7662b7&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9ob3VzZS8zMjE4MjY4LTN4MTItdnMtM3g2LXN1YndheS10aWxlLWJhY2tzcGxhc2guaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8c9719dff5c91f0d5ba5dfac90eeca420de7278f7b72d54782692e871c6c95f8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05df75b2-ecec-6301-3574-6253ed7662b7&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9uZXcteW9yay1jaXR5LzM0NDYxODctanVzdC1wb3N0ZWQtdmlkLW1vbnRyZWFsLW1ldHJvLXN1YndheS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=adc551e62eecff71acea15088d39e79c10fab596e4fbdff89b3286b52eb1cb78JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05df75b2-ecec-6301-3574-6253ed7662b7&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9uZXcteW9yay1jaXR5LzM0NTc0Mjktc3Vid2F5LWJhbGFuY2UtcXVlc3Rpb25zLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c34e36674295305cf3315f8ca2f669ced8a167f03938ea3125df5a8f22a33bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05df75b2-ecec-6301-3574-6253ed7662b7&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9sb2NhdGlvbnMvU3Vid2F5L0x5bm53b29kLVdhc2hpbmd0b24uaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6831a8766b4c2b315cb2507151b80f70db454508bd11791ffa87be7731eab7aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02dca666-5cfe-62a0-34cb-b1875d8963a4&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ab520a85bb399a9e5bdb4f53346af3a136501bad485bb27c94056eb6a3c5b31JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02dca666-5cfe-62a0-34cb-b1875d8963a4&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d8cb3aef95ab863b72f6dd50ba17ab391f2dc57ad7a9957080290b82e1c2fc6bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02dca666-5cfe-62a0-34cb-b1875d8963a4&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvZnJhaWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ca0e91da849322b9714449bddefa6629634906f8d365b28362dd425309c7ad6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02dca666-5cfe-62a0-34cb-b1875d8963a4&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b97e95f8e68ef564a6cbc54c6ae7c44c70e5583d4d19ceebff9ea179ebae0e99JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02dca666-5cfe-62a0-34cb-b1875d8963a4&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9mcmFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=229a3d0f1625846b3f85486d365293a2634fa1a2f740f7d1555926f424cb52c7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02dca666-5cfe-62a0-34cb-b1875d8963a4&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=51243225f8a3c82bddfbe0d49cf0f75337942f6882be7f281ceb315f86a73a44JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02dca666-5cfe-62a0-34cb-b1875d8963a4&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2d1bd93938e55cafc07cf38a359b7f84b7861ec92ec16c274712c8dd0cefd31JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02dca666-5cfe-62a0-34cb-b1875d8963a4&amp;u=a1aHR0cHM6Ly9lbi5tLndpa3Rpb25hcnkub3JnL3dpa2kvZnJhaWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3ddd410b8545d217a1ab315e4b9f91e2dc39f0891e96b7171acca4b317a03433JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02dca666-5cfe-62a0-34cb-b1875d8963a4&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL2RpY3Rpb25hcnkvZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=caaaad88ab6e7cb9bc8b4662a7e785dd42a0ecc76eacadd00585b486294f8dedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02dca666-5cfe-62a0-34cb-b1875d8963a4&amp;u=a1aHR0cHM6Ly93d3cub3hmb3JkbGVhcm5lcnNkaWN0aW9uYXJpZXMuY29tL2RlZmluaXRpb24vZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34a63ab98bd4ce7cb3cbe306133440be58d8fb130c6e1556239dc803c5d2c031JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f8e373-06ad-669c-0ed1-f49207e967e6&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FnZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=795363ee5907ed766b7471a7cdda8fe00006e2e32433701fda7d4569f6652ccbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f8e373-06ad-669c-0ed1-f49207e967e6&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FnZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e04d89283e5c10e72ff0775c4a8184d80d83f24f3ff4fe436462fb245e778776JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f8e373-06ad-669c-0ed1-f49207e967e6&amp;u=a1aHR0cHM6Ly9jb3JyZWN0d29yZGluZy5jb20vYWdlZC1vci1hZ2Uv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=744f138822658f5117c9bd589b941d086b301fe934f54e977b03b8d72451a4afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f8e373-06ad-669c-0ed1-f49207e967e6&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FnZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9000577a7ad6c863c6dfca015dc091eb7b4518541b85435983f42570ea1b2f69JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f8e373-06ad-669c-0ed1-f49207e967e6&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3RoZSUyMGFnZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=67313a88bf387b2297489fa817d0d690e2f0cd47f4d0bc7dc42c27655c214544JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f8e373-06ad-669c-0ed1-f49207e967e6&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2FnZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d584b5789d5a5a389c1702d93b739d533cd75ff4074fcf9710e27b9092b441beJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f8e373-06ad-669c-0ed1-f49207e967e6&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNzA0NDAyMA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8387a9d090ea31f154a543c5cde4f05cb8b82fe672767196ec444184bd6d7697JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f8e373-06ad-669c-0ed1-f49207e967e6&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FnZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc1fe714d55466c3582a00cc043cbf86a20df96906d6567d88100c72fda6a087JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f8e373-06ad-669c-0ed1-f49207e967e6&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2FnZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f50b0ee371ddab8a6cb4c2a4eeab05f20b28094176c667ab8545a6b031f47e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f8e373-06ad-669c-0ed1-f49207e967e6&amp;u=a1aHR0cHM6Ly90cnVzdGFnZWQub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2d885be9cc52cf0a36f65542b27882047433cf4440392a54f7126f258a2ca37JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3b4ab75e-4f7f-6395-129c-a0bf4e6162e2&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZWFzeS1kaW5uZXItaWRlYXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c1ae5ede3f4fc3d5a16e139748b5c58468a3ac8bd5600406495cd4cccce543cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3b4ab75e-4f7f-6395-129c-a0bf4e6162e2&amp;u=a1aHR0cHM6Ly93d3cuYWxscmVjaXBlcy5jb20vMTAwLWVhc3ktbWVhbHMtMTE2OTUyMjc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97de0b0718fff585fa7f7f07efbff4799f0713d715f49f49bb380dc186eb387eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3b4ab75e-4f7f-6395-129c-a0bf4e6162e2&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzY4OTA2OTk3L2Jlc3QtZWFzeS1kaW5uZXItcmVjaXBlcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=88280f465dcad1c167921a8d17be072f602ed1d356a1b087edb45004ecfad5c7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3b4ab75e-4f7f-6395-129c-a0bf4e6162e2&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6bdff5fd2e4b9b2442881d8fe4478d5e13519844095ad385daf5c0ac120e0e91JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3b4ab75e-4f7f-6395-129c-a0bf4e6162e2&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zLzMwLW1pbnV0ZS1kaW5uZXItcmVjaXBlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a35f258145f8b9adb5eb269b31024514af74dda12cf3b1da3e2f89054a169b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3b4ab75e-4f7f-6395-129c-a0bf4e6162e2&amp;u=a1aHR0cHM6Ly90aGVyZWFsZm9vZGRpZXRpdGlhbnMuY29tL2Vhc3ktZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8877924e0555fee400d0755a5542ea6fc549339e8e237b22d198f701468b8fb6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3b4ab75e-4f7f-6395-129c-a0bf4e6162e2&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzMyMjY0Mjg0L2Vhc3ktZGlubmVyLXJlY2lwZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0963911d8cfcf7d243201ef2dc4282c51fd1fc8de284f22ea8b5d98b9c11b8b4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3b4ab75e-4f7f-6395-129c-a0bf4e6162e2&amp;u=a1aHR0cHM6Ly9tZWFsc29ud2hlZWxzc212Lm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e955a5e8c4485706f79274917db12ac8d5237345d4748b4b1a104c4c5e9fae8cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3b4ab75e-4f7f-6395-129c-a0bf4e6162e2&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zL2Vhc3ktZGlubmVyLXJlY2lwZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7fd794d79a490daed898ece9b8e01435587146521a6e58aa216dde0ddeecff92JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3b4ab75e-4f7f-6395-129c-a0bf4e6162e2&amp;u=a1aHR0cHM6Ly93d3cuaGVsbG9mcmVzaC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0aa44d6b7f24b7ef6881f9887557a8f7ceac45dde8dddd9d7385225abdc03682JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24d07d1d-9039-67bb-3c03-6afc914e666e&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3N0b3B3YXRjaC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=44f0108baa55ad0020f51e8bae604acbbb81db93ecbeaa21f93dc2666a023bb0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24d07d1d-9039-67bb-3c03-6afc914e666e&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3RpbWVyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0bdb708b9b86dac3a5d71c30719814077577a25f9e86a3c208418524e9197d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24d07d1d-9039-67bb-3c03-6afc914e666e&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL2RhdGUvZGF0ZWFkZC5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e28805b2f9124d716ade1640d048088810cb28e4e28d40f5df0904bc426e8b3cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24d07d1d-9039-67bb-3c03-6afc914e666e&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87bd0a949af5426c26cd5a5293ee5fcae5e43151170df049d6b243372799c9cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24d07d1d-9039-67bb-3c03-6afc914e666e&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL2NvdW50ZG93bi9jcmVhdGU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b8a1ecd97b50f2464b19737022a797ef6a35a414c2abf66a813f179f292557e9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24d07d1d-9039-67bb-3c03-6afc914e666e&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL2NhbGVuZGFyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9e76536e605e970dba39bd3b38e011dc172a0722955e34d96a7f73103e03d5b9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24d07d1d-9039-67bb-3c03-6afc914e666e&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL2RhdGUvd29ya2RheXMuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=878052f65cac53ec3cc56ed7f1681bb427d6ab1ee213cce45738b913ec4a76cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24d07d1d-9039-67bb-3c03-6afc914e666e&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3N1bi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a5e34a724ecb7bef884233dd6bcec01f199b07c594b3a896b3e3a29b60f308eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24d07d1d-9039-67bb-3c03-6afc914e666e&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL2Nsb2Nrcy9mcmVlLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0bdeeac21abbe957848b8004e62a9da5c153986d5a6ee1d650edcd47926dce32JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24d07d1d-9039-67bb-3c03-6afc914e666e&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3N0b3B3YXRjaC9oZWxwLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a16a534b60b1b8fba8170bd808782771b8ecff9792b4b3014be7ba03fa0109bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cebbfc5-6505-6f70-17c3-a824641b6e2f&amp;u=a1aHR0cHM6Ly93YWxsZXRodWIuY29tL2Fuc3dlcnMvY2MvYmFuay1vZi1hbWVyaWNhLXRyYXZlbC1pbnN1cmFuY2UtMTAwMDM3NS0yMTQwNjY5OTE0Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=994124b9f64983470ac91d6a9d39ff02cba5994049ca65811b8ca95658c40a9eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cebbfc5-6505-6f70-17c3-a824641b6e2f&amp;u=a1aHR0cHM6Ly93YWxsZXRodWIuY29tL2QvYmFuay1vZi1hbWVyaWNhLXByZW1pdW0tcmV3YXJkcy1jcmVkaXQtY2FyZC0zMDY1Yw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d8915bd5815a8a7d7010f61b24d20fe0c701c5ee7684453fa11f15ec5e7e4a58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cebbfc5-6505-6f70-17c3-a824641b6e2f&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9sb2NhdGlvbnMvQmFua29mQW1lcmljYS9BbGJhbnktR2VvcmdpYS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94f920c28f1b3a921f70fff6fba252c92c102af899ad40f786a84137d29dbfddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cebbfc5-6505-6f70-17c3-a824641b6e2f&amp;u=a1aHR0cHM6Ly93YWxsZXRodWIuY29tL2Fuc3dlcnMvY2MvYmFuay1vZi1hbWVyaWNhLXJlbnRhbC1jYXItaW5zdXJhbmNlLTEwMDA0MDUtMjE0MDY2OTE0MC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d444a9854e6e88f0661aab6eaed7560310eaad59ad635f9b91158e900b388dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cebbfc5-6505-6f70-17c3-a824641b6e2f&amp;u=a1aHR0cHM6Ly93YWxsZXRodWIuY29tL2QvYmFuay1vZi1hbWVyaWNhLWJ1c2luZXNzLWFkdmFudGFnZS10cmF2ZWwtcmV3YXJkcy01MzZj&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cffbc2aeaf40ef2dde6254155365820dba5555846a6d87efaa8029b92fc2fe22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cebbfc5-6505-6f70-17c3-a824641b6e2f&amp;u=a1aHR0cHM6Ly93YWxsZXRodWIuY29tL2QvYmFuay1vZi1hbWVyaWNhLWNhc2gtcmV3YXJkcy1zdHVkZW50cy1jcmVkaXQtY2FyZC03MDZj&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=93fda1cb986eeb01502205a93f2b2452c9fac2ca4fc93d18b5ca970b34f9ded1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cebbfc5-6505-6f70-17c3-a824641b6e2f&amp;u=a1aHR0cHM6Ly93YWxsZXRodWIuY29tL2Fuc3dlcnMvY2MvdmVudHVyZW9uZS12cy1iYW5rLW9mLWFtZXJpY2EtdHJhdmVsLXJld2FyZHMtMjE0MDY5MTM4Ny8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bab457771969e27ea821cddf4f2573a9f76c8a112d1eab632c76b921c63d75edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cebbfc5-6505-6f70-17c3-a824641b6e2f&amp;u=a1aHR0cHM6Ly93YWxsZXRodWIuY29tL2QvYmFuay1vZi1hbWVyaWNhLWNhc2gtcmV3YXJkcy1zZWN1cmVkLWNyZWRpdC1jYXJkLTMyNzRj&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=77b58d5f6d5c6f59498ae934176d88e197554ba956c910f038314ca6d49b60c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cebbfc5-6505-6f70-17c3-a824641b6e2f&amp;u=a1aHR0cHM6Ly93YWxsZXRodWIuY29tL2Fuc3dlcnMvY2MvYmFuay1vZi1hbWVyaWNhLXRyYXZlbC1yZXdhcmRzLXBvaW50cy1yZWRlbXB0aW9uLTEwMDAzNTQtMjE0MDY3NDE5NS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c91883d9f73794fc833892f2baf48a551d2dc86462f6e637e5efb0ce08b5873cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2cebbfc5-6505-6f70-17c3-a824641b6e2f&amp;u=a1aHR0cHM6Ly93YWxsZXRodWIuY29tL2Fuc3dlcnMvY2MvaW50ZXJuYXRpb25hbC1zdHVkZW50LWNyZWRpdC1jYXJkLWJhbmstb2YtYW1lcmljYS0yMTQwNjc2MTYwLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fdc99b54de40664659e4a04ab04b0d1ea2522f07eed9ac97d9ee8a0e8faa6300JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e306636-199a-6440-3a4d-71d7184465fa&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cz9tc29ja2lkPTFlMzA2NjM2MTk5YTY0NDAzYTRkNzFkNzE4NDQ2NWZh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a99121bce597a5a9d6e5fb31c9468e57f4c32406207dc30fcf352298d1720d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e306636-199a-6440-3a4d-71d7184465fa&amp;u=a1aHR0cHM6Ly9hY2NvdW50Lm1pY3Jvc29mdC5jb20vYWNjb3VudA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94c52094a3b90d9d8370644ccd3f45d2217034b2b710f19ae9d4fa8c8c6368e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e306636-199a-6440-3a4d-71d7184465fa&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=50d5f2c4f5ed26eca3c6f216827a61fe3a521c89d03e2f6fb3e18b624ba815a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e306636-199a-6440-3a4d-71d7184465fa&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cy9taWNyb3NvZnQtMzY1P21zb2NraWQ9MWUzMDY2MzYxOTlhNjQ0MDNhNGQ3MWQ3MTg0NDY1ZmE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2382760bd061f9cabed9849b4d582811240d9039920e3bbf0d8417572554ca56JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e306636-199a-6440-3a4d-71d7184465fa&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWljcm9zb2Z0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=662884e40953ea562fc628d840b17d68b10776d8998b9a266749c5d9b7e9897fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e306636-199a-6440-3a4d-71d7184465fa&amp;u=a1aHR0cHM6Ly9zaWdudXAubGl2ZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1885d07ff003a72b4858305057ca475c94f29f0fad994f346dc41e96450590f5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e306636-199a-6440-3a4d-71d7184465fa&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS9tL2hvbWU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c2aa27598bc0f29e3a1066fa5e850e230ab0eae72fa8330926a9ceb46548b74JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e306636-199a-6440-3a4d-71d7184465fa&amp;u=a1aHR0cHM6Ly9tMzY1LmNsb3VkLm1pY3Jvc29mdC8_b3JpZ2luZG9tYWluPU9mZmljZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47d5c2532e1d50ff4215ddb1435357b2e4e9bb3951781063f3036bfbc8dc228bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e306636-199a-6440-3a4d-71d7184465fa&amp;u=a1aHR0cHM6Ly9vdXRsb29rLm9mZmljZS5jb20vbWFpbC9pbmJveA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aefeb0caa97457592af32c15e339b6f8f3e8bbdd3f06592a37ab9a2f009a2434JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e306636-199a-6440-3a4d-71d7184465fa&amp;u=a1aHR0cHM6Ly9hY2NvdW50Lm1pY3Jvc29mdC5jb20vYWNjb3VudC1jaGVja3Vw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=17a26323cc727c1396c90905b850fe37918429c34cc6b695449a2403f40e3f2aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e1272f1-97a9-6680-0300-651096076750&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tZ2IvY29udGFjdHVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=152ab24234e00acd1684c9b072e1625b01a4bc0972bb259cb92a6d31f9fdcd95JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e1272f1-97a9-6680-0300-651096076750&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvYWNjb3VudHMtYmlsbGluZy9tYW5hZ2UvaG93LXRvLXNpZ24taW4tdG8taG90bWFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a418beb61319e23beb06c6d6fddf38469fe6a80fbaae7cffb28516696704c82JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e1272f1-97a9-6680-0300-651096076750&amp;u=a1aHR0cHM6Ly90ZWNoY29tbXVuaXR5Lm1pY3Jvc29mdC5jb20vY2F0ZWdvcnkvbWljcm9zb2Z0LWNvcGlsb3QvYmxvZy9taWNyb3NvZnQtY29waWxvdC1ibG9n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91e8876f89e4abb97ab59e1954078e65c1f0b6686e83698bc3997dd81de07bd7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e1272f1-97a9-6680-0300-651096076750&amp;u=a1aHR0cHM6Ly90ZWNoY29tbXVuaXR5Lm1pY3Jvc29mdC5jb20vYmxvZy9leGNoYW5nZS9leGNoYW5nZS1vbmxpbmUtZXdzLXlvdXItdGltZS1pcy1hbG1vc3QtdXAvNDQ5MjM2MQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b075935c40887c1d3302c2f6831d16721167fe608b7162b5f28a77857011d0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e1272f1-97a9-6680-0300-651096076750&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9kZXBsb3ltZW50L2luc3RhbGwtdXBncmFkZS9nZXR0aW5nLXJlYWR5LWZvci10aGUtd2luZG93cy0xMS11cGdyYWRl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c64285013b5ea911da80ea92eddccdea9aff09d797d556e96da0867aaccebeeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e1272f1-97a9-6680-0300-651096076750&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZnItZnIvd2luZG93cy9tZXR0cmUtJUMzJUEwLWpvdXItbGVzLXBpbG90ZXMtdmlhLWdlc3Rpb25uYWlyZS1kZS1wJUMzJUE5cmlwaCVDMyVBOXJpcXVlcy1kYW5zLXdpbmRvd3MtZWM2MmY0NmMtZmYxNC1jOTFkLWVlYWQtZDcxMjZkYzFmN2I2&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e306f7084514acc2a7f83dbb25b3385c18f146a137ad172f1004155a43550c2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e1272f1-97a9-6680-0300-651096076750&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvd2luZG93cy9ha3R1YWxpc2llcmVuLXZvbi10cmVpYmVybi0lQzMlQkNiZXItZ2VyJUMzJUE0dGUtbWFuYWdlci1pbi13aW5kb3dzLWVjNjJmNDZjLWZmMTQtYzkxZC1lZWFkLWQ3MTI2ZGMxZjdiNg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e3ba5f65575d13ae26c9e8cbf01218c2a894a38e0bb77d727fd633ad786bc12JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e1272f1-97a9-6680-0300-651096076750&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvZWRnZS9nZXR0aW5nLXRoZS1sYXRlc3QtbWljcm9zb2Z0LWVkZ2UtdXBkYXRlLWp1c3QtZ290LWVhc2llcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=956a02b254c5e59ce246b2b006105be14d328287657087079c771265e54498afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e1272f1-97a9-6680-0300-651096076750&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvb3V0bG9vay90cmFpbmluZy9zaGFyZS15b3VyLWNhbGVuZGFyLWluLW91dGxvb2s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f26710c0f70197192b3c7f68e69e212926c1ccf5deff9e52922bba365ed5414JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e1272f1-97a9-6680-0300-651096076750&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvZm9ybXMvc2lnbi1pbi10by1taWNyb3NvZnQtZm9ybXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2e2dab36f1930c6692d3fa40dda1ec5c5f5212f8c0490837dc45273e788d4c62JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35e4094d-fca7-616e-0c9a-1eacfd9b60a0&amp;u=a1aHR0cHM6Ly93d3cud2VhdGhlci5nb3YvOTQxMTQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ddc0fc25ac21061077dbadef3de680eec77cfe712a6c3debf81dadacfffae8aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35e4094d-fca7-616e-0c9a-1eacfd9b60a0&amp;u=a1aHR0cHM6Ly93d3cud2VhdGhlci5nb3YvOTQxMjE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5d1bfc87687db53cc3202dba690713498d4a59c8ede0655e9df803b9cc5da223JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35e4094d-fca7-616e-0c9a-1eacfd9b60a0&amp;u=a1aHR0cHM6Ly9wcmV2aWV3LWZvcmVjYXN0LndlYXRoZXIuZ292L01hcENsaWNrLnBocD96b25laWQ9UFpaNTMw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cc065930f8587dbcb6c9fda9eeed613ee5bb26f953ca2de0ba6928d922fc27edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35e4094d-fca7-616e-0c9a-1eacfd9b60a0&amp;u=a1aHR0cHM6Ly9tYXJpbmUud2VhdGhlci5nb3YvTWFwQ2xpY2sucGhwP3pvbmVpZD1DQVowMDY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8786d791d20db67433c1067ffac1d13a400a472f7d305953e24671daff8bec3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35e4094d-fca7-616e-0c9a-1eacfd9b60a0&amp;u=a1aHR0cHM6Ly93d3cubG9jYWxjb25kaXRpb25zLmNvbS91cy9zYW4tZnJhbmNpc2NvL2NhbGlmb3JuaWEvd2VhdGhlci9mb3JlY2FzdC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ff7e72059da9597061a6177d1892c50ca3ff00f7f66e6f0b63608c9a82c6fe7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35e4094d-fca7-616e-0c9a-1eacfd9b60a0&amp;u=a1aHR0cHM6Ly9raXJhbmludGwuY29tL3Rvb2xzL3dlYXRoZXIvcmFpbi1wcm9iYWJpbGl0eS1jaGVja2VyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=029efbee6be66d0a58c44fe92a7453efd017b59fef7f1ef926537fd081009d24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35e4094d-fca7-616e-0c9a-1eacfd9b60a0&amp;u=a1aHR0cHM6Ly93d3cuYWNjdXdlYXRoZXIuY29tL2VuL3VzL3Nhbi1mcmFuY2lzY28vOTQxMDMvd2VhdGhlci10b21vcnJvdy8zNDc2Mjk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=495aedc68f7d1f89fba3ec379de375f5c863843ce12eb560437b8b0377abb61fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35e4094d-fca7-616e-0c9a-1eacfd9b60a0&amp;u=a1aHR0cHM6Ly93d3cuZWFzZXdlYXRoZXIuY29tL25vcnRoLWFtZXJpY2EvdW5pdGVkLXN0YXRlcy9jYWxpZm9ybmlhL2NpdHktYW5kLWNvdW50eS1vZi1zYW4tZnJhbmNpc2NvL3Nhbi1mcmFuY2lzY28vdG9tb3Jyb3c&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=90703d491754cdbdba832a299432a5f6ef0506f61b7734c4f48ae098fe8c1402JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1afcee5a-154c-6735-20db-f9bb14076634&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvbS9uZXdzL3dvcmxkLXVzLWNhbmFkYS02Njc5Mjk3Nw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8d275e91f1e9d2930e270c3fe1412b9f79a05c07f9d4ae35f438adf9bdf7b80JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1afcee5a-154c-6735-20db-f9bb14076634&amp;u=a1aHR0cHM6Ly9hbGx0aGF0c2ludGVyZXN0aW5nLmNvbS93aG8ta2lsbGVkLWpmaw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2bf45a0a7133a8f76c7111921120e9b188f33f1e88382be423f4969404a3a013JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1afcee5a-154c-6735-20db-f9bb14076634&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQXNzYXNzaW5hdGlvbl9vZl9Kb2huX0YuX0tlbm5lZHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e9bbbf62ea809629afdb6ef65ddb1abd5c9bca246db8ff76c89aa594c4815f4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1afcee5a-154c-6735-20db-f9bb14076634&amp;u=a1aHR0cHM6Ly9oaXN0b3J5Y2hyb25pY2xlcy5vcmcvdGhlLWFzc2Fzc2luYXRpb24tb2Ytam9obi1mLWtlbm5lZHktb2ZmaWNpYWwtc3RvcnktdnMtcGVyc2lzdGVudC1jb25zcGlyYWN5LXRoZW9yaWVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=156d8e82b12f7deb67e596f9df0edc6e2de177d73ddb8037ee9f3581d95373b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1afcee5a-154c-6735-20db-f9bb14076634&amp;u=a1aHR0cHM6Ly9hbGx0aGF0c2ludGVyZXN0aW5nLmNvbS9oaXN0b3J5LXVuY292ZXJlZC93aG8ta2lsbGVkLWpmaw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3c13f236b5cfc23a8d8131b0171e2d5e7d8f51df56fe7597da458e5c0cf9e706JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1afcee5a-154c-6735-20db-f9bb14076634&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vZXZlbnQvYXNzYXNzaW5hdGlvbi1vZi1Kb2huLUYtS2VubmVkeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=338a77de9f5c313f60e5f9269ecefa95fc05db95c404831a15c13e2c659df513JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1afcee5a-154c-6735-20db-f9bb14076634&amp;u=a1aHR0cHM6Ly93d3cuZmJpLmdvdi9oaXN0b3J5L2Nhc2VzLWFuZC1jcmltaW5hbHMvamZrLWFzc2Fzc2luYXRpb24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a506d2710e0b04e40e3413d75991821845c56338365fdfae474e8782b057233JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1afcee5a-154c-6735-20db-f9bb14076634&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGVlX0hhcnZleV9Pc3dhbGQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d35082bfeef12f2020261966611b6ca814c5325ba7ceb91598696232d2aa42ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1afcee5a-154c-6735-20db-f9bb14076634&amp;u=a1aHR0cHM6Ly93d3cuaGlzdG9yeS5jby51ay9hcnRpY2xlL2RpZC10aGUtbW9iLWtpbGwtamZrLW5ldy1ldmlkZW5jZS1zdWdnZXN0cy10aGV5LWRpZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a670ddc3e4a4dd686968c24ed2a834d3f903fac7b9d3dae701863a2dbe09191JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1afcee5a-154c-6735-20db-f9bb14076634&amp;u=a1aHR0cHM6Ly93d3cuaGlzdG9yeS5jb20vYXJ0aWNsZXMvamZrLWFzc2Fzc2luYXRpb24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc017d854dc903234486aec882a243f7e0a9923f85980b4b868213f7be78a66cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013cbadf-02d9-682b-2b7d-ad3e03de699b&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vbWFpbC9hbnN3ZXIvODQ5ND9obD1lbi1JTiZjbz1HRU5JRS5QbGF0Zm9ybSUzRERlc2t0b3A&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=42410dc7ea79c489d779ba0acd3e6d61845784a6bdd221996b0bcba0b1645ecbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013cbadf-02d9-682b-2b7d-ad3e03de699b&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3dlYmRldi9jb21tZW50cy8ybTYxN3MvZmFjZWJvb2tfbG9naW5fcGxlYXNlX25vX21vcmUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=13755feb8daa0eda4c040c5b05244a4ad8ddb273746ba386ef157de0d44654ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013cbadf-02d9-682b-2b7d-ad3e03de699b&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3NvY2lhbG1lZGlhL2NvbW1lbnRzL2FkOXJ6bS9mYWNlYm9va19ob3dfZG9feW91X2dldF9wYXN0X3RoZV9zZWVfbW9yZV9vZi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8edfb4b2592f6370c9108b3207b5d7378fa9ef12a3ae6c34c9d04981349d609cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013cbadf-02d9-682b-2b7d-ad3e03de699b&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vYWNjb3VudHMvYW5zd2VyLzEyODQ5NDU4P2hsPWVu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=37c74aa1b4f4701b6a3e08d517591f259d49d4ee642180fd7150da49ad150999JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013cbadf-02d9-682b-2b7d-ad3e03de699b&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3VCbG9ja09yaWdpbi9jb21tZW50cy9id2U4azMvZGlzYWJsZV9mYWNlYm9va19sb2dpbl9wb3B1cC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=18f273bc3000c6a71c90244084af78eaafce7a90aadb802491a87f1f4c8d364eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013cbadf-02d9-682b-2b7d-ad3e03de699b&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2ZhY2Vib29rL2NvbW1lbnRzL2wzNDZuMy9kaWRfYW55b25lX2Vsc2VfZ2V0X3Byb21wdGVkX3RvX3NpZ25faW5fYWdhaW5fdG8v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aed1e8c6d02eba94dab450665e9e5c21d49c3ba290836b841d3879fdb098da43JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013cbadf-02d9-682b-2b7d-ad3e03de699b&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3ByaXZhY3l0b29sc0lPL2NvbW1lbnRzL28yaDVzdy9ob3dfdG9fYnJvd3NlX2ZhY2Vib29rX3dpdGhvdXRfbG9nZ2luZ19pbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=afb8539d002dec42d86adadac715cb1bd858d520f3e89ed502713e8e79c927f1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013cbadf-02d9-682b-2b7d-ad3e03de699b&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2xpbmVhcHAvY29tbWVudHMvMWFjbDV4OS9mYWNlYm9va19sb2dpbl9ub19sb25nZXJfcG9zc2libGVfbGl0dGxlX2hlbHAv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c5bc0207bf5ce6070286c83f17d3dfbe216341f786e5e8f52d830fab802cc4eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013cbadf-02d9-682b-2b7d-ad3e03de699b&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2ZhY2Vib29rL2NvbW1lbnRzLzFkZ3c5NTcvdW5leHBlY3RlZF9lcnJvcl9vY2N1cnJlZF93aGVuX2lfdHJpZWRfbG9nZ2luZ19pbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=105cab7f27b6ae3642b4a7321a1310d8fc3e0605d123001a12df520b6891238bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013cbadf-02d9-682b-2b7d-ad3e03de699b&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2ZhY2Vib29rL2NvbW1lbnRzLzEzcWtxbGMvZmFjZWJvb2tfMmZhX3R3b19mYWN0b3JfYXV0aGVudGljYXRpb25fbG9naW4v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7394ba0d75a8787b09bc0fcdeb58071becbc2a7b1a9161378c6ef39f8c0c3dd1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d131cd-8508-631d-1a1d-262c8454623f&amp;u=a1aHR0cHM6Ly9vbGVtaXNzLmVkdS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=477bf5ae5a399492abcfe980543fa92d42daf27cf85e96bd0a1f592d6ecc6660JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d131cd-8508-631d-1a1d-262c8454623f&amp;u=a1aHR0cHM6Ly9hZG1pc3Npb25zLm9sZW1pc3MuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=23fbe2806334ad3e30061fd94e76f226b9dd8fc5abd69d5d1c4c9344ed8fed01JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d131cd-8508-631d-1a1d-262c8454623f&amp;u=a1aHR0cHM6Ly9jYXJlZXJzLm9sZW1pc3MuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9f6722837beda51cbcea853a90328645c08dbfdd58a7b25deadeb91baf675ae5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d131cd-8508-631d-1a1d-262c8454623f&amp;u=a1aHR0cHM6Ly9saWJyYXJpZXMub2xlbWlzcy5lZHUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3829e3eaa522d59e6b92f4729f6a878a33dba70be96ab61b32f57f364b424ad0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d131cd-8508-631d-1a1d-262c8454623f&amp;u=a1aHR0cHM6Ly9vbGVtaXNzLmVkdS9wcm9maWxlcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb5bd108cca9f83cd1006134b9eb967cf558aee37a797c9171bced1766ade5d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d131cd-8508-631d-1a1d-262c8454623f&amp;u=a1aHR0cDovL21hcC5vbGVtaXNzLmVkdS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ea99a46ab601e768099ff9230e6c465021b6d24e9fb927afe0cdc546492739d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d131cd-8508-631d-1a1d-262c8454623f&amp;u=a1aHR0cDovL215Lm9sZW1pc3MuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8c125471aed123e50c3f39acf5def460128f30e251be302dd51715e661bccb35JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d131cd-8508-631d-1a1d-262c8454623f&amp;u=a1aHR0cHM6Ly9zdHMub2xlbWlzcy5lZHUvYWRmcy9scy8_d2E9d3NpZ25pbjEuMCZ3dHJlYWxtPXVybiUzQWZlZGVyYXRpb24lM0FNaWNyb3NvZnRPbmxpbmU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=26b332243c9495d5292abc9df7efd3af98b09b37c976b621fe22899b2d7b8723JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d131cd-8508-631d-1a1d-262c8454623f&amp;u=a1aHR0cHM6Ly9jb25uZWN0Lm9sZW1pc3MuZWR1L2FwcGx5Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3fb7e991c78f283e2db7ffd041752b40a0c90e0be0585583b9610b11449e3d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d131cd-8508-631d-1a1d-262c8454623f&amp;u=a1aHR0cHM6Ly9ldmVudGNhbGVuZGFyLm9sZW1pc3MuZWR1L2V2ZW50LzIwMjYtY29tbWVuY2VtZW50LWNvbnZvY2F0aW9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bfbe947cec3910d9a6dfdbe8b942c0b0fbd89a7205519d49c86157183ed1cfffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d6e3a0f-ff20-6bde-1835-2deefef46a74&amp;u=a1aHR0cHM6Ly93d3cubWVuYXJkcy5jb20vc3RvcmUtZGV0YWlscy9zdG9yZS5odG1sP3N0b3JlPTMwNTU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d36450a83567d22764f5ea9dc58ccae1d47b3ad712bb702967fd5bd5880c4ce5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d6e3a0f-ff20-6bde-1835-2deefef46a74&amp;u=a1aHR0cHM6Ly93d3cubWVuYXJkcy5jb20vbWFpbi9zaG9wLWFsbC1kZXBhcnRtZW50cy9jLTE5Mzg0Lmh0bQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7da42fa12ea3f8e2b193b6109970ef7aa426521359aaa89e674d2832181542f6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d6e3a0f-ff20-6bde-1835-2deefef46a74&amp;u=a1aHR0cHM6Ly93d3cubWVuYXJkcy5jb20vbWFpbi9mb290ZXIvY29tcGFueS1pbmZvcm1hdGlvbi9tZW5hcmRzLWNhcmVlcnMvYy0xNDAxNi5odG0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94d0d863a498924b3e760f81155ae71c0b73e730e18af5b95042f5b5e856d47bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d6e3a0f-ff20-6bde-1835-2deefef46a74&amp;u=a1aHR0cHM6Ly93d3cubWVuYXJkcy5jb20vbWFpbi9zaG9wLWFsbC9jLTE2NDI4NzQzMTc3NDYyOTIuaHRt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=43dd8faff5ef72b87917f795a958f6fca5c9201497a3a0bd4b6b8167b40dbe67JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d6e3a0f-ff20-6bde-1835-2deefef46a74&amp;u=a1aHR0cHM6Ly93d3cubWVuYXJkcy5jb20vbWFpbi9mbHllci5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c6b558a0934626f127cfbb624f559a788ed725bea6607cead15e17ae84196b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d6e3a0f-ff20-6bde-1835-2deefef46a74&amp;u=a1aHR0cHM6Ly93d3cubWVuYXJkcy5jb20vbWFpbi8vbG9naW4uaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=602677a0b2757fb1378f7a19d3f06bc2946216ea273ec26aebd713fafbf66abcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d6e3a0f-ff20-6bde-1835-2deefef46a74&amp;u=a1aHR0cHM6Ly93d3cubWVuYXJkcy5jb20vbWFpbi8vaG9tZS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6f356b0698dcd2acde2f0acd865c6b95b13b350fb24afbe5e299624f4ac59f3cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d6e3a0f-ff20-6bde-1835-2deefef46a74&amp;u=a1aHR0cHM6Ly93d3cubWVuYXJkcy5jb20vbWFpbi9zdG9yZS1jYXJlZXJzL2MtMTQwMjIuaHRt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9429e9351b359942386e04d2665131fd4f51cc0330f48766c749538f455f8c32JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d6e3a0f-ff20-6bde-1835-2deefef46a74&amp;u=a1aHR0cHM6Ly93d3cubWVuYXJkcy5jb20vbWFpbi9saWdodGluZy1jZWlsaW5nLWZhbnMvaW5kb29yLWxpZ2h0aW5nL2MtNzQ4OS5odG0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ac3b670826d7589323ca1409ca092c7d03afb7194570a942809a5196a39c109cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d6e3a0f-ff20-6bde-1835-2deefef46a74&amp;u=a1aHR0cHM6Ly93d3cubWVuYXJkcy5jb20vbWFpbi9idWlsZGluZy1tYXRlcmlhbHMvZGVja2luZy1kZWNrLW1hdGVyaWFscy9jLTU3MjcuaHRt&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
+  </si>
+  <si>
+    <t>Sea Point</t>
+  </si>
+  <si>
+    <t>Green Point</t>
+  </si>
+  <si>
+    <t>Woodstock</t>
+  </si>
+  <si>
+    <t>Observatory</t>
+  </si>
+  <si>
+    <t>Salt River</t>
   </si>
   <si>
     <t>Bing</t>
@@ -934,7 +1357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -968,19 +1391,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="G2" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H2" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -988,19 +1411,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="G3" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H3" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1008,19 +1431,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="G4" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H4" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1028,19 +1451,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="G5" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1048,19 +1471,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="G6" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H6" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1068,19 +1491,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="G7" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H7" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1088,19 +1511,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="G8" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1108,19 +1531,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>107</v>
+        <v>175</v>
       </c>
       <c r="G9" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H9" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1128,19 +1551,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="G10" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H10" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1148,19 +1571,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="G11" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H11" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1168,19 +1591,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="G12" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H12" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1188,19 +1611,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="G13" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H13" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1208,19 +1631,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="G14" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H14" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1228,19 +1651,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>113</v>
+        <v>181</v>
       </c>
       <c r="G15" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H15" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1248,19 +1671,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="G16" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H16" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1268,19 +1691,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="G17" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H17" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1288,19 +1711,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G18" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H18" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1308,19 +1731,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="G19" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H19" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1328,19 +1751,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>118</v>
+        <v>186</v>
       </c>
       <c r="G20" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H20" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1348,19 +1771,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="G21" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H21" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1368,19 +1791,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="G22" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H22" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1388,19 +1811,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="G23" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H23" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1408,19 +1831,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="G24" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H24" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1428,19 +1851,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="G25" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H25" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1448,19 +1871,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="G26" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H26" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1468,19 +1891,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="G27" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H27" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1488,19 +1911,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
       <c r="G28" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H28" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1508,19 +1931,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>127</v>
+        <v>195</v>
       </c>
       <c r="G29" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H29" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1528,19 +1951,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="G30" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H30" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1548,19 +1971,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="G31" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H31" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1568,19 +1991,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="G32" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H32" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1588,19 +2011,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="G33" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H33" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1608,19 +2031,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="G34" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H34" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1628,19 +2051,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="G35" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H35" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1648,19 +2071,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>134</v>
+        <v>202</v>
       </c>
       <c r="G36" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H36" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1668,19 +2091,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="G37" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H37" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1688,19 +2111,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="G38" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H38" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1708,19 +2131,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="G39" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H39" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1728,19 +2151,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>138</v>
+        <v>206</v>
       </c>
       <c r="G40" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H40" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1748,19 +2171,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C41" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="G41" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H41" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1768,19 +2191,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C42" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="G42" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H42" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1788,19 +2211,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="G43" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H43" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1808,19 +2231,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="G44" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H44" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1828,19 +2251,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="G45" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H45" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1848,19 +2271,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="G46" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H46" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1868,19 +2291,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C47" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>145</v>
+        <v>213</v>
       </c>
       <c r="G47" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H47" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1888,19 +2311,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>146</v>
+        <v>214</v>
       </c>
       <c r="G48" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H48" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1908,19 +2331,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C49" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="G49" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H49" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1928,19 +2351,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="G50" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H50" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1948,19 +2371,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="G51" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H51" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1968,19 +2391,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="G52" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H52" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1988,19 +2411,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C53" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="G53" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H53" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2008,19 +2431,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C54" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="G54" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H54" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2028,19 +2451,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C55" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="G55" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H55" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2048,19 +2471,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C56" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="G56" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H56" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2068,19 +2491,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C57" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="G57" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H57" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2088,19 +2511,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C58" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="G58" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H58" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2108,19 +2531,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C59" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="G59" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H59" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2128,19 +2551,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C60" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="G60" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H60" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2148,19 +2571,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C61" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>159</v>
+        <v>227</v>
       </c>
       <c r="G61" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H61" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2168,19 +2591,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C62" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="G62" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H62" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2188,19 +2611,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C63" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
       <c r="G63" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H63" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2208,19 +2631,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C64" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="G64" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H64" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2228,19 +2651,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C65" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
       <c r="G65" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H65" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2248,19 +2671,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C66" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="G66" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H66" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2268,19 +2691,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C67" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="G67" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H67" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2288,19 +2711,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C68" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="G68" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H68" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2308,19 +2731,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C69" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>167</v>
+        <v>235</v>
       </c>
       <c r="G69" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H69" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2328,19 +2751,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C70" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>168</v>
+        <v>236</v>
       </c>
       <c r="G70" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H70" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2348,19 +2771,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C71" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>169</v>
+        <v>237</v>
       </c>
       <c r="G71" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H71" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2368,19 +2791,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C72" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>170</v>
+        <v>238</v>
       </c>
       <c r="G72" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H72" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2388,19 +2811,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C73" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>171</v>
+        <v>239</v>
       </c>
       <c r="G73" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H73" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2408,19 +2831,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C74" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="G74" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H74" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2428,19 +2851,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C75" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="G75" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H75" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2448,19 +2871,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C76" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="G76" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H76" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2468,19 +2891,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C77" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>175</v>
+        <v>243</v>
       </c>
       <c r="G77" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H77" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2488,19 +2911,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C78" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>176</v>
+        <v>244</v>
       </c>
       <c r="G78" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H78" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2508,19 +2931,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C79" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="G79" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H79" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2528,19 +2951,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C80" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="G80" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H80" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2548,19 +2971,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C81" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="G81" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="H81" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2568,19 +2991,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C82" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="G82" t="s">
-        <v>190</v>
+        <v>327</v>
       </c>
       <c r="H82" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2588,19 +3011,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C83" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="G83" t="s">
-        <v>190</v>
+        <v>327</v>
       </c>
       <c r="H83" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2608,19 +3031,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C84" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="G84" t="s">
-        <v>190</v>
+        <v>327</v>
       </c>
       <c r="H84" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2628,19 +3051,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C85" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="G85" t="s">
-        <v>190</v>
+        <v>327</v>
       </c>
       <c r="H85" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2648,19 +3071,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C86" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="G86" t="s">
-        <v>190</v>
+        <v>327</v>
       </c>
       <c r="H86" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2668,19 +3091,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C87" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="G87" t="s">
-        <v>190</v>
+        <v>327</v>
       </c>
       <c r="H87" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -2688,19 +3111,19 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C88" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="G88" t="s">
-        <v>190</v>
+        <v>327</v>
       </c>
       <c r="H88" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -2708,19 +3131,19 @@
         <v>95</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C89" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="G89" t="s">
-        <v>190</v>
+        <v>327</v>
       </c>
       <c r="H89" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2728,19 +3151,19 @@
         <v>96</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C90" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="G90" t="s">
-        <v>190</v>
+        <v>327</v>
       </c>
       <c r="H90" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2748,19 +3171,1379 @@
         <v>97</v>
       </c>
       <c r="B91" t="s">
+        <v>166</v>
+      </c>
+      <c r="C91" t="s">
+        <v>167</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G91" t="s">
+        <v>327</v>
+      </c>
+      <c r="H91" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
         <v>98</v>
       </c>
-      <c r="C91" t="s">
+      <c r="B92" t="s">
+        <v>166</v>
+      </c>
+      <c r="C92" t="s">
+        <v>167</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G92" t="s">
+        <v>327</v>
+      </c>
+      <c r="H92" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
         <v>99</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G91" t="s">
-        <v>190</v>
-      </c>
-      <c r="H91" t="s">
-        <v>191</v>
+      <c r="B93" t="s">
+        <v>166</v>
+      </c>
+      <c r="C93" t="s">
+        <v>167</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G93" t="s">
+        <v>327</v>
+      </c>
+      <c r="H93" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" t="s">
+        <v>166</v>
+      </c>
+      <c r="C94" t="s">
+        <v>167</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G94" t="s">
+        <v>327</v>
+      </c>
+      <c r="H94" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" t="s">
+        <v>166</v>
+      </c>
+      <c r="C95" t="s">
+        <v>167</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G95" t="s">
+        <v>327</v>
+      </c>
+      <c r="H95" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" t="s">
+        <v>166</v>
+      </c>
+      <c r="C96" t="s">
+        <v>167</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G96" t="s">
+        <v>327</v>
+      </c>
+      <c r="H96" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" t="s">
+        <v>166</v>
+      </c>
+      <c r="C97" t="s">
+        <v>167</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G97" t="s">
+        <v>327</v>
+      </c>
+      <c r="H97" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" t="s">
+        <v>166</v>
+      </c>
+      <c r="C98" t="s">
+        <v>167</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G98" t="s">
+        <v>327</v>
+      </c>
+      <c r="H98" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" t="s">
+        <v>166</v>
+      </c>
+      <c r="C99" t="s">
+        <v>167</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G99" t="s">
+        <v>327</v>
+      </c>
+      <c r="H99" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" t="s">
+        <v>166</v>
+      </c>
+      <c r="C100" t="s">
+        <v>167</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G100" t="s">
+        <v>327</v>
+      </c>
+      <c r="H100" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" t="s">
+        <v>166</v>
+      </c>
+      <c r="C101" t="s">
+        <v>167</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G101" t="s">
+        <v>327</v>
+      </c>
+      <c r="H101" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" t="s">
+        <v>166</v>
+      </c>
+      <c r="C102" t="s">
+        <v>167</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G102" t="s">
+        <v>328</v>
+      </c>
+      <c r="H102" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" t="s">
+        <v>166</v>
+      </c>
+      <c r="C103" t="s">
+        <v>167</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="G103" t="s">
+        <v>328</v>
+      </c>
+      <c r="H103" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" t="s">
+        <v>166</v>
+      </c>
+      <c r="C104" t="s">
+        <v>167</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G104" t="s">
+        <v>328</v>
+      </c>
+      <c r="H104" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" t="s">
+        <v>166</v>
+      </c>
+      <c r="C105" t="s">
+        <v>167</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G105" t="s">
+        <v>328</v>
+      </c>
+      <c r="H105" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" t="s">
+        <v>166</v>
+      </c>
+      <c r="C106" t="s">
+        <v>167</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G106" t="s">
+        <v>328</v>
+      </c>
+      <c r="H106" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" t="s">
+        <v>166</v>
+      </c>
+      <c r="C107" t="s">
+        <v>167</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G107" t="s">
+        <v>328</v>
+      </c>
+      <c r="H107" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" t="s">
+        <v>166</v>
+      </c>
+      <c r="C108" t="s">
+        <v>167</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G108" t="s">
+        <v>328</v>
+      </c>
+      <c r="H108" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" t="s">
+        <v>166</v>
+      </c>
+      <c r="C109" t="s">
+        <v>167</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G109" t="s">
+        <v>328</v>
+      </c>
+      <c r="H109" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" t="s">
+        <v>166</v>
+      </c>
+      <c r="C110" t="s">
+        <v>167</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G110" t="s">
+        <v>328</v>
+      </c>
+      <c r="H110" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" t="s">
+        <v>166</v>
+      </c>
+      <c r="C111" t="s">
+        <v>167</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G111" t="s">
+        <v>328</v>
+      </c>
+      <c r="H111" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" t="s">
+        <v>166</v>
+      </c>
+      <c r="C112" t="s">
+        <v>167</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G112" t="s">
+        <v>328</v>
+      </c>
+      <c r="H112" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" t="s">
+        <v>166</v>
+      </c>
+      <c r="C113" t="s">
+        <v>167</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G113" t="s">
+        <v>328</v>
+      </c>
+      <c r="H113" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" t="s">
+        <v>166</v>
+      </c>
+      <c r="C114" t="s">
+        <v>167</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G114" t="s">
+        <v>328</v>
+      </c>
+      <c r="H114" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" t="s">
+        <v>166</v>
+      </c>
+      <c r="C115" t="s">
+        <v>167</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G115" t="s">
+        <v>328</v>
+      </c>
+      <c r="H115" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" t="s">
+        <v>166</v>
+      </c>
+      <c r="C116" t="s">
+        <v>167</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G116" t="s">
+        <v>328</v>
+      </c>
+      <c r="H116" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>123</v>
+      </c>
+      <c r="B117" t="s">
+        <v>166</v>
+      </c>
+      <c r="C117" t="s">
+        <v>167</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G117" t="s">
+        <v>328</v>
+      </c>
+      <c r="H117" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" t="s">
+        <v>166</v>
+      </c>
+      <c r="C118" t="s">
+        <v>167</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G118" t="s">
+        <v>328</v>
+      </c>
+      <c r="H118" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" t="s">
+        <v>166</v>
+      </c>
+      <c r="C119" t="s">
+        <v>167</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H119" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>126</v>
+      </c>
+      <c r="B120" t="s">
+        <v>166</v>
+      </c>
+      <c r="C120" t="s">
+        <v>167</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G120" t="s">
+        <v>329</v>
+      </c>
+      <c r="H120" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>127</v>
+      </c>
+      <c r="B121" t="s">
+        <v>166</v>
+      </c>
+      <c r="C121" t="s">
+        <v>167</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G121" t="s">
+        <v>329</v>
+      </c>
+      <c r="H121" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" t="s">
+        <v>166</v>
+      </c>
+      <c r="C122" t="s">
+        <v>167</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G122" t="s">
+        <v>329</v>
+      </c>
+      <c r="H122" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>129</v>
+      </c>
+      <c r="B123" t="s">
+        <v>166</v>
+      </c>
+      <c r="C123" t="s">
+        <v>167</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G123" t="s">
+        <v>329</v>
+      </c>
+      <c r="H123" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" t="s">
+        <v>166</v>
+      </c>
+      <c r="C124" t="s">
+        <v>167</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G124" t="s">
+        <v>329</v>
+      </c>
+      <c r="H124" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>131</v>
+      </c>
+      <c r="B125" t="s">
+        <v>166</v>
+      </c>
+      <c r="C125" t="s">
+        <v>167</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G125" t="s">
+        <v>329</v>
+      </c>
+      <c r="H125" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" t="s">
+        <v>166</v>
+      </c>
+      <c r="C126" t="s">
+        <v>167</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G126" t="s">
+        <v>329</v>
+      </c>
+      <c r="H126" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" t="s">
+        <v>166</v>
+      </c>
+      <c r="C127" t="s">
+        <v>167</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G127" t="s">
+        <v>329</v>
+      </c>
+      <c r="H127" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" t="s">
+        <v>166</v>
+      </c>
+      <c r="C128" t="s">
+        <v>167</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G128" t="s">
+        <v>329</v>
+      </c>
+      <c r="H128" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" t="s">
+        <v>166</v>
+      </c>
+      <c r="C129" t="s">
+        <v>167</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G129" t="s">
+        <v>329</v>
+      </c>
+      <c r="H129" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
+        <v>136</v>
+      </c>
+      <c r="B130" t="s">
+        <v>166</v>
+      </c>
+      <c r="C130" t="s">
+        <v>167</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G130" t="s">
+        <v>329</v>
+      </c>
+      <c r="H130" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" t="s">
+        <v>137</v>
+      </c>
+      <c r="B131" t="s">
+        <v>166</v>
+      </c>
+      <c r="C131" t="s">
+        <v>167</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G131" t="s">
+        <v>329</v>
+      </c>
+      <c r="H131" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" t="s">
+        <v>138</v>
+      </c>
+      <c r="B132" t="s">
+        <v>166</v>
+      </c>
+      <c r="C132" t="s">
+        <v>167</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G132" t="s">
+        <v>329</v>
+      </c>
+      <c r="H132" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>139</v>
+      </c>
+      <c r="B133" t="s">
+        <v>166</v>
+      </c>
+      <c r="C133" t="s">
+        <v>167</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G133" t="s">
+        <v>329</v>
+      </c>
+      <c r="H133" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>140</v>
+      </c>
+      <c r="B134" t="s">
+        <v>166</v>
+      </c>
+      <c r="C134" t="s">
+        <v>167</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="G134" t="s">
+        <v>329</v>
+      </c>
+      <c r="H134" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" t="s">
+        <v>141</v>
+      </c>
+      <c r="B135" t="s">
+        <v>166</v>
+      </c>
+      <c r="C135" t="s">
+        <v>167</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="G135" t="s">
+        <v>329</v>
+      </c>
+      <c r="H135" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>142</v>
+      </c>
+      <c r="B136" t="s">
+        <v>166</v>
+      </c>
+      <c r="C136" t="s">
+        <v>167</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G136" t="s">
+        <v>329</v>
+      </c>
+      <c r="H136" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="s">
+        <v>143</v>
+      </c>
+      <c r="B137" t="s">
+        <v>166</v>
+      </c>
+      <c r="C137" t="s">
+        <v>167</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G137" t="s">
+        <v>329</v>
+      </c>
+      <c r="H137" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="s">
+        <v>144</v>
+      </c>
+      <c r="B138" t="s">
+        <v>166</v>
+      </c>
+      <c r="C138" t="s">
+        <v>167</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G138" t="s">
+        <v>329</v>
+      </c>
+      <c r="H138" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="s">
+        <v>145</v>
+      </c>
+      <c r="B139" t="s">
+        <v>166</v>
+      </c>
+      <c r="C139" t="s">
+        <v>167</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G139" t="s">
+        <v>329</v>
+      </c>
+      <c r="H139" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="s">
+        <v>146</v>
+      </c>
+      <c r="B140" t="s">
+        <v>166</v>
+      </c>
+      <c r="C140" t="s">
+        <v>167</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G140" t="s">
+        <v>330</v>
+      </c>
+      <c r="H140" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="s">
+        <v>147</v>
+      </c>
+      <c r="B141" t="s">
+        <v>166</v>
+      </c>
+      <c r="C141" t="s">
+        <v>167</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G141" t="s">
+        <v>330</v>
+      </c>
+      <c r="H141" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" t="s">
+        <v>148</v>
+      </c>
+      <c r="B142" t="s">
+        <v>166</v>
+      </c>
+      <c r="C142" t="s">
+        <v>167</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G142" t="s">
+        <v>330</v>
+      </c>
+      <c r="H142" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" t="s">
+        <v>149</v>
+      </c>
+      <c r="B143" t="s">
+        <v>166</v>
+      </c>
+      <c r="C143" t="s">
+        <v>167</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="G143" t="s">
+        <v>330</v>
+      </c>
+      <c r="H143" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" t="s">
+        <v>150</v>
+      </c>
+      <c r="B144" t="s">
+        <v>166</v>
+      </c>
+      <c r="C144" t="s">
+        <v>167</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G144" t="s">
+        <v>330</v>
+      </c>
+      <c r="H144" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" t="s">
+        <v>151</v>
+      </c>
+      <c r="B145" t="s">
+        <v>166</v>
+      </c>
+      <c r="C145" t="s">
+        <v>167</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G145" t="s">
+        <v>330</v>
+      </c>
+      <c r="H145" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" t="s">
+        <v>152</v>
+      </c>
+      <c r="B146" t="s">
+        <v>166</v>
+      </c>
+      <c r="C146" t="s">
+        <v>167</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G146" t="s">
+        <v>330</v>
+      </c>
+      <c r="H146" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" t="s">
+        <v>153</v>
+      </c>
+      <c r="B147" t="s">
+        <v>166</v>
+      </c>
+      <c r="C147" t="s">
+        <v>167</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="G147" t="s">
+        <v>330</v>
+      </c>
+      <c r="H147" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>154</v>
+      </c>
+      <c r="B148" t="s">
+        <v>166</v>
+      </c>
+      <c r="C148" t="s">
+        <v>167</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G148" t="s">
+        <v>330</v>
+      </c>
+      <c r="H148" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" t="s">
+        <v>155</v>
+      </c>
+      <c r="B149" t="s">
+        <v>166</v>
+      </c>
+      <c r="C149" t="s">
+        <v>167</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G149" t="s">
+        <v>330</v>
+      </c>
+      <c r="H149" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" t="s">
+        <v>156</v>
+      </c>
+      <c r="B150" t="s">
+        <v>166</v>
+      </c>
+      <c r="C150" t="s">
+        <v>167</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G150" t="s">
+        <v>331</v>
+      </c>
+      <c r="H150" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" t="s">
+        <v>157</v>
+      </c>
+      <c r="B151" t="s">
+        <v>166</v>
+      </c>
+      <c r="C151" t="s">
+        <v>167</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G151" t="s">
+        <v>331</v>
+      </c>
+      <c r="H151" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" t="s">
+        <v>158</v>
+      </c>
+      <c r="B152" t="s">
+        <v>166</v>
+      </c>
+      <c r="C152" t="s">
+        <v>167</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G152" t="s">
+        <v>331</v>
+      </c>
+      <c r="H152" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" t="s">
+        <v>159</v>
+      </c>
+      <c r="B153" t="s">
+        <v>166</v>
+      </c>
+      <c r="C153" t="s">
+        <v>167</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="G153" t="s">
+        <v>331</v>
+      </c>
+      <c r="H153" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" t="s">
+        <v>160</v>
+      </c>
+      <c r="B154" t="s">
+        <v>166</v>
+      </c>
+      <c r="C154" t="s">
+        <v>167</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G154" t="s">
+        <v>331</v>
+      </c>
+      <c r="H154" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" t="s">
+        <v>161</v>
+      </c>
+      <c r="B155" t="s">
+        <v>166</v>
+      </c>
+      <c r="C155" t="s">
+        <v>167</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G155" t="s">
+        <v>331</v>
+      </c>
+      <c r="H155" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" t="s">
+        <v>162</v>
+      </c>
+      <c r="B156" t="s">
+        <v>166</v>
+      </c>
+      <c r="C156" t="s">
+        <v>167</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G156" t="s">
+        <v>331</v>
+      </c>
+      <c r="H156" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" t="s">
+        <v>163</v>
+      </c>
+      <c r="B157" t="s">
+        <v>166</v>
+      </c>
+      <c r="C157" t="s">
+        <v>167</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G157" t="s">
+        <v>331</v>
+      </c>
+      <c r="H157" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" t="s">
+        <v>164</v>
+      </c>
+      <c r="B158" t="s">
+        <v>166</v>
+      </c>
+      <c r="C158" t="s">
+        <v>167</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G158" t="s">
+        <v>331</v>
+      </c>
+      <c r="H158" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" t="s">
+        <v>165</v>
+      </c>
+      <c r="B159" t="s">
+        <v>166</v>
+      </c>
+      <c r="C159" t="s">
+        <v>167</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G159" t="s">
+        <v>331</v>
+      </c>
+      <c r="H159" t="s">
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -2855,6 +4638,74 @@
     <hyperlink ref="F89" r:id="rId88"/>
     <hyperlink ref="F90" r:id="rId89"/>
     <hyperlink ref="F91" r:id="rId90"/>
+    <hyperlink ref="F92" r:id="rId91"/>
+    <hyperlink ref="F93" r:id="rId92"/>
+    <hyperlink ref="F94" r:id="rId93"/>
+    <hyperlink ref="F95" r:id="rId94"/>
+    <hyperlink ref="F96" r:id="rId95"/>
+    <hyperlink ref="F97" r:id="rId96"/>
+    <hyperlink ref="F98" r:id="rId97"/>
+    <hyperlink ref="F99" r:id="rId98"/>
+    <hyperlink ref="F100" r:id="rId99"/>
+    <hyperlink ref="F101" r:id="rId100"/>
+    <hyperlink ref="F102" r:id="rId101"/>
+    <hyperlink ref="F103" r:id="rId102"/>
+    <hyperlink ref="F104" r:id="rId103"/>
+    <hyperlink ref="F105" r:id="rId104"/>
+    <hyperlink ref="F106" r:id="rId105"/>
+    <hyperlink ref="F107" r:id="rId106"/>
+    <hyperlink ref="F108" r:id="rId107"/>
+    <hyperlink ref="F109" r:id="rId108"/>
+    <hyperlink ref="F110" r:id="rId109"/>
+    <hyperlink ref="F111" r:id="rId110"/>
+    <hyperlink ref="F112" r:id="rId111"/>
+    <hyperlink ref="F113" r:id="rId112"/>
+    <hyperlink ref="F114" r:id="rId113"/>
+    <hyperlink ref="F115" r:id="rId114"/>
+    <hyperlink ref="F116" r:id="rId115"/>
+    <hyperlink ref="F117" r:id="rId116"/>
+    <hyperlink ref="F118" r:id="rId117"/>
+    <hyperlink ref="F119" r:id="rId118"/>
+    <hyperlink ref="F120" r:id="rId119"/>
+    <hyperlink ref="F121" r:id="rId120"/>
+    <hyperlink ref="F122" r:id="rId121"/>
+    <hyperlink ref="F123" r:id="rId122"/>
+    <hyperlink ref="F124" r:id="rId123"/>
+    <hyperlink ref="F125" r:id="rId124"/>
+    <hyperlink ref="F126" r:id="rId125"/>
+    <hyperlink ref="F127" r:id="rId126"/>
+    <hyperlink ref="F128" r:id="rId127"/>
+    <hyperlink ref="F129" r:id="rId128"/>
+    <hyperlink ref="F130" r:id="rId129"/>
+    <hyperlink ref="F131" r:id="rId130"/>
+    <hyperlink ref="F132" r:id="rId131"/>
+    <hyperlink ref="F133" r:id="rId132"/>
+    <hyperlink ref="F134" r:id="rId133"/>
+    <hyperlink ref="F135" r:id="rId134"/>
+    <hyperlink ref="F136" r:id="rId135"/>
+    <hyperlink ref="F137" r:id="rId136"/>
+    <hyperlink ref="F138" r:id="rId137"/>
+    <hyperlink ref="F139" r:id="rId138"/>
+    <hyperlink ref="F140" r:id="rId139"/>
+    <hyperlink ref="F141" r:id="rId140"/>
+    <hyperlink ref="F142" r:id="rId141"/>
+    <hyperlink ref="F143" r:id="rId142"/>
+    <hyperlink ref="F144" r:id="rId143"/>
+    <hyperlink ref="F145" r:id="rId144"/>
+    <hyperlink ref="F146" r:id="rId145"/>
+    <hyperlink ref="F147" r:id="rId146"/>
+    <hyperlink ref="F148" r:id="rId147"/>
+    <hyperlink ref="F149" r:id="rId148"/>
+    <hyperlink ref="F150" r:id="rId149"/>
+    <hyperlink ref="F151" r:id="rId150"/>
+    <hyperlink ref="F152" r:id="rId151"/>
+    <hyperlink ref="F153" r:id="rId152"/>
+    <hyperlink ref="F154" r:id="rId153"/>
+    <hyperlink ref="F155" r:id="rId154"/>
+    <hyperlink ref="F156" r:id="rId155"/>
+    <hyperlink ref="F157" r:id="rId156"/>
+    <hyperlink ref="F158" r:id="rId157"/>
+    <hyperlink ref="F159" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Senior_Care.xlsx
+++ b/results/scraped_Cape_Town_Senior_Care.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="407">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -49,115 +49,112 @@
     <t>Old(2021) - IMDb</t>
   </si>
   <si>
+    <t>Old| Rotten Tomatoes</t>
+  </si>
+  <si>
     <t>OLDDefinition &amp; Meaning - Merriam-Webster</t>
   </si>
   <si>
+    <t>OLD| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
     <t>Old-Official Trailer[HD] - YouTube</t>
   </si>
   <si>
-    <t>Old| Rotten Tomatoes</t>
-  </si>
-  <si>
-    <t>OLD| English meaning - Cambridge Dictionary</t>
+    <t>Old(Film) -TV Tropes</t>
+  </si>
+  <si>
+    <t>Oldstreaming: where to watch movie online? - JustWatch</t>
   </si>
   <si>
     <t>Old- YouTube</t>
   </si>
   <si>
-    <t>Old(2021) - Full cast &amp; crew - IMDb</t>
-  </si>
-  <si>
-    <t>WatchOld| Netflix</t>
-  </si>
-  <si>
-    <t>Retirement benefits| SSA</t>
-  </si>
-  <si>
-    <t>Retirement- News, Advice &amp; Resources fromAARP</t>
-  </si>
-  <si>
-    <t>RetirementCalculator - NerdWallet</t>
-  </si>
-  <si>
-    <t>Retirement- Wikipedia</t>
-  </si>
-  <si>
-    <t>Retirement Calculator</t>
-  </si>
-  <si>
-    <t>10 Steps to Take as You Get Ready to Retire - AARP</t>
-  </si>
-  <si>
-    <t>Retirementplanning tools - USAGov</t>
-  </si>
-  <si>
-    <t>Plan forRetirement| SSA</t>
-  </si>
-  <si>
-    <t>Log Into Your Account |Transamerica</t>
-  </si>
-  <si>
-    <t>Account Login</t>
-  </si>
-  <si>
-    <t>Home -SeniorResources</t>
-  </si>
-  <si>
-    <t>Senior Services- City ofMilwaukee</t>
-  </si>
-  <si>
-    <t>Home - TrinitySeniorServices</t>
-  </si>
-  <si>
-    <t>SeniorCenters &amp; Dining | Department on Aging |MilwaukeeCounty</t>
-  </si>
-  <si>
-    <t>SeniorDining Menus | Department on Aging |MilwaukeeCounty</t>
-  </si>
-  <si>
-    <t>SeniorLivingWisconsin| HeritageSeniorLiving</t>
-  </si>
-  <si>
-    <t>SeniorExpress - Transportation for Seniors -Milwaukee Wi</t>
-  </si>
-  <si>
-    <t>Wisconsin Senior Employment Program(WISE)</t>
-  </si>
-  <si>
-    <t>148SeniorLiving Communities inMilwaukee,Wisconsin</t>
-  </si>
-  <si>
-    <t>Senior Centers– Serving Older Adults</t>
-  </si>
-  <si>
-    <t>ELDERLYDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Old age -Wikipedia</t>
-  </si>
-  <si>
-    <t>What Age Is ConsideredElderly? - MedicareAdvantage.com</t>
-  </si>
-  <si>
-    <t>THEELDERLYDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Elderly Instruments| New, Used &amp; Vintage Musical Instruments</t>
-  </si>
-  <si>
-    <t>ELDERLY| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>At What Age Are You Officially ConsideredElderly?</t>
-  </si>
-  <si>
-    <t>What IsElderly? Understanding the Age Group</t>
-  </si>
-  <si>
-    <t>What Age Is Legally Considered Elderly? - Informed Senior Living</t>
-  </si>
-  <si>
-    <t>ELDERLY| definition in the Cambridge English Dictionary</t>
+    <t>RetirementPlanning Spreadsheet - PDF2XL</t>
+  </si>
+  <si>
+    <t>RetirementPlanning Spreadsheet - MAF Companies</t>
+  </si>
+  <si>
+    <t>FlexibleRetirementPlanner</t>
+  </si>
+  <si>
+    <t>Smartsheet</t>
+  </si>
+  <si>
+    <t>U.S. Army Garrisons</t>
+  </si>
+  <si>
+    <t>assets.cobbcounty.gov</t>
+  </si>
+  <si>
+    <t>Montana State University</t>
+  </si>
+  <si>
+    <t>RetirementForms Spreadsheets (PSPRS)</t>
+  </si>
+  <si>
+    <t>Spreadsheet Daddy: The Ultimate AI Tool for Google Sheets</t>
+  </si>
+  <si>
+    <t>EXCEL WORKING</t>
+  </si>
+  <si>
+    <t>Marjorie StewartSeniorCommunity Center - City ofSherwood</t>
+  </si>
+  <si>
+    <t>Marjorie Stewart Senior Community Center</t>
+  </si>
+  <si>
+    <t>Marjorie StewartSeniorCommunity Center |Sherwood OR</t>
+  </si>
+  <si>
+    <t>SENIORDefinition &amp; Meaning - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>SeniorLivingSherwood,OR|The Springs at Sherwood</t>
+  </si>
+  <si>
+    <t>2026Senior Information-SherwoodHigh School</t>
+  </si>
+  <si>
+    <t>55+ Communities &amp;SeniorLiving inSherwood,Oregon| After55</t>
+  </si>
+  <si>
+    <t>Stewart TerraceSeniorApartments | Apartments inSherwood,OR</t>
+  </si>
+  <si>
+    <t>Senior Sherwood Apartments for Rent|Sherwood,OR</t>
+  </si>
+  <si>
+    <t>Microsoft– AI, Cloud, Productivity, Computing, Gaming &amp; Apps</t>
+  </si>
+  <si>
+    <t>Microsoftaccount | Sign In or Create Your Account Today –Microsoft</t>
+  </si>
+  <si>
+    <t>Sign in to your account</t>
+  </si>
+  <si>
+    <t>Microsoft- Wikipedia</t>
+  </si>
+  <si>
+    <t>Microsoft365 for Individuals: Subscription for Productivity Apps</t>
+  </si>
+  <si>
+    <t>Sign in to your account - myaccount.microsoft.com</t>
+  </si>
+  <si>
+    <t>Home |MicrosoftCareers</t>
+  </si>
+  <si>
+    <t>Create yourMicrosoftaccount</t>
+  </si>
+  <si>
+    <t>Microsoft365 - Sign into Copilot</t>
+  </si>
+  <si>
+    <t>Outlook</t>
   </si>
   <si>
     <t>FRAILDefinition &amp; Meaning -Merriam-Webster</t>
@@ -169,85 +166,463 @@
     <t>FRAILSynonyms: 223 Similar and Opposite Words -Merriam-Webster</t>
   </si>
   <si>
+    <t>Frail- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
+  </si>
+  <si>
     <t>FRAILDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
-    <t>Frail- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
+    <t>FRAIL| definition in the Cambridge English Dictionary</t>
   </si>
   <si>
     <t>Frail- definition offrailby The Free Dictionary</t>
   </si>
   <si>
-    <t>FRAIL| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
     <t>frail- Wiktionary, the free dictionary</t>
   </si>
   <si>
     <t>FRAIL definitionand meaning | Collins English Dictionary</t>
   </si>
   <si>
-    <t>What DoesfrailMean? Definition &amp; Examples | Dictionary.net</t>
-  </si>
-  <si>
-    <t>AGEDDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>AGEDTrust Home -AgedTrust | Non-Profit</t>
-  </si>
-  <si>
-    <t>AGED| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>AGEDDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
-    <t>Aged(2023) - IMDb</t>
-  </si>
-  <si>
-    <t>Aged- definition ofagedby The Free Dictionary</t>
-  </si>
-  <si>
-    <t>AGED| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>aged- Wiktionary, the free dictionary</t>
-  </si>
-  <si>
-    <t>Agedvs. Age - Which is Correct?</t>
-  </si>
-  <si>
-    <t>THEAGEDDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>67Easy Dinner IdeasWe Love - Taste of Home</t>
+    <t>frailadjective - Definition, pictures, pronunciation and usage notes ...</t>
+  </si>
+  <si>
+    <t>Enroll in Chase Online Banking | Chase</t>
+  </si>
+  <si>
+    <t>Credit Card, Mortgage, Banking, Auto | Chase Online | Chase.com</t>
+  </si>
+  <si>
+    <t>Chase Account login</t>
+  </si>
+  <si>
+    <t>Credit Card Resources, Login &amp; Customer Service | Chase</t>
+  </si>
+  <si>
+    <t>Compare Checking Accounts &amp; Apply Online | Chase</t>
+  </si>
+  <si>
+    <t>Ultimate Rewards | Credit Cards | Chase.com</t>
+  </si>
+  <si>
+    <t>Online Payments | Credit Card | Chase.com</t>
+  </si>
+  <si>
+    <t>Online Bill Pay | Personal Banking | Chase</t>
+  </si>
+  <si>
+    <t>Chase MyMortgage: Your Mortgage Online Portal | Home Lending</t>
+  </si>
+  <si>
+    <t>Amazon Account Activity | Credit Card | Chase</t>
+  </si>
+  <si>
+    <t>Meal Planning Made Simple - eMeals</t>
   </si>
   <si>
     <t>100 of the EasiestMealsWe’ve Ever Made - Allrecipes</t>
   </si>
   <si>
-    <t>50 Easy Dinner Recipes for Busy Weeknights - The Pioneer Woman</t>
-  </si>
-  <si>
-    <t>92 Dinner Ideas You Can Make in a Flash | Taste of Home</t>
-  </si>
-  <si>
-    <t>70 Easy Dinner Ideas</t>
+    <t>67Easy Dinner IdeasWe Love -Taste of Home</t>
+  </si>
+  <si>
+    <t>EATMeals| Get 50 FreeMealsAt Sign Up - GourmetMealsTo Your …</t>
   </si>
   <si>
     <t>104 Quick Dinner Ideas in 30 Minutes or Less | Food Network</t>
   </si>
   <si>
+    <t>92 Dinner Ideas You Can Make in a Flash |Taste of Home</t>
+  </si>
+  <si>
+    <t>Nutritious, Home-DeliveredMeals| Mom'sMeals</t>
+  </si>
+  <si>
+    <t>52Easy Dinner Recipes&amp; Ideas | Food Network</t>
+  </si>
+  <si>
     <t>100Easy DinnerRecipes for Busy Weeknights - The Pioneer Woman</t>
   </si>
   <si>
-    <t>22 Easy Dinner Recipes to Make With 5 Ingredients (Or Fewer!)</t>
-  </si>
-  <si>
-    <t>Recipes, Dinners and Easy Meal Ideas | Food Network</t>
-  </si>
-  <si>
-    <t>HelloFresh® Meal Kits | Free Breakfast for Life + 10 FreeMeals</t>
+    <t>FuelMeals| Custom Meal Prep | Meal Prep at Your Doorstep</t>
+  </si>
+  <si>
+    <t>Contact Us - Microsoft Support</t>
+  </si>
+  <si>
+    <t>Anmelden bei Hotmail | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Microsoft Copilot Blog | Microsoft Community Hub</t>
+  </si>
+  <si>
+    <t>Exchange Online EWS, Your Time is Almost Up | Microsoft …</t>
+  </si>
+  <si>
+    <t>Getting ready for the Windows 11 upgrade | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Mettre à jour les pilotes via Gestionnaire de périphériques dans ...</t>
+  </si>
+  <si>
+    <t>Aktualisieren von Treibern über Geräte-Manager in Windows</t>
+  </si>
+  <si>
+    <t>Getting the latest Microsoft Edge update just got easier</t>
+  </si>
+  <si>
+    <t>Share your calendar in Outlook | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Sign in to Microsoft Forms</t>
+  </si>
+  <si>
+    <t>Salt Lake City Public Library system</t>
+  </si>
+  <si>
+    <t>Visit The LIBRARY STORE - services.slcpl.org</t>
+  </si>
+  <si>
+    <t>Library Card Application - Salt Lake City Public Library</t>
+  </si>
+  <si>
+    <t>Salt Lake City Public Library</t>
+  </si>
+  <si>
+    <t>Shops at Library Square - Salt Lake City Public Library</t>
+  </si>
+  <si>
+    <t>Utah's Online Library</t>
+  </si>
+  <si>
+    <t>Sign In to Pay Your Bill OR See if You Pre-Qualify for a Credit Card</t>
+  </si>
+  <si>
+    <t>Pay Bill FAQs | Credit One Bank</t>
+  </si>
+  <si>
+    <t>Credit One Bank</t>
+  </si>
+  <si>
+    <t>Resend Activation Email | Credit One Bank</t>
+  </si>
+  <si>
+    <t>Benefits - careers.creditonebank.com</t>
+  </si>
+  <si>
+    <t>Job Search Results - Credit One Bank</t>
+  </si>
+  <si>
+    <t>craigslist:san diegojobs, apartments, for sale, services ...</t>
+  </si>
+  <si>
+    <t>san diegofor sale -craigslist</t>
+  </si>
+  <si>
+    <t>craigslist| california</t>
+  </si>
+  <si>
+    <t>craigslist| united states</t>
+  </si>
+  <si>
+    <t>Buy and Sell inSan Diego, California |FacebookMarketplace</t>
+  </si>
+  <si>
+    <t>craigslistsitemap forsan diego</t>
+  </si>
+  <si>
+    <t>San Diego Craigslist-Facebook</t>
+  </si>
+  <si>
+    <t>Sign in - account.microsoft.com</t>
+  </si>
+  <si>
+    <t>NewJobPaperwork 101: IDs,Formsand Employer Requirements</t>
+  </si>
+  <si>
+    <t>I-9IDRequirements: AcceptedForms of IDList (2026)</t>
+  </si>
+  <si>
+    <t>FormI-9 Acceptable Documents -USCIS</t>
+  </si>
+  <si>
+    <t>Do You NeedanID to Get a Job: Acceptable Documents</t>
+  </si>
+  <si>
+    <t>2Forms of ID: Complete Guide to AcceptableIdentificationin ...</t>
+  </si>
+  <si>
+    <t>What counts as a validIDfora job? - LegalKnowledgeBase.com</t>
+  </si>
+  <si>
+    <t>Do You NeedanID to Get a Job? EmploymentIdentification...</t>
+  </si>
+  <si>
+    <t>Do You NeedanID to Get a Job- doors4jobs</t>
+  </si>
+  <si>
+    <t>What Proofof Identification Do You Needfora Job? - Work</t>
+  </si>
+  <si>
+    <t>Do You NeedanIDfora Job? The Required Documents - CLIMB</t>
+  </si>
+  <si>
+    <t>Tinnitus - Symptoms and causes - Mayo Clinic</t>
+  </si>
+  <si>
+    <t>Tinnitus - Diagnosis and treatment - Mayo Clinic</t>
+  </si>
+  <si>
+    <t>Mayo Clinic Patient Portal</t>
+  </si>
+  <si>
+    <t>Pulsatile tinnitus - has anyone found helpful solutions?</t>
+  </si>
+  <si>
+    <t>Mayo Clinic Q and A: Understanding tinnitus</t>
+  </si>
+  <si>
+    <t>What natural product can quiet my Tinnitus - Mayo Clinic Connect</t>
+  </si>
+  <si>
+    <t>Tinnitus: Ways to Reduce the Irritation - Mayo Clinic News Network</t>
+  </si>
+  <si>
+    <t>Home - Mayo Clinic Press</t>
+  </si>
+  <si>
+    <t>What Causes Ringing in the Ears? - Mayo Clinic Press</t>
+  </si>
+  <si>
+    <t>Primary Care in Rochester and Kasson - Mayo Clinic Health System</t>
+  </si>
+  <si>
+    <t>Subway, 6910 Fayetteville Rd, Durham, NC - Restaurant inspection ...</t>
+  </si>
+  <si>
+    <t>83-Year-Old Air Force Veteran Dies After Illegal Alien Shoves Him …</t>
+  </si>
+  <si>
+    <t>Abandoned Subway (Rochester, Irondequoit, Sodus: living in, cost, …</t>
+  </si>
+  <si>
+    <t>What are some movies that feature the L.A. subway? (construction, …</t>
+  </si>
+  <si>
+    <t>Subway locations in Lynnwood, WA - City-Data.com</t>
+  </si>
+  <si>
+    <t>SUBWAY #34195, 955 Catalina Blvd, San Diego, CA 92106</t>
+  </si>
+  <si>
+    <t>3x12 vs 3x6 Subway tile backsplash (granite countertops, stove, color ...</t>
+  </si>
+  <si>
+    <t>Subway balance questions (living in, bus, safest) - New York City</t>
+  </si>
+  <si>
+    <t>Just Posted Vid on Montreal Metro (Subway). Compare to NYC …</t>
+  </si>
+  <si>
+    <t>Subway #11394, 6736 Aloma Avenue, Winter Park, FL - Restaurant ...</t>
+  </si>
+  <si>
+    <t>Reddit - Dive into anything</t>
+  </si>
+  <si>
+    <t>r/GTA6 - Grand Theft Auto VI's Official Reddit Community!</t>
+  </si>
+  <si>
+    <t>Приложение «Instagram» — App Store</t>
+  </si>
+  <si>
+    <t>‎Facebook App - App Store</t>
+  </si>
+  <si>
+    <t>‎Messages App - App Store</t>
+  </si>
+  <si>
+    <t>TopCharacterTropes - Reddit</t>
+  </si>
+  <si>
+    <t>‎Instagram App - App Store</t>
+  </si>
+  <si>
+    <t>‎App Instagram - App Store</t>
+  </si>
+  <si>
+    <t>‎Instagram‑App – App Store</t>
+  </si>
+  <si>
+    <t>Instagram》App - App Store</t>
+  </si>
+  <si>
+    <t>TrackingYour Shipment or Packages |FedEx</t>
+  </si>
+  <si>
+    <t>Track&amp; Ship Online or Find Nearby Locations |FedEx</t>
+  </si>
+  <si>
+    <t>TrackYour Shipment |FedExFreight</t>
+  </si>
+  <si>
+    <t>PackageTracking- CourierTracking|FedExCanada</t>
+  </si>
+  <si>
+    <t>Advanced ShipmentTracking|FedEx</t>
+  </si>
+  <si>
+    <t>FedExAdvanced ShipmentTracking</t>
+  </si>
+  <si>
+    <t>TrackingYour Shipment or Packages |FedExUnited Kingdom</t>
+  </si>
+  <si>
+    <t>FedEx tracking-Trackyour package viatrackingnumber</t>
+  </si>
+  <si>
+    <t>FedExExpress</t>
+  </si>
+  <si>
+    <t>Where is my package? -FedEx</t>
+  </si>
+  <si>
+    <t>Is FlexJobs worth it? : r/remotework - Reddit</t>
+  </si>
+  <si>
+    <t>What job sites is everyone using? : r/jobs - Reddit</t>
+  </si>
+  <si>
+    <t>Is the phrase "it's just a matter of semantics" meaningless?</t>
+  </si>
+  <si>
+    <t>Usage of "Indeed" in "Thank you very much indeed"</t>
+  </si>
+  <si>
+    <t>Is there anything better than Indeed for job listings? - Reddit</t>
+  </si>
+  <si>
+    <t>Does anyone actually get jobs through LinkedIn and Indeed?</t>
+  </si>
+  <si>
+    <t>Having little success with indeed.com are there any other ... - Reddit</t>
+  </si>
+  <si>
+    <t>LinkedIn vs. indeed : r/recruitinghell - Reddit</t>
+  </si>
+  <si>
+    <t>Do you guys ever take company reviews seriously on indeed.com?</t>
+  </si>
+  <si>
+    <t>Best job board for hiring locals? Not Indeed. : r/Calgary - Reddit</t>
+  </si>
+  <si>
+    <t>unsolicited "Your new account on XNXX GOLD" email - Reddit</t>
+  </si>
+  <si>
+    <t>datingoverfifty - Reddit</t>
+  </si>
+  <si>
+    <t>Legal Teens - Reddit</t>
+  </si>
+  <si>
+    <t>TikTok - humanity in all forms - Reddit</t>
+  </si>
+  <si>
+    <t>verysmalltits - Reddit</t>
+  </si>
+  <si>
+    <t>Iranian discussion forum to discuss all things Iran - Reddit</t>
+  </si>
+  <si>
+    <t>WhatBug Looks Like An AntButFliesAnd Gray?</t>
+  </si>
+  <si>
+    <t>18Bugs That Look LikeAnts (Pictures and Identification)</t>
+  </si>
+  <si>
+    <t>BugFinder-Insect Identification</t>
+  </si>
+  <si>
+    <t>Insects That Look LikeFlying Ants: Identification, Causes, and Control</t>
+  </si>
+  <si>
+    <t>FlyingInsects That Look LikeAnts – A Gardener’S Guide</t>
+  </si>
+  <si>
+    <t>Antlion-Wikipedia</t>
+  </si>
+  <si>
+    <t>WhatBugIs This? Free AIBugIdentifier by Photo</t>
+  </si>
+  <si>
+    <t>What Are TheInsects That Look LikeFlying Ants?</t>
+  </si>
+  <si>
+    <t>Insect That Looks Like An AntWith Wings: Identifying Friend Vs. Foe</t>
+  </si>
+  <si>
+    <t>How to IdentifyCommonFlying Insects(and Get Rid ofFlies... -wikiHow</t>
+  </si>
+  <si>
+    <t>Why isKendamil not on Amazon? : r/FormulaFeeders -Reddit</t>
+  </si>
+  <si>
+    <t>Amazon.com:KendamilBaby Formula</t>
+  </si>
+  <si>
+    <t>Amazon.com:KendamilCereal</t>
+  </si>
+  <si>
+    <t>Why IsKendamilFormula Out Of Stock? | Urgent Supply Breakdown</t>
+  </si>
+  <si>
+    <t>KendamilOrganic Infant Formula, Milk-Based Powder (Cow Milk ...</t>
+  </si>
+  <si>
+    <t>Goat Stock Update –KendamilUSA</t>
+  </si>
+  <si>
+    <t>Kendamil- Walmart.com</t>
+  </si>
+  <si>
+    <t>European Organic Baby Formula | Infant Formula |Kendamil</t>
+  </si>
+  <si>
+    <t>KendamilOrganic Infant Formula Powder - 28.2oz - Target</t>
+  </si>
+  <si>
+    <t>Where to BuyKendamilFormula in the USA | EuromallUSA</t>
+  </si>
+  <si>
+    <t>RecordedMarriageLicenses</t>
+  </si>
+  <si>
+    <t>Marriage Records-Georgia Department of Public Health</t>
+  </si>
+  <si>
+    <t>www.georgiaprobaterecords.com</t>
+  </si>
+  <si>
+    <t>SEARCHOFMARRIAGEREQUESTFORM3913</t>
+  </si>
+  <si>
+    <t>Georgia MarriageLicenseSearch:Records&amp; Lookup</t>
+  </si>
+  <si>
+    <t>Georgia Marriage Records-SearchLicenseRecords</t>
+  </si>
+  <si>
+    <t>ProbateCourt Dougherty County,GA</t>
+  </si>
+  <si>
+    <t>ProbateCourt Information System –GeorgiaCourts</t>
+  </si>
+  <si>
+    <t>RecordsDivision | Fulton CountyProbateCourt,GA</t>
+  </si>
+  <si>
+    <t>MarriageLicenses andRecords| Thomas County Board of …</t>
   </si>
   <si>
     <t>Senior Care</t>
@@ -256,217 +631,607 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=187ac0c8c00a21afde2c592e008e0ead30acac223ff6ae27fc03a893cc561f8cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=098c2c02-a0f0-663f-0c86-3be3a143678b&amp;u=a1aHR0cHM6Ly9vbGRuYXZ5LmdhcC5jb20vP21zb2NraWQ9MDk4YzJjMDJhMGYwNjYzZjBjODYzYmUzYTE0MzY3OGI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6602814082f7d81236d0237b93979b4a4bdd809dda8414ed34968c8e4fdb0b05JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=098c2c02-a0f0-663f-0c86-3be3a143678b&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9PbGRfKGZpbG0p&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=09633ed8bc737ce414e5061b92fcec47a4e3b8729cfc3c2159af8827df37ebf0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=098c2c02-a0f0-663f-0c86-3be3a143678b&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTA5NTQ2NTIv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38c73754ff0f1b53dc627f6126e95a3f83d8d5f3eeaaf514d66b620f1dd4cbc9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=098c2c02-a0f0-663f-0c86-3be3a143678b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L29sZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=649339469c52f35bbcaa5c498daee3606004c798bc325c48addc0201cfbff357JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=098c2c02-a0f0-663f-0c86-3be3a143678b&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9QTRVMnBNUlY5X2s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed7f83eddd494dfe33ef3faa280af625678a6d0472212666e8a8a5665fc477deJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=098c2c02-a0f0-663f-0c86-3be3a143678b&amp;u=a1aHR0cHM6Ly93d3cucm90dGVudG9tYXRvZXMuY29tL20vb2xk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=266963034d115a97cc6a2749d1689c218bb0429e5b8d09920be2c2d683be1a50JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=098c2c02-a0f0-663f-0c86-3be3a143678b&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL29sZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5d6ce8863ad86c4b2ff77d6ba24abb571829d7abf361a9e135df6167ce5c5027JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=098c2c02-a0f0-663f-0c86-3be3a143678b&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9ODR4QUQ0ci05a0U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=57ba91f9a0cffa5b460b12ed9a9cd122574ecc3d1a10bde9c5248e30daf170c0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=098c2c02-a0f0-663f-0c86-3be3a143678b&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTA5NTQ2NTIvZnVsbGNyZWRpdHMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3377c1534f2120506498ab18090134624a3bab78595f3340a90061b25b0d71fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=098c2c02-a0f0-663f-0c86-3be3a143678b&amp;u=a1aHR0cHM6Ly93d3cubmV0ZmxpeC5jb20vdGl0bGUvODE0MTAzODY&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=362a6d96622c57651c5e1f6161c92d0668543dcc9cbeeabed9b38cd137714029JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2676beb8-34c7-608c-1708-a959356f61c6&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d07f9958c72099a6a8f94e8897936898956f5f6079f57520b676001ede7dc6c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2676beb8-34c7-608c-1708-a959356f61c6&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC8_bXNvY2tpZD0yNjc2YmViODM0Yzc2MDhjMTcwOGE5NTkzNTZmNjFjNg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1089e7d69b05145b334aaad1bb1f80d1a1cd2fbbef9dbd38fe2d68fa9f065688JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2676beb8-34c7-608c-1708-a959356f61c6&amp;u=a1aHR0cHM6Ly93d3cubmVyZHdhbGxldC5jb20vaW52ZXN0aW5nL2NhbGN1bGF0b3JzL3JldGlyZW1lbnQtY2FsY3VsYXRvcj9tc29ja2lkPTI2NzZiZWI4MzRjNzYwOGMxNzA4YTk1OTM1NmY2MWM2&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0a3537bee941c93bbd749b2f729ebad87df5db64ec1715e3d6966380b15649efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2676beb8-34c7-608c-1708-a959356f61c6&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9SZXRpcmVtZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b7d21eae6a9cd09bd76d487461b54d39af210b3d0c4aeaadd509e00da80cd3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2676beb8-34c7-608c-1708-a959356f61c6&amp;u=a1aHR0cHM6Ly93d3cuY2FsY3VsYXRvci5uZXQvcmV0aXJlbWVudC1jYWxjdWxhdG9yLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91651253ac0ff49134944a140f62397518da2730e04143199fa065791b1479b2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2676beb8-34c7-608c-1708-a959356f61c6&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC9zdGVwcy10by10YWtlLWJlZm9yZS15b3UtcmV0aXJlLz9tc29ja2lkPTI2NzZiZWI4MzRjNzYwOGMxNzA4YTk1OTM1NmY2MWM2&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c182bc6fd74337fc5f5b4d78927f02abf1c788c4345a62e9f83c90fc30cde8a1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2676beb8-34c7-608c-1708-a959356f61c6&amp;u=a1aHR0cHM6Ly93d3cudXNhLmdvdi9yZXRpcmVtZW50LXBsYW5uaW5nLXRvb2xz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0a5a7fb43ff0706213f976143da098b69912dcbb98de91fa1643b18eaf86a06bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2676beb8-34c7-608c-1708-a959356f61c6&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50L3BsYW4tZm9yLXJldGlyZW1lbnQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aa8176325e7b95d88585c815a583c7d2937df9a8ee1fb8a9b4e531491bf59f54JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2676beb8-34c7-608c-1708-a959356f61c6&amp;u=a1aHR0cHM6Ly93d3cudHJhbnNhbWVyaWNhLmNvbS9sb2dpbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8190236ba6be96f373b6db32700143518481849dc65ba881486d137a03931aa2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2676beb8-34c7-608c-1708-a959356f61c6&amp;u=a1aHR0cHM6Ly9sb2dpbi52b3lhLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=90def48e6711dd0c9c7eb0a89ae90ecae579f7be38d0ccea29e8b466c6fc453bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04bf6855-189e-6510-0c57-7fb419d664cd&amp;u=a1aHR0cHM6Ly9zZW5pb3JyZXNvdXJjZXNvbmxpbmUuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f34fb726145d55912acee35eb4f6afc662c34475f0238a4df9a3424941294c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04bf6855-189e-6510-0c57-7fb419d664cd&amp;u=a1aHR0cHM6Ly9jaXR5Lm1pbHdhdWtlZS5nb3YvY29tbW9uY291bmNpbC9EaXN0cmljdDYvU2VuaW9yU2VydmljZXMuaHRt&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0a002ca2e34fa40b2d670413aa154604a0aa2ff42fb5129310016257a614f711JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04bf6855-189e-6510-0c57-7fb419d664cd&amp;u=a1aHR0cHM6Ly90cmluaXR5c2VuaW9yc2VydmljZXMub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61f82beba43679108c1427bfc62d006a573f39d9e731f2c208626e12ad6cb511JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04bf6855-189e-6510-0c57-7fb419d664cd&amp;u=a1aHR0cHM6Ly9jb3VudHkubWlsd2F1a2VlLmdvdi9FTi9ESEhTL09sZGVyLUFkdWx0cy1TZXJ2aWNlcy9TZW5pb3ItQ2VudGVycy0tRGluaW5n&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=da05cd897554ce3fb35e147b48f0856d975ab96016762febb29c203bdd77045fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04bf6855-189e-6510-0c57-7fb419d664cd&amp;u=a1aHR0cHM6Ly9jb3VudHkubWlsd2F1a2VlLmdvdi9FTi9ESEhTL09sZGVyLUFkdWx0cy1TZXJ2aWNlcy9TZW5pb3ItQ2VudGVycy0tRGluaW5nL1Nlbmlvci1EaW5pbmctTWVudXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47a5e8fb147bb2a1a991a1cb021b1149ebfcec59b4ff327585a3dfd0327c842fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04bf6855-189e-6510-0c57-7fb419d664cd&amp;u=a1aHR0cHM6Ly9oZXJpdGFnZXNlbmlvci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb015cb387fcf73a7ca5edcc3c608cddf899d22d43ff3feefda03d9e2d0a811fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04bf6855-189e-6510-0c57-7fb419d664cd&amp;u=a1aHR0cHM6Ly9zZW5pb3JleHByZXNzd2kuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1f8c79d8069e14f15768f1f436770b71daac8c28b956d5b48c71d44b4979cafJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04bf6855-189e-6510-0c57-7fb419d664cd&amp;u=a1aHR0cHM6Ly93d3cuZGhzLndpc2NvbnNpbi5nb3Yvd2lzZS9pbmRleC5odG0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ac0ff38b0bca8c4902db5e00713626374ff1dc234ba420a6e9985e2d9c5455deJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04bf6855-189e-6510-0c57-7fb419d664cd&amp;u=a1aHR0cHM6Ly93d3cuYWZ0ZXI1NS5jb20vc2VhcmNoL3dpL21pbHdhdWtlZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6fe199a43fb71c7ca795e3a4cb624224433ca44dc6353a5f8cf9851c0f3d1e96JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04bf6855-189e-6510-0c57-7fb419d664cd&amp;u=a1aHR0cHM6Ly9zZXJ2aW5nb2xkZXJhZHVsdHMub3JnL3Nlbmlvci1jZW50ZXJzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b85e4b890c6f0a9258fb15936d08de57dbe0575c5cb5bffab0b7bc14e182b4cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0944443d-c807-6905-2d12-53dcc988680b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=546b4a4b706f381ab2b3b42a153a356b03e8289d1d8b44dcf51ca547a44edf6cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0944443d-c807-6905-2d12-53dcc988680b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT2xkX2FnZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=83b32094da2c169a217740cbb485b62ff31e0cb60a247041a1ea048d7c0fa8dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0944443d-c807-6905-2d12-53dcc988680b&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhcmVhZHZhbnRhZ2UuY29tL2NvbW1vbi1xdWVzdGlvbnMvd2hhdC1hZ2UtaXMtY29uc2lkZXJlZC1lbGRlcmx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b311d00470e229bbb6ea8951a35a24da19a7ac0112868ba396aba49dca9db33fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0944443d-c807-6905-2d12-53dcc988680b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3RoZSUyMGVsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e680b23ad190bba0a8e9583904de71e73e2f3dfc9f99856328f45d0e1b0c1a1aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0944443d-c807-6905-2d12-53dcc988680b&amp;u=a1aHR0cHM6Ly93d3cuZWxkZXJseS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9f347d16b14cff0831a7bcb84a6eb92805a76e3c93341a15646223c141734967JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0944443d-c807-6905-2d12-53dcc988680b&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5cb5c0775af30938455046b4f355714648c695f5cc264f39f9c4a898d7a83960JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0944443d-c807-6905-2d12-53dcc988680b&amp;u=a1aHR0cHM6Ly93d3cuc2VuaW9yc3Ryb25nLm9yZy9hdC13aGF0LWFnZS1hcmUteW91LWNvbnNpZGVyZWQtZWxkZXJseS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a4e0c1eb3408afdb6c60cf19ac1633415386af6576dcf6f8d53a6627dc33bbe5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0944443d-c807-6905-2d12-53dcc988680b&amp;u=a1aHR0cHM6Ly93d3cudGhlZWxkZXJseXdlbGxuZXNzLmNvbS9ibG9ncy93aGF0LWlzLWVsZGVybHkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34b30078a2a4a6cc03631ac55fcbaa8c8c306b95f962b7b5462a8b61b6f83011JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0944443d-c807-6905-2d12-53dcc988680b&amp;u=a1aHR0cHM6Ly9pbmZvcm1lZHNlbmlvcmxpdmluZy5jb20vd2hhdC1hZ2UtaXMtbGVnYWxseS1jb25zaWRlcmVkLWVsZGVybHkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=42dcdb9a6c8ea5bdbb7aa4015135f776eb1eaa53b35e5915ee7bf90d73d3f382JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0944443d-c807-6905-2d12-53dcc988680b&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2VsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5179f78be1f2006555b707ff2f702f35ee16ce09f4b3904b1af8acce57cb83aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d52b906-8ccb-62e0-3cb4-aee78d636390&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c53f37a2dec60667e0d4fa2199ba80aa24edd5c0b9f7817b1176435f87e9781aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d52b906-8ccb-62e0-3cb4-aee78d636390&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f7d613fc4f3b86b1647288658abf948fedc52e93a02dc4a802ac05ef90fbfb6bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d52b906-8ccb-62e0-3cb4-aee78d636390&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvZnJhaWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12b6a92fb842a728f558eb67e41f05f156fe26c57fb2580a225c0c0db188684bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d52b906-8ccb-62e0-3cb4-aee78d636390&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=99b44efa4a52ed77767cc69a88965d14147782fca0915bb574a5fa89cc8e800dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d52b906-8ccb-62e0-3cb4-aee78d636390&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c93c88e80383093773e68a69bf54372ee1e43b9059be7821cf0305f93de07570JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d52b906-8ccb-62e0-3cb4-aee78d636390&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c40f64cde323409c55579e5f64c05794894317c7cced5662a8adb8bb533730caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d52b906-8ccb-62e0-3cb4-aee78d636390&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a675d7f6fcddd26226aab6c471e9211b040e435e41156c5fc16b2ee21e8b5a2fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d52b906-8ccb-62e0-3cb4-aee78d636390&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c888ed1db97b607d2c817ca08cfecc0389d41dff86429b8dcb32ed53750afcaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d52b906-8ccb-62e0-3cb4-aee78d636390&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL2RpY3Rpb25hcnkvZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ecf3af7e41498313ff2c4b70d8eeb8886b0e5fa4604804f20fa824c22426fe2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d52b906-8ccb-62e0-3cb4-aee78d636390&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5uZXQvZGljdGlvbmFyeS9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38a61b892be5492a6cad420f07470bb75dca322397473ad1785f751f5d80f420JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18918284-d378-69c0-10f3-9565d2c968f8&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12d65dbf6a4fec89dfe2b6530506d89e07715aa078a1d0b06a7db811f79bb07fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18918284-d378-69c0-10f3-9565d2c968f8&amp;u=a1aHR0cHM6Ly90cnVzdGFnZWQub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f3e515457d6727d7d43c806cb444164b6990632823bb0dda2ce82bd6bd8d759JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18918284-d378-69c0-10f3-9565d2c968f8&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=51b2a6bb7735ba49ae71eafa1e7c68c2b9213e538ebc3aa8f2c9616080b96cccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18918284-d378-69c0-10f3-9565d2c968f8&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a34f79bdf441bae973db5f6cdfd5e4bd7daa81c2ee1a929ce236c14532a2e2ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18918284-d378-69c0-10f3-9565d2c968f8&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNzA0NDAyMA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9c68f61e0754c36a5f75fb406f4eedaeea86c3158c201493fafc24c4b73a286JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18918284-d378-69c0-10f3-9565d2c968f8&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce856ff71214b357ebb2327592a4e6bd5fccac98525451b30f5472c9c21b7d97JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18918284-d378-69c0-10f3-9565d2c968f8&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40f8f95256679aed86b67f44ff4c0172227a4d609e8555f47b03bb48da3c02a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18918284-d378-69c0-10f3-9565d2c968f8&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60d35fc4d57faabaebaf8244633286c0c61e543b38047ec3ad0f418c40f956e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18918284-d378-69c0-10f3-9565d2c968f8&amp;u=a1aHR0cHM6Ly9jb3JyZWN0d29yZGluZy5jb20vYWdlZC1vci1hZ2Uv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba06ecb982e67a7acf54a8af2f20ff6fe8629a07388b0e3a8961f5a94ba999acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18918284-d378-69c0-10f3-9565d2c968f8&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3RoZSUyMGFnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e28c10ee64f3d45c8e3fad8a30d4e5d99321696967a9d1b5f8510f6d90f7c82JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f6d73a-28b6-6e6f-3f99-c0db29696f26&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZWFzeS1kaW5uZXItaWRlYXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b24c2a7ea1fb6499a37ecdf19b7e1354b20b1b50b26b58882f37225224a1ccaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f6d73a-28b6-6e6f-3f99-c0db29696f26&amp;u=a1aHR0cHM6Ly93d3cuYWxscmVjaXBlcy5jb20vMTAwLWVhc3ktbWVhbHMtMTE2OTUyMjc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16336d04a5cd624c199255c00233122e84974c65d253b24a4d1f5c6da7f8cae1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f6d73a-28b6-6e6f-3f99-c0db29696f26&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzY4OTA2OTk3L2Jlc3QtZWFzeS1kaW5uZXItcmVjaXBlcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ab58cb3431537f00bf38844754aa87e6f6f843818c725b9e4033d052d82c93abJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f6d73a-28b6-6e6f-3f99-c0db29696f26&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee71f974ff0d0478d9440aeea2c3d4b62158e193eb7674f2e6eeed49a7ee050dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f6d73a-28b6-6e6f-3f99-c0db29696f26&amp;u=a1aHR0cHM6Ly90aGVyZWFsZm9vZGRpZXRpdGlhbnMuY29tL2Vhc3ktZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d573f3899ffb660e3960c12cdbed1d7df1661ec6cd6646f3a9055f3af652f0fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f6d73a-28b6-6e6f-3f99-c0db29696f26&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zLzMwLW1pbnV0ZS1kaW5uZXItcmVjaXBlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f1c8ad2e93874d6b28835033b8ff31934922aa7b5898efd02b9f06ccb98ccaaaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f6d73a-28b6-6e6f-3f99-c0db29696f26&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzMyMjY0Mjg0L2Vhc3ktZGlubmVyLXJlY2lwZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82fd9472f933cc0bbaae36f0aa7f776354ba99d02a40a08f158820ba65f3c38dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f6d73a-28b6-6e6f-3f99-c0db29696f26&amp;u=a1aHR0cHM6Ly93d3cuYWxscmVjaXBlcy5jb20vNS1pbmdyZWRpZW50LWRpbm5lci1yZWNpcGVzLTExODQxODYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8451651f8385273a59747715e139899fbe743a15323a976e7e7e64268a3a21dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f6d73a-28b6-6e6f-3f99-c0db29696f26&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cece25d323f3bc6024250f57b163516bc09c3fa7afc16d149bc1f544ab81483aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f6d73a-28b6-6e6f-3f99-c0db29696f26&amp;u=a1aHR0cHM6Ly93d3cuaGVsbG9mcmVzaC5jb20v&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa224fb88a30c3a0a0809322d483d615f42a22bee114a7e00e010904064d399cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly9vbGRuYXZ5LmdhcC5jb20vP21zb2NraWQ9MzkxNzUwZWQwMjQ0Njc3YzEzMjM0NzBjMDNkZjY2ZDU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66e792d4cc210852164adc65f0db2be3714c1c7b93eaea36cba6722f337c0f33JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9PbGRfKGZpbG0p&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f89b331ff567e8d744319a0ba5d493f9dd9232b7f67c9c5aa6c1d7a42c1f174dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTA5NTQ2NTIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66738eb9ac579c4a0425362056fbaad434901bfcf64bd3af78f43e359fad272fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly93d3cucm90dGVudG9tYXRvZXMuY29tL20vb2xk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0d8d5a91be0b964d4b2a8d488bb6323c6bc63a23aeb42f9aa362e152c6953c99JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L29sZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d99d244f299b2f70c8329b3bd2e0a1913ceb0bd34d19f45d2fc810c3a889fbfdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL29sZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2d170972ddbba42fa70c54689f3c1def33eade167f16704db44b3a7c2c44704JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9QTRVMnBNUlY5X2s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1dde2ff78b454997bd82478551ec0f9ca0f842fa9b7e24339781b2f8e97caf0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly90dnRyb3Blcy5vcmcvcG13aWtpL3Btd2lraS5waHAvRmlsbS9PbGQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b9ec450b0c95fab25617ad3ee8dca3be9bdb1127ffed2a02369b7151867f91afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly93d3cuanVzdHdhdGNoLmNvbS91cy9tb3ZpZS9vbGQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f158f685f433a88f1fb2f398daf7f6c92f5774830e6ec73390f99336c9d6e36JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9ODR4QUQ0ci05a0U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=308988f077771f952dcf809848bc1f610015f55c07deecc80cf176be00d7b4f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly9wZGYyeGwuY29tL3dwLWNvbnRlbnQvdXBsb2Fkcy8yMDE4LzA1L3JldGlyZW1lbnQtcGxhbm5pbmctc3ByZWFkc2hlZXQueGxz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d3d98edc83022fafa4f23ecbdb87063e85ecaf425765b01a01064458de2453e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly9tYWZjb21wYW5pZXMuY29tL3dwLWNvbnRlbnQvdXBsb2Fkcy9SZXRpcmVtZW50LVBsYW5uaW5nLUdBUDEueGxz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b348e3c74f3d8ea32e514ea5d87d2a3a8429e64b28fa30b5c437da61d5b108bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly93d3cuZmxleGlibGVyZXRpcmVtZW50cGxhbm5lci5jb20vdG9vbHMvUmV0aXJlbWVudFdpdGhkcmF3YWxTaW11bGF0b3IueGxz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df9f4096b0f61d50efa786c8e91054f929e7bf7f8d5a507885be351e3f9bc8bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly93d3cuc21hcnRzaGVldC5jb20vc2l0ZXMvZGVmYXVsdC9maWxlcy8yMDI1LTAyL0lDLVJldGlyZW1lbnQtRmluYW5jaWFsLVBsYW5uaW5nLTEyMzMyX1RlbXBsYXRlLnhsc3g&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a09be570c16cc71202cf87a895b76e81e56d5b8ef2d75c90010f6f328ec3a2fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly9ob21lLmFybXkubWlsL2RydW0vNTExNy8zMTA5LzYyMzgvQ1NQX1BsYW5uaW5nX0NhbGN1bGF0b3IueGxzeA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48287cf2879f55bea3f4ab1c2f7e49a43885d6f508fadea519ba83d1b605dddfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly9hc3NldHMuY29iYmNvdW50eS5nb3YvZmlsZXMvMjAyNS0xMi9SZXRpcmVtZW50LUNhbGN1bGF0b3IueGxzeA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24db6cc1487b436b7d40d07f476e88d09af725439b25046410a2735ce9dfd445JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly93d3cubW9udGFuYS5lZHUvZXh0ZW5zaW9uZWNvbi9kb2N1bWVudHMvcmV0aXJlbWVudGluY29tZXdpdGhkcmF3YWx3b3Jrc2hlZXQueGxzeA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2e330de4c9c67a8493bafb9d1f1382d75d3f235c45c91fbe46a3497bfa2cef4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly93d3cucHNwcnMuY29tL3dwLWNvbnRlbnQvdXBsb2Fkcy8yMDI1LzExL1BTX0RST1BfVGllci0xX1Jldi0xMS0yMDIyLnhscw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=becf322ef3989266c9ecfce92629c1e2aea38876a356c12668a0f8d9d776dfb7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly9zcHJlYWRzaGVldGRhZGR5LmNvbS93cC1jb250ZW50L3VwbG9hZHMvMjAyMy8wOS9SZXRpcmVtZW50LUNhc2gtRmxvdy1TcHJlYWRzaGVldC1mcm9tLUdldC1TbWFydGVyLUFib3V0LU1vbmV5LWZvci1FeGNlbC54bHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c01f10a1c0b79a157369e7d28d4da3841f311dd51e87d96681121c8c7e9d77cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly93d3cucGxpbmRpYS5jb20vd3AtY29udGVudC91cGxvYWRzLzIwMjUvMDMvcmV0aXJlbWVudC1wbGFubmluZy54bHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a67897b9e55db0fd322989e350015921908b4635ba03231878e9500744e2dc6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly93d3cuc2hlcndvb2RvcmVnb24uZ292L2NvbW11bml0eS1mYWNpbGl0aWVzL3Nlbmlvci1jZW50ZXIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebf9a6bf30c78d94cdf7808e8f747e42616a96686f11b55fec425a108cbae27aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly9zZW5pb3JjZW50ZXIudXMvc2Mvc2hlcndvb2Rfc2VuaW9yX2NlbnRlcl9zaGVyd29vZF9vcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27986df24ee0bb959ef262d3da1314d58c9a977ca8c7e822c6ae1d94e2221226JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly9zaGVyd29vZG9yLmNpdmljcGx1c3dlYm9wZW4uY29tL21hcmpvcmllc3Rld2FydGNlbnRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=adfbeaf8cd9beb31e38245ba06bddef5ea00cc3148b91ef61d1bf1e0bd44e44aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Nlbmlvcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f20c2201e532504cce7e37cd42f9d47f2a507c5beac28b8deeee5253e1dfd9eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly93d3cudGhlc3ByaW5nc2xpdmluZy5jb20vc2VuaW9yLWxpdmluZy9zaGVyd29vZC9vcmVnb24vc2hlcndvb2Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=08cf77f1e3fed9a40224bb0b9687845b81bc09da74eb671c2e15fb6ae6a76636JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly9zaHMuc2hlcndvb2QuazEyLm9yLnVzL3NjaG9vbC1pbmZvL3Nlbmlvci1pbmZvcm1hdGlvbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7253cb0284402c5c4371487d33dff89a5c301beeea8cb4986539b6e0b2ab1b88JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly93d3cuYWZ0ZXI1NS5jb20vc2VhcmNoL29yL3NoZXJ3b29k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a00cfec185ef930ae867a3dbc4eaa97fb835d31e98da7081b604d3f4d14f5a39JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly93d3cuc3Rld2FydHRlcnJhY2VzcmFwdHMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9afe480455bdd8059bf2dce5e3d2c8c5510e6ccae44e98aa51474a4b7cafff19JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly93d3cuYXBhcnRtZW50aG9tZWxpdmluZy5jb20vc2hlcndvb2Qtb3IvYXBhcnRtZW50cy1mb3ItcmVudC9zZW5pb3I_bXNvY2tpZD0zYmY5OTNiMDU4ZjA2NjM2MGI5Mjg0NTE1OWExNjc3Nw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e611a35dc3ccb50815324c5986b38136e02447465529f6d30e9194002f7c13d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cz9tc29ja2lkPTNlNWNjZmI4YmRkYjYyMjkzMjU3ZDg1OWJjY2Q2MzQy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=231012a387d4ec53a655bfcf3c619ee0a4a226d7080673d1766c7d19c0f62586JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9hY2NvdW50Lm1pY3Jvc29mdC5jb20vYWNjb3VudA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ba67d2acbe53424d920e4e3cd4fee6fd5f5795dbfc5f83227262a60878e9fd7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a7da95254c1c2f834701ccf78b36fdf84de27557c603e5432fe40097c96e40dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWljcm9zb2Z0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=813890850d0653ffcaa917fe4664c3d8b80f1f913a0ce3d7daf21ce299e5921cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cy9taWNyb3NvZnQtMzY1P21zb2NraWQ9M2U1Y2NmYjhiZGRiNjIyOTMyNTdkODU5YmNjZDYzNDI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25376799f10259513213d4b595dc7e7847951f2102227ba89f6d6353d17ad4eaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS8lQzIlQTAtJTNF&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d5cbbba6a9772b3863d33258ed389379792c2cf97f2343a0efc592a2233ec289JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9jYXJlZXJzLm1pY3Jvc29mdC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c041149eff6438133db0a58921ab4462f7c34842272b1eed81c6517a7e97c1acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9zaWdudXAubGl2ZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a4e19c2f6bf4a6ed88392f60ce310680a8a0c5a582c5f05de234352934fb6afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9tMzY1LmNsb3VkLm1pY3Jvc29mdC8_b3JpZ2luZG9tYWluPW1pY3Jvc29mdDM2NQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82ed53fc1fa004a7261cdbdcf56b58c806957d6eb5f3d525668e1a5cb87990dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9vdXRsb29rLm9mZmljZS5jb20vbWFpbC9pbmJveA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd4ae9d4c2f8315a049fabde33abcd2954986d54e08af2d9bdcb2dbf08733a1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7eaf6a5b5a38197e4ab2de19eccdc155004e0958def07f5b58e79d762702799JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11954947b6029ac9408550a30836db7ccc9922f567e0700f6e5fda1d2d4049daJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvZnJhaWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc62b6e4889076e3b1b7a98705b4905dd0415a74cd4df8c1957ca17c645625a4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9mcmFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f7eba3b64507d63a4e8ba476b244a020bff82e71aa0e93b97186b3417e749b27JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be55a4690a59b4416cd6288769155604241527d2fd793ec3a992eab0f1613dffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f06f3a1f7d3978a470de86442dc008ffa5144d3796b2a24506af0d12cba85e1aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c18ccde5c45df255ce99af4fc457cdcf05f111d6de4bce1f70719a45d4a6876dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly9lbi5tLndpa3Rpb25hcnkub3JnL3dpa2kvZnJhaWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7096825fc9a89d401e9fb0a0b8222f26d0f0508ede8bcdd8f2b9b3cf3d92fd8cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL2RpY3Rpb25hcnkvZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d670ba9ed67bfcd6f2a40dc17361cbe6fe8396d1d51f8cd2a90243966f52196JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cub3hmb3JkbGVhcm5lcnNkaWN0aW9uYXJpZXMuY29tL2RlZmluaXRpb24vZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=17022b465b957e07ea9392e206afa7ee0fc8ac3359a071a68ec21a8e38626645JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL2RpZ2l0YWwvb25saW5lLWJhbmtpbmc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80c829aab17458382887948d1afc7b392256c2851f50717598ade2f3fef1381dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c9f59d373619b817a1305a7293fc2d2d67133e9084029194a0ab56d62afcb03JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly9zZWN1cmUuY2hhc2UuY29tL3dlYi9hdXRoL2xvZ29uYm94&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e612eaa3ef9ade0fbbe5cd1124f2bb767fc12a3d443a0d671062fc68826c107fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL3BlcnNvbmFsL2NyZWRpdC1jYXJkcy9jYXJkLXJlc291cmNlLWNlbnRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aa370f7da574fffa768c995ce6ea0f139007817bdd298f28fd1eb60755b39dc2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly9wZXJzb25hbC5jaGFzZS5jb20vcGVyc29uYWwvY2hlY2tpbmc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cd5799e0bec6e8f763928dceee32638bae3863f6406d0653c586404bda4e7360JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL3BlcnNvbmFsL2NyZWRpdC1jYXJkcy91bHRpbWF0ZS1yZXdhcmRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27f97456bc952ed65a51c26beaee40622a7231d92e29795d00cc29fb3cda4ed7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL3BlcnNvbmFsL2NyZWRpdC1jYXJkcy9sb2dpbi1lcGF5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7fd9338e61833ab24741bf97be29de7d00cced0a7fbcc64b8657323c0a5da863JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL2RpZ2l0YWwvb25saW5lLWJpbGwtcGF5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5adbd6b6f8f6e0f38ca13df8dc6c8a5532c2f7025b73c5d6db0e1207d14e48d1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL3BlcnNvbmFsL21vcnRnYWdlL215LW1vcnRnYWdlL2hvbWU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bddb5a4d780270cc7a057e979575974b18a7c6bcfcc19d112a6630f784f4842cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL3BlcnNvbmFsL2NyZWRpdC1jYXJkcy9hbWF6b24vdmlldy1hY2NvdW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b666abc564985e8fab26ddf4894de2387a5574ab735cb529238c1b63c8acdc9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly9lbWVhbHMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9b37f1fb6cf66aea38220e9409f29632363f0401cb2cc8824f2e607d773c56dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cuYWxscmVjaXBlcy5jb20vMTAwLWVhc3ktbWVhbHMtMTE2OTUyMjc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d18d01b7d21eb185ce21ac93a6d8c5f30c8517789fa0a33881e007ef770f8500JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZWFzeS1kaW5uZXItaWRlYXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=65a9e5af6fbf575948f34a6802bf92f28735f590736a9b66a9c5232d8c12fe22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly9lYXRtZWFscy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c42ea2b44b64c9c8ef444cf386a6fa7796a14fd60f2f829147b5d3196e8a5e00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zLzMwLW1pbnV0ZS1kaW5uZXItcmVjaXBlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=188ee2298b307c97943779f15c5a9a9779944e69e0882743f54f71d7e1a05a7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=060f6138d48ec2e30599facac2a2b7c6ce5a515770482f62a749fa4c1eb028a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cubW9tc21lYWxzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f81c8532289f4d12f20322248663fb80b534cd47eabe1b16005288e958b8950fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zL2Vhc3ktZGlubmVyLXJlY2lwZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2c5d0119071ef10f4e883b3c1fbebe740e9d5251d168b5a49c9e3d86371cfe5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzMyMjY0Mjg0L2Vhc3ktZGlubmVyLXJlY2lwZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56b309329dbdbff7dea8e083ca92568810e78b8ae56a357e3c8d02e7b7d69ceeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cuZnVlbG1lYWxzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f3972b4dfc0eebe88782171f7c7e31a2206f4fab6cb9b940cccfc5e01da0f5aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tZ2IvY29udGFjdHVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e038fffefbb3e1cfbd244e995eea1fb27bf9fbf509d464ee2217884f8e6b450JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvYWNjb3VudHMtYmlsbGluZy9tYW5hZ2UvaG93LXRvLXNpZ24taW4tdG8taG90bWFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=09102301c15c006cd276b79b48db4e5320e4d2a189bb0158b77a9ec8450aadd1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly90ZWNoY29tbXVuaXR5Lm1pY3Jvc29mdC5jb20vY2F0ZWdvcnkvbWljcm9zb2Z0LWNvcGlsb3QvYmxvZy9taWNyb3NvZnQtY29waWxvdC1ibG9n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d170c81ba80016e5e15ee3220e5b185b1931a13d2351ab2caf44172aa102e2aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly90ZWNoY29tbXVuaXR5Lm1pY3Jvc29mdC5jb20vYmxvZy9leGNoYW5nZS9leGNoYW5nZS1vbmxpbmUtZXdzLXlvdXItdGltZS1pcy1hbG1vc3QtdXAvNDQ5MjM2MQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75230c9d3e1d92736a35e47f01d53f79aabae78be4bddc65ef63a83834d66b5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9kZXBsb3ltZW50L2luc3RhbGwtdXBncmFkZS9nZXR0aW5nLXJlYWR5LWZvci10aGUtd2luZG93cy0xMS11cGdyYWRl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fd697a6d85e873336ca79753bfbefed7988ed4cf687998358ee97640a9fd8c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZnItZnIvd2luZG93cy9tZXR0cmUtJUMzJUEwLWpvdXItbGVzLXBpbG90ZXMtdmlhLWdlc3Rpb25uYWlyZS1kZS1wJUMzJUE5cmlwaCVDMyVBOXJpcXVlcy1kYW5zLXdpbmRvd3MtZWM2MmY0NmMtZmYxNC1jOTFkLWVlYWQtZDcxMjZkYzFmN2I2&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dda202a11cf86182f0daec9139965b1648cbf9c1d749d2c0f868485192507299JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvd2luZG93cy9ha3R1YWxpc2llcmVuLXZvbi10cmVpYmVybi0lQzMlQkNiZXItZ2VyJUMzJUE0dGUtbWFuYWdlci1pbi13aW5kb3dzLWVjNjJmNDZjLWZmMTQtYzkxZC1lZWFkLWQ3MTI2ZGMxZjdiNg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c6e7615e8e7b2a35d95aa92f28a7fc1be36f40f81a3925618378d2ca5a45665JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvZWRnZS9nZXR0aW5nLXRoZS1sYXRlc3QtbWljcm9zb2Z0LWVkZ2UtdXBkYXRlLWp1c3QtZ290LWVhc2llcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81dc9b62b0ce2eddd383201ffd1458aac967c4e59c0c053e7f8f87fc72f2686aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvb3V0bG9vay90cmFpbmluZy9zaGFyZS15b3VyLWNhbGVuZGFyLWluLW91dGxvb2s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2cb396f2dff15f7d4330c11b4bea1b03849f838e1105ef03b86d4c4555114d89JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvZm9ybXMvc2lnbi1pbi10by1taWNyb3NvZnQtZm9ybXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=637f1e2de8b7a13c3a1fca4bf1345289a593fadfc461b9eb708bb0ccd552e026JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01572cce-81f1-6d33-122c-3b2f80726c5c&amp;u=a1aHR0cHM6Ly9zZXJ2aWNlcy5zbGNwbC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96d7926c3966653e49184b0d7bffc5720f47ae12d014944eb43417bd7cb5cbc6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01572cce-81f1-6d33-122c-3b2f80726c5c&amp;u=a1aHR0cHM6Ly9zZXJ2aWNlcy5zbGNwbC5vcmcvbGlicmFyeS1zdG9yZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=138be10af53d3a31f0f947e743ba9efcf22eeb2b9690d7ac7333e5f898ca1a16JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01572cce-81f1-6d33-122c-3b2f80726c5c&amp;u=a1aHR0cHM6Ly9zZXJ2aWNlcy5zbGNwbC5vcmcvbGlicmFyeS1jYXJkLWFwcGxpY2F0aW9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dff34a5378eeb3a0a8cdf6ed967dc805383b291beaad6119e2f09c002a7c41afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01572cce-81f1-6d33-122c-3b2f80726c5c&amp;u=a1aHR0cHM6Ly9zZXJ2aWNlcy5zbGNwbC5vcmcvcHJpbnRpbmc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb1a8540e8a2f0d925ecf06d0776b2e908d443ef03d8478a56d45641fff191e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01572cce-81f1-6d33-122c-3b2f80726c5c&amp;u=a1aHR0cHM6Ly9zZXJ2aWNlcy5zbGNwbC5vcmcvc2hvcHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=49cbff0da7ccd59e0083139a0efe32a1316f31e512f1e94328cbff3ddb45e442JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01572cce-81f1-6d33-122c-3b2f80726c5c&amp;u=a1aHR0cHM6Ly9zZXJ2aWNlcy5zbGNwbC5vcmcvdXRhaHMtb25saW5lLWxpYnJhcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=809b2eb4ad57ef0e9b78732d8b0a0ec273896cd15c46a49817bfe54fbf42e7a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33cd3874-c10f-6605-0170-2f95c077674d&amp;u=a1aHR0cHM6Ly93d3cuY3JlZGl0b25lYmFuay5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3e7447c86ed24c8c18e36d8ed7ae891c859449ddff9b5531f1600bbd52a7d3eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33cd3874-c10f-6605-0170-2f95c077674d&amp;u=a1aHR0cHM6Ly93d3cuY3JlZGl0b25lYmFuay5jb20vZmFxcy9wYXktYmlsbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12a167a41b630d17179fc73e0d4a1992f8ec9bde177c3006e5e683b15d5e832fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33cd3874-c10f-6605-0170-2f95c077674d&amp;u=a1aHR0cHM6Ly9zZWN1cmUuY3JlZGl0b25lYmFuay5jb20vYWNjZXNzL2hvbWU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e087493234a3c5e76026c1411438de6a04114f9da42bfd7b707fdf398e1d6209JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33cd3874-c10f-6605-0170-2f95c077674d&amp;u=a1aHR0cHM6Ly9zZWN1cmUuY3JlZGl0b25lYmFuay5jb20vcmVzZW5kLWFjdGl2YXRpb24tZW1haWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=63bc3d5a7b910a63b9db7b32879fc902c6cd19f47dc4877ee5bce354bfa5a705JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33cd3874-c10f-6605-0170-2f95c077674d&amp;u=a1aHR0cHM6Ly9jYXJlZXJzLmNyZWRpdG9uZWJhbmsuY29tL3BhZ2VzL2JlbmVmaXRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e3decc41e13f42c6278384cefda91ce9d8fc9663a4b192673bedae11940ffe4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33cd3874-c10f-6605-0170-2f95c077674d&amp;u=a1aHR0cHM6Ly9jYXJlZXJzLmNyZWRpdG9uZWJhbmsuY29tL3NlYXJjaC9qb2Jz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e2cd41d2c406fe8d736e2f04e44cbd52f4ff39dd945679c9287f1855a9b9e10JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly93d3cuY3JhaWdzbGlzdC5vcmcvYXJlYS9zYW5kaWVnbw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=367a3b3933f18507a31eb246a906d5612b41fcc89707ac7b12b564aaa3a16c66JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly93d3cuY3JhaWdzbGlzdC5vcmcvc2VhcmNoL2FyZWEvc2FuZGllZ28_Y2F0PXNzcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a913a4fb0b8123aaef770deabe4721235b486448520246328abaa159377d36f6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly9nZW8uY3JhaWdzbGlzdC5vcmcvaXNvL3VzL2NhL3NhbmRpZWdv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a195574a712552e0483606347937668b6388be0c8a6a3c908b38c73a97c08407JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly9nZW8uY3JhaWdzbGlzdC5vcmcvaXNvL3Vz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91d9ae764e0df04348e9a81760162c1b37581d9cfe3640a72dc81d5123b47c55JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL21hcmtldHBsYWNlL3NhbmRpZWdvLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f72d43723b7c9e74bd703d90650bc1948545716ff7be3b2d835c517a374aa163JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly9zYW5kaWVnby5jcmFpZ3NsaXN0Lm9yZy9zaXRlbWFwLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b251044fc48f807f15d51216587a68a1b0a235c3ce1900fc2b5d1580ba2b19bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2dyb3Vwcy8yMTc0OTMxMzU0NDc2OTUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de47488cf2f455f36c6d9b3c44b68424ffbe575497341919e5d754af308325d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1456b719-9cc3-6121-13cd-a0f89d316088&amp;u=a1aHR0cHM6Ly9hY2NvdW50Lm1pY3Jvc29mdC5jb20vYWNjb3VudC1jaGVja3Vw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1212d59be8d1f437a8d4c3c835423bf21b79610e90110a82d252f2caa85eda3dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly93d3cuaW5kZWVkLmNvbS9jYXJlZXItYWR2aWNlL2ludGVydmlld2luZy8yLWZvcm1zLW9mLWlkLWZvci1qb2ItaW50ZXJ2aWV3&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=384490ff3b30fcd56b0742fbb0f15bd07f831aeeee7a031536aef85ec7f1287fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly93d3cuaS05aW50ZWxsaWdlbmNlLmNvbS9hcnRpY2xlcy92YWxpZC1mb3Jtcy1vZi1pZC1mb3ItdGhlLWktOQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7211da59e8062f2a43e22bfbd3ffe34f851f314375a42329351a7d6383927a4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly93d3cudXNjaXMuZ292L2ktOS1jZW50cmFsL2Zvcm0taS05LWFjY2VwdGFibGUtZG9jdW1lbnRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e3776671fe0b0a2a2124bf7e1a51727002c830e01794b7a779082ceb7b5c5651JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly9jbGltYnRoZWxhZGRlci5jb20vZG8teW91LW5lZWQtYW4taWQtdG8tZ2V0LWEtam9iLWFjY2VwdGFibGUtZG9jdW1lbnRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d74852ac25ad66ddf3f9eeaa2f62ef43406f8de3503a3cb807adfe3a84f8556aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly93d3cudml0YWxyZWNvcmRzb25saW5lLmNvbS9ibG9nL2FjY2NlcHRhYmxlLWZvcm1zLXVzLWlk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=299f7764427a4e4d383937a38969b467e5fd1daad6783a517f4685e3a917c62eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly9sZWdhbGtub3dsZWRnZWJhc2UuY29tL3doYXQtY291bnRzLWFzLWEtdmFsaWQtaWQtZm9yLWEtam9i&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89c3626e7315c3930986d03fc2ff20db9b2c6c9c5375a1a51153e08244680dceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly9za2lsbHNmb3JjaGFuZ2UuY29tL2RvLXlvdS1uZWVkLWFuLWlkLXRvLWdldC1hLWpvYi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4228a075167777fff39c5d59fe01e5593d7e08fdcbd956ad71e9d6d36d180a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly9kb29yczRqb2JzLmNvbS9lbXBsb3ltZW50LWxlZ2FsaXRpZXMvZG8teW91LW5lZWQtYW4taWQtdG8tZ2V0LWEtam9iLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d8086c9837e6c863fddaf0a5b72e05caf100385f605c91400a087402691cc7e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly93b3JrLmNocm9uLmNvbS9wcm9vZi1pZGVudGlmaWNhdGlvbi1uZWVkLWpvYi0zMTE3MS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c75fba25635bba8a9dc6193c9921536cb10943d505e3883552e9cee04c4fd836JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly9jbGltYnRoZWxhZGRlci5jb20vZG8teW91LW5lZWQtYW4taWQtZm9yLWEtam9iLXRoZS1yZXF1aXJlZC1kb2N1bWVudHMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=13cafcc6c86653f0a83e6957d2dbf01d60d002a437cd2d69c90e117a36bf72acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvZGlzZWFzZXMtY29uZGl0aW9ucy90aW5uaXR1cy9zeW1wdG9tcy1jYXVzZXMvc3ljLTIwMzUwMTU2&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7cb5acb375d90eb30d12927ef4512baf8fdb474e3f1137216b4cfc4bc818d1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvZGlzZWFzZXMtY29uZGl0aW9ucy90aW5uaXR1cy9kaWFnbm9zaXMtdHJlYXRtZW50L2RyYy0yMDM1MDE2Mg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d739bddbdaab6ee6b38263e3ee7eda1f78bae641a85c760aa47b8c544c522f2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9vbmxpbmVzZXJ2aWNlcy5tYXlvY2xpbmljLm9yZy9wYXRpZW50cG9ydGFs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f8fa62c91178efa15ded0826e1817adb4ef35fa16261a1085fb6c15f5f76bf7fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9jb25uZWN0Lm1heW9jbGluaWMub3JnL2Rpc2N1c3Npb24vcHVsc2F0aWxlLXRpbm5pdHVzLTQv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48681578330d9a049e7e905697b046b1d69ddd8af4fb5e6ff6db8c7890f684c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9uZXdzbmV0d29yay5tYXlvY2xpbmljLm9yZy9kaXNjdXNzaW9uL21heW8tY2xpbmljLXEtYW5kLWEtdW5kZXJzdGFuZGluZy10aW5uaXR1cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3bc41427cf38382c53d284ff5f2164032dccec3468e51ef7ba7a5898f17c67a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9jb25uZWN0Lm1heW9jbGluaWMub3JnL2Rpc2N1c3Npb24vd2hhdC1uYXR1cmFsLXByb2R1Y3QtY2FuLXF1aWV0LW15LXRpbm5pdHVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=188db571b83d7655c90abc9067766df69142426ae7585d388bf0dcdcabe83d2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9uZXdzbmV0d29yay5tYXlvY2xpbmljLm9yZy9kaXNjdXNzaW9uL3Rpbm5pdHVzLXdheXMtdG8tcmVkdWNlLXRoZS1pcnJpdGF0aW9uLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=115e7337ddf14cdac8eb46cb7e74afb1cb3571007c45a57f56ce7fdaeda37530JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9tY3ByZXNzLm1heW9jbGluaWMub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=318e6acaf107bf5a4dcf5cf763c9058379cf457bc45af07cef9b8c571ba6c014JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9tY3ByZXNzLm1heW9jbGluaWMub3JnL2xpdmluZy13ZWxsL3doYXQtY2F1c2VzLXJpbmdpbmctaW4tdGhlLWVhcnMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=14be6dcc3b1779be4d8128d770cc831abda4cb0ae2af7ec43caab6d39e2b3fe6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHloZWFsdGgubWF5b2NsaW5pYy5vcmcvZmVhdHVyZWQtc3Rvcmllcy90aW5uaXR1cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71095d9d67dcbf69c46a26908970e5baecdb32d63e17b135f87fb0cbadd6ea81JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9kdXJoYW0tY291bnR5LXJlc3RhdXJhbnRzL3N1YndheTE2Lmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be38148098f43bc641093bb07930a760727495ceddb5973d30739136e78234deJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9uZXcteW9yay1jaXR5LzM1MjgwNjctODMteWVhci1vbGQtYWlyLWZvcmNlLXZldGVyYW4tMi5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a0d0ca54546dedb121e08696a51c9cdd312e7d0f494b3a5b8def9f8377bc67aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9yb2NoZXN0ZXItYXJlYS8yNjAxOTU0LWFiYW5kb25lZC1zdWJ3YXkuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3dce001442919a042a5d765ca9855343ecbbd430f58ad623b126149a0d2a82d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9sb3MtYW5nZWxlcy8xODQ0NzYwLXdoYXQtc29tZS1tb3ZpZXMtZmVhdHVyZS1sLXN1YndheS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e359dec2ee3f9802f0fc534fea23f35279dc02685632a0c0679cdfcd2712a414JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9sb2NhdGlvbnMvU3Vid2F5L0x5bm53b29kLVdhc2hpbmd0b24uaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a930cfcfa0170dcdee5bc5ec7d05fc3e5da8cf2d2ca6285ab17ba9f4ca46ce6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9zYW4tZGllZ28tY291bnR5LXJlc3RhdXJhbnRzL3N1YndheS0zNDE5NS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b8d8e0be5c407eaf08e57867033368e2850708b751715c8cb0ccb56b81124a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9ob3VzZS8zMjE4MjY4LTN4MTItdnMtM3g2LXN1YndheS10aWxlLWJhY2tzcGxhc2guaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=204305dc146fa64417b3be08f49421d7449a650260b4ba1d016f5817f0f2bc2eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9uZXcteW9yay1jaXR5LzM0NTc0Mjktc3Vid2F5LWJhbGFuY2UtcXVlc3Rpb25zLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a0b3d754c685c0f733ecec6122b44ec0e4b73f11cf533db7dd6773d61e6d6cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9uZXcteW9yay1jaXR5LzM0NDYxODctanVzdC1wb3N0ZWQtdmlkLW1vbnRyZWFsLW1ldHJvLXN1YndheS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ca9a87c96dad8d3f28d206724dbba3ede8ad8836aa927cc9f6ecdeaa836e8c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9yZXN0YXVyYW50cy9GTC9TVUJXQVktMTEzOTQuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffd52beeb8b9f1d788653edf53d81a334664933f93541014013f72f508cf5a1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=59062c38dab6ba92cec5baa7d0ea85590d90382424ee18ece8b79e795a10aab0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0dUQTYvaG90Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=99ed2a846a9136dd4f363fa92b0fc7c11d9e54647bd4017780e512d4e32205e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS9ydS9hcHAvaW5zdGFncmFtL2lkMzg5ODAxMjUy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c6b7c5f8c4124ea3b0f7ed88959079faf69339cf58402f1fa4d830f0003f97d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS91cy9hcHAvZmFjZWJvb2svaWQyODQ4ODIyMTU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4798709ad6ed63b6a15836eae595f87ddf9d27c2ad7988236a66b94fae7f120aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS91cy9hcHAvbWVzc2FnZXMvaWQxMTQ2NTYwNDcz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ce259cc987c7b08bcea8468fc31108d773f21c4e9d423f4c2f453d01f18a388JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL1RvcENoYXJhY3RlclRyb3Blcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d23b52da059bcf605e4f6c54019de797094d8cde64e4db936640044ff2932f53JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS91cy9hcHAvaW5zdGFncmFtL2lkMzg5ODAxMjUy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4bb5799fc326c03e117bf33ad4aa12bce71f6044e380cd57b351ad899c696789JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS9lcy9hcHAvaW5zdGFncmFtL2lkMzg5ODAxMjUy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0624d26b21686b9a71214111c38dda30880b6fd2f1c5a97ea6f95f8302bf28a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS9kZS9hcHAvaW5zdGFncmFtL2lkMzg5ODAxMjUy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16dd25742ac726c57287e24b1d448196dc8c54757c53cb6e654b707d745b5c97JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS9oay9hcHAvaW5zdGFncmFtL2lkMzg5ODAxMjUy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=46fd63a1320b19e6c067a0ec98cf2161467ad87646269e653376abd23fe5d6d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cuZmVkZXguY29tL2VuLXVzL3RyYWNraW5nLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f1075e2e527352d2cf0589f1a435c8b632a3b736dac65287c3e11bc9e020b798JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cuZmVkZXguY29tL2VuLXVzL2hvbWUuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=78aba676ff3b0047250a794b8c745b7ee08a6e07fa3f05ca4781b0347e77bd98JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cuZmVkZXhmcmVpZ2h0LmNvbS9lbi11cy90cmFja2luZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bbdb5f75732ff3174426a434a507d152fd766819ede9cd698fadbca7e19cf288JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cuZmVkZXguY29tL2VuLWNhL3RyYWNraW5nLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7bbf01c209710756d3e2d50541cb6123b72780b76b467c8b5a9da27c647bf24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cuZmVkZXguY29tL2VuLXVzL3RyYWNraW5nL2FkdmFuY2VkLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d88357d104d6429d228b13ee54363b4b9764529bd5bce8e373fa833e982c67aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly9pbWFnZXMuZmVkZXguY29tL3d0cmsvZmVkZXh0cmFja2luZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=570e12d875e7a947bced92de05eef7ac406d679040acbf498cc2577abb9b8901JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cuZmVkZXguY29tL2VuLWdiL3RyYWNraW5nLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=790d3c03b572a40aba3548488474b9de2c6ae70231bd1ceb9cfdda89ec896b41JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cub3JkZXJ0cmFja2VyLmNvbS9jYXJyaWVycy9mZWRleA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3dac014e724657a949da12b082e2acf2a266476f0ba8a765102361e16654931cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly9maWN0cmFja2luZy5mZWRleC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae2ed4b758f33a779e7b8258cda4153967baf381a19124eaeee4a5a3374389d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly9pbWFnZXMuZmVkZXguY29tL2VuLWdiL2N1c3RvbWVyLXN1cHBvcnQvZmFxL3JlY2VpdmluZy90cmFja2luZy1xdWVzdGlvbnMvd2hlcmUtaXMtbXktcGFja2FnZS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=37fa9975a3340cbea58b8d5bc28f377ef7db010768c9e3920140f8af10d29e09JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3JlbW90ZXdvcmsvY29tbWVudHMvMTdibGx0Ny9pc19mbGV4am9ic193b3J0aF9pdC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d988ac53fdabfc2015cb6b80a913414afc60eaa4959e2b6010647d7157332804JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2pvYnMvY29tbWVudHMvMTh3enF4ZS93aGF0X2pvYl9zaXRlc19pc19ldmVyeW9uZV91c2luZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=53a51bd6bfcded14c84b97d4b0f9e3731f835be35725b28c1fb72c4a836a58eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly9lbmdsaXNoLnN0YWNrZXhjaGFuZ2UuY29tL3F1ZXN0aW9ucy85NzMxOC9pcy10aGUtcGhyYXNlLWl0cy1qdXN0LWEtbWF0dGVyLW9mLXNlbWFudGljcy1tZWFuaW5nbGVzcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0034201784934d4cfab7b6a3974cb86ad85415d866a6c469cb9cc1356998e701JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly9lbmdsaXNoLnN0YWNrZXhjaGFuZ2UuY29tL3F1ZXN0aW9ucy8zNDQ1MjMvdXNhZ2Utb2YtaW5kZWVkLWluLXRoYW5rLXlvdS12ZXJ5LW11Y2gtaW5kZWVk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e1a6bc90308caa036abb9d33c9f766887d1220b0ce0232c96761809d01e1fa3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2pvYnMvY29tbWVudHMvNXU4b3ZkL2lzX3RoZXJlX2FueXRoaW5nX2JldHRlcl90aGFuX2luZGVlZF9mb3Jfam9iLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=038f75fbbf1357e6906478c6d6cfa58a037aa5bcf4d0c9a06bf91d13ed54ab69JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2pvYnMvY29tbWVudHMvYjMyMW1pL2RvZXNfYW55b25lX2FjdHVhbGx5X2dldF9qb2JzX3Rocm91Z2hfbGlua2VkaW4v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b574a814716194bc46da0c181080975d9ea21704cc1d90d2f9af03e5fe615737JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2pvYnMvY29tbWVudHMvNXNhdmp4L2hhdmluZ19saXR0bGVfc3VjY2Vzc193aXRoX2luZGVlZGNvbV9hcmVfdGhlcmUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a78bf2fe5a91ccb394251e6364d87f1c5bc1039cec4fb2fe4d712bf4d5240e68JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3JlY3J1aXRpbmdoZWxsL2NvbW1lbnRzLzEwdWZwNXcvbGlua2VkaW5fdnNfaW5kZWVkLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4df6eec6d8ec99bc9f5d2176822bc35102a5a5d8cc68825db81b6be12048e28JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2NhcmVlcmd1aWRhbmNlL2NvbW1lbnRzLzE4bzU3ZzUvZG9feW91X2d1eXNfZXZlcl90YWtlX2NvbXBhbnlfcmV2aWV3c19zZXJpb3VzbHkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=902eb7e7b0628183e20d7215df7c3352aa8b0578a1a0b5a3b4b3e57537c51085JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0NhbGdhcnkvY29tbWVudHMvMWFsZHY4eC9iZXN0X2pvYl9ib2FyZF9mb3JfaGlyaW5nX2xvY2Fsc19ub3RfaW5kZWVkLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=186e1aee978c480ede365645e71c4585696fff96c2c7980afd61c9335bba4fb2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=193df9d2-bcdb-62c6-0ffd-ee33bdb263df&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL1NjYW1zL2NvbW1lbnRzL3dpcDE0by91bnNvbGljaXRlZF95b3VyX25ld19hY2NvdW50X29uX3hueHhfZ29sZF9lbWFpbC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fb42e250f4017bf2b235cdc9c9843f0c7ee905c5943180773a96bfc33648794JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=193df9d2-bcdb-62c6-0ffd-ee33bdb263df&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2RhdGluZ292ZXJmaWZ0eS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4af81796163ab0f3cd5ff9043c7ea010c1bfeeec2b4e01efb52e41e01dfda212JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=193df9d2-bcdb-62c6-0ffd-ee33bdb263df&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0xlZ2FsVGVlbnMvd2lraS9pbmRleC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48a5c6c7365bbee73be0aff9a3bbeb0c7a088b4b92716b61187a25757dc66c2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=193df9d2-bcdb-62c6-0ffd-ee33bdb263df&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL1Rpa1Rvay8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b9bed1462d395598bd2d3c5644fbb6f8c1a628145152c013e2cfed0be843c59JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=193df9d2-bcdb-62c6-0ffd-ee33bdb263df&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3ZlcnlzbWFsbHRpdHMvdG9wLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae51cf8cda714b22a04b78bc0279a2d1e17d40f0e3cb01f8a25592247a74a049JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=193df9d2-bcdb-62c6-0ffd-ee33bdb263df&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2lyYW5pYW4v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb20556af5562a5abd8f86bdd429c3fdccbe49e28d7edf76e2757e2831957639JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly9ibG9nLmVudG9tb2xvZ2lzdC5uZXQvd2hhdC1idWctbG9va3MtbGlrZS1hbi1hbnQtYnV0LWZsaWVzLWFuZC1ncmF5Lmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00f23a5ce7015f331852c04e1d7f2bff99b62eb7e4466fb062b5f482537787f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly90aGVwZXRlbnRodXNpYXN0LmNvbS9idWdzLXRoYXQtbG9vay1saWtlLWFudHMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7711789ee63aa82ffcd58a834eb3d5a6aeb39b4097db40b0319949e73c9cdfc0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly93d3cuaW5zZWN0aWRlbnRpZmljYXRpb24ub3JnL2J1Z2ZpbmRlci1zdGFydC5waHA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d643c0213dcf17faddfe46807e3ab54e1fd5f8b17eccae2b34054dfa4fe010a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly9pbnNlY3RzYWR2LmNvbS9pbnNlY3RzLXRoYXQtbG9vay1saWtlLWZseWluZy1hbnRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c35ac850c5adb44e7cd26aedda98026f8d19c379eb9761eca06a582253eaf7e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly9ncmVlbnlnYXJkZW5lci5jb20vZmx5aW5nLWluc2VjdHMtdGhhdC1sb29rLWxpa2UtYW50cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8adc96f9930b9d42eb595c623e2828f759298ac5a827f080d932c27eb14a8c19JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQW50bGlvbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a372a5978482d12ba891f1db98234314dd92e6af1b66aab7afb8c245a244549eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly93aGF0YnVnaXN0aGlzLmNvbS9lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce75e781fd8d9e692c87283791af5f2a9dc6f0e726f6cf04fe19c44ba2fbd779JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly9ibG9nLmVudG9tb2xvZ2lzdC5uZXQvd2hhdC1hcmUtdGhlLWluc2VjdHMtdGhhdC1sb29rLWxpa2UtZmx5aW5nLWFudHMuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d1c32d5d74fbedfd35cf1f3a0de7a668e1a4538bdb869dab01c6307071134bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly9ncmVlbnlnYXJkZW5lci5jb20vaW5zZWN0LXRoYXQtbG9va3MtbGlrZS1hbi1hbnQtd2l0aC13aW5ncy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2980322a8217325e9584eaf2deff5e80f9eab28edbb9e729c63eabaa490cd06JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vSWRlbnRpZnktRmx5aW5nLUluc2VjdHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=088e6249992dee4940fa3f493020ec5ee5efa2a0b422b2c27bd221a397d54268JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0Zvcm11bGFGZWVkZXJzL2NvbW1lbnRzLzE2dTMydTMvd2h5X2lzX2tlbmRhbWlsX25vdF9vbl9hbWF6b24v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8dc67ef950426fceffdb37c03e8216c66a6568158f940797fc24dec78c1ce33JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly93d3cuYW1hem9uLmNvbS9rZW5kYW1pbC1iYWJ5LWZvcm11bGEvcz9rPWtlbmRhbWlsK2JhYnkrZm9ybXVsYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97e71fc2c859af0b650330e7129b86d87933aa17a30504ffece52a0119e16ef1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly93d3cuYW1hem9uLmNvbS9rZW5kYW1pbC1jZXJlYWwvcz9rPWtlbmRhbWlsK2NlcmVhbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6fd423e176b8b3d8af7a617e1bf908cb6d9956a8ed24d94c58f1bcccced8a69fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly9zbnVnZ3ltb20uY29tL3doeS1pcy1rZW5kYW1pbC1mb3JtdWxhLW91dC1vZi1zdG9jay8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d862c4e63c49e42b229ee4373fc77c152768d5c49a1d28e1e13f7902d75c0542JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly90YW1hcmFydWJpbi5jb20vMjAyNC8xMS9rZW5kbWFpbC1vcmdhbmljLWNvdy1taWxrLWluZmFudC1mb3JtdWxhLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9db824250b1df22a7e2bce624ab802ac2890354820cdf35e1af129347462c02bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly91cy5rZW5kYW1pbC5jb20vcGFnZXMva2VuZGFtaWwtZ29hdC1zdG9jay11cGRhdGU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48a5a8695514a266fa879e4580072b9e7bd2e1999c001196339b1037d4813b67JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly93d3cud2FsbWFydC5jb20vYnJhbmQva2VuZGFtaWwvMTAwNTk1MTI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1e04bb53b9b2b7c992346c0f9cd28b820a918ee62e3cfe5fa0d5cf2dc0e422eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly91cy5rZW5kYW1pbC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=efdba06fe9f969dd9a1a4862a9db421d67705095c8c86e485b21c7458566c626JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly93d3cudGFyZ2V0LmNvbS9wL2tlbmRhbWlsLW9yZ2FuaWMtaW5mYW50LWZvcm11bGEtcG93ZGVyLTI4LTJvei8tL0EtODY5MTg1ODY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80987290fd3b37af1d07b13412bfccef68957fcc1b66e845f88dace7484679e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly9ldXJvbWFsbHVzYS5jb20vYmxvZ3MvbmV3cy93aGVyZS10by1idXkta2VuZGFtaWwtZm9ybXVsYS11c2E&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c14816c7cd5866f99d8fb1cdc939f212eafe5a3c233246cbfccf526271abf5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly93d3cuZ2VvcmdpYXByb2JhdGVyZWNvcmRzLmNvbS9NYXJyaWFnZS9TZWFyY2hNYXJyaWFnZXMuYXNweA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0859ac2e1315cc8acbc0b55dd7868951937fa68d3ccea3655d0d824ea20d84e9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly9kcGguZ2VvcmdpYS5nb3Yvd2F5cy1yZXF1ZXN0LXZpdGFsLXJlY29yZC9tYXJyaWFnZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1fe6173e92b8209d1c95c5e4bc4f2f6d4f6d9be1549be33ccdb7eb6714856e3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly93d3cuZ2VvcmdpYXByb2JhdGVyZWNvcmRzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c5aee25a73e681a52f728d6b06b670bcc953490660dbb6438f62090871324ca7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly9kcGguZ2VvcmdpYS5nb3YvZG9jdW1lbnQvZG9jdW1lbnQvcmVxdWVzdC1zZWFyY2gtbWFycmlhZ2UtZm9ybS0zOTEzL2Rvd25sb2Fk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=708f8f6c4c050234aab98f19956ba67f9a9db444f5ddb140c3b47646b4560f12JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly9tYXJyaWFnZS1saWNlbnNlLm9yZy9tYXJyaWFnZS1saWNlbnNlLXJlY29yZHMtZ2Ev&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34c20773df6b9b4b23393a087bb0baea78e8c04677ca668f4b8471ea5fe874cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly9tYXJyaWFnZXJlY29yZHMuZ2VvcmdpYW9mZmljaWFscmVjb3Jkcy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10052c0577d90858ff4d63d3b7f1b309919de751e23d5e7f5b70c814a03c4b64JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly93d3cuZG91Z2hlcnR5LmdhLnVzL0NvdXJ0cy9Qcm9iYXRlLUNvdXJ0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=444ddac726bb758448f8bc4095a36e0ae94ecb11adc94564719653f795673d9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly9nZW9yZ2lhY291cnRzLmdvdi9wY2lzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=69ecaee0292ff4885efbe3e41e1d7771881ad9a676fa3a18dee88bad0ea37377JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly93d3cuZnVsdG9ucHJvYmF0ZWdhLm9yZy8yMjcvUmVjb3Jkcy1EaXZpc2lvbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=03171a1c1f9f478d86153baa3ebb1a15304049911ddb4c6da4d4f1a4c5c61cdaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly90aG9tYXNjb3VudHlib2Mub3JnL3Byb2JhdGUtY291cnQvbWFycmlhZ2UtbGljZW5zZXMtYW5kLXJlY29yZHM&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
+  </si>
+  <si>
+    <t>Sea Point</t>
+  </si>
+  <si>
+    <t>Green Point</t>
+  </si>
+  <si>
+    <t>Woodstock</t>
+  </si>
+  <si>
+    <t>Observatory</t>
+  </si>
+  <si>
+    <t>Salt River</t>
   </si>
   <si>
     <t>Bing</t>
@@ -814,7 +1579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -848,19 +1613,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="G2" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H2" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -868,19 +1633,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="G3" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H3" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -888,19 +1653,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="G4" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H4" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -908,19 +1673,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="G5" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H5" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -928,19 +1693,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>84</v>
+        <v>209</v>
       </c>
       <c r="G6" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H6" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -948,19 +1713,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="G7" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H7" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -968,19 +1733,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>86</v>
+        <v>211</v>
       </c>
       <c r="G8" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H8" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -988,19 +1753,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>87</v>
+        <v>212</v>
       </c>
       <c r="G9" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H9" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1008,19 +1773,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>88</v>
+        <v>213</v>
       </c>
       <c r="G10" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H10" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1028,19 +1793,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>89</v>
+        <v>214</v>
       </c>
       <c r="G11" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H11" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1048,19 +1813,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>90</v>
+        <v>215</v>
       </c>
       <c r="G12" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H12" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1068,19 +1833,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>91</v>
+        <v>216</v>
       </c>
       <c r="G13" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H13" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1088,19 +1853,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>92</v>
+        <v>217</v>
       </c>
       <c r="G14" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H14" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1108,19 +1873,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>93</v>
+        <v>218</v>
       </c>
       <c r="G15" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H15" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1128,19 +1893,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>94</v>
+        <v>219</v>
       </c>
       <c r="G16" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H16" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1148,19 +1913,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>95</v>
+        <v>220</v>
       </c>
       <c r="G17" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H17" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1168,19 +1933,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>96</v>
+        <v>221</v>
       </c>
       <c r="G18" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H18" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1188,19 +1953,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="G19" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H19" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1208,19 +1973,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>98</v>
+        <v>223</v>
       </c>
       <c r="G20" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H20" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1228,19 +1993,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="G21" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H21" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1248,19 +2013,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="G22" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H22" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1268,19 +2033,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>101</v>
+        <v>226</v>
       </c>
       <c r="G23" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H23" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1288,19 +2053,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>102</v>
+        <v>227</v>
       </c>
       <c r="G24" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H24" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1308,19 +2073,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>103</v>
+        <v>228</v>
       </c>
       <c r="G25" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H25" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1328,19 +2093,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>104</v>
+        <v>229</v>
       </c>
       <c r="G26" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H26" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1348,19 +2113,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>105</v>
+        <v>230</v>
       </c>
       <c r="G27" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H27" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1368,19 +2133,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>106</v>
+        <v>231</v>
       </c>
       <c r="G28" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H28" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1388,19 +2153,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>107</v>
+        <v>232</v>
       </c>
       <c r="G29" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H29" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1408,19 +2173,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="G30" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H30" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1428,19 +2193,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>109</v>
+        <v>234</v>
       </c>
       <c r="G31" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H31" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1448,19 +2213,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>110</v>
+        <v>235</v>
       </c>
       <c r="G32" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H32" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1468,19 +2233,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>111</v>
+        <v>236</v>
       </c>
       <c r="G33" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H33" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1488,19 +2253,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>112</v>
+        <v>237</v>
       </c>
       <c r="G34" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H34" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1508,19 +2273,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>113</v>
+        <v>238</v>
       </c>
       <c r="G35" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H35" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1528,19 +2293,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>114</v>
+        <v>239</v>
       </c>
       <c r="G36" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H36" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1548,19 +2313,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>115</v>
+        <v>240</v>
       </c>
       <c r="G37" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H37" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1568,19 +2333,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>116</v>
+        <v>241</v>
       </c>
       <c r="G38" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H38" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1588,19 +2353,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>117</v>
+        <v>242</v>
       </c>
       <c r="G39" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H39" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1608,19 +2373,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>118</v>
+        <v>243</v>
       </c>
       <c r="G40" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H40" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1628,19 +2393,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C41" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>119</v>
+        <v>244</v>
       </c>
       <c r="G41" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H41" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1648,19 +2413,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C42" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>120</v>
+        <v>245</v>
       </c>
       <c r="G42" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H42" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1668,19 +2433,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>121</v>
+        <v>246</v>
       </c>
       <c r="G43" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H43" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1688,19 +2453,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C44" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>122</v>
+        <v>247</v>
       </c>
       <c r="G44" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H44" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1708,19 +2473,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>123</v>
+        <v>248</v>
       </c>
       <c r="G45" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H45" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1728,19 +2493,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C46" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>124</v>
+        <v>249</v>
       </c>
       <c r="G46" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H46" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1748,19 +2513,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C47" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="G47" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H47" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1768,19 +2533,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="G48" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H48" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1788,19 +2553,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>127</v>
+        <v>252</v>
       </c>
       <c r="G49" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H49" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1808,19 +2573,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C50" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>128</v>
+        <v>253</v>
       </c>
       <c r="G50" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H50" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1828,19 +2593,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C51" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>129</v>
+        <v>254</v>
       </c>
       <c r="G51" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H51" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1848,19 +2613,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="G52" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H52" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1868,19 +2633,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C53" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>131</v>
+        <v>256</v>
       </c>
       <c r="G53" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H53" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1888,19 +2653,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C54" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>132</v>
+        <v>257</v>
       </c>
       <c r="G54" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H54" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -1908,19 +2673,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C55" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>133</v>
+        <v>258</v>
       </c>
       <c r="G55" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H55" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -1928,19 +2693,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C56" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>134</v>
+        <v>259</v>
       </c>
       <c r="G56" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H56" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -1948,19 +2713,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C57" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>135</v>
+        <v>260</v>
       </c>
       <c r="G57" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H57" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -1968,19 +2733,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C58" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>136</v>
+        <v>261</v>
       </c>
       <c r="G58" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H58" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -1988,19 +2753,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C59" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>137</v>
+        <v>262</v>
       </c>
       <c r="G59" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H59" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2008,19 +2773,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>138</v>
+        <v>263</v>
       </c>
       <c r="G60" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H60" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2028,19 +2793,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C61" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>139</v>
+        <v>264</v>
       </c>
       <c r="G61" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H61" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2048,19 +2813,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C62" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>140</v>
+        <v>265</v>
       </c>
       <c r="G62" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H62" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2068,19 +2833,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C63" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>141</v>
+        <v>266</v>
       </c>
       <c r="G63" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H63" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2088,19 +2853,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C64" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>142</v>
+        <v>267</v>
       </c>
       <c r="G64" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H64" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2108,19 +2873,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>143</v>
+        <v>268</v>
       </c>
       <c r="G65" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H65" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2128,19 +2893,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C66" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>144</v>
+        <v>269</v>
       </c>
       <c r="G66" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H66" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2148,19 +2913,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C67" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>145</v>
+        <v>270</v>
       </c>
       <c r="G67" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H67" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2168,19 +2933,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C68" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>146</v>
+        <v>271</v>
       </c>
       <c r="G68" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H68" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2188,19 +2953,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C69" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>147</v>
+        <v>272</v>
       </c>
       <c r="G69" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H69" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2208,19 +2973,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="C70" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>148</v>
+        <v>273</v>
       </c>
       <c r="G70" t="s">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H70" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2228,19 +2993,2519 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
+        <v>203</v>
+      </c>
+      <c r="C71" t="s">
+        <v>204</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G71" t="s">
+        <v>400</v>
+      </c>
+      <c r="H71" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
         <v>78</v>
       </c>
-      <c r="C71" t="s">
+      <c r="B72" t="s">
+        <v>203</v>
+      </c>
+      <c r="C72" t="s">
+        <v>204</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G72" t="s">
+        <v>400</v>
+      </c>
+      <c r="H72" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
         <v>79</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="B73" t="s">
+        <v>203</v>
+      </c>
+      <c r="C73" t="s">
+        <v>204</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G73" t="s">
+        <v>400</v>
+      </c>
+      <c r="H73" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" t="s">
+        <v>203</v>
+      </c>
+      <c r="C74" t="s">
+        <v>204</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G74" t="s">
+        <v>400</v>
+      </c>
+      <c r="H74" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" t="s">
+        <v>203</v>
+      </c>
+      <c r="C75" t="s">
+        <v>204</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G75" t="s">
+        <v>400</v>
+      </c>
+      <c r="H75" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" t="s">
+        <v>203</v>
+      </c>
+      <c r="C76" t="s">
+        <v>204</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G76" t="s">
+        <v>400</v>
+      </c>
+      <c r="H76" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" t="s">
+        <v>203</v>
+      </c>
+      <c r="C77" t="s">
+        <v>204</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G77" t="s">
+        <v>400</v>
+      </c>
+      <c r="H77" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" t="s">
+        <v>203</v>
+      </c>
+      <c r="C78" t="s">
+        <v>204</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G78" t="s">
+        <v>400</v>
+      </c>
+      <c r="H78" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" t="s">
+        <v>203</v>
+      </c>
+      <c r="C79" t="s">
+        <v>204</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G79" t="s">
+        <v>400</v>
+      </c>
+      <c r="H79" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" t="s">
+        <v>203</v>
+      </c>
+      <c r="C80" t="s">
+        <v>204</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G80" t="s">
+        <v>400</v>
+      </c>
+      <c r="H80" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" t="s">
+        <v>203</v>
+      </c>
+      <c r="C81" t="s">
+        <v>204</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G81" t="s">
+        <v>401</v>
+      </c>
+      <c r="H81" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" t="s">
+        <v>203</v>
+      </c>
+      <c r="C82" t="s">
+        <v>204</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G82" t="s">
+        <v>401</v>
+      </c>
+      <c r="H82" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" t="s">
+        <v>203</v>
+      </c>
+      <c r="C83" t="s">
+        <v>204</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G83" t="s">
+        <v>401</v>
+      </c>
+      <c r="H83" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" t="s">
+        <v>203</v>
+      </c>
+      <c r="C84" t="s">
+        <v>204</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G84" t="s">
+        <v>401</v>
+      </c>
+      <c r="H84" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" t="s">
+        <v>203</v>
+      </c>
+      <c r="C85" t="s">
+        <v>204</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G85" t="s">
+        <v>401</v>
+      </c>
+      <c r="H85" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" t="s">
+        <v>203</v>
+      </c>
+      <c r="C86" t="s">
+        <v>204</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G86" t="s">
+        <v>401</v>
+      </c>
+      <c r="H86" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" t="s">
+        <v>203</v>
+      </c>
+      <c r="C87" t="s">
+        <v>204</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G87" t="s">
+        <v>401</v>
+      </c>
+      <c r="H87" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" t="s">
+        <v>203</v>
+      </c>
+      <c r="C88" t="s">
+        <v>204</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G88" t="s">
+        <v>401</v>
+      </c>
+      <c r="H88" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" t="s">
+        <v>203</v>
+      </c>
+      <c r="C89" t="s">
+        <v>204</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G89" t="s">
+        <v>401</v>
+      </c>
+      <c r="H89" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" t="s">
+        <v>203</v>
+      </c>
+      <c r="C90" t="s">
+        <v>204</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G90" t="s">
+        <v>401</v>
+      </c>
+      <c r="H90" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" t="s">
+        <v>203</v>
+      </c>
+      <c r="C91" t="s">
+        <v>204</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G91" t="s">
+        <v>401</v>
+      </c>
+      <c r="H91" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" t="s">
+        <v>203</v>
+      </c>
+      <c r="C92" t="s">
+        <v>204</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G92" t="s">
+        <v>401</v>
+      </c>
+      <c r="H92" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" t="s">
+        <v>203</v>
+      </c>
+      <c r="C93" t="s">
+        <v>204</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G93" t="s">
+        <v>401</v>
+      </c>
+      <c r="H93" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" t="s">
+        <v>203</v>
+      </c>
+      <c r="C94" t="s">
+        <v>204</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G94" t="s">
+        <v>401</v>
+      </c>
+      <c r="H94" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" t="s">
+        <v>203</v>
+      </c>
+      <c r="C95" t="s">
+        <v>204</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G95" t="s">
+        <v>401</v>
+      </c>
+      <c r="H95" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" t="s">
+        <v>203</v>
+      </c>
+      <c r="C96" t="s">
+        <v>204</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G96" t="s">
+        <v>401</v>
+      </c>
+      <c r="H96" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" t="s">
+        <v>203</v>
+      </c>
+      <c r="C97" t="s">
+        <v>204</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="G97" t="s">
+        <v>401</v>
+      </c>
+      <c r="H97" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" t="s">
+        <v>203</v>
+      </c>
+      <c r="C98" t="s">
+        <v>204</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="G98" t="s">
+        <v>401</v>
+      </c>
+      <c r="H98" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" t="s">
+        <v>203</v>
+      </c>
+      <c r="C99" t="s">
+        <v>204</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G99" t="s">
+        <v>401</v>
+      </c>
+      <c r="H99" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" t="s">
+        <v>203</v>
+      </c>
+      <c r="C100" t="s">
+        <v>204</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G100" t="s">
+        <v>402</v>
+      </c>
+      <c r="H100" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" t="s">
+        <v>203</v>
+      </c>
+      <c r="C101" t="s">
+        <v>204</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G101" t="s">
+        <v>402</v>
+      </c>
+      <c r="H101" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" t="s">
+        <v>203</v>
+      </c>
+      <c r="C102" t="s">
+        <v>204</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G102" t="s">
+        <v>402</v>
+      </c>
+      <c r="H102" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" t="s">
+        <v>203</v>
+      </c>
+      <c r="C103" t="s">
+        <v>204</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G103" t="s">
+        <v>402</v>
+      </c>
+      <c r="H103" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" t="s">
+        <v>203</v>
+      </c>
+      <c r="C104" t="s">
+        <v>204</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G104" t="s">
+        <v>402</v>
+      </c>
+      <c r="H104" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" t="s">
+        <v>203</v>
+      </c>
+      <c r="C105" t="s">
+        <v>204</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G105" t="s">
+        <v>402</v>
+      </c>
+      <c r="H105" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" t="s">
+        <v>203</v>
+      </c>
+      <c r="C106" t="s">
+        <v>204</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="G106" t="s">
+        <v>402</v>
+      </c>
+      <c r="H106" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" t="s">
+        <v>203</v>
+      </c>
+      <c r="C107" t="s">
+        <v>204</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G107" t="s">
+        <v>402</v>
+      </c>
+      <c r="H107" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" t="s">
+        <v>203</v>
+      </c>
+      <c r="C108" t="s">
+        <v>204</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G108" t="s">
+        <v>402</v>
+      </c>
+      <c r="H108" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" t="s">
+        <v>203</v>
+      </c>
+      <c r="C109" t="s">
+        <v>204</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G109" t="s">
+        <v>402</v>
+      </c>
+      <c r="H109" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" t="s">
+        <v>203</v>
+      </c>
+      <c r="C110" t="s">
+        <v>204</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="G110" t="s">
+        <v>402</v>
+      </c>
+      <c r="H110" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" t="s">
+        <v>203</v>
+      </c>
+      <c r="C111" t="s">
+        <v>204</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G111" t="s">
+        <v>402</v>
+      </c>
+      <c r="H111" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" t="s">
+        <v>203</v>
+      </c>
+      <c r="C112" t="s">
+        <v>204</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G112" t="s">
+        <v>402</v>
+      </c>
+      <c r="H112" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" t="s">
+        <v>203</v>
+      </c>
+      <c r="C113" t="s">
+        <v>204</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G113" t="s">
+        <v>402</v>
+      </c>
+      <c r="H113" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" t="s">
+        <v>203</v>
+      </c>
+      <c r="C114" t="s">
+        <v>204</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G114" t="s">
+        <v>402</v>
+      </c>
+      <c r="H114" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" t="s">
+        <v>203</v>
+      </c>
+      <c r="C115" t="s">
+        <v>204</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G115" t="s">
+        <v>402</v>
+      </c>
+      <c r="H115" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" t="s">
+        <v>203</v>
+      </c>
+      <c r="C116" t="s">
+        <v>204</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="G116" t="s">
+        <v>402</v>
+      </c>
+      <c r="H116" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>123</v>
+      </c>
+      <c r="B117" t="s">
+        <v>203</v>
+      </c>
+      <c r="C117" t="s">
+        <v>204</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G117" t="s">
+        <v>402</v>
+      </c>
+      <c r="H117" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" t="s">
+        <v>203</v>
+      </c>
+      <c r="C118" t="s">
+        <v>204</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G118" t="s">
+        <v>402</v>
+      </c>
+      <c r="H118" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" t="s">
+        <v>203</v>
+      </c>
+      <c r="C119" t="s">
+        <v>204</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G119" t="s">
+        <v>402</v>
+      </c>
+      <c r="H119" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>126</v>
+      </c>
+      <c r="B120" t="s">
+        <v>203</v>
+      </c>
+      <c r="C120" t="s">
+        <v>204</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G120" t="s">
+        <v>402</v>
+      </c>
+      <c r="H120" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>127</v>
+      </c>
+      <c r="B121" t="s">
+        <v>203</v>
+      </c>
+      <c r="C121" t="s">
+        <v>204</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G121" t="s">
+        <v>403</v>
+      </c>
+      <c r="H121" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" t="s">
+        <v>203</v>
+      </c>
+      <c r="C122" t="s">
+        <v>204</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G122" t="s">
+        <v>403</v>
+      </c>
+      <c r="H122" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>129</v>
+      </c>
+      <c r="B123" t="s">
+        <v>203</v>
+      </c>
+      <c r="C123" t="s">
+        <v>204</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G123" t="s">
+        <v>403</v>
+      </c>
+      <c r="H123" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" t="s">
+        <v>203</v>
+      </c>
+      <c r="C124" t="s">
+        <v>204</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G124" t="s">
+        <v>403</v>
+      </c>
+      <c r="H124" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>131</v>
+      </c>
+      <c r="B125" t="s">
+        <v>203</v>
+      </c>
+      <c r="C125" t="s">
+        <v>204</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G125" t="s">
+        <v>403</v>
+      </c>
+      <c r="H125" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" t="s">
+        <v>203</v>
+      </c>
+      <c r="C126" t="s">
+        <v>204</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="G126" t="s">
+        <v>403</v>
+      </c>
+      <c r="H126" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" t="s">
+        <v>203</v>
+      </c>
+      <c r="C127" t="s">
+        <v>204</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G127" t="s">
+        <v>403</v>
+      </c>
+      <c r="H127" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" t="s">
+        <v>203</v>
+      </c>
+      <c r="C128" t="s">
+        <v>204</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G128" t="s">
+        <v>403</v>
+      </c>
+      <c r="H128" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" t="s">
+        <v>203</v>
+      </c>
+      <c r="C129" t="s">
+        <v>204</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G129" t="s">
+        <v>403</v>
+      </c>
+      <c r="H129" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
+        <v>136</v>
+      </c>
+      <c r="B130" t="s">
+        <v>203</v>
+      </c>
+      <c r="C130" t="s">
+        <v>204</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G130" t="s">
+        <v>403</v>
+      </c>
+      <c r="H130" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" t="s">
+        <v>137</v>
+      </c>
+      <c r="B131" t="s">
+        <v>203</v>
+      </c>
+      <c r="C131" t="s">
+        <v>204</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G131" t="s">
+        <v>403</v>
+      </c>
+      <c r="H131" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" t="s">
+        <v>138</v>
+      </c>
+      <c r="B132" t="s">
+        <v>203</v>
+      </c>
+      <c r="C132" t="s">
+        <v>204</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G132" t="s">
+        <v>403</v>
+      </c>
+      <c r="H132" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>139</v>
+      </c>
+      <c r="B133" t="s">
+        <v>203</v>
+      </c>
+      <c r="C133" t="s">
+        <v>204</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="G133" t="s">
+        <v>403</v>
+      </c>
+      <c r="H133" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>140</v>
+      </c>
+      <c r="B134" t="s">
+        <v>203</v>
+      </c>
+      <c r="C134" t="s">
+        <v>204</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G134" t="s">
+        <v>403</v>
+      </c>
+      <c r="H134" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" t="s">
+        <v>141</v>
+      </c>
+      <c r="B135" t="s">
+        <v>203</v>
+      </c>
+      <c r="C135" t="s">
+        <v>204</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G135" t="s">
+        <v>403</v>
+      </c>
+      <c r="H135" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>142</v>
+      </c>
+      <c r="B136" t="s">
+        <v>203</v>
+      </c>
+      <c r="C136" t="s">
+        <v>204</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="G136" t="s">
+        <v>403</v>
+      </c>
+      <c r="H136" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="s">
+        <v>143</v>
+      </c>
+      <c r="B137" t="s">
+        <v>203</v>
+      </c>
+      <c r="C137" t="s">
+        <v>204</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="G137" t="s">
+        <v>403</v>
+      </c>
+      <c r="H137" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="s">
+        <v>144</v>
+      </c>
+      <c r="B138" t="s">
+        <v>203</v>
+      </c>
+      <c r="C138" t="s">
+        <v>204</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G138" t="s">
+        <v>403</v>
+      </c>
+      <c r="H138" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="s">
+        <v>145</v>
+      </c>
+      <c r="B139" t="s">
+        <v>203</v>
+      </c>
+      <c r="C139" t="s">
+        <v>204</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="G139" t="s">
+        <v>403</v>
+      </c>
+      <c r="H139" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="s">
+        <v>146</v>
+      </c>
+      <c r="B140" t="s">
+        <v>203</v>
+      </c>
+      <c r="C140" t="s">
+        <v>204</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="G140" t="s">
+        <v>403</v>
+      </c>
+      <c r="H140" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="s">
+        <v>147</v>
+      </c>
+      <c r="B141" t="s">
+        <v>203</v>
+      </c>
+      <c r="C141" t="s">
+        <v>204</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G141" t="s">
+        <v>403</v>
+      </c>
+      <c r="H141" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" t="s">
+        <v>148</v>
+      </c>
+      <c r="B142" t="s">
+        <v>203</v>
+      </c>
+      <c r="C142" t="s">
+        <v>204</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="G142" t="s">
+        <v>403</v>
+      </c>
+      <c r="H142" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" t="s">
         <v>149</v>
       </c>
-      <c r="G71" t="s">
+      <c r="B143" t="s">
+        <v>203</v>
+      </c>
+      <c r="C143" t="s">
+        <v>204</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G143" t="s">
+        <v>403</v>
+      </c>
+      <c r="H143" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" t="s">
         <v>150</v>
       </c>
-      <c r="H71" t="s">
+      <c r="B144" t="s">
+        <v>203</v>
+      </c>
+      <c r="C144" t="s">
+        <v>204</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G144" t="s">
+        <v>403</v>
+      </c>
+      <c r="H144" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" t="s">
         <v>151</v>
+      </c>
+      <c r="B145" t="s">
+        <v>203</v>
+      </c>
+      <c r="C145" t="s">
+        <v>204</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="G145" t="s">
+        <v>403</v>
+      </c>
+      <c r="H145" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" t="s">
+        <v>152</v>
+      </c>
+      <c r="B146" t="s">
+        <v>203</v>
+      </c>
+      <c r="C146" t="s">
+        <v>204</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="G146" t="s">
+        <v>403</v>
+      </c>
+      <c r="H146" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" t="s">
+        <v>153</v>
+      </c>
+      <c r="B147" t="s">
+        <v>203</v>
+      </c>
+      <c r="C147" t="s">
+        <v>204</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="G147" t="s">
+        <v>403</v>
+      </c>
+      <c r="H147" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>154</v>
+      </c>
+      <c r="B148" t="s">
+        <v>203</v>
+      </c>
+      <c r="C148" t="s">
+        <v>204</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="G148" t="s">
+        <v>403</v>
+      </c>
+      <c r="H148" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" t="s">
+        <v>155</v>
+      </c>
+      <c r="B149" t="s">
+        <v>203</v>
+      </c>
+      <c r="C149" t="s">
+        <v>204</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="G149" t="s">
+        <v>403</v>
+      </c>
+      <c r="H149" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" t="s">
+        <v>156</v>
+      </c>
+      <c r="B150" t="s">
+        <v>203</v>
+      </c>
+      <c r="C150" t="s">
+        <v>204</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G150" t="s">
+        <v>403</v>
+      </c>
+      <c r="H150" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" t="s">
+        <v>157</v>
+      </c>
+      <c r="B151" t="s">
+        <v>203</v>
+      </c>
+      <c r="C151" t="s">
+        <v>204</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G151" t="s">
+        <v>404</v>
+      </c>
+      <c r="H151" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" t="s">
+        <v>158</v>
+      </c>
+      <c r="B152" t="s">
+        <v>203</v>
+      </c>
+      <c r="C152" t="s">
+        <v>204</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G152" t="s">
+        <v>404</v>
+      </c>
+      <c r="H152" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" t="s">
+        <v>159</v>
+      </c>
+      <c r="B153" t="s">
+        <v>203</v>
+      </c>
+      <c r="C153" t="s">
+        <v>204</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="G153" t="s">
+        <v>404</v>
+      </c>
+      <c r="H153" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" t="s">
+        <v>160</v>
+      </c>
+      <c r="B154" t="s">
+        <v>203</v>
+      </c>
+      <c r="C154" t="s">
+        <v>204</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G154" t="s">
+        <v>404</v>
+      </c>
+      <c r="H154" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" t="s">
+        <v>161</v>
+      </c>
+      <c r="B155" t="s">
+        <v>203</v>
+      </c>
+      <c r="C155" t="s">
+        <v>204</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="G155" t="s">
+        <v>404</v>
+      </c>
+      <c r="H155" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" t="s">
+        <v>162</v>
+      </c>
+      <c r="B156" t="s">
+        <v>203</v>
+      </c>
+      <c r="C156" t="s">
+        <v>204</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G156" t="s">
+        <v>404</v>
+      </c>
+      <c r="H156" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" t="s">
+        <v>163</v>
+      </c>
+      <c r="B157" t="s">
+        <v>203</v>
+      </c>
+      <c r="C157" t="s">
+        <v>204</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G157" t="s">
+        <v>404</v>
+      </c>
+      <c r="H157" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" t="s">
+        <v>164</v>
+      </c>
+      <c r="B158" t="s">
+        <v>203</v>
+      </c>
+      <c r="C158" t="s">
+        <v>204</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G158" t="s">
+        <v>404</v>
+      </c>
+      <c r="H158" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" t="s">
+        <v>165</v>
+      </c>
+      <c r="B159" t="s">
+        <v>203</v>
+      </c>
+      <c r="C159" t="s">
+        <v>204</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G159" t="s">
+        <v>404</v>
+      </c>
+      <c r="H159" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" t="s">
+        <v>166</v>
+      </c>
+      <c r="B160" t="s">
+        <v>203</v>
+      </c>
+      <c r="C160" t="s">
+        <v>204</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G160" t="s">
+        <v>404</v>
+      </c>
+      <c r="H160" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" t="s">
+        <v>167</v>
+      </c>
+      <c r="B161" t="s">
+        <v>203</v>
+      </c>
+      <c r="C161" t="s">
+        <v>204</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G161" t="s">
+        <v>404</v>
+      </c>
+      <c r="H161" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" t="s">
+        <v>168</v>
+      </c>
+      <c r="B162" t="s">
+        <v>203</v>
+      </c>
+      <c r="C162" t="s">
+        <v>204</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G162" t="s">
+        <v>404</v>
+      </c>
+      <c r="H162" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" t="s">
+        <v>169</v>
+      </c>
+      <c r="B163" t="s">
+        <v>203</v>
+      </c>
+      <c r="C163" t="s">
+        <v>204</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="G163" t="s">
+        <v>404</v>
+      </c>
+      <c r="H163" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" t="s">
+        <v>170</v>
+      </c>
+      <c r="B164" t="s">
+        <v>203</v>
+      </c>
+      <c r="C164" t="s">
+        <v>204</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G164" t="s">
+        <v>404</v>
+      </c>
+      <c r="H164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" t="s">
+        <v>171</v>
+      </c>
+      <c r="B165" t="s">
+        <v>203</v>
+      </c>
+      <c r="C165" t="s">
+        <v>204</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="G165" t="s">
+        <v>404</v>
+      </c>
+      <c r="H165" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" t="s">
+        <v>172</v>
+      </c>
+      <c r="B166" t="s">
+        <v>203</v>
+      </c>
+      <c r="C166" t="s">
+        <v>204</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G166" t="s">
+        <v>404</v>
+      </c>
+      <c r="H166" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" t="s">
+        <v>173</v>
+      </c>
+      <c r="B167" t="s">
+        <v>203</v>
+      </c>
+      <c r="C167" t="s">
+        <v>204</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G167" t="s">
+        <v>405</v>
+      </c>
+      <c r="H167" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" t="s">
+        <v>174</v>
+      </c>
+      <c r="B168" t="s">
+        <v>203</v>
+      </c>
+      <c r="C168" t="s">
+        <v>204</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G168" t="s">
+        <v>405</v>
+      </c>
+      <c r="H168" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" t="s">
+        <v>175</v>
+      </c>
+      <c r="B169" t="s">
+        <v>203</v>
+      </c>
+      <c r="C169" t="s">
+        <v>204</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="G169" t="s">
+        <v>405</v>
+      </c>
+      <c r="H169" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" t="s">
+        <v>176</v>
+      </c>
+      <c r="B170" t="s">
+        <v>203</v>
+      </c>
+      <c r="C170" t="s">
+        <v>204</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="G170" t="s">
+        <v>405</v>
+      </c>
+      <c r="H170" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" t="s">
+        <v>177</v>
+      </c>
+      <c r="B171" t="s">
+        <v>203</v>
+      </c>
+      <c r="C171" t="s">
+        <v>204</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G171" t="s">
+        <v>405</v>
+      </c>
+      <c r="H171" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" t="s">
+        <v>178</v>
+      </c>
+      <c r="B172" t="s">
+        <v>203</v>
+      </c>
+      <c r="C172" t="s">
+        <v>204</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G172" t="s">
+        <v>405</v>
+      </c>
+      <c r="H172" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" t="s">
+        <v>179</v>
+      </c>
+      <c r="B173" t="s">
+        <v>203</v>
+      </c>
+      <c r="C173" t="s">
+        <v>204</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="G173" t="s">
+        <v>405</v>
+      </c>
+      <c r="H173" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" t="s">
+        <v>180</v>
+      </c>
+      <c r="B174" t="s">
+        <v>203</v>
+      </c>
+      <c r="C174" t="s">
+        <v>204</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G174" t="s">
+        <v>405</v>
+      </c>
+      <c r="H174" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" t="s">
+        <v>181</v>
+      </c>
+      <c r="B175" t="s">
+        <v>203</v>
+      </c>
+      <c r="C175" t="s">
+        <v>204</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="G175" t="s">
+        <v>405</v>
+      </c>
+      <c r="H175" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" t="s">
+        <v>182</v>
+      </c>
+      <c r="B176" t="s">
+        <v>203</v>
+      </c>
+      <c r="C176" t="s">
+        <v>204</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="G176" t="s">
+        <v>405</v>
+      </c>
+      <c r="H176" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" t="s">
+        <v>183</v>
+      </c>
+      <c r="B177" t="s">
+        <v>203</v>
+      </c>
+      <c r="C177" t="s">
+        <v>204</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G177" t="s">
+        <v>405</v>
+      </c>
+      <c r="H177" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" t="s">
+        <v>184</v>
+      </c>
+      <c r="B178" t="s">
+        <v>203</v>
+      </c>
+      <c r="C178" t="s">
+        <v>204</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G178" t="s">
+        <v>405</v>
+      </c>
+      <c r="H178" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="A179" t="s">
+        <v>185</v>
+      </c>
+      <c r="B179" t="s">
+        <v>203</v>
+      </c>
+      <c r="C179" t="s">
+        <v>204</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G179" t="s">
+        <v>405</v>
+      </c>
+      <c r="H179" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" t="s">
+        <v>186</v>
+      </c>
+      <c r="B180" t="s">
+        <v>203</v>
+      </c>
+      <c r="C180" t="s">
+        <v>204</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G180" t="s">
+        <v>405</v>
+      </c>
+      <c r="H180" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181" t="s">
+        <v>187</v>
+      </c>
+      <c r="B181" t="s">
+        <v>203</v>
+      </c>
+      <c r="C181" t="s">
+        <v>204</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="G181" t="s">
+        <v>405</v>
+      </c>
+      <c r="H181" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" t="s">
+        <v>188</v>
+      </c>
+      <c r="B182" t="s">
+        <v>203</v>
+      </c>
+      <c r="C182" t="s">
+        <v>204</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="G182" t="s">
+        <v>405</v>
+      </c>
+      <c r="H182" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" t="s">
+        <v>189</v>
+      </c>
+      <c r="B183" t="s">
+        <v>203</v>
+      </c>
+      <c r="C183" t="s">
+        <v>204</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="G183" t="s">
+        <v>405</v>
+      </c>
+      <c r="H183" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" t="s">
+        <v>190</v>
+      </c>
+      <c r="B184" t="s">
+        <v>203</v>
+      </c>
+      <c r="C184" t="s">
+        <v>204</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="G184" t="s">
+        <v>405</v>
+      </c>
+      <c r="H184" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" t="s">
+        <v>191</v>
+      </c>
+      <c r="B185" t="s">
+        <v>203</v>
+      </c>
+      <c r="C185" t="s">
+        <v>204</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="G185" t="s">
+        <v>405</v>
+      </c>
+      <c r="H185" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" t="s">
+        <v>192</v>
+      </c>
+      <c r="B186" t="s">
+        <v>203</v>
+      </c>
+      <c r="C186" t="s">
+        <v>204</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="G186" t="s">
+        <v>405</v>
+      </c>
+      <c r="H186" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" t="s">
+        <v>193</v>
+      </c>
+      <c r="B187" t="s">
+        <v>203</v>
+      </c>
+      <c r="C187" t="s">
+        <v>204</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G187" t="s">
+        <v>405</v>
+      </c>
+      <c r="H187" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" t="s">
+        <v>194</v>
+      </c>
+      <c r="B188" t="s">
+        <v>203</v>
+      </c>
+      <c r="C188" t="s">
+        <v>204</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="G188" t="s">
+        <v>405</v>
+      </c>
+      <c r="H188" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189" t="s">
+        <v>195</v>
+      </c>
+      <c r="B189" t="s">
+        <v>203</v>
+      </c>
+      <c r="C189" t="s">
+        <v>204</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G189" t="s">
+        <v>405</v>
+      </c>
+      <c r="H189" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" t="s">
+        <v>196</v>
+      </c>
+      <c r="B190" t="s">
+        <v>203</v>
+      </c>
+      <c r="C190" t="s">
+        <v>204</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="G190" t="s">
+        <v>405</v>
+      </c>
+      <c r="H190" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191" t="s">
+        <v>197</v>
+      </c>
+      <c r="B191" t="s">
+        <v>203</v>
+      </c>
+      <c r="C191" t="s">
+        <v>204</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G191" t="s">
+        <v>405</v>
+      </c>
+      <c r="H191" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" t="s">
+        <v>198</v>
+      </c>
+      <c r="B192" t="s">
+        <v>203</v>
+      </c>
+      <c r="C192" t="s">
+        <v>204</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="G192" t="s">
+        <v>405</v>
+      </c>
+      <c r="H192" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" t="s">
+        <v>199</v>
+      </c>
+      <c r="B193" t="s">
+        <v>203</v>
+      </c>
+      <c r="C193" t="s">
+        <v>204</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="G193" t="s">
+        <v>405</v>
+      </c>
+      <c r="H193" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194" t="s">
+        <v>200</v>
+      </c>
+      <c r="B194" t="s">
+        <v>203</v>
+      </c>
+      <c r="C194" t="s">
+        <v>204</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="G194" t="s">
+        <v>405</v>
+      </c>
+      <c r="H194" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195" t="s">
+        <v>201</v>
+      </c>
+      <c r="B195" t="s">
+        <v>203</v>
+      </c>
+      <c r="C195" t="s">
+        <v>204</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="G195" t="s">
+        <v>405</v>
+      </c>
+      <c r="H195" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" t="s">
+        <v>202</v>
+      </c>
+      <c r="B196" t="s">
+        <v>203</v>
+      </c>
+      <c r="C196" t="s">
+        <v>204</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G196" t="s">
+        <v>405</v>
+      </c>
+      <c r="H196" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -2315,6 +5580,131 @@
     <hyperlink ref="F69" r:id="rId68"/>
     <hyperlink ref="F70" r:id="rId69"/>
     <hyperlink ref="F71" r:id="rId70"/>
+    <hyperlink ref="F72" r:id="rId71"/>
+    <hyperlink ref="F73" r:id="rId72"/>
+    <hyperlink ref="F74" r:id="rId73"/>
+    <hyperlink ref="F75" r:id="rId74"/>
+    <hyperlink ref="F76" r:id="rId75"/>
+    <hyperlink ref="F77" r:id="rId76"/>
+    <hyperlink ref="F78" r:id="rId77"/>
+    <hyperlink ref="F79" r:id="rId78"/>
+    <hyperlink ref="F80" r:id="rId79"/>
+    <hyperlink ref="F81" r:id="rId80"/>
+    <hyperlink ref="F82" r:id="rId81"/>
+    <hyperlink ref="F83" r:id="rId82"/>
+    <hyperlink ref="F84" r:id="rId83"/>
+    <hyperlink ref="F85" r:id="rId84"/>
+    <hyperlink ref="F86" r:id="rId85"/>
+    <hyperlink ref="F87" r:id="rId86"/>
+    <hyperlink ref="F88" r:id="rId87"/>
+    <hyperlink ref="F89" r:id="rId88"/>
+    <hyperlink ref="F90" r:id="rId89"/>
+    <hyperlink ref="F91" r:id="rId90"/>
+    <hyperlink ref="F92" r:id="rId91"/>
+    <hyperlink ref="F93" r:id="rId92"/>
+    <hyperlink ref="F94" r:id="rId93"/>
+    <hyperlink ref="F95" r:id="rId94"/>
+    <hyperlink ref="F96" r:id="rId95"/>
+    <hyperlink ref="F97" r:id="rId96"/>
+    <hyperlink ref="F98" r:id="rId97"/>
+    <hyperlink ref="F99" r:id="rId98"/>
+    <hyperlink ref="F100" r:id="rId99"/>
+    <hyperlink ref="F101" r:id="rId100"/>
+    <hyperlink ref="F102" r:id="rId101"/>
+    <hyperlink ref="F103" r:id="rId102"/>
+    <hyperlink ref="F104" r:id="rId103"/>
+    <hyperlink ref="F105" r:id="rId104"/>
+    <hyperlink ref="F106" r:id="rId105"/>
+    <hyperlink ref="F107" r:id="rId106"/>
+    <hyperlink ref="F108" r:id="rId107"/>
+    <hyperlink ref="F109" r:id="rId108"/>
+    <hyperlink ref="F110" r:id="rId109"/>
+    <hyperlink ref="F111" r:id="rId110"/>
+    <hyperlink ref="F112" r:id="rId111"/>
+    <hyperlink ref="F113" r:id="rId112"/>
+    <hyperlink ref="F114" r:id="rId113"/>
+    <hyperlink ref="F115" r:id="rId114"/>
+    <hyperlink ref="F116" r:id="rId115"/>
+    <hyperlink ref="F117" r:id="rId116"/>
+    <hyperlink ref="F118" r:id="rId117"/>
+    <hyperlink ref="F119" r:id="rId118"/>
+    <hyperlink ref="F120" r:id="rId119"/>
+    <hyperlink ref="F121" r:id="rId120"/>
+    <hyperlink ref="F122" r:id="rId121"/>
+    <hyperlink ref="F123" r:id="rId122"/>
+    <hyperlink ref="F124" r:id="rId123"/>
+    <hyperlink ref="F125" r:id="rId124"/>
+    <hyperlink ref="F126" r:id="rId125"/>
+    <hyperlink ref="F127" r:id="rId126"/>
+    <hyperlink ref="F128" r:id="rId127"/>
+    <hyperlink ref="F129" r:id="rId128"/>
+    <hyperlink ref="F130" r:id="rId129"/>
+    <hyperlink ref="F131" r:id="rId130"/>
+    <hyperlink ref="F132" r:id="rId131"/>
+    <hyperlink ref="F133" r:id="rId132"/>
+    <hyperlink ref="F134" r:id="rId133"/>
+    <hyperlink ref="F135" r:id="rId134"/>
+    <hyperlink ref="F136" r:id="rId135"/>
+    <hyperlink ref="F137" r:id="rId136"/>
+    <hyperlink ref="F138" r:id="rId137"/>
+    <hyperlink ref="F139" r:id="rId138"/>
+    <hyperlink ref="F140" r:id="rId139"/>
+    <hyperlink ref="F141" r:id="rId140"/>
+    <hyperlink ref="F142" r:id="rId141"/>
+    <hyperlink ref="F143" r:id="rId142"/>
+    <hyperlink ref="F144" r:id="rId143"/>
+    <hyperlink ref="F145" r:id="rId144"/>
+    <hyperlink ref="F146" r:id="rId145"/>
+    <hyperlink ref="F147" r:id="rId146"/>
+    <hyperlink ref="F148" r:id="rId147"/>
+    <hyperlink ref="F149" r:id="rId148"/>
+    <hyperlink ref="F150" r:id="rId149"/>
+    <hyperlink ref="F151" r:id="rId150"/>
+    <hyperlink ref="F152" r:id="rId151"/>
+    <hyperlink ref="F153" r:id="rId152"/>
+    <hyperlink ref="F154" r:id="rId153"/>
+    <hyperlink ref="F155" r:id="rId154"/>
+    <hyperlink ref="F156" r:id="rId155"/>
+    <hyperlink ref="F157" r:id="rId156"/>
+    <hyperlink ref="F158" r:id="rId157"/>
+    <hyperlink ref="F159" r:id="rId158"/>
+    <hyperlink ref="F160" r:id="rId159"/>
+    <hyperlink ref="F161" r:id="rId160"/>
+    <hyperlink ref="F162" r:id="rId161"/>
+    <hyperlink ref="F163" r:id="rId162"/>
+    <hyperlink ref="F164" r:id="rId163"/>
+    <hyperlink ref="F165" r:id="rId164"/>
+    <hyperlink ref="F166" r:id="rId165"/>
+    <hyperlink ref="F167" r:id="rId166"/>
+    <hyperlink ref="F168" r:id="rId167"/>
+    <hyperlink ref="F169" r:id="rId168"/>
+    <hyperlink ref="F170" r:id="rId169"/>
+    <hyperlink ref="F171" r:id="rId170"/>
+    <hyperlink ref="F172" r:id="rId171"/>
+    <hyperlink ref="F173" r:id="rId172"/>
+    <hyperlink ref="F174" r:id="rId173"/>
+    <hyperlink ref="F175" r:id="rId174"/>
+    <hyperlink ref="F176" r:id="rId175"/>
+    <hyperlink ref="F177" r:id="rId176"/>
+    <hyperlink ref="F178" r:id="rId177"/>
+    <hyperlink ref="F179" r:id="rId178"/>
+    <hyperlink ref="F180" r:id="rId179"/>
+    <hyperlink ref="F181" r:id="rId180"/>
+    <hyperlink ref="F182" r:id="rId181"/>
+    <hyperlink ref="F183" r:id="rId182"/>
+    <hyperlink ref="F184" r:id="rId183"/>
+    <hyperlink ref="F185" r:id="rId184"/>
+    <hyperlink ref="F186" r:id="rId185"/>
+    <hyperlink ref="F187" r:id="rId186"/>
+    <hyperlink ref="F188" r:id="rId187"/>
+    <hyperlink ref="F189" r:id="rId188"/>
+    <hyperlink ref="F190" r:id="rId189"/>
+    <hyperlink ref="F191" r:id="rId190"/>
+    <hyperlink ref="F192" r:id="rId191"/>
+    <hyperlink ref="F193" r:id="rId192"/>
+    <hyperlink ref="F194" r:id="rId193"/>
+    <hyperlink ref="F195" r:id="rId194"/>
+    <hyperlink ref="F196" r:id="rId195"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Senior_Care.xlsx
+++ b/results/scraped_Cape_Town_Senior_Care.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="521">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -187,66 +187,6 @@
     <t>frailadjective - Definition, pictures, pronunciation and usage notes ...</t>
   </si>
   <si>
-    <t>Enroll in Chase Online Banking | Chase</t>
-  </si>
-  <si>
-    <t>Credit Card, Mortgage, Banking, Auto | Chase Online | Chase.com</t>
-  </si>
-  <si>
-    <t>Chase Account login</t>
-  </si>
-  <si>
-    <t>Credit Card Resources, Login &amp; Customer Service | Chase</t>
-  </si>
-  <si>
-    <t>Compare Checking Accounts &amp; Apply Online | Chase</t>
-  </si>
-  <si>
-    <t>Ultimate Rewards | Credit Cards | Chase.com</t>
-  </si>
-  <si>
-    <t>Online Payments | Credit Card | Chase.com</t>
-  </si>
-  <si>
-    <t>Online Bill Pay | Personal Banking | Chase</t>
-  </si>
-  <si>
-    <t>Chase MyMortgage: Your Mortgage Online Portal | Home Lending</t>
-  </si>
-  <si>
-    <t>Amazon Account Activity | Credit Card | Chase</t>
-  </si>
-  <si>
-    <t>Meal Planning Made Simple - eMeals</t>
-  </si>
-  <si>
-    <t>100 of the EasiestMealsWe’ve Ever Made - Allrecipes</t>
-  </si>
-  <si>
-    <t>67Easy Dinner IdeasWe Love -Taste of Home</t>
-  </si>
-  <si>
-    <t>EATMeals| Get 50 FreeMealsAt Sign Up - GourmetMealsTo Your …</t>
-  </si>
-  <si>
-    <t>104 Quick Dinner Ideas in 30 Minutes or Less | Food Network</t>
-  </si>
-  <si>
-    <t>92 Dinner Ideas You Can Make in a Flash |Taste of Home</t>
-  </si>
-  <si>
-    <t>Nutritious, Home-DeliveredMeals| Mom'sMeals</t>
-  </si>
-  <si>
-    <t>52Easy Dinner Recipes&amp; Ideas | Food Network</t>
-  </si>
-  <si>
-    <t>100Easy DinnerRecipes for Busy Weeknights - The Pioneer Woman</t>
-  </si>
-  <si>
-    <t>FuelMeals| Custom Meal Prep | Meal Prep at Your Doorstep</t>
-  </si>
-  <si>
     <t>Contact Us - Microsoft Support</t>
   </si>
   <si>
@@ -277,352 +217,583 @@
     <t>Sign in to Microsoft Forms</t>
   </si>
   <si>
-    <t>Salt Lake City Public Library system</t>
-  </si>
-  <si>
-    <t>Visit The LIBRARY STORE - services.slcpl.org</t>
-  </si>
-  <si>
-    <t>Library Card Application - Salt Lake City Public Library</t>
-  </si>
-  <si>
-    <t>Salt Lake City Public Library</t>
-  </si>
-  <si>
-    <t>Shops at Library Square - Salt Lake City Public Library</t>
-  </si>
-  <si>
-    <t>Utah's Online Library</t>
-  </si>
-  <si>
-    <t>Sign In to Pay Your Bill OR See if You Pre-Qualify for a Credit Card</t>
-  </si>
-  <si>
-    <t>Pay Bill FAQs | Credit One Bank</t>
-  </si>
-  <si>
-    <t>Credit One Bank</t>
-  </si>
-  <si>
-    <t>Resend Activation Email | Credit One Bank</t>
-  </si>
-  <si>
-    <t>Benefits - careers.creditonebank.com</t>
-  </si>
-  <si>
-    <t>Job Search Results - Credit One Bank</t>
-  </si>
-  <si>
-    <t>craigslist:san diegojobs, apartments, for sale, services ...</t>
-  </si>
-  <si>
-    <t>san diegofor sale -craigslist</t>
-  </si>
-  <si>
-    <t>craigslist| california</t>
-  </si>
-  <si>
-    <t>craigslist| united states</t>
-  </si>
-  <si>
-    <t>Buy and Sell inSan Diego, California |FacebookMarketplace</t>
-  </si>
-  <si>
-    <t>craigslistsitemap forsan diego</t>
-  </si>
-  <si>
-    <t>San Diego Craigslist-Facebook</t>
-  </si>
-  <si>
-    <t>Sign in - account.microsoft.com</t>
-  </si>
-  <si>
-    <t>NewJobPaperwork 101: IDs,Formsand Employer Requirements</t>
-  </si>
-  <si>
-    <t>I-9IDRequirements: AcceptedForms of IDList (2026)</t>
-  </si>
-  <si>
-    <t>FormI-9 Acceptable Documents -USCIS</t>
-  </si>
-  <si>
-    <t>Do You NeedanID to Get a Job: Acceptable Documents</t>
-  </si>
-  <si>
-    <t>2Forms of ID: Complete Guide to AcceptableIdentificationin ...</t>
-  </si>
-  <si>
-    <t>What counts as a validIDfora job? - LegalKnowledgeBase.com</t>
-  </si>
-  <si>
-    <t>Do You NeedanID to Get a Job? EmploymentIdentification...</t>
-  </si>
-  <si>
-    <t>Do You NeedanID to Get a Job- doors4jobs</t>
-  </si>
-  <si>
-    <t>What Proofof Identification Do You Needfora Job? - Work</t>
-  </si>
-  <si>
-    <t>Do You NeedanIDfora Job? The Required Documents - CLIMB</t>
-  </si>
-  <si>
-    <t>Tinnitus - Symptoms and causes - Mayo Clinic</t>
-  </si>
-  <si>
-    <t>Tinnitus - Diagnosis and treatment - Mayo Clinic</t>
-  </si>
-  <si>
-    <t>Mayo Clinic Patient Portal</t>
-  </si>
-  <si>
-    <t>Pulsatile tinnitus - has anyone found helpful solutions?</t>
-  </si>
-  <si>
-    <t>Mayo Clinic Q and A: Understanding tinnitus</t>
-  </si>
-  <si>
-    <t>What natural product can quiet my Tinnitus - Mayo Clinic Connect</t>
-  </si>
-  <si>
-    <t>Tinnitus: Ways to Reduce the Irritation - Mayo Clinic News Network</t>
-  </si>
-  <si>
-    <t>Home - Mayo Clinic Press</t>
-  </si>
-  <si>
-    <t>What Causes Ringing in the Ears? - Mayo Clinic Press</t>
-  </si>
-  <si>
-    <t>Primary Care in Rochester and Kasson - Mayo Clinic Health System</t>
-  </si>
-  <si>
-    <t>Subway, 6910 Fayetteville Rd, Durham, NC - Restaurant inspection ...</t>
-  </si>
-  <si>
-    <t>83-Year-Old Air Force Veteran Dies After Illegal Alien Shoves Him …</t>
-  </si>
-  <si>
-    <t>Abandoned Subway (Rochester, Irondequoit, Sodus: living in, cost, …</t>
-  </si>
-  <si>
-    <t>What are some movies that feature the L.A. subway? (construction, …</t>
-  </si>
-  <si>
-    <t>Subway locations in Lynnwood, WA - City-Data.com</t>
-  </si>
-  <si>
-    <t>SUBWAY #34195, 955 Catalina Blvd, San Diego, CA 92106</t>
-  </si>
-  <si>
-    <t>3x12 vs 3x6 Subway tile backsplash (granite countertops, stove, color ...</t>
-  </si>
-  <si>
-    <t>Subway balance questions (living in, bus, safest) - New York City</t>
-  </si>
-  <si>
-    <t>Just Posted Vid on Montreal Metro (Subway). Compare to NYC …</t>
-  </si>
-  <si>
-    <t>Subway #11394, 6736 Aloma Avenue, Winter Park, FL - Restaurant ...</t>
-  </si>
-  <si>
-    <t>Reddit - Dive into anything</t>
-  </si>
-  <si>
-    <t>r/GTA6 - Grand Theft Auto VI's Official Reddit Community!</t>
-  </si>
-  <si>
-    <t>Приложение «Instagram» — App Store</t>
-  </si>
-  <si>
-    <t>‎Facebook App - App Store</t>
-  </si>
-  <si>
-    <t>‎Messages App - App Store</t>
-  </si>
-  <si>
-    <t>TopCharacterTropes - Reddit</t>
-  </si>
-  <si>
-    <t>‎Instagram App - App Store</t>
-  </si>
-  <si>
-    <t>‎App Instagram - App Store</t>
-  </si>
-  <si>
-    <t>‎Instagram‑App – App Store</t>
-  </si>
-  <si>
-    <t>Instagram》App - App Store</t>
-  </si>
-  <si>
-    <t>TrackingYour Shipment or Packages |FedEx</t>
-  </si>
-  <si>
-    <t>Track&amp; Ship Online or Find Nearby Locations |FedEx</t>
-  </si>
-  <si>
-    <t>TrackYour Shipment |FedExFreight</t>
-  </si>
-  <si>
-    <t>PackageTracking- CourierTracking|FedExCanada</t>
-  </si>
-  <si>
-    <t>Advanced ShipmentTracking|FedEx</t>
-  </si>
-  <si>
-    <t>FedExAdvanced ShipmentTracking</t>
-  </si>
-  <si>
-    <t>TrackingYour Shipment or Packages |FedExUnited Kingdom</t>
-  </si>
-  <si>
-    <t>FedEx tracking-Trackyour package viatrackingnumber</t>
-  </si>
-  <si>
-    <t>FedExExpress</t>
-  </si>
-  <si>
-    <t>Where is my package? -FedEx</t>
-  </si>
-  <si>
-    <t>Is FlexJobs worth it? : r/remotework - Reddit</t>
-  </si>
-  <si>
-    <t>What job sites is everyone using? : r/jobs - Reddit</t>
-  </si>
-  <si>
-    <t>Is the phrase "it's just a matter of semantics" meaningless?</t>
-  </si>
-  <si>
-    <t>Usage of "Indeed" in "Thank you very much indeed"</t>
-  </si>
-  <si>
-    <t>Is there anything better than Indeed for job listings? - Reddit</t>
-  </si>
-  <si>
-    <t>Does anyone actually get jobs through LinkedIn and Indeed?</t>
-  </si>
-  <si>
-    <t>Having little success with indeed.com are there any other ... - Reddit</t>
-  </si>
-  <si>
-    <t>LinkedIn vs. indeed : r/recruitinghell - Reddit</t>
-  </si>
-  <si>
-    <t>Do you guys ever take company reviews seriously on indeed.com?</t>
-  </si>
-  <si>
-    <t>Best job board for hiring locals? Not Indeed. : r/Calgary - Reddit</t>
-  </si>
-  <si>
-    <t>unsolicited "Your new account on XNXX GOLD" email - Reddit</t>
-  </si>
-  <si>
-    <t>datingoverfifty - Reddit</t>
-  </si>
-  <si>
-    <t>Legal Teens - Reddit</t>
-  </si>
-  <si>
-    <t>TikTok - humanity in all forms - Reddit</t>
-  </si>
-  <si>
-    <t>verysmalltits - Reddit</t>
-  </si>
-  <si>
-    <t>Iranian discussion forum to discuss all things Iran - Reddit</t>
-  </si>
-  <si>
-    <t>WhatBug Looks Like An AntButFliesAnd Gray?</t>
-  </si>
-  <si>
-    <t>18Bugs That Look LikeAnts (Pictures and Identification)</t>
-  </si>
-  <si>
-    <t>BugFinder-Insect Identification</t>
-  </si>
-  <si>
-    <t>Insects That Look LikeFlying Ants: Identification, Causes, and Control</t>
-  </si>
-  <si>
-    <t>FlyingInsects That Look LikeAnts – A Gardener’S Guide</t>
-  </si>
-  <si>
-    <t>Antlion-Wikipedia</t>
-  </si>
-  <si>
-    <t>WhatBugIs This? Free AIBugIdentifier by Photo</t>
-  </si>
-  <si>
-    <t>What Are TheInsects That Look LikeFlying Ants?</t>
-  </si>
-  <si>
-    <t>Insect That Looks Like An AntWith Wings: Identifying Friend Vs. Foe</t>
-  </si>
-  <si>
-    <t>How to IdentifyCommonFlying Insects(and Get Rid ofFlies... -wikiHow</t>
-  </si>
-  <si>
-    <t>Why isKendamil not on Amazon? : r/FormulaFeeders -Reddit</t>
-  </si>
-  <si>
-    <t>Amazon.com:KendamilBaby Formula</t>
-  </si>
-  <si>
-    <t>Amazon.com:KendamilCereal</t>
-  </si>
-  <si>
-    <t>Why IsKendamilFormula Out Of Stock? | Urgent Supply Breakdown</t>
-  </si>
-  <si>
-    <t>KendamilOrganic Infant Formula, Milk-Based Powder (Cow Milk ...</t>
-  </si>
-  <si>
-    <t>Goat Stock Update –KendamilUSA</t>
-  </si>
-  <si>
-    <t>Kendamil- Walmart.com</t>
-  </si>
-  <si>
-    <t>European Organic Baby Formula | Infant Formula |Kendamil</t>
-  </si>
-  <si>
-    <t>KendamilOrganic Infant Formula Powder - 28.2oz - Target</t>
-  </si>
-  <si>
-    <t>Where to BuyKendamilFormula in the USA | EuromallUSA</t>
-  </si>
-  <si>
-    <t>RecordedMarriageLicenses</t>
-  </si>
-  <si>
-    <t>Marriage Records-Georgia Department of Public Health</t>
-  </si>
-  <si>
-    <t>www.georgiaprobaterecords.com</t>
-  </si>
-  <si>
-    <t>SEARCHOFMARRIAGEREQUESTFORM3913</t>
-  </si>
-  <si>
-    <t>Georgia MarriageLicenseSearch:Records&amp; Lookup</t>
-  </si>
-  <si>
-    <t>Georgia Marriage Records-SearchLicenseRecords</t>
-  </si>
-  <si>
-    <t>ProbateCourt Dougherty County,GA</t>
-  </si>
-  <si>
-    <t>ProbateCourt Information System –GeorgiaCourts</t>
-  </si>
-  <si>
-    <t>RecordsDivision | Fulton CountyProbateCourt,GA</t>
-  </si>
-  <si>
-    <t>MarriageLicenses andRecords| Thomas County Board of …</t>
+    <t>FullSizeBed- Ashley</t>
+  </si>
+  <si>
+    <t>FullSizedBedFrame - Wayfair</t>
+  </si>
+  <si>
+    <t>Full Beds- Macy's</t>
+  </si>
+  <si>
+    <t>Full Beds-FullSizeBedFrames - IKEA</t>
+  </si>
+  <si>
+    <t>FULL BEDS&amp;BEDFRAMES -The Home Depot</t>
+  </si>
+  <si>
+    <t>Double &amp;FullSizeBeds| DoubleBedFurniture &amp;FullSizeBedFrame</t>
+  </si>
+  <si>
+    <t>Amazon.com:Full Beds</t>
+  </si>
+  <si>
+    <t>Full Beds- Ashley</t>
+  </si>
+  <si>
+    <t>Full beds- IKEA</t>
+  </si>
+  <si>
+    <t>Amazon.com:FullSizeBed</t>
+  </si>
+  <si>
+    <t>2026 PaydaysforCalPERSRetirees and Beneficiaries</t>
+  </si>
+  <si>
+    <t>Retirement Checks&amp;Paydays|CalPERS</t>
+  </si>
+  <si>
+    <t>2026Retirement CheckPaydays-CalPERSPERSpective</t>
+  </si>
+  <si>
+    <t>2026State of CaliforniaPay Days- cajobblog.com</t>
+  </si>
+  <si>
+    <t>OfficialCalPERSRetirement Pay Dates for 2025 and2026</t>
+  </si>
+  <si>
+    <t>What Retirees Need to Knowfor 2026-CalPERSPERSpective</t>
+  </si>
+  <si>
+    <t>CalSTRS Pay Dates Calendar</t>
+  </si>
+  <si>
+    <t>Japanese Momポルノ動画 - EPORNER</t>
+  </si>
+  <si>
+    <t>FreeJapanese MomPorn Videos |xHamster</t>
+  </si>
+  <si>
+    <t>GenreMOTHER|JapaneseAdult Video | JAVIDEO</t>
+  </si>
+  <si>
+    <t>Japanese MotherPorn -Japanese MotherIn Law &amp; Mother In LawJapanese...</t>
+  </si>
+  <si>
+    <t>JAPANESE MOMPORN @ HD Hole</t>
+  </si>
+  <si>
+    <t>'japanese-mom' Search -XNXX.COM</t>
+  </si>
+  <si>
+    <t>Japanese mom- 958,191 videos - iWank TV</t>
+  </si>
+  <si>
+    <t>MATUREJAPANESE MOMPORN @ A Mature Tube</t>
+  </si>
+  <si>
+    <t>Japanese MomPorn (309,066) @ Porzo.com</t>
+  </si>
+  <si>
+    <t>Japanese Mom PornVideos</t>
+  </si>
+  <si>
+    <t>罗技鼠标驱动不知道下哪个? - 知乎</t>
+  </si>
+  <si>
+    <t>What is your take on Bilibili opening up 8K resolution for user ...</t>
+  </si>
+  <si>
+    <t>哔哩哔哩（bilibili）电脑版怎么下载安装 - 百度经验</t>
+  </si>
+  <si>
+    <t>bilibili哔哩哔哩黑名单在那里，怎么查看黑名单-百度经验</t>
+  </si>
+  <si>
+    <t>哔哩哔哩 - 知乎</t>
+  </si>
+  <si>
+    <t>B站（bilibili）百万粉丝up主收入大概是多少？</t>
+  </si>
+  <si>
+    <t>怎么解决b站网页版看视频卡顿？ - 知乎</t>
+  </si>
+  <si>
+    <t>怎么把B站视频下载下来？ - 知乎</t>
+  </si>
+  <si>
+    <t>B站大会员、超级会员怎么买划算？‌</t>
+  </si>
+  <si>
+    <t>Bilibili（哔哩哔哩）上有哪些值得一看的纪录片？ - 知乎</t>
+  </si>
+  <si>
+    <t>Finally met the majestic yet terrifying Komodo Dragons ... - Reddit</t>
+  </si>
+  <si>
+    <t>Komodo Dragon cannibalism : r/HardcoreNature - Reddit</t>
+  </si>
+  <si>
+    <t>Komodo Dragon, the "living dinosaur" (lizard) that eats living ...</t>
+  </si>
+  <si>
+    <t>Komodo Dragon acting like Godzilla : r/NatureIsFuckingLit</t>
+  </si>
+  <si>
+    <t>Komodo Dragons can be cute : r/reptiles - Reddit</t>
+  </si>
+  <si>
+    <t>A komodo dragon snacking on an eel : r/interestingasfuck - Reddit</t>
+  </si>
+  <si>
+    <t>Yesterday someone mentioned we do not have a komodo dragon</t>
+  </si>
+  <si>
+    <t>Komodo dragon eating one of its own : r/natureismetal - Reddit</t>
+  </si>
+  <si>
+    <t>TIL Before 1912, the Komodo Dragon was once thought to be a</t>
+  </si>
+  <si>
+    <t>Komodo Dragon hunting a Javan Rusa Deer : r/HardcoreNature - Reddit</t>
+  </si>
+  <si>
+    <t>ArtecAPEX Front Swap Kit Brackets - northridge4x4.com</t>
+  </si>
+  <si>
+    <t>TJ Rear Coil Correction Kit –ArtecIndustries</t>
+  </si>
+  <si>
+    <t>Artec TJ1000JL JT 2 TJ APEX Front Swap Kit with OEM Coil ... - eBay</t>
+  </si>
+  <si>
+    <t>TJ Brackets –ArtecIndustries</t>
+  </si>
+  <si>
+    <t>Artec TJ1000Front JL JT 2 TJ APEX Swap Kit with OEM Coil ... - eBay</t>
+  </si>
+  <si>
+    <t>Project TJ (stretch, tons, 37s, V8) -Jeep Enthusiast Forums</t>
+  </si>
+  <si>
+    <t>ArtecTJ back half Frame kit / RearStretchbuild</t>
+  </si>
+  <si>
+    <t>ArtecAPEX Front Swap Kit Brackets |TJ1000-Fits Jeep Wrangler TJ</t>
+  </si>
+  <si>
+    <t>ArtecIndustries Apex Front Swap Kit for Wrangler (TJ1000...</t>
+  </si>
+  <si>
+    <t>Motobilt Underground -Facebook</t>
+  </si>
+  <si>
+    <t>Home - Bellevue High School</t>
+  </si>
+  <si>
+    <t>Contact Us - Bellevue High School</t>
+  </si>
+  <si>
+    <t>Home - Bellevue School District</t>
+  </si>
+  <si>
+    <t>Home - Newport High School</t>
+  </si>
+  <si>
+    <t>Performing Arts Centers - Bellevue School District</t>
+  </si>
+  <si>
+    <t>Counseling - Sammamish High School</t>
+  </si>
+  <si>
+    <t>2026 National Merit Scholarship Program Winners | News Details</t>
+  </si>
+  <si>
+    <t>Home - Interlake High School</t>
+  </si>
+  <si>
+    <t>Home - Highland Middle School</t>
+  </si>
+  <si>
+    <t>Contact Us - Sammamish High School - Bellevue School District</t>
+  </si>
+  <si>
+    <t>Slate Magazine - Politics, Business, Technology, and the Arts</t>
+  </si>
+  <si>
+    <t>News and Politics | Slate</t>
+  </si>
+  <si>
+    <t>Human Interest | Slate</t>
+  </si>
+  <si>
+    <t>Slate | Dear Prudence</t>
+  </si>
+  <si>
+    <t>Theo of Golden - Slate Magazine</t>
+  </si>
+  <si>
+    <t>Slate | The Slatest</t>
+  </si>
+  <si>
+    <t>Life | Slate</t>
+  </si>
+  <si>
+    <t>Slate Games</t>
+  </si>
+  <si>
+    <t>The End of the End of Trumpism - Slate Magazine</t>
+  </si>
+  <si>
+    <t>Crossword: Slate’s daily puzzle for Aug. 28, 2026.</t>
+  </si>
+  <si>
+    <t>Bill Gates-Wikipedia</t>
+  </si>
+  <si>
+    <t>Bill Gates| Microsoft Cofounder, Philanthropist, &amp; Author | Britannica ...</t>
+  </si>
+  <si>
+    <t>Bill Gates:Biography, Microsoft Cofounder,GatesFoundation</t>
+  </si>
+  <si>
+    <t>Bill Gates-Forbes</t>
+  </si>
+  <si>
+    <t>Bill GatesFacts: Net Worth, Achievements and History</t>
+  </si>
+  <si>
+    <t>Bill Gates Facts| Britannica</t>
+  </si>
+  <si>
+    <t>Bill Gates- Simple EnglishWikipedia, the free encyclopedia</t>
+  </si>
+  <si>
+    <t>Bill Gates: Inside the Life and Career of the Microsoft Co-Founder ...</t>
+  </si>
+  <si>
+    <t>The website ofBill Gates|GatesNotes</t>
+  </si>
+  <si>
+    <t>Bill Gates- Wikiwand</t>
+  </si>
+  <si>
+    <t>AnnualReports -FIS</t>
+  </si>
+  <si>
+    <t>SEC Filings|FIS</t>
+  </si>
+  <si>
+    <t>Fidelity National Information Services Annual Report 2026</t>
+  </si>
+  <si>
+    <t>Fidelity National Information Services Annual Report 2024</t>
+  </si>
+  <si>
+    <t>Fidelity National Information Services, Inc. -SEC.gov</t>
+  </si>
+  <si>
+    <t>Fidelity National Information Services(FIS) 10K Form and ...</t>
+  </si>
+  <si>
+    <t>Fidelity National Information Services, Inc. (FIS) 10-K ...</t>
+  </si>
+  <si>
+    <t>Index Fórum</t>
+  </si>
+  <si>
+    <t>Retroautók és egyéb modellsorozatok - Index Fórum</t>
+  </si>
+  <si>
+    <t>A világ legsúlyosabb weboldalai (part - Index Fórum</t>
+  </si>
+  <si>
+    <t>A kijevi helyzet fokozódik - Index Fórum</t>
+  </si>
+  <si>
+    <t>Feminista topik - Index Fórum</t>
+  </si>
+  <si>
+    <t>Mi a titka egy igazán figyelemfelkeltő k - Index Fórum</t>
+  </si>
+  <si>
+    <t>Aki ma nem tankolt... - Index Fórum</t>
+  </si>
+  <si>
+    <t>Target QueensburyStore,Queensbury,NY</t>
+  </si>
+  <si>
+    <t>Target QueensburyGrocery inQueensbury,NY| Hours &amp; Pickup</t>
+  </si>
+  <si>
+    <t>Target - Queensbury, NY- Hours &amp; Weekly Ad</t>
+  </si>
+  <si>
+    <t>TargetinQueensbury,New York- Hours &amp; Locations - StoresInfo</t>
+  </si>
+  <si>
+    <t>TARGET- 578 Aviation Rd Suite 1S,Queensbury NY- Hours, …</t>
+  </si>
+  <si>
+    <t>Target-Queensbury,New York- Location &amp; Store Hours</t>
+  </si>
+  <si>
+    <t>Target - Queensbury, NY12804 - The Real Yellow Pages</t>
+  </si>
+  <si>
+    <t>TargetinQueensbury,NY– Reviews, Hours, and Contact Details</t>
+  </si>
+  <si>
+    <t>Target - Queensbury, NY</t>
+  </si>
+  <si>
+    <t>Target-Queensbury,New York| Hours &amp; Location - StoresInfo</t>
+  </si>
+  <si>
+    <t>Google Translate</t>
+  </si>
+  <si>
+    <t>Google Translate - A Personal Interpreter on Your Phone or Computer</t>
+  </si>
+  <si>
+    <t>Google Traductor: Un intérprete personal en tu teléfono o computadora</t>
+  </si>
+  <si>
+    <t>El Traductor de Google: un intérprete personal en ... - Google Translate</t>
+  </si>
+  <si>
+    <t>Překladač Google – osobní překladatel ve vašem telefonu nebo počítači</t>
+  </si>
+  <si>
+    <t>Google Translate - Een persoonlijke tolk op je telefoon of computer</t>
+  </si>
+  <si>
+    <t>Google Traduction : un interprète personnel sur votre téléphone ou ...</t>
+  </si>
+  <si>
+    <t>Taittiriya UpanishadWithShankaraBhasyaCommentaryAnand ...</t>
+  </si>
+  <si>
+    <t>Taittiriya UpanishadwithCommentary| PDF | Ātman (Hinduism ...</t>
+  </si>
+  <si>
+    <t>Taittiriya UpanishadwithCommentaries| PDF | Brahman ...</t>
+  </si>
+  <si>
+    <t>TaittiriyaUpanisad with thecommentaryof Sankaracarya ...</t>
+  </si>
+  <si>
+    <t>Taittiriya Upanishad- Wisdom Library</t>
+  </si>
+  <si>
+    <t>Taittiriya UpanishadBhashya Vartika - Wisdom Library</t>
+  </si>
+  <si>
+    <t>Taitiriya Upanishad With Translated Shankara BhashyaGita ...</t>
+  </si>
+  <si>
+    <t>Microsoft Community</t>
+  </si>
+  <si>
+    <t>Baked Chicken Wings Recipe</t>
+  </si>
+  <si>
+    <t>Crispy Oven Baked Chicken Wings (any flavor!)</t>
+  </si>
+  <si>
+    <t>OvenBakedChicken Wings- The Kitchen Girl</t>
+  </si>
+  <si>
+    <t>Oven-Baked Chicken Wings Recipe</t>
+  </si>
+  <si>
+    <t>PerfectChicken Wings in Oven: The UltimateRecipe(2025)</t>
+  </si>
+  <si>
+    <t>BakedChicken Wings Recipe: How to Make It - Taste of Home</t>
+  </si>
+  <si>
+    <t>Crispy BakedChicken Wings- Natasha's Kitchen</t>
+  </si>
+  <si>
+    <t>Extra Crispy BakedChicken Wings- Craving Tasty</t>
+  </si>
+  <si>
+    <t>24 BestBaked Chicken Wing Recipes| Food Network</t>
+  </si>
+  <si>
+    <t>OvenBakedChicken Wings(Crispy &amp; Easy) - Wholesome Yum</t>
+  </si>
+  <si>
+    <t>Orlando Theme Parks | Disney, Universal, SeaWorld &amp; LEGOLAND</t>
+  </si>
+  <si>
+    <t>Things to Do in Orlando | Theme Parks, Attractions &amp; Activities</t>
+  </si>
+  <si>
+    <t>Universal Orlando Resort : Parkführer und Informationen</t>
+  </si>
+  <si>
+    <t>Themenparks in Orlando | Disney, Universal &amp; SeaWorld</t>
+  </si>
+  <si>
+    <t>Disney's Hollywood Studios in Orlando | Guide &amp; Tickets Info</t>
+  </si>
+  <si>
+    <t>Orlando - Hotels, Restaurants, Things to Do &amp; Vacation Guide</t>
+  </si>
+  <si>
+    <t>SeaWorld, Discovery Cove &amp; Aquatica | Orlando Theme Parks</t>
+  </si>
+  <si>
+    <t>Walt Disney World | Theme Parks, Water Parks, Hotels &amp; More - Visit …</t>
+  </si>
+  <si>
+    <t>Universal Orlando Resort: Epic Universe, Islands of Adventure ...</t>
+  </si>
+  <si>
+    <t>Orlando’s Best Budget-Priced Attractions &amp; Activities</t>
+  </si>
+  <si>
+    <t>I try porn hub blokin but iam fail how to block porn - Google Help</t>
+  </si>
+  <si>
+    <t>بارگیری و نصب Google Chrome</t>
+  </si>
+  <si>
+    <t>8 Roads to Universal: [Democratic Health Care Plans] - Page 6</t>
+  </si>
+  <si>
+    <t>- Penny Arcade</t>
+  </si>
+  <si>
+    <t>I don't see porn hub - Google Chrome Community</t>
+  </si>
+  <si>
+    <t>How do you know what email account and password is for porn hub …</t>
+  </si>
+  <si>
+    <t>Get help removing explicit or intimate personal images</t>
+  </si>
+  <si>
+    <t>How can I transfer pictures on my computer to Google Photos on my ...</t>
+  </si>
+  <si>
+    <t>Troubleshoot a failed or declined payment for a purchase</t>
+  </si>
+  <si>
+    <t>Find your purchases, reservations &amp; subscriptions</t>
+  </si>
+  <si>
+    <t>Unusualpipefittingabovemybathtub.</t>
+  </si>
+  <si>
+    <t>How Do I Have Plumbing ComingOutof the Walls?</t>
+  </si>
+  <si>
+    <t>What Is thePipe AboveMy Shower? Expert Q&amp;A Guide -JustAnswer</t>
+  </si>
+  <si>
+    <t>What Is aBathtubOverflow Drain? 2025 Guide to Tub Overflow ...</t>
+  </si>
+  <si>
+    <t>Tub Wasteand Overflow Guide- fergusonhome.com</t>
+  </si>
+  <si>
+    <t>Shower plumbing diagram: layout, components &amp; how it works</t>
+  </si>
+  <si>
+    <t>Why Are Plumbing Waste DrainPipes Sticking OutOf Exterior ...</t>
+  </si>
+  <si>
+    <t>Jordan 4RetroUNC(PE) Men's - Sneakers - US - StockX</t>
+  </si>
+  <si>
+    <t>Air Jordan 4 Retro 'UNCFootball'PE- GOAT</t>
+  </si>
+  <si>
+    <t>Jordan 4 Retro 'UNC'PE-Flight Club</t>
+  </si>
+  <si>
+    <t>Air Jordan 4UNC PE- Detailed Look at the Exclusive Player Edition ...</t>
+  </si>
+  <si>
+    <t>Buy Air Jordan 4 Retro 'UNC'PE- HO12MNJDLS247 |GOAT</t>
+  </si>
+  <si>
+    <t>Air Jordan 4 'UNC'PEPlayer Exclusive Details | Ultra-Rare</t>
+  </si>
+  <si>
+    <t>Jordan 4Unc Pe- eBay</t>
+  </si>
+  <si>
+    <t>UNCJordan 4PE2025 |SneakerNews.com</t>
+  </si>
+  <si>
+    <t>Unc4 for sale | eBay</t>
+  </si>
+  <si>
+    <t>Buy Air Jordan 4 Retro 'UNC'PESU18-MNJDLS-731-LNM-AJ4-904284</t>
+  </si>
+  <si>
+    <t>DuckDuckGo- Protection. Privacy. Peace of mind.</t>
+  </si>
+  <si>
+    <t>DownloadDuckDuckGofor Windows, Mac, iOS and Android</t>
+  </si>
+  <si>
+    <t>DuckDuckGo— Privacy, simplified.</t>
+  </si>
+  <si>
+    <t>DuckDuckGo-Wikipedia</t>
+  </si>
+  <si>
+    <t>DuckDuckGoNo-AI: Private Search Without AI</t>
+  </si>
+  <si>
+    <t>How To GetDuckDuckGo-DuckDuckGoHelp Pages</t>
+  </si>
+  <si>
+    <t>Download theDuckDuckGoBrowser for Windows</t>
+  </si>
+  <si>
+    <t>Login -DuckDuckGo</t>
+  </si>
+  <si>
+    <t>AboutDuckDuckGo</t>
+  </si>
+  <si>
+    <t>DuckDuckGosubscription including VPN and advanced AI</t>
+  </si>
+  <si>
+    <t>WestMonth™ - Premium 1000GSMMattress Topper–West Month</t>
+  </si>
+  <si>
+    <t>West Month Mattress Topper: Scam or Legit? Full Review</t>
+  </si>
+  <si>
+    <t>WestMonth™ - Premium 1000GSMMattress Topper</t>
+  </si>
+  <si>
+    <t>WestMonth™ — Premium 1000GSM BambooTopper–West Month</t>
+  </si>
+  <si>
+    <t>Amazon.com:West Month Mattress Topper,West Month Mattress...</t>
+  </si>
+  <si>
+    <t>WestMonth Premium Quilted 1000GSM Luxury Extra ... - amazon.com</t>
+  </si>
+  <si>
+    <t>West Month Mattress Topper,West Month Mattress... - Amazon</t>
+  </si>
+  <si>
+    <t>WestMonth™ | 1000GSM Hotel-QualityMattress Topperfor Better ...</t>
+  </si>
+  <si>
+    <t>Usewestmonth Reviews | Read Customer Service Reviews of ...</t>
+  </si>
+  <si>
+    <t>CanadianMade Mattress TopperBrands 2026 |MattressMiracle</t>
   </si>
   <si>
     <t>Senior Care</t>
@@ -631,589 +802,760 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa224fb88a30c3a0a0809322d483d615f42a22bee114a7e00e010904064d399cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly9vbGRuYXZ5LmdhcC5jb20vP21zb2NraWQ9MzkxNzUwZWQwMjQ0Njc3YzEzMjM0NzBjMDNkZjY2ZDU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66e792d4cc210852164adc65f0db2be3714c1c7b93eaea36cba6722f337c0f33JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9PbGRfKGZpbG0p&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f89b331ff567e8d744319a0ba5d493f9dd9232b7f67c9c5aa6c1d7a42c1f174dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTA5NTQ2NTIv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66738eb9ac579c4a0425362056fbaad434901bfcf64bd3af78f43e359fad272fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly93d3cucm90dGVudG9tYXRvZXMuY29tL20vb2xk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0d8d5a91be0b964d4b2a8d488bb6323c6bc63a23aeb42f9aa362e152c6953c99JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L29sZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d99d244f299b2f70c8329b3bd2e0a1913ceb0bd34d19f45d2fc810c3a889fbfdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL29sZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2d170972ddbba42fa70c54689f3c1def33eade167f16704db44b3a7c2c44704JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9QTRVMnBNUlY5X2s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1dde2ff78b454997bd82478551ec0f9ca0f842fa9b7e24339781b2f8e97caf0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly90dnRyb3Blcy5vcmcvcG13aWtpL3Btd2lraS5waHAvRmlsbS9PbGQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b9ec450b0c95fab25617ad3ee8dca3be9bdb1127ffed2a02369b7151867f91afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly93d3cuanVzdHdhdGNoLmNvbS91cy9tb3ZpZS9vbGQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f158f685f433a88f1fb2f398daf7f6c92f5774830e6ec73390f99336c9d6e36JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=391750ed-0244-677c-1323-470c03df66d5&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9ODR4QUQ0ci05a0U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=308988f077771f952dcf809848bc1f610015f55c07deecc80cf176be00d7b4f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly9wZGYyeGwuY29tL3dwLWNvbnRlbnQvdXBsb2Fkcy8yMDE4LzA1L3JldGlyZW1lbnQtcGxhbm5pbmctc3ByZWFkc2hlZXQueGxz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d3d98edc83022fafa4f23ecbdb87063e85ecaf425765b01a01064458de2453e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly9tYWZjb21wYW5pZXMuY29tL3dwLWNvbnRlbnQvdXBsb2Fkcy9SZXRpcmVtZW50LVBsYW5uaW5nLUdBUDEueGxz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b348e3c74f3d8ea32e514ea5d87d2a3a8429e64b28fa30b5c437da61d5b108bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly93d3cuZmxleGlibGVyZXRpcmVtZW50cGxhbm5lci5jb20vdG9vbHMvUmV0aXJlbWVudFdpdGhkcmF3YWxTaW11bGF0b3IueGxz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df9f4096b0f61d50efa786c8e91054f929e7bf7f8d5a507885be351e3f9bc8bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly93d3cuc21hcnRzaGVldC5jb20vc2l0ZXMvZGVmYXVsdC9maWxlcy8yMDI1LTAyL0lDLVJldGlyZW1lbnQtRmluYW5jaWFsLVBsYW5uaW5nLTEyMzMyX1RlbXBsYXRlLnhsc3g&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a09be570c16cc71202cf87a895b76e81e56d5b8ef2d75c90010f6f328ec3a2fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly9ob21lLmFybXkubWlsL2RydW0vNTExNy8zMTA5LzYyMzgvQ1NQX1BsYW5uaW5nX0NhbGN1bGF0b3IueGxzeA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48287cf2879f55bea3f4ab1c2f7e49a43885d6f508fadea519ba83d1b605dddfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly9hc3NldHMuY29iYmNvdW50eS5nb3YvZmlsZXMvMjAyNS0xMi9SZXRpcmVtZW50LUNhbGN1bGF0b3IueGxzeA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24db6cc1487b436b7d40d07f476e88d09af725439b25046410a2735ce9dfd445JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly93d3cubW9udGFuYS5lZHUvZXh0ZW5zaW9uZWNvbi9kb2N1bWVudHMvcmV0aXJlbWVudGluY29tZXdpdGhkcmF3YWx3b3Jrc2hlZXQueGxzeA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2e330de4c9c67a8493bafb9d1f1382d75d3f235c45c91fbe46a3497bfa2cef4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly93d3cucHNwcnMuY29tL3dwLWNvbnRlbnQvdXBsb2Fkcy8yMDI1LzExL1BTX0RST1BfVGllci0xX1Jldi0xMS0yMDIyLnhscw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=becf322ef3989266c9ecfce92629c1e2aea38876a356c12668a0f8d9d776dfb7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly9zcHJlYWRzaGVldGRhZGR5LmNvbS93cC1jb250ZW50L3VwbG9hZHMvMjAyMy8wOS9SZXRpcmVtZW50LUNhc2gtRmxvdy1TcHJlYWRzaGVldC1mcm9tLUdldC1TbWFydGVyLUFib3V0LU1vbmV5LWZvci1FeGNlbC54bHM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c01f10a1c0b79a157369e7d28d4da3841f311dd51e87d96681121c8c7e9d77cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0eb60a73-e88b-60b7-24c0-1d92e9056144&amp;u=a1aHR0cHM6Ly93d3cucGxpbmRpYS5jb20vd3AtY29udGVudC91cGxvYWRzLzIwMjUvMDMvcmV0aXJlbWVudC1wbGFubmluZy54bHM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a67897b9e55db0fd322989e350015921908b4635ba03231878e9500744e2dc6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly93d3cuc2hlcndvb2RvcmVnb24uZ292L2NvbW11bml0eS1mYWNpbGl0aWVzL3Nlbmlvci1jZW50ZXIv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebf9a6bf30c78d94cdf7808e8f747e42616a96686f11b55fec425a108cbae27aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly9zZW5pb3JjZW50ZXIudXMvc2Mvc2hlcndvb2Rfc2VuaW9yX2NlbnRlcl9zaGVyd29vZF9vcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27986df24ee0bb959ef262d3da1314d58c9a977ca8c7e822c6ae1d94e2221226JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly9zaGVyd29vZG9yLmNpdmljcGx1c3dlYm9wZW4uY29tL21hcmpvcmllc3Rld2FydGNlbnRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=adfbeaf8cd9beb31e38245ba06bddef5ea00cc3148b91ef61d1bf1e0bd44e44aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Nlbmlvcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f20c2201e532504cce7e37cd42f9d47f2a507c5beac28b8deeee5253e1dfd9eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly93d3cudGhlc3ByaW5nc2xpdmluZy5jb20vc2VuaW9yLWxpdmluZy9zaGVyd29vZC9vcmVnb24vc2hlcndvb2Q&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=08cf77f1e3fed9a40224bb0b9687845b81bc09da74eb671c2e15fb6ae6a76636JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly9zaHMuc2hlcndvb2QuazEyLm9yLnVzL3NjaG9vbC1pbmZvL3Nlbmlvci1pbmZvcm1hdGlvbi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7253cb0284402c5c4371487d33dff89a5c301beeea8cb4986539b6e0b2ab1b88JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly93d3cuYWZ0ZXI1NS5jb20vc2VhcmNoL29yL3NoZXJ3b29k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a00cfec185ef930ae867a3dbc4eaa97fb835d31e98da7081b604d3f4d14f5a39JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly93d3cuc3Rld2FydHRlcnJhY2VzcmFwdHMuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9afe480455bdd8059bf2dce5e3d2c8c5510e6ccae44e98aa51474a4b7cafff19JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bf993b0-58f0-6636-0b92-845159a16777&amp;u=a1aHR0cHM6Ly93d3cuYXBhcnRtZW50aG9tZWxpdmluZy5jb20vc2hlcndvb2Qtb3IvYXBhcnRtZW50cy1mb3ItcmVudC9zZW5pb3I_bXNvY2tpZD0zYmY5OTNiMDU4ZjA2NjM2MGI5Mjg0NTE1OWExNjc3Nw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e611a35dc3ccb50815324c5986b38136e02447465529f6d30e9194002f7c13d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cz9tc29ja2lkPTNlNWNjZmI4YmRkYjYyMjkzMjU3ZDg1OWJjY2Q2MzQy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=231012a387d4ec53a655bfcf3c619ee0a4a226d7080673d1766c7d19c0f62586JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9hY2NvdW50Lm1pY3Jvc29mdC5jb20vYWNjb3VudA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ba67d2acbe53424d920e4e3cd4fee6fd5f5795dbfc5f83227262a60878e9fd7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a7da95254c1c2f834701ccf78b36fdf84de27557c603e5432fe40097c96e40dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWljcm9zb2Z0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=813890850d0653ffcaa917fe4664c3d8b80f1f913a0ce3d7daf21ce299e5921cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cy9taWNyb3NvZnQtMzY1P21zb2NraWQ9M2U1Y2NmYjhiZGRiNjIyOTMyNTdkODU5YmNjZDYzNDI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25376799f10259513213d4b595dc7e7847951f2102227ba89f6d6353d17ad4eaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS8lQzIlQTAtJTNF&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d5cbbba6a9772b3863d33258ed389379792c2cf97f2343a0efc592a2233ec289JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9jYXJlZXJzLm1pY3Jvc29mdC5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c041149eff6438133db0a58921ab4462f7c34842272b1eed81c6517a7e97c1acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9zaWdudXAubGl2ZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a4e19c2f6bf4a6ed88392f60ce310680a8a0c5a582c5f05de234352934fb6afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9tMzY1LmNsb3VkLm1pY3Jvc29mdC8_b3JpZ2luZG9tYWluPW1pY3Jvc29mdDM2NQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82ed53fc1fa004a7261cdbdcf56b58c806957d6eb5f3d525668e1a5cb87990dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e5ccfb8-bddb-6229-3257-d859bccd6342&amp;u=a1aHR0cHM6Ly9vdXRsb29rLm9mZmljZS5jb20vbWFpbC9pbmJveA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd4ae9d4c2f8315a049fabde33abcd2954986d54e08af2d9bdcb2dbf08733a1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7eaf6a5b5a38197e4ab2de19eccdc155004e0958def07f5b58e79d762702799JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11954947b6029ac9408550a30836db7ccc9922f567e0700f6e5fda1d2d4049daJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvZnJhaWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc62b6e4889076e3b1b7a98705b4905dd0415a74cd4df8c1957ca17c645625a4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f7eba3b64507d63a4e8ba476b244a020bff82e71aa0e93b97186b3417e749b27JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be55a4690a59b4416cd6288769155604241527d2fd793ec3a992eab0f1613dffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f06f3a1f7d3978a470de86442dc008ffa5144d3796b2a24506af0d12cba85e1aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c18ccde5c45df255ce99af4fc457cdcf05f111d6de4bce1f70719a45d4a6876dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly9lbi5tLndpa3Rpb25hcnkub3JnL3dpa2kvZnJhaWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7096825fc9a89d401e9fb0a0b8222f26d0f0508ede8bcdd8f2b9b3cf3d92fd8cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL2RpY3Rpb25hcnkvZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d670ba9ed67bfcd6f2a40dc17361cbe6fe8396d1d51f8cd2a90243966f52196JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32f75211-6cd4-6a3a-1436-45f06d6f6b36&amp;u=a1aHR0cHM6Ly93d3cub3hmb3JkbGVhcm5lcnNkaWN0aW9uYXJpZXMuY29tL2RlZmluaXRpb24vZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=17022b465b957e07ea9392e206afa7ee0fc8ac3359a071a68ec21a8e38626645JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL2RpZ2l0YWwvb25saW5lLWJhbmtpbmc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80c829aab17458382887948d1afc7b392256c2851f50717598ade2f3fef1381dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c9f59d373619b817a1305a7293fc2d2d67133e9084029194a0ab56d62afcb03JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly9zZWN1cmUuY2hhc2UuY29tL3dlYi9hdXRoL2xvZ29uYm94&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e612eaa3ef9ade0fbbe5cd1124f2bb767fc12a3d443a0d671062fc68826c107fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL3BlcnNvbmFsL2NyZWRpdC1jYXJkcy9jYXJkLXJlc291cmNlLWNlbnRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aa370f7da574fffa768c995ce6ea0f139007817bdd298f28fd1eb60755b39dc2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly9wZXJzb25hbC5jaGFzZS5jb20vcGVyc29uYWwvY2hlY2tpbmc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cd5799e0bec6e8f763928dceee32638bae3863f6406d0653c586404bda4e7360JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL3BlcnNvbmFsL2NyZWRpdC1jYXJkcy91bHRpbWF0ZS1yZXdhcmRz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27f97456bc952ed65a51c26beaee40622a7231d92e29795d00cc29fb3cda4ed7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL3BlcnNvbmFsL2NyZWRpdC1jYXJkcy9sb2dpbi1lcGF5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7fd9338e61833ab24741bf97be29de7d00cced0a7fbcc64b8657323c0a5da863JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL2RpZ2l0YWwvb25saW5lLWJpbGwtcGF5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5adbd6b6f8f6e0f38ca13df8dc6c8a5532c2f7025b73c5d6db0e1207d14e48d1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL3BlcnNvbmFsL21vcnRnYWdlL215LW1vcnRnYWdlL2hvbWU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bddb5a4d780270cc7a057e979575974b18a7c6bcfcc19d112a6630f784f4842cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39ae81e6-e163-67e2-1ef8-9607e025667a&amp;u=a1aHR0cHM6Ly93d3cuY2hhc2UuY29tL3BlcnNvbmFsL2NyZWRpdC1jYXJkcy9hbWF6b24vdmlldy1hY2NvdW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b666abc564985e8fab26ddf4894de2387a5574ab735cb529238c1b63c8acdc9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly9lbWVhbHMuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9b37f1fb6cf66aea38220e9409f29632363f0401cb2cc8824f2e607d773c56dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cuYWxscmVjaXBlcy5jb20vMTAwLWVhc3ktbWVhbHMtMTE2OTUyMjc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d18d01b7d21eb185ce21ac93a6d8c5f30c8517789fa0a33881e007ef770f8500JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZWFzeS1kaW5uZXItaWRlYXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=65a9e5af6fbf575948f34a6802bf92f28735f590736a9b66a9c5232d8c12fe22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly9lYXRtZWFscy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c42ea2b44b64c9c8ef444cf386a6fa7796a14fd60f2f829147b5d3196e8a5e00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zLzMwLW1pbnV0ZS1kaW5uZXItcmVjaXBlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=188ee2298b307c97943779f15c5a9a9779944e69e0882743f54f71d7e1a05a7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=060f6138d48ec2e30599facac2a2b7c6ce5a515770482f62a749fa4c1eb028a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cubW9tc21lYWxzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f81c8532289f4d12f20322248663fb80b534cd47eabe1b16005288e958b8950fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zL2Vhc3ktZGlubmVyLXJlY2lwZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2c5d0119071ef10f4e883b3c1fbebe740e9d5251d168b5a49c9e3d86371cfe5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzMyMjY0Mjg0L2Vhc3ktZGlubmVyLXJlY2lwZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56b309329dbdbff7dea8e083ca92568810e78b8ae56a357e3c8d02e7b7d69ceeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299c6ead-6cbc-6195-05f1-794c6d2e60b6&amp;u=a1aHR0cHM6Ly93d3cuZnVlbG1lYWxzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f3972b4dfc0eebe88782171f7c7e31a2206f4fab6cb9b940cccfc5e01da0f5aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tZ2IvY29udGFjdHVz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e038fffefbb3e1cfbd244e995eea1fb27bf9fbf509d464ee2217884f8e6b450JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvYWNjb3VudHMtYmlsbGluZy9tYW5hZ2UvaG93LXRvLXNpZ24taW4tdG8taG90bWFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=09102301c15c006cd276b79b48db4e5320e4d2a189bb0158b77a9ec8450aadd1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly90ZWNoY29tbXVuaXR5Lm1pY3Jvc29mdC5jb20vY2F0ZWdvcnkvbWljcm9zb2Z0LWNvcGlsb3QvYmxvZy9taWNyb3NvZnQtY29waWxvdC1ibG9n&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d170c81ba80016e5e15ee3220e5b185b1931a13d2351ab2caf44172aa102e2aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly90ZWNoY29tbXVuaXR5Lm1pY3Jvc29mdC5jb20vYmxvZy9leGNoYW5nZS9leGNoYW5nZS1vbmxpbmUtZXdzLXlvdXItdGltZS1pcy1hbG1vc3QtdXAvNDQ5MjM2MQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75230c9d3e1d92736a35e47f01d53f79aabae78be4bddc65ef63a83834d66b5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9kZXBsb3ltZW50L2luc3RhbGwtdXBncmFkZS9nZXR0aW5nLXJlYWR5LWZvci10aGUtd2luZG93cy0xMS11cGdyYWRl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fd697a6d85e873336ca79753bfbefed7988ed4cf687998358ee97640a9fd8c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZnItZnIvd2luZG93cy9tZXR0cmUtJUMzJUEwLWpvdXItbGVzLXBpbG90ZXMtdmlhLWdlc3Rpb25uYWlyZS1kZS1wJUMzJUE5cmlwaCVDMyVBOXJpcXVlcy1kYW5zLXdpbmRvd3MtZWM2MmY0NmMtZmYxNC1jOTFkLWVlYWQtZDcxMjZkYzFmN2I2&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dda202a11cf86182f0daec9139965b1648cbf9c1d749d2c0f868485192507299JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvd2luZG93cy9ha3R1YWxpc2llcmVuLXZvbi10cmVpYmVybi0lQzMlQkNiZXItZ2VyJUMzJUE0dGUtbWFuYWdlci1pbi13aW5kb3dzLWVjNjJmNDZjLWZmMTQtYzkxZC1lZWFkLWQ3MTI2ZGMxZjdiNg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c6e7615e8e7b2a35d95aa92f28a7fc1be36f40f81a3925618378d2ca5a45665JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvZWRnZS9nZXR0aW5nLXRoZS1sYXRlc3QtbWljcm9zb2Z0LWVkZ2UtdXBkYXRlLWp1c3QtZ290LWVhc2llcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81dc9b62b0ce2eddd383201ffd1458aac967c4e59c0c053e7f8f87fc72f2686aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvb3V0bG9vay90cmFpbmluZy9zaGFyZS15b3VyLWNhbGVuZGFyLWluLW91dGxvb2s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2cb396f2dff15f7d4330c11b4bea1b03849f838e1105ef03b86d4c4555114d89JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d671f62-0f75-66e3-1a41-08830e3367dc&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvZm9ybXMvc2lnbi1pbi10by1taWNyb3NvZnQtZm9ybXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=637f1e2de8b7a13c3a1fca4bf1345289a593fadfc461b9eb708bb0ccd552e026JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01572cce-81f1-6d33-122c-3b2f80726c5c&amp;u=a1aHR0cHM6Ly9zZXJ2aWNlcy5zbGNwbC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96d7926c3966653e49184b0d7bffc5720f47ae12d014944eb43417bd7cb5cbc6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01572cce-81f1-6d33-122c-3b2f80726c5c&amp;u=a1aHR0cHM6Ly9zZXJ2aWNlcy5zbGNwbC5vcmcvbGlicmFyeS1zdG9yZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=138be10af53d3a31f0f947e743ba9efcf22eeb2b9690d7ac7333e5f898ca1a16JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01572cce-81f1-6d33-122c-3b2f80726c5c&amp;u=a1aHR0cHM6Ly9zZXJ2aWNlcy5zbGNwbC5vcmcvbGlicmFyeS1jYXJkLWFwcGxpY2F0aW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dff34a5378eeb3a0a8cdf6ed967dc805383b291beaad6119e2f09c002a7c41afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01572cce-81f1-6d33-122c-3b2f80726c5c&amp;u=a1aHR0cHM6Ly9zZXJ2aWNlcy5zbGNwbC5vcmcvcHJpbnRpbmc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb1a8540e8a2f0d925ecf06d0776b2e908d443ef03d8478a56d45641fff191e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01572cce-81f1-6d33-122c-3b2f80726c5c&amp;u=a1aHR0cHM6Ly9zZXJ2aWNlcy5zbGNwbC5vcmcvc2hvcHM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=49cbff0da7ccd59e0083139a0efe32a1316f31e512f1e94328cbff3ddb45e442JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01572cce-81f1-6d33-122c-3b2f80726c5c&amp;u=a1aHR0cHM6Ly9zZXJ2aWNlcy5zbGNwbC5vcmcvdXRhaHMtb25saW5lLWxpYnJhcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=809b2eb4ad57ef0e9b78732d8b0a0ec273896cd15c46a49817bfe54fbf42e7a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33cd3874-c10f-6605-0170-2f95c077674d&amp;u=a1aHR0cHM6Ly93d3cuY3JlZGl0b25lYmFuay5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3e7447c86ed24c8c18e36d8ed7ae891c859449ddff9b5531f1600bbd52a7d3eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33cd3874-c10f-6605-0170-2f95c077674d&amp;u=a1aHR0cHM6Ly93d3cuY3JlZGl0b25lYmFuay5jb20vZmFxcy9wYXktYmlsbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12a167a41b630d17179fc73e0d4a1992f8ec9bde177c3006e5e683b15d5e832fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33cd3874-c10f-6605-0170-2f95c077674d&amp;u=a1aHR0cHM6Ly9zZWN1cmUuY3JlZGl0b25lYmFuay5jb20vYWNjZXNzL2hvbWU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e087493234a3c5e76026c1411438de6a04114f9da42bfd7b707fdf398e1d6209JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33cd3874-c10f-6605-0170-2f95c077674d&amp;u=a1aHR0cHM6Ly9zZWN1cmUuY3JlZGl0b25lYmFuay5jb20vcmVzZW5kLWFjdGl2YXRpb24tZW1haWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=63bc3d5a7b910a63b9db7b32879fc902c6cd19f47dc4877ee5bce354bfa5a705JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33cd3874-c10f-6605-0170-2f95c077674d&amp;u=a1aHR0cHM6Ly9jYXJlZXJzLmNyZWRpdG9uZWJhbmsuY29tL3BhZ2VzL2JlbmVmaXRz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e3decc41e13f42c6278384cefda91ce9d8fc9663a4b192673bedae11940ffe4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33cd3874-c10f-6605-0170-2f95c077674d&amp;u=a1aHR0cHM6Ly9jYXJlZXJzLmNyZWRpdG9uZWJhbmsuY29tL3NlYXJjaC9qb2Jz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e2cd41d2c406fe8d736e2f04e44cbd52f4ff39dd945679c9287f1855a9b9e10JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly93d3cuY3JhaWdzbGlzdC5vcmcvYXJlYS9zYW5kaWVnbw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=367a3b3933f18507a31eb246a906d5612b41fcc89707ac7b12b564aaa3a16c66JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly93d3cuY3JhaWdzbGlzdC5vcmcvc2VhcmNoL2FyZWEvc2FuZGllZ28_Y2F0PXNzcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a913a4fb0b8123aaef770deabe4721235b486448520246328abaa159377d36f6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly9nZW8uY3JhaWdzbGlzdC5vcmcvaXNvL3VzL2NhL3NhbmRpZWdv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a195574a712552e0483606347937668b6388be0c8a6a3c908b38c73a97c08407JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly9nZW8uY3JhaWdzbGlzdC5vcmcvaXNvL3Vz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91d9ae764e0df04348e9a81760162c1b37581d9cfe3640a72dc81d5123b47c55JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL21hcmtldHBsYWNlL3NhbmRpZWdvLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f72d43723b7c9e74bd703d90650bc1948545716ff7be3b2d835c517a374aa163JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly9zYW5kaWVnby5jcmFpZ3NsaXN0Lm9yZy9zaXRlbWFwLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b251044fc48f807f15d51216587a68a1b0a235c3ce1900fc2b5d1580ba2b19bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e817a5-fe79-6f8a-034e-0044fff36e2b&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2dyb3Vwcy8yMTc0OTMxMzU0NDc2OTUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de47488cf2f455f36c6d9b3c44b68424ffbe575497341919e5d754af308325d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1456b719-9cc3-6121-13cd-a0f89d316088&amp;u=a1aHR0cHM6Ly9hY2NvdW50Lm1pY3Jvc29mdC5jb20vYWNjb3VudC1jaGVja3Vw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1212d59be8d1f437a8d4c3c835423bf21b79610e90110a82d252f2caa85eda3dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly93d3cuaW5kZWVkLmNvbS9jYXJlZXItYWR2aWNlL2ludGVydmlld2luZy8yLWZvcm1zLW9mLWlkLWZvci1qb2ItaW50ZXJ2aWV3&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=384490ff3b30fcd56b0742fbb0f15bd07f831aeeee7a031536aef85ec7f1287fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly93d3cuaS05aW50ZWxsaWdlbmNlLmNvbS9hcnRpY2xlcy92YWxpZC1mb3Jtcy1vZi1pZC1mb3ItdGhlLWktOQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7211da59e8062f2a43e22bfbd3ffe34f851f314375a42329351a7d6383927a4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly93d3cudXNjaXMuZ292L2ktOS1jZW50cmFsL2Zvcm0taS05LWFjY2VwdGFibGUtZG9jdW1lbnRz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e3776671fe0b0a2a2124bf7e1a51727002c830e01794b7a779082ceb7b5c5651JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly9jbGltYnRoZWxhZGRlci5jb20vZG8teW91LW5lZWQtYW4taWQtdG8tZ2V0LWEtam9iLWFjY2VwdGFibGUtZG9jdW1lbnRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d74852ac25ad66ddf3f9eeaa2f62ef43406f8de3503a3cb807adfe3a84f8556aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly93d3cudml0YWxyZWNvcmRzb25saW5lLmNvbS9ibG9nL2FjY2NlcHRhYmxlLWZvcm1zLXVzLWlk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=299f7764427a4e4d383937a38969b467e5fd1daad6783a517f4685e3a917c62eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly9sZWdhbGtub3dsZWRnZWJhc2UuY29tL3doYXQtY291bnRzLWFzLWEtdmFsaWQtaWQtZm9yLWEtam9i&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89c3626e7315c3930986d03fc2ff20db9b2c6c9c5375a1a51153e08244680dceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly9za2lsbHNmb3JjaGFuZ2UuY29tL2RvLXlvdS1uZWVkLWFuLWlkLXRvLWdldC1hLWpvYi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4228a075167777fff39c5d59fe01e5593d7e08fdcbd956ad71e9d6d36d180a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly9kb29yczRqb2JzLmNvbS9lbXBsb3ltZW50LWxlZ2FsaXRpZXMvZG8teW91LW5lZWQtYW4taWQtdG8tZ2V0LWEtam9iLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d8086c9837e6c863fddaf0a5b72e05caf100385f605c91400a087402691cc7e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly93b3JrLmNocm9uLmNvbS9wcm9vZi1pZGVudGlmaWNhdGlvbi1uZWVkLWpvYi0zMTE3MS5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c75fba25635bba8a9dc6193c9921536cb10943d505e3883552e9cee04c4fd836JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=370265ee-22a1-6b58-2601-720f23e76a3e&amp;u=a1aHR0cHM6Ly9jbGltYnRoZWxhZGRlci5jb20vZG8teW91LW5lZWQtYW4taWQtZm9yLWEtam9iLXRoZS1yZXF1aXJlZC1kb2N1bWVudHMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=13cafcc6c86653f0a83e6957d2dbf01d60d002a437cd2d69c90e117a36bf72acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvZGlzZWFzZXMtY29uZGl0aW9ucy90aW5uaXR1cy9zeW1wdG9tcy1jYXVzZXMvc3ljLTIwMzUwMTU2&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7cb5acb375d90eb30d12927ef4512baf8fdb474e3f1137216b4cfc4bc818d1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvZGlzZWFzZXMtY29uZGl0aW9ucy90aW5uaXR1cy9kaWFnbm9zaXMtdHJlYXRtZW50L2RyYy0yMDM1MDE2Mg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d739bddbdaab6ee6b38263e3ee7eda1f78bae641a85c760aa47b8c544c522f2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9vbmxpbmVzZXJ2aWNlcy5tYXlvY2xpbmljLm9yZy9wYXRpZW50cG9ydGFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f8fa62c91178efa15ded0826e1817adb4ef35fa16261a1085fb6c15f5f76bf7fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9jb25uZWN0Lm1heW9jbGluaWMub3JnL2Rpc2N1c3Npb24vcHVsc2F0aWxlLXRpbm5pdHVzLTQv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48681578330d9a049e7e905697b046b1d69ddd8af4fb5e6ff6db8c7890f684c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9uZXdzbmV0d29yay5tYXlvY2xpbmljLm9yZy9kaXNjdXNzaW9uL21heW8tY2xpbmljLXEtYW5kLWEtdW5kZXJzdGFuZGluZy10aW5uaXR1cy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3bc41427cf38382c53d284ff5f2164032dccec3468e51ef7ba7a5898f17c67a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9jb25uZWN0Lm1heW9jbGluaWMub3JnL2Rpc2N1c3Npb24vd2hhdC1uYXR1cmFsLXByb2R1Y3QtY2FuLXF1aWV0LW15LXRpbm5pdHVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=188db571b83d7655c90abc9067766df69142426ae7585d388bf0dcdcabe83d2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9uZXdzbmV0d29yay5tYXlvY2xpbmljLm9yZy9kaXNjdXNzaW9uL3Rpbm5pdHVzLXdheXMtdG8tcmVkdWNlLXRoZS1pcnJpdGF0aW9uLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=115e7337ddf14cdac8eb46cb7e74afb1cb3571007c45a57f56ce7fdaeda37530JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9tY3ByZXNzLm1heW9jbGluaWMub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=318e6acaf107bf5a4dcf5cf763c9058379cf457bc45af07cef9b8c571ba6c014JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9tY3ByZXNzLm1heW9jbGluaWMub3JnL2xpdmluZy13ZWxsL3doYXQtY2F1c2VzLXJpbmdpbmctaW4tdGhlLWVhcnMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=14be6dcc3b1779be4d8128d770cc831abda4cb0ae2af7ec43caab6d39e2b3fe6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=138ca8ee-d715-6b26-0aa8-bf0fd68f6aa5&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHloZWFsdGgubWF5b2NsaW5pYy5vcmcvZmVhdHVyZWQtc3Rvcmllcy90aW5uaXR1cw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71095d9d67dcbf69c46a26908970e5baecdb32d63e17b135f87fb0cbadd6ea81JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9kdXJoYW0tY291bnR5LXJlc3RhdXJhbnRzL3N1YndheTE2Lmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be38148098f43bc641093bb07930a760727495ceddb5973d30739136e78234deJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9uZXcteW9yay1jaXR5LzM1MjgwNjctODMteWVhci1vbGQtYWlyLWZvcmNlLXZldGVyYW4tMi5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a0d0ca54546dedb121e08696a51c9cdd312e7d0f494b3a5b8def9f8377bc67aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9yb2NoZXN0ZXItYXJlYS8yNjAxOTU0LWFiYW5kb25lZC1zdWJ3YXkuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3dce001442919a042a5d765ca9855343ecbbd430f58ad623b126149a0d2a82d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9sb3MtYW5nZWxlcy8xODQ0NzYwLXdoYXQtc29tZS1tb3ZpZXMtZmVhdHVyZS1sLXN1YndheS5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e359dec2ee3f9802f0fc534fea23f35279dc02685632a0c0679cdfcd2712a414JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9sb2NhdGlvbnMvU3Vid2F5L0x5bm53b29kLVdhc2hpbmd0b24uaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a930cfcfa0170dcdee5bc5ec7d05fc3e5da8cf2d2ca6285ab17ba9f4ca46ce6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9zYW4tZGllZ28tY291bnR5LXJlc3RhdXJhbnRzL3N1YndheS0zNDE5NS5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b8d8e0be5c407eaf08e57867033368e2850708b751715c8cb0ccb56b81124a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9ob3VzZS8zMjE4MjY4LTN4MTItdnMtM3g2LXN1YndheS10aWxlLWJhY2tzcGxhc2guaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=204305dc146fa64417b3be08f49421d7449a650260b4ba1d016f5817f0f2bc2eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9uZXcteW9yay1jaXR5LzM0NTc0Mjktc3Vid2F5LWJhbGFuY2UtcXVlc3Rpb25zLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a0b3d754c685c0f733ecec6122b44ec0e4b73f11cf533db7dd6773d61e6d6cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9mb3J1bS9uZXcteW9yay1jaXR5LzM0NDYxODctanVzdC1wb3N0ZWQtdmlkLW1vbnRyZWFsLW1ldHJvLXN1YndheS5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ca9a87c96dad8d3f28d206724dbba3ede8ad8836aa927cc9f6ecdeaa836e8c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=153ecc2f-f132-6dc7-303a-dbcef00b6cc6&amp;u=a1aHR0cHM6Ly93d3cuY2l0eS1kYXRhLmNvbS9yZXN0YXVyYW50cy9GTC9TVUJXQVktMTEzOTQuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffd52beeb8b9f1d788653edf53d81a334664933f93541014013f72f508cf5a1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=59062c38dab6ba92cec5baa7d0ea85590d90382424ee18ece8b79e795a10aab0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0dUQTYvaG90Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=99ed2a846a9136dd4f363fa92b0fc7c11d9e54647bd4017780e512d4e32205e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS9ydS9hcHAvaW5zdGFncmFtL2lkMzg5ODAxMjUy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c6b7c5f8c4124ea3b0f7ed88959079faf69339cf58402f1fa4d830f0003f97d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS91cy9hcHAvZmFjZWJvb2svaWQyODQ4ODIyMTU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4798709ad6ed63b6a15836eae595f87ddf9d27c2ad7988236a66b94fae7f120aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS91cy9hcHAvbWVzc2FnZXMvaWQxMTQ2NTYwNDcz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ce259cc987c7b08bcea8468fc31108d773f21c4e9d423f4c2f453d01f18a388JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL1RvcENoYXJhY3RlclRyb3Blcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d23b52da059bcf605e4f6c54019de797094d8cde64e4db936640044ff2932f53JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS91cy9hcHAvaW5zdGFncmFtL2lkMzg5ODAxMjUy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4bb5799fc326c03e117bf33ad4aa12bce71f6044e380cd57b351ad899c696789JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS9lcy9hcHAvaW5zdGFncmFtL2lkMzg5ODAxMjUy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0624d26b21686b9a71214111c38dda30880b6fd2f1c5a97ea6f95f8302bf28a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS9kZS9hcHAvaW5zdGFncmFtL2lkMzg5ODAxMjUy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16dd25742ac726c57287e24b1d448196dc8c54757c53cb6e654b707d745b5c97JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388a6f72-b4d8-64b8-0af3-7893b5ae65de&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS9oay9hcHAvaW5zdGFncmFtL2lkMzg5ODAxMjUy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=46fd63a1320b19e6c067a0ec98cf2161467ad87646269e653376abd23fe5d6d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cuZmVkZXguY29tL2VuLXVzL3RyYWNraW5nLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f1075e2e527352d2cf0589f1a435c8b632a3b736dac65287c3e11bc9e020b798JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cuZmVkZXguY29tL2VuLXVzL2hvbWUuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=78aba676ff3b0047250a794b8c745b7ee08a6e07fa3f05ca4781b0347e77bd98JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cuZmVkZXhmcmVpZ2h0LmNvbS9lbi11cy90cmFja2luZw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bbdb5f75732ff3174426a434a507d152fd766819ede9cd698fadbca7e19cf288JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cuZmVkZXguY29tL2VuLWNhL3RyYWNraW5nLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7bbf01c209710756d3e2d50541cb6123b72780b76b467c8b5a9da27c647bf24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cuZmVkZXguY29tL2VuLXVzL3RyYWNraW5nL2FkdmFuY2VkLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d88357d104d6429d228b13ee54363b4b9764529bd5bce8e373fa833e982c67aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly9pbWFnZXMuZmVkZXguY29tL3d0cmsvZmVkZXh0cmFja2luZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=570e12d875e7a947bced92de05eef7ac406d679040acbf498cc2577abb9b8901JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cuZmVkZXguY29tL2VuLWdiL3RyYWNraW5nLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=790d3c03b572a40aba3548488474b9de2c6ae70231bd1ceb9cfdda89ec896b41JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly93d3cub3JkZXJ0cmFja2VyLmNvbS9jYXJyaWVycy9mZWRleA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3dac014e724657a949da12b082e2acf2a266476f0ba8a765102361e16654931cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly9maWN0cmFja2luZy5mZWRleC5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae2ed4b758f33a779e7b8258cda4153967baf381a19124eaeee4a5a3374389d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2eca5f18-8723-605d-0a4c-48f986ff610b&amp;u=a1aHR0cHM6Ly9pbWFnZXMuZmVkZXguY29tL2VuLWdiL2N1c3RvbWVyLXN1cHBvcnQvZmFxL3JlY2VpdmluZy90cmFja2luZy1xdWVzdGlvbnMvd2hlcmUtaXMtbXktcGFja2FnZS5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=37fa9975a3340cbea58b8d5bc28f377ef7db010768c9e3920140f8af10d29e09JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3JlbW90ZXdvcmsvY29tbWVudHMvMTdibGx0Ny9pc19mbGV4am9ic193b3J0aF9pdC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d988ac53fdabfc2015cb6b80a913414afc60eaa4959e2b6010647d7157332804JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2pvYnMvY29tbWVudHMvMTh3enF4ZS93aGF0X2pvYl9zaXRlc19pc19ldmVyeW9uZV91c2luZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=53a51bd6bfcded14c84b97d4b0f9e3731f835be35725b28c1fb72c4a836a58eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly9lbmdsaXNoLnN0YWNrZXhjaGFuZ2UuY29tL3F1ZXN0aW9ucy85NzMxOC9pcy10aGUtcGhyYXNlLWl0cy1qdXN0LWEtbWF0dGVyLW9mLXNlbWFudGljcy1tZWFuaW5nbGVzcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0034201784934d4cfab7b6a3974cb86ad85415d866a6c469cb9cc1356998e701JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly9lbmdsaXNoLnN0YWNrZXhjaGFuZ2UuY29tL3F1ZXN0aW9ucy8zNDQ1MjMvdXNhZ2Utb2YtaW5kZWVkLWluLXRoYW5rLXlvdS12ZXJ5LW11Y2gtaW5kZWVk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e1a6bc90308caa036abb9d33c9f766887d1220b0ce0232c96761809d01e1fa3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2pvYnMvY29tbWVudHMvNXU4b3ZkL2lzX3RoZXJlX2FueXRoaW5nX2JldHRlcl90aGFuX2luZGVlZF9mb3Jfam9iLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=038f75fbbf1357e6906478c6d6cfa58a037aa5bcf4d0c9a06bf91d13ed54ab69JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2pvYnMvY29tbWVudHMvYjMyMW1pL2RvZXNfYW55b25lX2FjdHVhbGx5X2dldF9qb2JzX3Rocm91Z2hfbGlua2VkaW4v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b574a814716194bc46da0c181080975d9ea21704cc1d90d2f9af03e5fe615737JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2pvYnMvY29tbWVudHMvNXNhdmp4L2hhdmluZ19saXR0bGVfc3VjY2Vzc193aXRoX2luZGVlZGNvbV9hcmVfdGhlcmUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a78bf2fe5a91ccb394251e6364d87f1c5bc1039cec4fb2fe4d712bf4d5240e68JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3JlY3J1aXRpbmdoZWxsL2NvbW1lbnRzLzEwdWZwNXcvbGlua2VkaW5fdnNfaW5kZWVkLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4df6eec6d8ec99bc9f5d2176822bc35102a5a5d8cc68825db81b6be12048e28JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2NhcmVlcmd1aWRhbmNlL2NvbW1lbnRzLzE4bzU3ZzUvZG9feW91X2d1eXNfZXZlcl90YWtlX2NvbXBhbnlfcmV2aWV3c19zZXJpb3VzbHkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=902eb7e7b0628183e20d7215df7c3352aa8b0578a1a0b5a3b4b3e57537c51085JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2466bc8e-87c4-68f5-0efb-ab6f86f26986&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0NhbGdhcnkvY29tbWVudHMvMWFsZHY4eC9iZXN0X2pvYl9ib2FyZF9mb3JfaGlyaW5nX2xvY2Fsc19ub3RfaW5kZWVkLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=186e1aee978c480ede365645e71c4585696fff96c2c7980afd61c9335bba4fb2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=193df9d2-bcdb-62c6-0ffd-ee33bdb263df&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL1NjYW1zL2NvbW1lbnRzL3dpcDE0by91bnNvbGljaXRlZF95b3VyX25ld19hY2NvdW50X29uX3hueHhfZ29sZF9lbWFpbC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fb42e250f4017bf2b235cdc9c9843f0c7ee905c5943180773a96bfc33648794JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=193df9d2-bcdb-62c6-0ffd-ee33bdb263df&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2RhdGluZ292ZXJmaWZ0eS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4af81796163ab0f3cd5ff9043c7ea010c1bfeeec2b4e01efb52e41e01dfda212JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=193df9d2-bcdb-62c6-0ffd-ee33bdb263df&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0xlZ2FsVGVlbnMvd2lraS9pbmRleC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48a5c6c7365bbee73be0aff9a3bbeb0c7a088b4b92716b61187a25757dc66c2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=193df9d2-bcdb-62c6-0ffd-ee33bdb263df&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL1Rpa1Rvay8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b9bed1462d395598bd2d3c5644fbb6f8c1a628145152c013e2cfed0be843c59JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=193df9d2-bcdb-62c6-0ffd-ee33bdb263df&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3ZlcnlzbWFsbHRpdHMvdG9wLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae51cf8cda714b22a04b78bc0279a2d1e17d40f0e3cb01f8a25592247a74a049JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=193df9d2-bcdb-62c6-0ffd-ee33bdb263df&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2lyYW5pYW4v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb20556af5562a5abd8f86bdd429c3fdccbe49e28d7edf76e2757e2831957639JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly9ibG9nLmVudG9tb2xvZ2lzdC5uZXQvd2hhdC1idWctbG9va3MtbGlrZS1hbi1hbnQtYnV0LWZsaWVzLWFuZC1ncmF5Lmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00f23a5ce7015f331852c04e1d7f2bff99b62eb7e4466fb062b5f482537787f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly90aGVwZXRlbnRodXNpYXN0LmNvbS9idWdzLXRoYXQtbG9vay1saWtlLWFudHMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7711789ee63aa82ffcd58a834eb3d5a6aeb39b4097db40b0319949e73c9cdfc0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly93d3cuaW5zZWN0aWRlbnRpZmljYXRpb24ub3JnL2J1Z2ZpbmRlci1zdGFydC5waHA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d643c0213dcf17faddfe46807e3ab54e1fd5f8b17eccae2b34054dfa4fe010a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly9pbnNlY3RzYWR2LmNvbS9pbnNlY3RzLXRoYXQtbG9vay1saWtlLWZseWluZy1hbnRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c35ac850c5adb44e7cd26aedda98026f8d19c379eb9761eca06a582253eaf7e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly9ncmVlbnlnYXJkZW5lci5jb20vZmx5aW5nLWluc2VjdHMtdGhhdC1sb29rLWxpa2UtYW50cy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8adc96f9930b9d42eb595c623e2828f759298ac5a827f080d932c27eb14a8c19JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQW50bGlvbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a372a5978482d12ba891f1db98234314dd92e6af1b66aab7afb8c245a244549eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly93aGF0YnVnaXN0aGlzLmNvbS9lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce75e781fd8d9e692c87283791af5f2a9dc6f0e726f6cf04fe19c44ba2fbd779JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly9ibG9nLmVudG9tb2xvZ2lzdC5uZXQvd2hhdC1hcmUtdGhlLWluc2VjdHMtdGhhdC1sb29rLWxpa2UtZmx5aW5nLWFudHMuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d1c32d5d74fbedfd35cf1f3a0de7a668e1a4538bdb869dab01c6307071134bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly9ncmVlbnlnYXJkZW5lci5jb20vaW5zZWN0LXRoYXQtbG9va3MtbGlrZS1hbi1hbnQtd2l0aC13aW5ncy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2980322a8217325e9584eaf2deff5e80f9eab28edbb9e729c63eabaa490cd06JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=043d0ceb-e6bd-6164-0c33-1b0ae7ab60a2&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vSWRlbnRpZnktRmx5aW5nLUluc2VjdHM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=088e6249992dee4940fa3f493020ec5ee5efa2a0b422b2c27bd221a397d54268JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0Zvcm11bGFGZWVkZXJzL2NvbW1lbnRzLzE2dTMydTMvd2h5X2lzX2tlbmRhbWlsX25vdF9vbl9hbWF6b24v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8dc67ef950426fceffdb37c03e8216c66a6568158f940797fc24dec78c1ce33JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly93d3cuYW1hem9uLmNvbS9rZW5kYW1pbC1iYWJ5LWZvcm11bGEvcz9rPWtlbmRhbWlsK2JhYnkrZm9ybXVsYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97e71fc2c859af0b650330e7129b86d87933aa17a30504ffece52a0119e16ef1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly93d3cuYW1hem9uLmNvbS9rZW5kYW1pbC1jZXJlYWwvcz9rPWtlbmRhbWlsK2NlcmVhbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6fd423e176b8b3d8af7a617e1bf908cb6d9956a8ed24d94c58f1bcccced8a69fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly9zbnVnZ3ltb20uY29tL3doeS1pcy1rZW5kYW1pbC1mb3JtdWxhLW91dC1vZi1zdG9jay8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d862c4e63c49e42b229ee4373fc77c152768d5c49a1d28e1e13f7902d75c0542JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly90YW1hcmFydWJpbi5jb20vMjAyNC8xMS9rZW5kbWFpbC1vcmdhbmljLWNvdy1taWxrLWluZmFudC1mb3JtdWxhLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9db824250b1df22a7e2bce624ab802ac2890354820cdf35e1af129347462c02bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly91cy5rZW5kYW1pbC5jb20vcGFnZXMva2VuZGFtaWwtZ29hdC1zdG9jay11cGRhdGU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48a5a8695514a266fa879e4580072b9e7bd2e1999c001196339b1037d4813b67JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly93d3cud2FsbWFydC5jb20vYnJhbmQva2VuZGFtaWwvMTAwNTk1MTI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1e04bb53b9b2b7c992346c0f9cd28b820a918ee62e3cfe5fa0d5cf2dc0e422eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly91cy5rZW5kYW1pbC5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=efdba06fe9f969dd9a1a4862a9db421d67705095c8c86e485b21c7458566c626JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly93d3cudGFyZ2V0LmNvbS9wL2tlbmRhbWlsLW9yZ2FuaWMtaW5mYW50LWZvcm11bGEtcG93ZGVyLTI4LTJvei8tL0EtODY5MTg1ODY&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80987290fd3b37af1d07b13412bfccef68957fcc1b66e845f88dace7484679e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fb642be-eae3-68f7-3c84-555feb926936&amp;u=a1aHR0cHM6Ly9ldXJvbWFsbHVzYS5jb20vYmxvZ3MvbmV3cy93aGVyZS10by1idXkta2VuZGFtaWwtZm9ybXVsYS11c2E&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c14816c7cd5866f99d8fb1cdc939f212eafe5a3c233246cbfccf526271abf5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly93d3cuZ2VvcmdpYXByb2JhdGVyZWNvcmRzLmNvbS9NYXJyaWFnZS9TZWFyY2hNYXJyaWFnZXMuYXNweA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0859ac2e1315cc8acbc0b55dd7868951937fa68d3ccea3655d0d824ea20d84e9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly9kcGguZ2VvcmdpYS5nb3Yvd2F5cy1yZXF1ZXN0LXZpdGFsLXJlY29yZC9tYXJyaWFnZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1fe6173e92b8209d1c95c5e4bc4f2f6d4f6d9be1549be33ccdb7eb6714856e3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly93d3cuZ2VvcmdpYXByb2JhdGVyZWNvcmRzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c5aee25a73e681a52f728d6b06b670bcc953490660dbb6438f62090871324ca7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly9kcGguZ2VvcmdpYS5nb3YvZG9jdW1lbnQvZG9jdW1lbnQvcmVxdWVzdC1zZWFyY2gtbWFycmlhZ2UtZm9ybS0zOTEzL2Rvd25sb2Fk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=708f8f6c4c050234aab98f19956ba67f9a9db444f5ddb140c3b47646b4560f12JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly9tYXJyaWFnZS1saWNlbnNlLm9yZy9tYXJyaWFnZS1saWNlbnNlLXJlY29yZHMtZ2Ev&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34c20773df6b9b4b23393a087bb0baea78e8c04677ca668f4b8471ea5fe874cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly9tYXJyaWFnZXJlY29yZHMuZ2VvcmdpYW9mZmljaWFscmVjb3Jkcy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10052c0577d90858ff4d63d3b7f1b309919de751e23d5e7f5b70c814a03c4b64JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly93d3cuZG91Z2hlcnR5LmdhLnVzL0NvdXJ0cy9Qcm9iYXRlLUNvdXJ0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=444ddac726bb758448f8bc4095a36e0ae94ecb11adc94564719653f795673d9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly9nZW9yZ2lhY291cnRzLmdvdi9wY2lzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=69ecaee0292ff4885efbe3e41e1d7771881ad9a676fa3a18dee88bad0ea37377JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly93d3cuZnVsdG9ucHJvYmF0ZWdhLm9yZy8yMjcvUmVjb3Jkcy1EaXZpc2lvbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=03171a1c1f9f478d86153baa3ebb1a15304049911ddb4c6da4d4f1a4c5c61cdaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=174614b0-b35f-636d-07be-0351b2ef62d8&amp;u=a1aHR0cHM6Ly90aG9tYXNjb3VudHlib2Mub3JnL3Byb2JhdGUtY291cnQvbWFycmlhZ2UtbGljZW5zZXMtYW5kLXJlY29yZHM&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7421c039173c5d70f66551ae50bacfd04d6971ef3fc84b1c5bac85376d9e713fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3794d7eb-e863-65e2-1c1f-c00ae98d645f&amp;u=a1aHR0cHM6Ly9vbGRuYXZ5LmdhcC5jb20vP21zb2NraWQ9Mzc5NGQ3ZWJlODYzNjVlMjFjMWZjMDBhZTk4ZDY0NWY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=69e8ab44979cf3091caa6b3de16089c7b53946ac496af9a8952f4a1b10fe4ce4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3794d7eb-e863-65e2-1c1f-c00ae98d645f&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9PbGRfKGZpbG0p&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e9556ae63084839b3269f3e988038e3a4021131b01cc8b00fe14187dc26a149JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3794d7eb-e863-65e2-1c1f-c00ae98d645f&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTA5NTQ2NTIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cd2c0a30d8b5f79c970167d3261dafd3e645cbb3c2e9b6313b128cb30ab92e87JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3794d7eb-e863-65e2-1c1f-c00ae98d645f&amp;u=a1aHR0cHM6Ly93d3cucm90dGVudG9tYXRvZXMuY29tL20vb2xk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e7da9af564ccd411d69f7a6f5fe572376d2d7ffe5620c94a0c595e9b65d1082JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3794d7eb-e863-65e2-1c1f-c00ae98d645f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L29sZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f759074bcf26dd5784c3e4057e9afd8fd83b0a09af6a119ec79995628cf354c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3794d7eb-e863-65e2-1c1f-c00ae98d645f&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL29sZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa54d7a90691809bdb5b6470b303bfbabeeb4a5fad9a8500ebba571f02da6a1eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3794d7eb-e863-65e2-1c1f-c00ae98d645f&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9QTRVMnBNUlY5X2s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ab172b4ce191c437b51bd15d8ef0ca1911ab1257c41286d0e68c78a2fafe62bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3794d7eb-e863-65e2-1c1f-c00ae98d645f&amp;u=a1aHR0cHM6Ly90dnRyb3Blcy5vcmcvcG13aWtpL3Btd2lraS5waHAvRmlsbS9PbGQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cacce0280ee8afb4e87ef6994b3bef31cd17c707d2a508e48e2108d91680e992JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3794d7eb-e863-65e2-1c1f-c00ae98d645f&amp;u=a1aHR0cHM6Ly93d3cuanVzdHdhdGNoLmNvbS91cy9tb3ZpZS9vbGQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8814689170aa630a5720f052bd9d5b1c37a25178386c73a1d4bc50ece2c74e41JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3794d7eb-e863-65e2-1c1f-c00ae98d645f&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9ODR4QUQ0ci05a0U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bf5869afd8b40443fe198d88f46fce0d1d587bb730234b5a179e81d87bff2026JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31f3a1dc-d213-61d4-07be-b63dd332608d&amp;u=a1aHR0cHM6Ly9wZGYyeGwuY29tL3dwLWNvbnRlbnQvdXBsb2Fkcy8yMDE4LzA1L3JldGlyZW1lbnQtcGxhbm5pbmctc3ByZWFkc2hlZXQueGxz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=770c92d6091a49c8f8506f6f03f2990c36ccc483977eff5b7bcfc932ec1f959cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31f3a1dc-d213-61d4-07be-b63dd332608d&amp;u=a1aHR0cHM6Ly9tYWZjb21wYW5pZXMuY29tL3dwLWNvbnRlbnQvdXBsb2Fkcy9SZXRpcmVtZW50LVBsYW5uaW5nLUdBUDEueGxz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed7259068cfa2be7ebd08f02db29ad37ccdc0c0e41733cd7ebed1b992abfcac9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31f3a1dc-d213-61d4-07be-b63dd332608d&amp;u=a1aHR0cHM6Ly93d3cuZmxleGlibGVyZXRpcmVtZW50cGxhbm5lci5jb20vdG9vbHMvUmV0aXJlbWVudFdpdGhkcmF3YWxTaW11bGF0b3IueGxz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=688e660b9fa23b4b630a4fe827d40d0520b371f0698d2904a77c4154a218c147JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31f3a1dc-d213-61d4-07be-b63dd332608d&amp;u=a1aHR0cHM6Ly93d3cuc21hcnRzaGVldC5jb20vc2l0ZXMvZGVmYXVsdC9maWxlcy8yMDI1LTAyL0lDLVJldGlyZW1lbnQtRmluYW5jaWFsLVBsYW5uaW5nLTEyMzMyX1RlbXBsYXRlLnhsc3g&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e704a6c37112a26b52d17ee2c6f700e0efc8ba9f7b456c4a159015dcd60be41bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31f3a1dc-d213-61d4-07be-b63dd332608d&amp;u=a1aHR0cHM6Ly9ob21lLmFybXkubWlsL2RydW0vNTExNy8zMTA5LzYyMzgvQ1NQX1BsYW5uaW5nX0NhbGN1bGF0b3IueGxzeA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d5ca88657637c9f7f8ee24fce412b75d098fd424d7282dfc977208629023e6bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31f3a1dc-d213-61d4-07be-b63dd332608d&amp;u=a1aHR0cHM6Ly9hc3NldHMuY29iYmNvdW50eS5nb3YvZmlsZXMvMjAyNS0xMi9SZXRpcmVtZW50LUNhbGN1bGF0b3IueGxzeA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9a3316fbb6454d6b69704e3ee6a8c36b1ca14108ed6b0a05eeacdbc3fd79de2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31f3a1dc-d213-61d4-07be-b63dd332608d&amp;u=a1aHR0cHM6Ly93d3cubW9udGFuYS5lZHUvZXh0ZW5zaW9uZWNvbi9kb2N1bWVudHMvcmV0aXJlbWVudGluY29tZXdpdGhkcmF3YWx3b3Jrc2hlZXQueGxzeA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94f66fa46f571bcd3ab7dda6f91ff2d3c1d92f3d9174be27a2365be64a035c79JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31f3a1dc-d213-61d4-07be-b63dd332608d&amp;u=a1aHR0cHM6Ly93d3cucHNwcnMuY29tL3dwLWNvbnRlbnQvdXBsb2Fkcy8yMDI1LzExL1BTX0RST1BfVGllci0xX1Jldi0xMS0yMDIyLnhscw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2aa4a31c96c3f7df82587cdd21cbabaea7122c949616c35d02b6b47c0bec42aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31f3a1dc-d213-61d4-07be-b63dd332608d&amp;u=a1aHR0cHM6Ly9zcHJlYWRzaGVldGRhZGR5LmNvbS93cC1jb250ZW50L3VwbG9hZHMvMjAyMy8wOS9SZXRpcmVtZW50LUNhc2gtRmxvdy1TcHJlYWRzaGVldC1mcm9tLUdldC1TbWFydGVyLUFib3V0LU1vbmV5LWZvci1FeGNlbC54bHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ba7d44db837b5ad4eb490d36109b7ec3ab4dd848385add37239d21673b9a765JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31f3a1dc-d213-61d4-07be-b63dd332608d&amp;u=a1aHR0cHM6Ly93d3cucGxpbmRpYS5jb20vd3AtY29udGVudC91cGxvYWRzLzIwMjUvMDMvcmV0aXJlbWVudC1wbGFubmluZy54bHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7380f871e0063b06d9f001b1975a1facb2a3191716248ba70caf363be5582bb4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3df92eba-f0d3-6998-3bd9-395bf151681c&amp;u=a1aHR0cHM6Ly93d3cuc2hlcndvb2RvcmVnb24uZ292L2NvbW11bml0eS1mYWNpbGl0aWVzL3Nlbmlvci1jZW50ZXIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=087ca91d93ee6a3c8777e7e365f1dd386b27f6524eea7b54aa760cc0c0970e3dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3df92eba-f0d3-6998-3bd9-395bf151681c&amp;u=a1aHR0cHM6Ly9zZW5pb3JjZW50ZXIudXMvc2Mvc2hlcndvb2Rfc2VuaW9yX2NlbnRlcl9zaGVyd29vZF9vcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e2e5d216a4d977cb8122a2a07b76417c280ea6e5393a712a659f5d39b56c8acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3df92eba-f0d3-6998-3bd9-395bf151681c&amp;u=a1aHR0cHM6Ly9zaGVyd29vZG9yLmNpdmljcGx1c3dlYm9wZW4uY29tL21hcmpvcmllc3Rld2FydGNlbnRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aed2d3b7b3ac78aea44d38aacc61ebd400c5fdda5f3c4e3a9397de745877f587JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3df92eba-f0d3-6998-3bd9-395bf151681c&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Nlbmlvcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=77fcaa793d38462719792f376ed21a9d0bf816b0b19810456b60fd23a8c0d6aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3df92eba-f0d3-6998-3bd9-395bf151681c&amp;u=a1aHR0cHM6Ly93d3cudGhlc3ByaW5nc2xpdmluZy5jb20vc2VuaW9yLWxpdmluZy9zaGVyd29vZC9vcmVnb24vc2hlcndvb2Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d29fca41359f028ddd90ecad6d9cd76f673faa93458b1205b65bbea4907a169fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3df92eba-f0d3-6998-3bd9-395bf151681c&amp;u=a1aHR0cHM6Ly9zaHMuc2hlcndvb2QuazEyLm9yLnVzL3NjaG9vbC1pbmZvL3Nlbmlvci1pbmZvcm1hdGlvbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a04e381df4659adfdb34e6fd63567d94f1fa6f79fcb6a393ba9ce7ec96ee7b63JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3df92eba-f0d3-6998-3bd9-395bf151681c&amp;u=a1aHR0cHM6Ly93d3cuYWZ0ZXI1NS5jb20vc2VhcmNoL29yL3NoZXJ3b29k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=709d74046cfe92cf59c3e5f60991e6fd6b624870a8e2e556f9e58a9a8d4b393aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3df92eba-f0d3-6998-3bd9-395bf151681c&amp;u=a1aHR0cHM6Ly93d3cuc3Rld2FydHRlcnJhY2VzcmFwdHMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9a3c1187ed4e7afe43f25a1fddd455723d57cc6d0ee5683ba9d42500db2b845JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3df92eba-f0d3-6998-3bd9-395bf151681c&amp;u=a1aHR0cHM6Ly93d3cuYXBhcnRtZW50aG9tZWxpdmluZy5jb20vc2hlcndvb2Qtb3IvYXBhcnRtZW50cy1mb3ItcmVudC9zZW5pb3I_bXNvY2tpZD0zZGY5MmViYWYwZDM2OTk4M2JkOTM5NWJmMTUxNjgxYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4003e8b991714d62ad1eef8b9f01ebafab6f2633b67e34aa7e35765fd9434a06JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a7629ed-624c-625b-299b-3e0c637a633a&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cz9tc29ja2lkPTFhNzYyOWVkNjI0YzYyNWIyOTliM2UwYzYzN2E2MzNh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0cdc093b09e771d62a29e544903fa075588118ad0a52edd8306c37e9f2a9ae75JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a7629ed-624c-625b-299b-3e0c637a633a&amp;u=a1aHR0cHM6Ly9hY2NvdW50Lm1pY3Jvc29mdC5jb20vYWNjb3VudA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45323e001b2b722a06fdd227e9fb14e49c55357eb645daabda0486dee2e9f272JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a7629ed-624c-625b-299b-3e0c637a633a&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8187633f9040ef1b3e60dbb53b1fd37e24b9ca494ed96f3683ff606f1e5aa104JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a7629ed-624c-625b-299b-3e0c637a633a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWljcm9zb2Z0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=967019f208d28f0c433fb39f26286789234cd1e13e6056c27e8d5cdd7380054eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a7629ed-624c-625b-299b-3e0c637a633a&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cy9taWNyb3NvZnQtMzY1P21zb2NraWQ9MWE3NjI5ZWQ2MjRjNjI1YjI5OWIzZTBjNjM3YTYzM2E&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd7c7361edc37f75abbba8cb1f36ca569b738e870f47d92c40201c697e5dd117JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a7629ed-624c-625b-299b-3e0c637a633a&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS9sb2dpbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2b39f30d9bc80643d270e435f0cb3e526449e6257828f8f28d6ddd5b7987be0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a7629ed-624c-625b-299b-3e0c637a633a&amp;u=a1aHR0cHM6Ly9jYXJlZXJzLm1pY3Jvc29mdC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1cb3200066927f0fce46788e7a746e38744196351b6815c9472e86a1804c9f45JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a7629ed-624c-625b-299b-3e0c637a633a&amp;u=a1aHR0cHM6Ly9zaWdudXAubGl2ZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e967bfc7ac08e80a340affa638d0ac6bccc76e019c5e49aaa381b6242d64a58cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a7629ed-624c-625b-299b-3e0c637a633a&amp;u=a1aHR0cHM6Ly9tMzY1LmNsb3VkLm1pY3Jvc29mdC8_b3JpZ2luZG9tYWluPW1pY3Jvc29mdDM2NQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7af69022d8c8b1378138be052193c0a769ceffc318b1f13a6fd7b7ccaddea40JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a7629ed-624c-625b-299b-3e0c637a633a&amp;u=a1aHR0cHM6Ly9vdXRsb29rLm9mZmljZS5jb20vbWFpbC9pbmJveA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9cee7263544eaa69f82679b90b8561d96cbb4ed908a75592134c31b487698972JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=326d848b-275a-65c9-00a1-936a26d66428&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6580f071a44864ce8124ab428cabbede342ae4535055f00d62d33b7da54acebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=326d848b-275a-65c9-00a1-936a26d66428&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ca76c87e5a226cf20eb23aac77aef31e09796300a4a6b72e80a4b0757af6cfa5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=326d848b-275a-65c9-00a1-936a26d66428&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvZnJhaWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=599d6ffd51f9004b14fd2e60bda0e26ef6166eb623871eb764fa3be1a9ca14dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=326d848b-275a-65c9-00a1-936a26d66428&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9mcmFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fca45f9e2c1272ec31c8afa2913af2bee6f32c4e3a4c1aa19756dd729fabdf6aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=326d848b-275a-65c9-00a1-936a26d66428&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=abefcf3b4e10797c7fd8e999516d439d039aa823a3901375955cd281cc51d24bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=326d848b-275a-65c9-00a1-936a26d66428&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bdc7c051869aa1e8ab5d8ea77a028394f97ef1005badd06aa665751296d228f4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=326d848b-275a-65c9-00a1-936a26d66428&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=996a48853db82f5e18081ef1b8d840913e2b0b294367e6dd42890f98c6a8e2e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=326d848b-275a-65c9-00a1-936a26d66428&amp;u=a1aHR0cHM6Ly9lbi5tLndpa3Rpb25hcnkub3JnL3dpa2kvZnJhaWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c16472ee274a7892fd5a2aa91976704fb4419465a8a2cc7e9334c82b813e5605JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=326d848b-275a-65c9-00a1-936a26d66428&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL2RpY3Rpb25hcnkvZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=557ef09ad80a218c958d674bbd52f0f9ee968d2e8e9e57fe0d2330e08ed74f7cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=326d848b-275a-65c9-00a1-936a26d66428&amp;u=a1aHR0cHM6Ly93d3cub3hmb3JkbGVhcm5lcnNkaWN0aW9uYXJpZXMuY29tL2RlZmluaXRpb24vZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=68db4f987c1f54230bf4d568dff827a4f8e43aabba2070d413858c9c1ee65c0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b0c13e-775d-6fc0-3939-d6df767e6e51&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tZ2IvY29udGFjdHVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd270e0af24110416a247f26c0965d53a7ef07e5621b8d2897236da451d85f35JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b0c13e-775d-6fc0-3939-d6df767e6e51&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvYWNjb3VudHMtYmlsbGluZy9tYW5hZ2UvaG93LXRvLXNpZ24taW4tdG8taG90bWFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=23dce75397ac78769458bd4344bc9333a9bcba282538754ecd32aea0c7c5ec0cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b0c13e-775d-6fc0-3939-d6df767e6e51&amp;u=a1aHR0cHM6Ly90ZWNoY29tbXVuaXR5Lm1pY3Jvc29mdC5jb20vY2F0ZWdvcnkvbWljcm9zb2Z0LWNvcGlsb3QvYmxvZy9taWNyb3NvZnQtY29waWxvdC1ibG9n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07ea92e967a0c5882425d41f3f343933e8229b3aa1752f6874e3cb1f0dca96dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b0c13e-775d-6fc0-3939-d6df767e6e51&amp;u=a1aHR0cHM6Ly90ZWNoY29tbXVuaXR5Lm1pY3Jvc29mdC5jb20vYmxvZy9leGNoYW5nZS9leGNoYW5nZS1vbmxpbmUtZXdzLXlvdXItdGltZS1pcy1hbG1vc3QtdXAvNDQ5MjM2MQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b7106245f30e5c694b7b5319288867097ad15fb5b7e713779b1add96118f9ef8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b0c13e-775d-6fc0-3939-d6df767e6e51&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9kZXBsb3ltZW50L2luc3RhbGwtdXBncmFkZS9nZXR0aW5nLXJlYWR5LWZvci10aGUtd2luZG93cy0xMS11cGdyYWRl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7741e576caabb498fdd49aa72cbbd860204fa59f0e0d13ed9dbda692aa3cad3bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b0c13e-775d-6fc0-3939-d6df767e6e51&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZnItZnIvd2luZG93cy9tZXR0cmUtJUMzJUEwLWpvdXItbGVzLXBpbG90ZXMtdmlhLWdlc3Rpb25uYWlyZS1kZS1wJUMzJUE5cmlwaCVDMyVBOXJpcXVlcy1kYW5zLXdpbmRvd3MtZWM2MmY0NmMtZmYxNC1jOTFkLWVlYWQtZDcxMjZkYzFmN2I2&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9fa66fc8493a1166710570c29d14cf05379eaf74e54becf2c18c391e66833dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b0c13e-775d-6fc0-3939-d6df767e6e51&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvd2luZG93cy9ha3R1YWxpc2llcmVuLXZvbi10cmVpYmVybi0lQzMlQkNiZXItZ2VyJUMzJUE0dGUtbWFuYWdlci1pbi13aW5kb3dzLWVjNjJmNDZjLWZmMTQtYzkxZC1lZWFkLWQ3MTI2ZGMxZjdiNg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b15b81accc3d7837c1d5a2c33c92d072cad82e3adcb660dc79b18184aa4a1f0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b0c13e-775d-6fc0-3939-d6df767e6e51&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvZWRnZS9nZXR0aW5nLXRoZS1sYXRlc3QtbWljcm9zb2Z0LWVkZ2UtdXBkYXRlLWp1c3QtZ290LWVhc2llcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4efbca18831ff13884f54deed871c08392342d1c51d9979c6cd1b66d4e97c24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b0c13e-775d-6fc0-3939-d6df767e6e51&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvb3V0bG9vay90cmFpbmluZy9zaGFyZS15b3VyLWNhbGVuZGFyLWluLW91dGxvb2s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a4977f28d45bc706d7f802a5b28cfe0dea2c88c7c2a29c8990071067c8d6896JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b0c13e-775d-6fc0-3939-d6df767e6e51&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvZm9ybXMvc2lnbi1pbi10by1taWNyb3NvZnQtZm9ybXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b8234e54265fbe2332f54afdc6df99094ad27a83145238cd42d678039ce5b394JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c1d1054-fa2e-6a3d-24b9-07b5fb2b6b7a&amp;u=a1aHR0cHM6Ly93d3cuYXNobGV5ZnVybml0dXJlLmNvbS9jL2Z1cm5pdHVyZS9iZWRyb29tL2JlZHMvZnVsbC1zaXplLWJlZC8_bXNvY2tpZD0zYzFkMTA1NGZhMmU2YTNkMjRiOTA3YjVmYjJiNmI3YQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41206a7b0e103e825d9273deff66fb025cb7a6e72045d529b49948102ecc27ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c1d1054-fa2e-6a3d-24b9-07b5fb2b6b7a&amp;u=a1aHR0cHM6Ly93d3cud2F5ZmFpci5jb20vZnVybml0dXJlL3NiMS9mdWxsLWJlZC1mcmFtZXMtYzI5Njg2NS1hNTg5Nn4xNjg5OS5odG1sP21zb2NraWQ9M2MxZDEwNTRmYTJlNmEzZDI0YjkwN2I1ZmIyYjZiN2E&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0cf7a6f8c3306293a17adfc5bfe8ce46db201a9303e6c4a088f5fbac016761c1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c1d1054-fa2e-6a3d-24b9-07b5fb2b6b7a&amp;u=a1aHR0cHM6Ly93d3cubWFjeXMuY29tL3Nob3AvaG9tZS9mdXJuaXR1cmUtbWF0dHJlc3MvYmVkcm9vbS9iZWRzL0JlZF9zaXplX3QvRnVsbD9pZD0zNTM4MCZtc29ja2lkPTNjMWQxMDU0ZmEyZTZhM2QyNGI5MDdiNWZiMmI2Yjdh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24c2190323b4d05bd252552e71ca84fa0ce17c0fd2b7491412ef2e11ce533a29JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c1d1054-fa2e-6a3d-24b9-07b5fb2b6b7a&amp;u=a1aHR0cHM6Ly93d3cuaWtlYS5jb20vdXMvZW4vY2F0L2JlZHMtYm0wMDMvZi9mdWxsLWJlZHMtZi10eXBlZC1yZWZlcmVuY2UtbWVhc3VyZW1lbnQtLWZ1bGwtYmVkLWZyYW1lcy8_bXNvY2tpZD0zYzFkMTA1NGZhMmU2YTNkMjRiOTA3YjVmYjJiNmI3YQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6cc0d90b420d1393d56956dfb72384eda3d6ca02eaec832634b051e0a7aaffa0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c1d1054-fa2e-6a3d-24b9-07b5fb2b6b7a&amp;u=a1aHR0cHM6Ly93d3cuaG9tZWRlcG90LmNvbS9iL0Z1cm5pdHVyZS1CZWRyb29tLUZ1cm5pdHVyZS1CZWRzLUJlZC1GcmFtZXMvRnVsbC9OLTV5YzF2WmM3b2haMXowemFjbw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e527f495fac34185a904a653f9571146ba29e187c43cf92924c7c23ea4df7ab3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c1d1054-fa2e-6a3d-24b9-07b5fb2b6b7a&amp;u=a1aHR0cHM6Ly93d3cud2F5ZmFpci5jb20vZnVybml0dXJlL3NiMS9mdWxsLWRvdWJsZS1iZWRzLWM0NjEyMi1hMTE1fjEyNi5odG1sP21zb2NraWQ9M2MxZDEwNTRmYTJlNmEzZDI0YjkwN2I1ZmIyYjZiN2E&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b532383bd7543b8612f8b8bb1a5c93608bd0d723a004ef241b692909cce3107JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c1d1054-fa2e-6a3d-24b9-07b5fb2b6b7a&amp;u=a1aHR0cHM6Ly93d3cuYW1hem9uLmNvbS9mdWxsLWJlZHMvcz9rPWZ1bGwrYmVkcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45eed0c15c5657dcf559d4cba2484caeb57003bd93f077467a65038812a2c06fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c1d1054-fa2e-6a3d-24b9-07b5fb2b6b7a&amp;u=a1aHR0cHM6Ly93d3cuYXNobGV5ZnVybml0dXJlLmNvbS9jL2Z1cm5pdHVyZS9iZWRyb29tL2JlZHMvZnVsbC8_bXNvY2tpZD0zYzFkMTA1NGZhMmU2YTNkMjRiOTA3YjVmYjJiNmI3YQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=17e803d1ef0fa94ad4d9ef54be4368710cf0d98e422da27bc31287204a2c0939JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c1d1054-fa2e-6a3d-24b9-07b5fb2b6b7a&amp;u=a1aHR0cHM6Ly93d3cuaWtlYS5jb20vdXMvZW4vY2F0L2JlZHMtYm0wMDMvZi9mdWxsLWJlZHMtZi10eXBlZC1yZWZlcmVuY2UtbWVhc3VyZW1lbnQtLUZ1bGxfYmVkX19fMjBmcmFtZXMvP21zb2NraWQ9M2MxZDEwNTRmYTJlNmEzZDI0YjkwN2I1ZmIyYjZiN2E&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b4fcd53cf26cbf2d913d68f1b295b18d2468c8c64a2f16f7fbbb36aabdeefc06JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c1d1054-fa2e-6a3d-24b9-07b5fb2b6b7a&amp;u=a1aHR0cHM6Ly93d3cuYW1hem9uLmNvbS9GdWxsLVNpemUtQmVkL3M_az1GdWxsK1NpemUrQmVk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3e8cff3e28a24dcd10d97e0e97bdc720eb669c20977586c129a110c8a4702876JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bffe37c-08f9-62d0-2f6f-f49d093563e6&amp;u=a1aHR0cHM6Ly93d3cuY2FscGVycy5jYS5nb3YvZG9jdW1lbnRzL3BheWRheS1zY2hlZHVsZS1yZXRpcmVlcy0yMDI2L2Rvd25sb2Fk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a5a82c15c88e9f5fdbb41a17f6496120885ec13f61bdb88f87a0c6b7e2cd6c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bffe37c-08f9-62d0-2f6f-f49d093563e6&amp;u=a1aHR0cHM6Ly93d3cuY2FscGVycy5jYS5nb3YvanVkZ2VzLXJldGlyZW1lbnQtc3lzdGVtL3JldGlyZW1lbnQtY2hlY2tz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=628b7a07aee9091b6db7e1a4c5c9d5a846c4ffa9bdf5e5a9d8606898f955de9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bffe37c-08f9-62d0-2f6f-f49d093563e6&amp;u=a1aHR0cHM6Ly9uZXdzLmNhbHBlcnMuY2EuZ292LzIwMjYtcmV0aXJlbWVudC1jaGVjay1wYXlkYXlzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=064543a089a0eaff963d15787e3ff028344f205ed8400300d8e2a9c29d5253c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bffe37c-08f9-62d0-2f6f-f49d093563e6&amp;u=a1aHR0cHM6Ly93d3cuY2Fqb2JibG9nLmNvbS8yMDI2LzAxLzIwMjYtc3RhdGUtb2YtY2FsaWZvcm5pYS1wYXktZGF5cy5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87c676fbc566857cfff6f32d2b06a14812ec39cad700765f339bb65dda0acf55JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bffe37c-08f9-62d0-2f6f-f49d093563e6&amp;u=a1aHR0cHM6Ly9hcmNoaXZlLm9yZWF0ZS5haS9jb2x1bW4vb2ZmaWNpYWwtY2FscGVycy1yZXRpcmVtZW50LXBheS1kYXRlcy1mb3ItMjAyNS1hbmQtMjAyNg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c41c588ee30a6ecb0a3e07b5c3b5dfb1206b3050fb97010a19807c70ee918e03JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bffe37c-08f9-62d0-2f6f-f49d093563e6&amp;u=a1aHR0cHM6Ly9uZXdzLmNhbHBlcnMuY2EuZ292L3doYXQtcmV0aXJlZXMtbmVlZC10by1rbm93LWZvci0yMDI2Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe999c57ccefb4d0e380b6a16d2c45af40af644046569599a246827bc4024fbdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bffe37c-08f9-62d0-2f6f-f49d093563e6&amp;u=a1aHR0cHM6Ly93d3cuY2Fsc3Rycy5jb20vZmlsZXMvM2YzY2E0NGYwL0NhbFNUUlNQYXlEYXRlczIwMjYucGRm&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e7477050679a9752e18ba9779f4aed9269dd5bc0e312904418bfa97119e67cf7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d483d98-303f-605c-17ca-2a7931f961ed&amp;u=a1aHR0cHM6Ly9qcC5lcG9ybmVyLmNvbS90YWcvamFwYW5lc2UtbW9tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b4c270631d429e4bcef95918bda3692709d43e3435879143951f5890f40f6dfaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d483d98-303f-605c-17ca-2a7931f961ed&amp;u=a1aHR0cHM6Ly94aGFtc3Rlci5jb20vdGFncy9qYXBhbmVzZS1tb20&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2d4712a045832983dd70fc30b6e866c1e45a3469e3cf471593e79b825fb2ee2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d483d98-303f-605c-17ca-2a7931f961ed&amp;u=a1aHR0cHM6Ly9qYXZpZGVvLm5ldC9lbi9nZW5yZS9tb3RoZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3dc440d9176b639925710a174f2454361ace6473edddbfba0640cc6532e49558JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d483d98-303f-605c-17ca-2a7931f961ed&amp;u=a1aHR0cHM6Ly93d3cuZXBvcm5lci5jb20vdGFnL2phcGFuZXNlLW1vdGhlci8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ddf470e44757fd063ae1cf4562cca490d594bb20e7a69d4d0a5cfbb50e4e1755JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d483d98-303f-605c-17ca-2a7931f961ed&amp;u=a1aHR0cHM6Ly9oZGhvbGUuY29tL2phcGFuZXNlLW1vbS12aWRlb3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f34bbba134b8ac49c7ff558ec36b0e6f3022fcf70b8a53abec72ad635de9ec8fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d483d98-303f-605c-17ca-2a7931f961ed&amp;u=a1aHR0cHM6Ly93d3cueG54eC5jb20vc2VhcmNoL2phcGFuZXNlLW1vbQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40b9f77cb37a3a888a5acbfed96d0267c48e6f5931a3add17f48eb640d23ccedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d483d98-303f-605c-17ca-2a7931f961ed&amp;u=a1aHR0cHM6Ly9pd2Fuay50di9lbi8xMDQzNTUvamFwYW5lc2VfbW9tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6acb94ade9be5fe0338ae61fd119bc1319eeb070f33275b4794e6db6b0805cb6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d483d98-303f-605c-17ca-2a7931f961ed&amp;u=a1aHR0cHM6Ly9hbWF0dXJldHViZS5jb20vamFwYW5lc2UtbW9tLXZpZGVvcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d53729afc0310951a04f3c92524facbea6df2c9948517b14ad3029fc6d14c2d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d483d98-303f-605c-17ca-2a7931f961ed&amp;u=a1aHR0cHM6Ly93d3cucG9yem8uY29tL2NhdGVnb3J5L2phcGFuZXNlLW1vbQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00e68c1e1c69baf02bad20ad2223bc33bc35e86b4d258425978b20a94b5b9616JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d483d98-303f-605c-17ca-2a7931f961ed&amp;u=a1aHR0cHM6Ly93d3cuZXBvcm5lci5jb20vdGFnL2phcGFuZXNlLW1vbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fff687a04e2ee20dcbefbe0a7f73ed92df5a40cd634452d42779c547b60bcb90JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10908bb6-642c-6981-31c4-9c576529684e&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzM1MDQzNjg4Ng&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b4838739fda3223ce5ebc0dcd6269eac892354215b32d8f3520d7b25aa53352dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10908bb6-642c-6981-31c4-9c576529684e&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL2VuL2Fuc3dlci8yMjU5NDc2ODU0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de06f34e96b321de9548b1377950ecede878be80464a14c158249bf2d37cddfbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10908bb6-642c-6981-31c4-9c576529684e&amp;u=a1aHR0cHM6Ly9qaW5neWFuLmJhaWR1LmNvbS9hcnRpY2xlL2YwMDYyMjI4NGU3ZDE0ZmJkM2YwYzgzZS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f241a9c3123cb2bdaffaac815ab4e630b4c1362cede3fc2f181caa3f45f5d86dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10908bb6-642c-6981-31c4-9c576529684e&amp;u=a1aHR0cHM6Ly9qaW5neWFuLmJhaWR1LmNvbS9hcnRpY2xlLzBmNWZiMDk5YjNhMTkwMmQ4MjM0ZWE1MS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c6d259f1caa0836ffd3e87e83fb9e974ba7e3d7b2c4df5d64557bd09b8491370JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10908bb6-642c-6981-31c4-9c576529684e&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3RvcGljLzE5NjI4OTU3L2hvdA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1bb1fdbfb5e1f99a6df7836c19d026e7aca214d2c5f4802892e176ade7121c47JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10908bb6-642c-6981-31c4-9c576529684e&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3RhcmRpcy9iZC9hbnMvMjk1MjU4NTc3Mg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=deb87926ca726a7368867b1002e0019d71f54859a67a29b46467523dbadf8f55JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10908bb6-642c-6981-31c4-9c576529684e&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzY1NDYyMjcyMA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2446aadf8fd6c34a970d73cd801fa639bd760c46e953caeade588bc776074aadJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10908bb6-642c-6981-31c4-9c576529684e&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzM1ODk3ODY4NA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=840910168bec99d061dd6153cd00abbe32f8da8c572044644d8f63c11c5abde5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10908bb6-642c-6981-31c4-9c576529684e&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3RhcmRpcy9iZC9hcnQvMTAwODc1NDk0NA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee62452d210eb6ded8e5dc281dba912a1eefdeb31f36aca5172e988e21e112cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10908bb6-642c-6981-31c4-9c576529684e&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzMxNTk1ODkxOA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b648479142eedcf8900b8178b4e21da02815e6f9bf049775a1d7bc300687c814JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08daa012-5f4e-6e7e-2654-b7f35e586f87&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3RyYXZlbC9jb21tZW50cy8xMWp0dG5tL2ZpbmFsbHlfbWV0X3RoZV9tYWplc3RpY195ZXRfdGVycmlmeWluZ19rb21vZG8v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c5ef7b03eb4976dd141e3d928cada27bd6882fdd35ec09b1c5229d4e8c2d1784JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08daa012-5f4e-6e7e-2654-b7f35e586f87&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0hhcmRjb3JlTmF0dXJlL2NvbW1lbnRzLzEzcjVicnQva29tb2RvX2RyYWdvbl9jYW5uaWJhbGlzbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9ecbf00552be8677f35131638ac61cf34c01a27bf41fd698d8f62367c30baa2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08daa012-5f4e-6e7e-2654-b7f35e586f87&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL1ByZWhpc3RvcmljTWVtZXMvY29tbWVudHMvbWg5ZGtjL2tvbW9kb19kcmFnb25fdGhlX2xpdmluZ19kaW5vc2F1cl9saXphcmRfdGhhdC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=17d54ce94ed728ac8c99ee65ca762c2e9961b8e2be652820c0edd131e3152f89JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08daa012-5f4e-6e7e-2654-b7f35e586f87&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL05hdHVyZUlzRnVja2luZ0xpdC9jb21tZW50cy8xYzZmbXZwL2tvbW9kb19kcmFnb25fYWN0aW5nX2xpa2VfZ29kemlsbGEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0d861a82b6e419462b4363dbb4ddebaa998623b9125e7084e7b49a8cf5a1b18cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08daa012-5f4e-6e7e-2654-b7f35e586f87&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3JlcHRpbGVzL2NvbW1lbnRzL2Fmanc2Ny9rb21vZG9fZHJhZ29uc19jYW5fYmVfY3V0ZS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=078a9688267c59d127b27ba1defdf1fd29c95bbaa7c775c8030e841b6329fecdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08daa012-5f4e-6e7e-2654-b7f35e586f87&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2ludGVyZXN0aW5nYXNmdWNrL2NvbW1lbnRzLzFkZW03aHEvYV9rb21vZG9fZHJhZ29uX3NuYWNraW5nX29uX2FuX2VlbC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91491ab78606d3ace522d985a0e1ff295a821744e4b4bda35c4e47e99d3b56d0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08daa012-5f4e-6e7e-2654-b7f35e586f87&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3Bva2Vtb24vY29tbWVudHMvMzU0aG9kL3llc3RlcmRheV9zb21lb25lX21lbnRpb25lZF93ZV9kb19ub3RfaGF2ZV9hLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8cfd6dc7cf0c6a4f0288fcba27a2b2905b6462da245a488df3de54d082fcf249JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08daa012-5f4e-6e7e-2654-b7f35e586f87&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL25hdHVyZWlzbWV0YWwvY29tbWVudHMvaG9oeHhoL2tvbW9kb19kcmFnb25fZWF0aW5nX29uZV9vZl9pdHNfb3duLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b42fda8562f80392a56d6e00260c98a03e0a8891d1dbf7024c08cd91525588c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08daa012-5f4e-6e7e-2654-b7f35e586f87&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3RvZGF5aWxlYXJuZWQvY29tbWVudHMvMW4wdTMxL3RpbF9iZWZvcmVfMTkxMl90aGVfa29tb2RvX2RyYWdvbl93YXNfb25jZS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89575c677b3a7902e57e6bee34886277ca8bc3a652251c0b72af1027c55c528cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08daa012-5f4e-6e7e-2654-b7f35e586f87&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0hhcmRjb3JlTmF0dXJlL2NvbW1lbnRzL2w0NHJiOS9rb21vZG9fZHJhZ29uX2h1bnRpbmdfYV9qYXZhbl9ydXNhX2RlZXIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8a7db048a6295d6b23d5207ecb5d1ad3139b67e5e2aed62a8bc52691bd59e22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11807a49-54c0-65ef-1841-6da8557464db&amp;u=a1aHR0cHM6Ly93d3cubm9ydGhyaWRnZTR4NC5jb20vcGFydC90ajEwMDAtYXJ0ZWMtYXBleC1mcm9udC1zd2FwLWtpdC1icmFja2V0cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ea933af5a1d369c37e2974b3ed0255cb1f2975e01a6c73a1a0aef57535c76ed6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11807a49-54c0-65ef-1841-6da8557464db&amp;u=a1aHR0cHM6Ly9hcnRlY2luZHVzdHJpZXMuY29tL3Byb2R1Y3RzL3RqLXJlYXItY29pbC1jb3JyZWN0aW9uLWtpdD9fdj0xLjA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b0cf7eca92b15a457e2d8aecf4287b682e37856dc6f5bbc7426fd8598b087dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11807a49-54c0-65ef-1841-6da8557464db&amp;u=a1aHR0cHM6Ly93d3cuZWJheS5jb20vaXRtLzI3NzkwNjgyNzUzMz9tc29ja2lkPTExODA3YTQ5NTRjMDY1ZWYxODQxNmRhODU1NzQ2NGRi&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9f1725791be79ca2ed79305d2d2aa087d8a5b74f71ee0c10098851e000f09ae7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11807a49-54c0-65ef-1841-6da8557464db&amp;u=a1aHR0cHM6Ly9hcnRlY2luZHVzdHJpZXMuY29tL2NvbGxlY3Rpb25zL3RqLWJyYWNrZXRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=554eb4d51a2c2f33921ee2b064f8c330dee245fef04b01dada3dbeaf3c57da5dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11807a49-54c0-65ef-1841-6da8557464db&amp;u=a1aHR0cHM6Ly93d3cuZWJheS5jb20vcC8yNzA5ODk1NzI0OD9tc29ja2lkPTExODA3YTQ5NTRjMDY1ZWYxODQxNmRhODU1NzQ2NGRi&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ee52b6cd3d0c5a6af4121b3a01aac392077285b2fa2c0eb7f5284426dc5fbbdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11807a49-54c0-65ef-1841-6da8557464db&amp;u=a1aHR0cHM6Ly93d3cuamVlcGZvcnVtLmNvbS90aHJlYWRzL3Byb2plY3QtdGotc3RyZXRjaC10b25zLTM3cy12OC40MDQ2MzYxLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e6f6f36075647504c00726b8b0e8b8f0c8c9955e99397448ffe257b9b2bdb11bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11807a49-54c0-65ef-1841-6da8557464db&amp;u=a1aHR0cHM6Ly93d3cuamVlcGZvcnVtLmNvbS90aHJlYWRzL2FydGVjLXRqLWJhY2staGFsZi1mcmFtZS1raXQtcmVhci1zdHJldGNoLWJ1aWxkLjE4NjE3NDYvcGFnZS0y&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b800b8f43389ba3e00b814f8332030a63e97da7353bcbfe27b0dbbc3c4781506JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11807a49-54c0-65ef-1841-6da8557464db&amp;u=a1aHR0cHM6Ly9vZmZyb2Fkc291cmNlLmNvbS9hcnRlYy1hcGV4LWZyb250LXN3YXAta2l0LWJyYWNrZXRzLXRqMTAwMC1maXRzLWplZXAtd3JhbmdsZXItdGov&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81fe056d74d194abc521d8f450773132b5b91b9a4343f8127308bc7a47951be1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11807a49-54c0-65ef-1841-6da8557464db&amp;u=a1aHR0cHM6Ly9mYXN0aGVtaXMuY29tL3Byb2R1Y3RzL2FydGVjLWluZHVzdHJpZXMtOTctMDYtamVlcC13cmFuZ2xlci10ai1sai1qbC1qdC0yLXRqLWFwZXgtZnJvbnQtc3dhcC1raXQtYnJhY2tldHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=789a0d1a841f8ad7a1a2d5c09f1e4c6527064ebabddd62e01ae4f4b16813079cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11807a49-54c0-65ef-1841-6da8557464db&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2dyb3Vwcy8yNzYzNjQ5NTgxNTM0NDgv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=28e4a8ba5ff7a37cf9dada9ff30cd6efcc70149489c194fa8fea6317c42f5c3bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04f523f2-dcdb-6f74-1a92-3413dd406eb6&amp;u=a1aHR0cHM6Ly9iZWxsZXZ1ZWhpZ2guYnNkNDA1Lm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f76c82f209714f8531db061dc9985f966ca396a84006802d2dc91ac972df4fb9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04f523f2-dcdb-6f74-1a92-3413dd406eb6&amp;u=a1aHR0cHM6Ly9iZWxsZXZ1ZWhpZ2guYnNkNDA1Lm9yZy9vdXItc2Nob29sL2NvbnRhY3QtdXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=15156ce9ac0c5925bd6c697dfb03582cf8d2ba4406e3981f40c26f7488c758b3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04f523f2-dcdb-6f74-1a92-3413dd406eb6&amp;u=a1aHR0cHM6Ly93d3cuYnNkNDA1Lm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34835e9bb86116ec285dabe526f01092fec699b641b28ea3cedccbba0da623cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04f523f2-dcdb-6f74-1a92-3413dd406eb6&amp;u=a1aHR0cHM6Ly9uZXdwb3J0aGlnaC5ic2Q0MDUub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e8bf6f31a6fb6d4f5ed0d015807b6851a27967d89ec552a8df35b953e9c346eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04f523f2-dcdb-6f74-1a92-3413dd406eb6&amp;u=a1aHR0cHM6Ly93d3cuYnNkNDA1Lm9yZy9wcm9ncmFtcy1hbmQtc2VydmljZXMvZmFjaWxpdGllcy9wZXJmb3JtaW5nLWFydHMtY2VudGVycw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=174246de7ba95261a35f7cc8b3284e2ed04c6c3628fa4f76d88b5a38cfdd17aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04f523f2-dcdb-6f74-1a92-3413dd406eb6&amp;u=a1aHR0cHM6Ly9zYW1tYW1pc2hoaWdoLmJzZDQwNS5vcmcvY291bnNlbGluZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d754aad5a13426a9a958cf5806a76606980d4518e57da82ea4699082e155e228JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04f523f2-dcdb-6f74-1a92-3413dd406eb6&amp;u=a1aHR0cHM6Ly9uZXdwb3J0aGlnaC5ic2Q0MDUub3JnL291ci1zY2hvb2wvbmV3cy9uZXdzLWRldGFpbHMvfmJvYXJkL2JzZC1uZXdzL3Bvc3QvMjAyNi1uYXRpb25hbC1tZXJpdC1zY2hvbGFyc2hpcC1wcm9ncmFt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d367cc47634414965be8ccdf4b4ff9ca7561863f60d1f7d9f67c7e46f1fed3dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04f523f2-dcdb-6f74-1a92-3413dd406eb6&amp;u=a1aHR0cHM6Ly9pbnRlcmxha2VoaWdoLmJzZDQwNS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b8bfa600b7d80cca11df4618d173ad6f55cb96bd4882b2af3fca0cbbb86c0aa7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04f523f2-dcdb-6f74-1a92-3413dd406eb6&amp;u=a1aHR0cHM6Ly9oaWdobGFuZC5ic2Q0MDUub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80a040ec3756082b80eff7d4ea62a84045300cb1202a13404bd690588db8612fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04f523f2-dcdb-6f74-1a92-3413dd406eb6&amp;u=a1aHR0cHM6Ly9zYW1tYW1pc2hoaWdoLmJzZDQwNS5vcmcvb3VyLXNjaG9vbC9jb250YWN0LXVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5d8a7566865566950daad45ef87329c178ba36f5ce1661d9c9cf0b89e6d9728JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26f2fdea-d40f-601a-2315-ea0bd5d56106&amp;u=a1aHR0cHM6Ly9zbGF0ZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c4066199e5619173faa904990959a4b8e1a38e39abe4804f629ad1c2d66a8218JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26f2fdea-d40f-601a-2315-ea0bd5d56106&amp;u=a1aHR0cHM6Ly9zbGF0ZS5jb20vbmV3cy1hbmQtcG9saXRpY3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=565a689060a0ed8960c94485df807f36700f8a312053c4eceaf82ebd49474820JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26f2fdea-d40f-601a-2315-ea0bd5d56106&amp;u=a1aHR0cHM6Ly9zbGF0ZS5jb20vaHVtYW4taW50ZXJlc3Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ab33e2071700f2a8e666eab936fc1738edbd5277d5671afc1e7079037b54c12JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26f2fdea-d40f-601a-2315-ea0bd5d56106&amp;u=a1aHR0cHM6Ly9zbGF0ZS5jb20vaHVtYW4taW50ZXJlc3QvZGVhci1wcnVkZW5jZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c384eaa11e1bc7dd28fa843d4e76abfb80c4fb2fcdb69f149aee345f533ab22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26f2fdea-d40f-601a-2315-ea0bd5d56106&amp;u=a1aHR0cHM6Ly9zbGF0ZS5jb20vY3VsdHVyZS8yMDI2LzAzL3RoZW8tb2YtZ29sZGVuLWJvb2stcmV2aWV3LWFsbGVuLWxldmktYmVzdHNlbGxlci5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cd79e110a4ea59f17d0162819bf28bf0957510028fa9f9c2e3e51cfb4f5a0b97JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26f2fdea-d40f-601a-2315-ea0bd5d56106&amp;u=a1aHR0cHM6Ly9zbGF0ZS5jb20vbmV3cy1hbmQtcG9saXRpY3MvdGhlLXNsYXRlc3Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a78305b55516513e7e654e256f5cd236eb45e7f16e8858c2dc0124df5b8edcd2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26f2fdea-d40f-601a-2315-ea0bd5d56106&amp;u=a1aHR0cHM6Ly9zbGF0ZS5jb20vbGlmZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0977ff54a0a6521c447376889a43d6e6cfce7fa0e1e78aae48131319e6153c06JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26f2fdea-d40f-601a-2315-ea0bd5d56106&amp;u=a1aHR0cHM6Ly9zbGF0ZS5jb20vdGFnL3NsYXRlLWdhbWVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=63fbfd0e5be947a0ed1f5740b6f30aec67ba98d893221006b40e7b3cccf63131JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26f2fdea-d40f-601a-2315-ea0bd5d56106&amp;u=a1aHR0cHM6Ly9zbGF0ZS5jb20vbmV3cy1hbmQtcG9saXRpY3MvMjAyNi8wMy9pcmFuLXdhci1kb25hbGQtdHJ1bXAtbmV3cy10dWNrZXItY2FybHNvbi5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1db7a5400e9e3f1fe6ac669f66abe2054362916081a88c5a8e38287d1f99c15bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26f2fdea-d40f-601a-2315-ea0bd5d56106&amp;u=a1aHR0cHM6Ly9zbGF0ZS5jb20vbGlmZS8yMDI2LzA4L2Nyb3Nzd29yZC1zbGF0ZS1kYWlseS1wdXp6bGUtYXVnLTI4LTIwMjYuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cdd966a6c1c339c82137f475ab0971a5fbf26361bcad1f071dd63d51d5d68b4eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d36dbdd-7297-66e6-361e-cc3c730e67a0&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9CaWxsX0dhdGVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0b0e46648034baa4e2cb5888ab984cce8ea2af46db2b9b65fc06894607ccf52fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d36dbdd-7297-66e6-361e-cc3c730e67a0&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vbW9uZXkvQmlsbC1HYXRlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed82498e0ac397c50a1c62f3d73c6adc618ba47a7d5bcd957546e9fa56f09692JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d36dbdd-7297-66e6-361e-cc3c730e67a0&amp;u=a1aHR0cHM6Ly93d3cuYmlvZ3JhcGh5LmNvbS9idXNpbmVzcy1sZWFkZXJzL2JpbGwtZ2F0ZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=707e0fc07dca6d18481d3d425dd4d0b699f0ed6672d3b9d4719b224c75e905c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d36dbdd-7297-66e6-361e-cc3c730e67a0&amp;u=a1aHR0cHM6Ly93d3cuZm9yYmVzLmNvbS9wcm9maWxlL2JpbGwtZ2F0ZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=298fe406a06aa7f1062110033930c6aae94e44128c39dc8fd8a12cd1bd629732JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d36dbdd-7297-66e6-361e-cc3c730e67a0&amp;u=a1aHR0cHM6Ly93d3cuaW52ZXN0aW5nLmNvbS9hY2FkZW15L3N0YXRpc3RpY3MvYmlsbC1nYXRlcy1mYWN0cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=abddd3f3ba105c162fb3f35ad46b7c0d679e3ce1524c59de7c64a85ea1630046JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d36dbdd-7297-66e6-361e-cc3c730e67a0&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vZmFjdHMvQmlsbC1HYXRlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9f0c2242667dc4570462fe336006adb20e922e287c12e7564740363bde720139JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d36dbdd-7297-66e6-361e-cc3c730e67a0&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvQmlsbF9HYXRlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=62d4c2bee3a58f14392147021398c4d66caba6b1c68c923ce953ddc6e7c18669JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d36dbdd-7297-66e6-361e-cc3c730e67a0&amp;u=a1aHR0cHM6Ly93d3cuYnVzaW5lc3NpbnNpZGVyLmNvbS9iaWxsLWdhdGVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=db9fa853b6f8eb31d5a87de755dbddb8f4a9bbeca9a08e2768fb6967c03e7f1aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d36dbdd-7297-66e6-361e-cc3c730e67a0&amp;u=a1aHR0cHM6Ly93d3cuZ2F0ZXNub3Rlcy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6cd0dfb9dbcd899cdbf558d5a4d990848bd381addf3931e229f39194230871cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d36dbdd-7297-66e6-361e-cc3c730e67a0&amp;u=a1aHR0cHM6Ly93d3cud2lraXdhbmQuY29tL2VuL0JpbGxfR2F0ZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10919610b8c02609541c3525b39c062da661cb098f0195f609c79fb29e50720fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dcde696-ec5c-6843-28af-f177ed256900&amp;u=a1aHR0cHM6Ly93d3cuaW52ZXN0b3IuZmlzZ2xvYmFsLmNvbS9maW5hbmNpYWwtaW5mb3JtYXRpb24vYW5udWFsLXJlcG9ydHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c981e24fdcf9d93f19c9218b48c826a2ad0f73fc7dd18203795ecc48cb830e13JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dcde696-ec5c-6843-28af-f177ed256900&amp;u=a1aHR0cHM6Ly93d3cuaW52ZXN0b3IuZmlzZ2xvYmFsLmNvbS9maW5hbmNpYWwtaW5mb3JtYXRpb24vc2VjLWZpbGluZ3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f1d2b791567643e2ed2bb3a291320d191e755c25f3a9dca397dfa8871168064eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dcde696-ec5c-6843-28af-f177ed256900&amp;u=a1aHR0cHM6Ly9zdG9ja2xpZ2h0LmNvbS9zdG9ja3MvdXMvbnlzZS1maXMvZmlkZWxpdHktbmF0aW9uYWwtaW5mb3JtYXRpb24tc2VydmljZXMvYW5udWFsLXJlcG9ydHMvbnlzZS1maXMtMjAyNi0xMEstMjY2NzE4ODMucGRm&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f16aba50ee7d3c45763c279adb85adcc336a5170915295a80b89d0ddc5977bb9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dcde696-ec5c-6843-28af-f177ed256900&amp;u=a1aHR0cHM6Ly9hcHAuc3RvY2tsaWdodC5jb20vc3RvY2tzL3VzL255c2UtZmlzL2ZpZGVsaXR5LW5hdGlvbmFsLWluZm9ybWF0aW9uLXNlcnZpY2VzL2FubnVhbC1yZXBvcnRzL255c2UtZmlzLTIwMjQtMTBLLTI0Njc4OTQyLnBkZg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=deaeb080848f70ba823e142564fc909d50f58bdbbc7f0cffb9bfeadbbf07a25eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dcde696-ec5c-6843-28af-f177ed256900&amp;u=a1aHR0cHM6Ly93d3cuc2VjLmdvdi9lZGdhci9icm93c2UvP0NJSz0wMDAxMTM2ODkz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8650c36de2783673520bc772d9003c5f6538f9f77c4f850cce22777b422e33d4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dcde696-ec5c-6843-28af-f177ed256900&amp;u=a1aHR0cHM6Ly93d3cubWFya2V0YmVhdC5jb20vc3RvY2tzL05ZU0UvRklTL3NlYy1maWxpbmdzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c37b88fbd4718c21fe133debae2228c3cf951e8fa56fd9ead100710903cd184eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dcde696-ec5c-6843-28af-f177ed256900&amp;u=a1aHR0cHM6Ly9sYXN0MTBrLmNvbS9zZWMtZmlsaW5ncy9maXMvMDAwMTEzNjg5My0yNS0wMDAwMTQuaHRt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=78b12ee549eab431664f2a268516c4b4cda41f13a8f4d5b95e40be2a185f70c0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a1d904b-f1d9-6474-04ca-87aaf02b65a1&amp;u=a1aHR0cHM6Ly9mb3J1bS5pbmRleC5odS9Ub3BpYy9zaG93VG9waWNMaXN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5002297b6a0a367984ce94e3e87f3482cc79e515843bcd4317f9a8e011764a2dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a1d904b-f1d9-6474-04ca-87aaf02b65a1&amp;u=a1aHR0cHM6Ly9mb3J1bS5pbmRleC5odS9BcnRpY2xlL3Nob3dBcnRpY2xlP3Q9OTE5NjE4Nw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27639110ba05ed800f92c31d142c88da85c9da20ae9e711f5c913d40379b79e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a1d904b-f1d9-6474-04ca-87aaf02b65a1&amp;u=a1aHR0cHM6Ly9mb3J1bS5pbmRleC5odS9BcnRpY2xlL3Nob3dBcnRpY2xlP2dvPTUwNTc4ODM0JnQ9MTAwMjIxNA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=26c071e9cb7ed034786b41fdbfcfaf3c713dd5c419222d5b8d1e5c9a3f50791bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a1d904b-f1d9-6474-04ca-87aaf02b65a1&amp;u=a1aHR0cHM6Ly9mb3J1bS5pbmRleC5odS9BcnRpY2xlL3Nob3dBcnRpY2xlP3Q9OTIxNzQ1MQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=547094e1900337b8901873ba0947c748502124b403dc63b5cca3369be00b52a1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a1d904b-f1d9-6474-04ca-87aaf02b65a1&amp;u=a1aHR0cHM6Ly9mb3J1bS5pbmRleC5odS9BcnRpY2xlL3Nob3dBcnRpY2xlP3Q9OTE2NTE3MA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8185d9f26912922f8aa153ad93da4cba245dadeb8cf146d62f1cdd464aae78b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a1d904b-f1d9-6474-04ca-87aaf02b65a1&amp;u=a1aHR0cHM6Ly9mb3J1bS5pbmRleC5odS9BcnRpY2xlL3Nob3dBcnRpY2xlP3Q9OTI1NjEyOQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba51d1e73baac435e4d66b3642ac204ceb235d2627dad04f09bac20cd5a83fafJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a1d904b-f1d9-6474-04ca-87aaf02b65a1&amp;u=a1aHR0cHM6Ly9mb3J1bS5pbmRleC5odS9BcnRpY2xlL3Nob3dBcnRpY2xlP3Q9OTI2MDAyOA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ca8c6147f55c2727a92821370ecbeb93e021da427a03a7052a3b7d2abbce6464JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba57d09-f20b-65d0-1bf7-6ae8f3296436&amp;u=a1aHR0cHM6Ly93d3cudGFyZ2V0LmNvbS9zbC9xdWVlbnNidXJ5LzE4MzA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bf5dcbf6f6b5ac36c2bec96d268ae36958c943fbeeddc597c52fb67021fe1fa0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba57d09-f20b-65d0-1bf7-6ae8f3296436&amp;u=a1aHR0cHM6Ly93d3cudGFyZ2V0LmNvbS9zbC9xdWVlbnNidXJ5LzE4MzAvZ3JvY2VyeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c5cf4b5723c957d15f86c45f9ba2c014ec9f4c656287f6e8c951aedda2debd45JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba57d09-f20b-65d0-1bf7-6ae8f3296436&amp;u=a1aHR0cHM6Ly93d3cuc3RvcmVvcGVuaW5naG91cnMuY29tL3RhcmdldC1xdWVlbnNidXJ5LW55&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4da1413952627e1ec7bb8b16da3a4ebb04d7f7d5954aee716ef78eba0fc7422JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba57d09-f20b-65d0-1bf7-6ae8f3296436&amp;u=a1aHR0cHM6Ly93d3cuc3RvcmVzaW5mby5jb20vdGFyZ2V0L25ldy15b3JrL3F1ZWVuc2J1cnkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fcd987fc0fba7f1261b8acd8a1075934cccbe1498dae4eedf76ebee1d620de47JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba57d09-f20b-65d0-1bf7-6ae8f3296436&amp;u=a1aHR0cHM6Ly93d3cubG9jOG5lYXJtZS5jb20vbmV3LXlvcmsvcXVlZW5zYnVyeS90YXJnZXQvNDg1MTkyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ba12537fe54394cd5c14f94d1abc46f910a199fc924e3700f970d4ba12fe3e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba57d09-f20b-65d0-1bf7-6ae8f3296436&amp;u=a1aHR0cHM6Ly93d3cubXlzdG9yZTQxMS5jb20vc3RvcmUvdmlldy81NzY3L1RhcmdldC1RdWVlbnNidXJ5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd44e3e6294e91ba80cb63296bc0b52d142d2ef88b346d7fec0060a423ce59acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba57d09-f20b-65d0-1bf7-6ae8f3296436&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL3F1ZWVuc2J1cnktbnkvbWlwL3RhcmdldC02MDMwMzEw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e10f416af01e636f1a2c5ddd5425bde33e396dc6b1e28e5644e5ce8e22675ff4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba57d09-f20b-65d0-1bf7-6ae8f3296436&amp;u=a1aHR0cHM6Ly9sb2NhbC55YWhvby5jb20vaW5mby0xNDMzNjUwNzUtdGFyZ2V0LXF1ZWVuc2J1cnkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81529ebcab53db43493620428300e5819ce2eec1f14b874a5444337c8abf2242JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba57d09-f20b-65d0-1bf7-6ae8f3296436&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vYml6L3RhcmdldC1xdWVlbnNidXJ5LTI_bXNvY2tpZD0wYmE1N2QwOWYyMGI2NWQwMWJmNzZhZThmMzI5NjQzNg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75e433e1aee4a932a76ecd611a4ca699f075f8b23fc76a5e300d7d3dc01a148dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba57d09-f20b-65d0-1bf7-6ae8f3296436&amp;u=a1aHR0cHM6Ly93d3cuc3RvcmVzaW5mby5jb20vdGFyZ2V0L25ldy15b3JrL3F1ZWVuc2J1cnkvNTc4LWF2aWF0aW9uLXJkLXN0ZS0xcy5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fef7b52971c9fe0f8720e662e0e1216bc1178163d6169f787111fc84d7e23d1fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235b5119-a9ce-6bac-3281-46f8a8466a4f&amp;u=a1aHR0cHM6Ly90cmFuc2xhdGUuZ29vZ2xlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d48e9c462a48b29e3efb49e64c1478e6b25008c19fb369c1ab5a0cf3c08e679JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235b5119-a9ce-6bac-3281-46f8a8466a4f&amp;u=a1aHR0cHM6Ly90cmFuc2xhdGUuZ29vZ2xlLmNvbS9hYm91dC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=53cd7fffb9ef47d32bcf3ffd27ab2b05984c2b09efdafc9584e10025b48688ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235b5119-a9ce-6bac-3281-46f8a8466a4f&amp;u=a1aHR0cHM6Ly90cmFuc2xhdGUuZ29vZ2xlLmNvbS9pbnRsL2VzLTQxOS9hYm91dC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cd5243080ba76386e1d05a1e4ae761e3fdd1a1e371d8eba3481ff8fd90d3ab47JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235b5119-a9ce-6bac-3281-46f8a8466a4f&amp;u=a1aHR0cHM6Ly90cmFuc2xhdGUuZ29vZ2xlLmNvbS9pbnRsL2VzL2Fib3V0Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d9f28e57cf91922181f756b97d236401799a4facdc91008cc55d7fde2a56b3bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235b5119-a9ce-6bac-3281-46f8a8466a4f&amp;u=a1aHR0cHM6Ly90cmFuc2xhdGUuZ29vZ2xlLmNvbS9pbnRsL2NzL2Fib3V0Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e72f48d2445b4053f007d4f03f432cf8928517e4d6d809f7a3e4bb498320c31aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235b5119-a9ce-6bac-3281-46f8a8466a4f&amp;u=a1aHR0cHM6Ly90cmFuc2xhdGUuZ29vZ2xlLmNvbS9pbnRsL25sL2Fib3V0Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=166cb031fa158ea928209248966adcfeac714238ebf98cc5299e6a1f2e6090b2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235b5119-a9ce-6bac-3281-46f8a8466a4f&amp;u=a1aHR0cHM6Ly90cmFuc2xhdGUuZ29vZ2xlLmNvbS9pbnRsL2ZyLUNBL2Fib3V0Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d3a7274717a1c91ba254c612724c9aa0528e98435418000a41143d9e7be9c0e6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ae5924d-5f72-6bb2-3139-85ac5ec86a35&amp;u=a1aHR0cHM6Ly9hcmNoaXZlLm9yZy9kZXRhaWxzL3ZwclVfdGFpdHRpcml5YS11cGFuaXNoYWQtd2l0aC1zaGFua2FyYS1iaGFzeWEtY29tbWVudGFyeS1hbmFuZC1naXJpLWJ5LXZpbmF5YWstZ2FuZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a4722be68257a81655b6601f2d7360ac99664ecc35e5cf9b59e115437283f12JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ae5924d-5f72-6bb2-3139-85ac5ec86a35&amp;u=a1aHR0cHM6Ly93d3cuc2NyaWJkLmNvbS9kb2N1bWVudC81MTE1NDE3NDcvVGFpdHRpcml5YS1VcGFuaXNoYWQtU2hhbmthcmFjaGFyeWEtQmhhc2h5YS1Fbmc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fed2cf441c49cb2a710e67defb98c1b9d24716e47aaa23330012218047e54d40JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ae5924d-5f72-6bb2-3139-85ac5ec86a35&amp;u=a1aHR0cHM6Ly93d3cuc2NyaWJkLmNvbS9kb2N1bWVudC80MDE1NjQ5NTQvU2hhbmthcmEtQmhhc2h5YS1UYWl0dGlyaXlhLVVwYW5pc2hhZC1XaXRoLUJoYXN5YXMtb2YtU3VyZXN2YXJhLVNheWFuYS1wZGY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f050ef696efba7a7cc309fef88088ceb140b3c5947465a995607fb20a98e723JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ae5924d-5f72-6bb2-3139-85ac5ec86a35&amp;u=a1aHR0cHM6Ly9zZnZlZGFudGEub3JnL2Jvb2tzL3RhaXR0aXJpeWEtdXBhbmlzYWQtd2l0aC10aGUtY29tbWVudGFyeS1vZi1zYW5rYXJhY2FyeWEtZ2FtYmhpcmFuYW5kYS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=39f0a56393c3909fdde57e978233a4d8fe9c4bf8fc6061159163bc7da1201a40JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ae5924d-5f72-6bb2-3139-85ac5ec86a35&amp;u=a1aHR0cHM6Ly93d3cud2lzZG9tbGliLm9yZy9oaW5kdWlzbS9ib29rL3RoZS10YWl0dGlyaXlhLXVwYW5pc2hhZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e860ae729bdb848b1dfb8c018fd3ffdc3d589eb5bd84eee306f091189499166JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ae5924d-5f72-6bb2-3139-85ac5ec86a35&amp;u=a1aHR0cHM6Ly93d3cud2lzZG9tbGliLm9yZy9oaW5kdWlzbS9ib29rL3RhaXR0aXJpeWEtdmFydGlrYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80f69b3c8a1115c21dd5f76fd808f75c3df7e57e64ff0752b3c03fd2e005604eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ae5924d-5f72-6bb2-3139-85ac5ec86a35&amp;u=a1aHR0cHM6Ly9hcmNoaXZlLm9yZy9kZXRhaWxzL25Jd25fdGFpdGlyaXlhLXVwYW5pc2hhZC13aXRoLXRyYW5zbGF0ZWQtc2hhbmthcmEtYmhhc2h5YS1naXRhLXByZXNz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b327250dc8c7f36c9e1c9a92f3e9d5fc5c789d9104ee86ff5e8cee08963c171cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=389973e3-9860-6d15-1abf-640299496c19&amp;u=a1aHR0cHM6Ly9hbnN3ZXJzLm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9mb3J1bS9hbGwvdmlydXMtdGhhdC10dXJucy1vbi1jb21wdXRlci1hZnRlci15b3Utc2h1dC1pdC8zMzllN2U1My1hNDkxLTQ3Y2ItYTE0Yi1hNDA3YmNlMmUwYWI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e34322908eb57f33b2ced6931ba9e119a979a0044227a28ab59b473116a50717JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=158ac761-fcaf-619d-1ce0-d080fd15600a&amp;u=a1aHR0cHM6Ly93d3cuYWxscmVjaXBlcy5jb20vcmVjaXBlLzE4NzgyMi9iYWtlZC1jaGlja2VuLXdpbmdzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=278f9214319a74eec379ff1fcf4394c79f35de3e1d69862f86348dc71e546d05JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=158ac761-fcaf-619d-1ce0-d080fd15600a&amp;u=a1aHR0cHM6Ly90aGVzdGF5YXRob21lY2hlZi5jb20vY2hpY2tlbi13aW5ncy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4611adf07cd78ea680b86ba5c21aa607cb9159e8a072b8e2f6a5d38fd52c7acbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=158ac761-fcaf-619d-1ce0-d080fd15600a&amp;u=a1aHR0cHM6Ly90aGVraXRjaGVuZ2lybC5jb20vYmFrZWQtY2hpY2tlbi13aW5ncy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0daebf409797f14b8d818532ca2b5aa6a6cae64adae95d44cb0028e2fd7f45cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=158ac761-fcaf-619d-1ce0-d080fd15600a&amp;u=a1aHR0cHM6Ly93d3cuYWxscmVjaXBlcy5jb20vcmVjaXBlLzI3NDY1My9vdmVuLWJha2VkLWNoaWNrZW4td2luZ3Mv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d0d1672565f729b87b2bc012dac0f0b88c9a196656b26f9b1a72807f761c04cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=158ac761-fcaf-619d-1ce0-d080fd15600a&amp;u=a1aHR0cHM6Ly9jaGlja2VuaW50aGVwYW4uY29tL2NoaWNrZW4td2luZ3MtaW4tb3Zlbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=84fe0312488d69c3a0520dba1288905efe90d74e6c9d65d7ee92eeb9470307c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=158ac761-fcaf-619d-1ce0-d080fd15600a&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL3JlY2lwZXMvYmFrZWQtY2hpY2tlbi13aW5ncy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24bc123c0902e6ce02a060e2baf2c97188ba23fd0f5d8397b478098c92aa2846JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=158ac761-fcaf-619d-1ce0-d080fd15600a&amp;u=a1aHR0cHM6Ly9uYXRhc2hhc2tpdGNoZW4uY29tL2Jha2VkLWNoaWNrZW4td2luZ3Mv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ec83e57be7415732f9d4374a211c52685b0e66de04f23439ce338a4b8cd3974dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=158ac761-fcaf-619d-1ce0-d080fd15600a&amp;u=a1aHR0cHM6Ly9jcmF2aW5ndGFzdHkuY29tL2Jha2VkLWNoaWNrZW4td2luZ3MtZXh0cmEtY3Jpc3B5Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2dd64fcd6d55b0ab00333354253a08db5e28a27b8c5b7e714ffeca23485ad674JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=158ac761-fcaf-619d-1ce0-d080fd15600a&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zL2Jha2VkLWNoaWNrZW4td2luZ3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6b8f198508eac1c2ec541871c62e67a33a1d3e21a331ea8ead1903b3366b56cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=158ac761-fcaf-619d-1ce0-d080fd15600a&amp;u=a1aHR0cHM6Ly93d3cud2hvbGVzb21leXVtLmNvbS9iYWtlZC1jaGlja2VuLXdpbmdzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25ca63df76f7835b2942513d7f246eedebac586cf47f5063e8c0ccd6cb4ca093JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123755fe-377f-6835-2cb3-421f365c69fb&amp;u=a1aHR0cHM6Ly93d3cudmlzaXRvcmxhbmRvLmNvbS90aGluZ3MtdG8tZG8vdGhlbWUtcGFya3Mv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8fad79954eceb76f857d0cf70be93d0f3141fdbf4fd01292dad16f5e095382cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123755fe-377f-6835-2cb3-421f365c69fb&amp;u=a1aHR0cHM6Ly93d3cudmlzaXRvcmxhbmRvLmNvbS90aGluZ3MtdG8tZG8v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e542d2fac1169055181857107c21b3db5621a5d0cc9e0646b858bbc5dce21dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123755fe-377f-6835-2cb3-421f365c69fb&amp;u=a1aHR0cHM6Ly9kZS52aXNpdG9ybGFuZG8uY29tL2FrdGl2aXRhZXRlbi90aGVtZW5wYXJrcy91bml2ZXJzYWwtb3JsYW5kby1yZXNvcnQv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4076dfc879138b320cdb181922f2c04b84f26a05f3f0c7b73e826ad86a605ad8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123755fe-377f-6835-2cb3-421f365c69fb&amp;u=a1aHR0cHM6Ly9kZS52aXNpdG9ybGFuZG8uY29tL2FrdGl2aXRhZXRlbi90aGVtZW5wYXJrcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=49b610bb07c9fe122718335093d9001a0afd92e60f6d429b2ac2ff1f37bd70d4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123755fe-377f-6835-2cb3-421f365c69fb&amp;u=a1aHR0cHM6Ly93d3cudmlzaXRvcmxhbmRvLmNvbS90aGluZ3MtdG8tZG8vdGhlbWUtcGFya3Mvd2FsdC1kaXNuZXktd29ybGQtcmVzb3J0L2hvbGx5d29vZC1zdHVkaW9zLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cf709333ac37371715d6b63ea1c05596c16bf945d62d5c2c90c73acd60461defJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123755fe-377f-6835-2cb3-421f365c69fb&amp;u=a1aHR0cHM6Ly93d3cudmlzaXRvcmxhbmRvLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cec490856176625997af9509d9319d48e69802336766436772b3a94452388214JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123755fe-377f-6835-2cb3-421f365c69fb&amp;u=a1aHR0cHM6Ly93d3cudmlzaXRvcmxhbmRvLmNvbS90aGluZ3MtdG8tZG8vdGhlbWUtcGFya3Mvc2Vhd29ybGQtb3JsYW5kby8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7be74d84b4b6545729de75a05cbf1f448656f349f64b7f51a36679ae5daf941bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123755fe-377f-6835-2cb3-421f365c69fb&amp;u=a1aHR0cHM6Ly93d3cudmlzaXRvcmxhbmRvLmNvbS90aGluZ3MtdG8tZG8vdGhlbWUtcGFya3Mvd2FsdC1kaXNuZXktd29ybGQtcmVzb3J0Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0afeded05d995ec92e692ed71351bbe17cd5fa972843638d211111e023c01b4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123755fe-377f-6835-2cb3-421f365c69fb&amp;u=a1aHR0cHM6Ly93d3cudmlzaXRvcmxhbmRvLmNvbS90aGluZ3MtdG8tZG8vdGhlbWUtcGFya3MvdW5pdmVyc2FsLW9ybGFuZG8tcmVzb3J0Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c1e1fbe99062c698e44311af77b467173d48c85889215dd82a2637fcb8979e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=123755fe-377f-6835-2cb3-421f365c69fb&amp;u=a1aHR0cHM6Ly93d3cudmlzaXRvcmxhbmRvLmNvbS9ibG9nL3Bvc3QvY2hlYXAtdGhpbmdzLXRvLWRvLW9ybGFuZG8v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=abb99ea528c3009af5185cecbe41445186b1e02a04cb9083152cbcae9d4914e9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d5fc67e-ed82-6876-0ded-d19fecc2695f&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vd2Vic2VhcmNoL3RocmVhZC8yMTQ1MTgyODYvaS10cnktcG9ybi1odWItYmxva2luLWJ1dC1pYW0tZmFpbC1ob3ctdG8tYmxvY2stcG9ybj9obD1lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ec4a616d6346efa6e6b7afb0307af698ab4fe84b59199e39860b1341ec43346cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d5fc67e-ed82-6876-0ded-d19fecc2695f&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lL2Fuc3dlci85NTM0Nj9obD1mYSZjbz1HRU5JRS5QbGF0Zm9ybSUzRERlc2t0b3A&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=547a7e5fc0985e19427c23775710f373d2f409cbc1ab1eda6a9b095a7ee18f5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d5fc67e-ed82-6876-0ded-d19fecc2695f&amp;u=a1aHR0cHM6Ly9mb3J1bXMucGVubnktYXJjYWRlLmNvbS9kaXNjdXNzaW9uLzIyMjk1NC84LXJvYWRzLXRvLXVuaXZlcnNhbC1kZW1vY3JhdGljLWhlYWx0aC1jYXJlLXBsYW5zL3A2&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f5278068f457877c2dc17993c4fe9a354c225343940108039b19f0082adad8fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d5fc67e-ed82-6876-0ded-d19fecc2695f&amp;u=a1aHR0cHM6Ly9mb3J1bXMucGVubnktYXJjYWRlLmNvbS9kaXNjdXNzaW9uLzE1MTAyMS9pdHMtcmFpbmluZy1pdHMtcG91cmluZy1jaGltZXJhLWlzLWZvcmVjYXN0aW5nLXRoZS13ZWF0aGVyLW5zZjU2ay9wNg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6cb314457efc518eeebf4e38a3e1c09590bf6f64f10acf643390fb4877331791JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d5fc67e-ed82-6876-0ded-d19fecc2695f&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lL3RocmVhZC8zNDA2OTYzOTEvaS1kb24tdC1zZWUtcG9ybi1odWI_aGw9ZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41c926bc09aa084510f44d0b9e096645784b531f53fb4ea3933b05a7894a6096JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d5fc67e-ed82-6876-0ded-d19fecc2695f&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lL3RocmVhZC81NTIyMzQwOC9ob3ctZG8teW91LWtub3ctd2hhdC1lbWFpbC1hY2NvdW50LWFuZC1wYXNzd29yZC1pcy1mb3ItcG9ybi1odWItcHJlbWl1bT9obD1lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7e16c40a10bfb684354ad632194d8fefc55c418765799e8c8db6d12305a6074JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d5fc67e-ed82-6876-0ded-d19fecc2695f&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vd2Vic2VhcmNoL2Fuc3dlci8xMzY1MDE0Mj9obD1lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96a8cb41b7f62b4ec95caf4f6debb21735881f7ee5faa265abda2dbdc38b2488JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d5fc67e-ed82-6876-0ded-d19fecc2695f&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vYWNjb3VudHMvdGhyZWFkLzEyMTQwOTkyOS9ob3ctY2FuLWktdHJhbnNmZXItcGljdHVyZXMtb24tbXktY29tcHV0ZXItdG8tZ29vZ2xlLXBob3Rvcy1vbi1teS1jb21wdXRlcj9obD1lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a31ce2730b41f08b99e30e95263e14cd3716d599ffc8198ecaf77814146477a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d5fc67e-ed82-6876-0ded-d19fecc2695f&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvOTk3MTY2ND9obD1lbiZjbz1HRU5JRS5QbGF0Zm9ybSUzREFuZHJvaWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e4e29382775717babc6dff76700ed1830cbd10b5378652f3c1d7b5bc3ab762eaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d5fc67e-ed82-6876-0ded-d19fecc2695f&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vYWNjb3VudHMvYW5zd2VyLzc2NzM5ODk_aGw9ZW4tNDE5JmNvPUdFTklFLlBsYXRmb3JtJTNERGVza3RvcA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6ad0bfc978716fed078935024495d63192cd815af6bb49a93914f569bd40714JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14f35d35-af75-6559-3e3e-4ad4aed46454&amp;u=a1aHR0cHM6Ly93d3cucGxiZy5jb20vZm9ydW0vcmVhZC5waHA_MSw1MDMwMTM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9179776d6151ad72d440911fc31039b6060393b68e84b5f67cd9eeebfd3064aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14f35d35-af75-6559-3e3e-4ad4aed46454&amp;u=a1aHR0cHM6Ly9wbHVtYmluZ3RpcHN0b2RheS5jb20vaG93LWRvLWktaGF2ZS1wbHVtYmluZy1jb21pbmctb3V0LW9mLXRoZS13YWxscy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2e1e9dce6cb77c7b84b5c02c5497d5d8466dd00d80b093bd750a95ba93cc9e2dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14f35d35-af75-6559-3e3e-4ad4aed46454&amp;u=a1aHR0cHM6Ly93d3cuanVzdGFuc3dlci5jb20vcGx1bWJpbmcvbmgxM2ItcGlwZS10aGlzLWdvZXMtc3RyYWlnaHQtYWJvdmUtc2hvd2VyLmh0bWw_bXNvY2tpZD0xNGYzNWQzNWFmNzU2NTU5M2UzZTRhZDRhZWQ0NjQ1NA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8847c66f88487c783471266f089acac0580ac20074c151930f47609d2bf89821JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14f35d35-af75-6559-3e3e-4ad4aed46454&amp;u=a1aHR0cHM6Ly9ob3Jvdy5jb20vYmxvZ3MvZ3VpZGUvd2hhdC1pcy1hLWJhdGh0dWItb3ZlcmZsb3ctZHJhaW4tMjAyNS1ndWlkZS10by10dWItb3ZlcmZsb3ctZHJhaW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5bbfcbc735b22aa9aa3ca229bf1303c1fa4e1335ca3b93907923a5ff5edd467bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14f35d35-af75-6559-3e3e-4ad4aed46454&amp;u=a1aHR0cHM6Ly93d3cuZmVyZ3Vzb25ob21lLmNvbS90dWItd2FzdGUtb3ZlcmZsb3ctZ3VpZGUvYTI1OTA3&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc3962479a5655caec8636cb612db06adae24787eb1e938c2b2e6127ec876194JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14f35d35-af75-6559-3e3e-4ad4aed46454&amp;u=a1aHR0cHM6Ly9ob21lZ3VpZGUuY29tL2FydGljbGVzL3Nob3dlci1wbHVtYmluZy1kaWFncmFt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ab3454b833001ac726be3a1873ae1b740c05a325f5063fd1128efdccb22cd52JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14f35d35-af75-6559-3e3e-4ad4aed46454&amp;u=a1aHR0cHM6Ly9wbHVtYmluZ3RpcHN0b2RheS5jb20vcGx1bWJpbmctd2FzdGUtZHJhaW4tcGlwZXMtc3RpY2tpbmctb3V0LW9mLWV4dGVyaW9yLXdhbGxzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40180c2529fb0bd632dd69c2c845719df977ae050cb5500651be00c3d9420b75JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0791596f-38e1-6eca-07f3-4e8e39e76fd9&amp;u=a1aHR0cHM6Ly9zdG9ja3guY29tL2Fpci1qb3JkYW4tNC1yZXRyby11bmMtcGU_bXNvY2tpZD0wNzkxNTk2ZjM4ZTE2ZWNhMDdmMzRlOGUzOWU3NmZkOQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cd86e2875bebeb5d14149129a0cd647f068bd03ec3a1a7808b237ec7ff09bd36JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0791596f-38e1-6eca-07f3-4e8e39e76fd9&amp;u=a1aHR0cHM6Ly93d3cuZ29hdC5jb20vc25lYWtlcnMvYWlyLWpvcmRhbi00LXJldHJvLXVuYy1wZS1zdTE4LW1uamRscy03MzEtbG5tLWFqNC05MDQyODQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=142e18f77a390a5e7a077b394827dd6623ad22810384cdcc3d68df6abfa9f3d2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0791596f-38e1-6eca-07f3-4e8e39e76fd9&amp;u=a1aHR0cHM6Ly93d3cuZmxpZ2h0Y2x1Yi5jb20vYWlyLWpvcmRhbi00LXJldHJvLXVuYy1wZS1zdTE4LW1uamRscy03MzEtbG5tLWFqNC05MDQyODQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b3f387cf10f740db0b780ed468dbd5459e0f8e58aa64a3b64905e3e16655f89JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0791596f-38e1-6eca-07f3-4e8e39e76fd9&amp;u=a1aHR0cHM6Ly9hdGhsb25zcG9ydHMuY29tL2tpY2tzL2Fpci1qb3JkYW4tNC11bmMtcGUtZXhjbHVzaXZlLWRldGFpbGVkLWxvb2stcmVsZWFzZS13aGVyZS10by1idXktcHJpY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45c0274b2c9d0a3a298df14b37f0bdf3f9ccff69e1815c9ce56390359aaa6b67JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0791596f-38e1-6eca-07f3-4e8e39e76fd9&amp;u=a1aHR0cHM6Ly93d3cuZ29hdC5jb20vc25lYWtlcnMvYWlyLWpvcmRhbi00LXJldHJvLXBlLXVuYy1obzEybW5qZGxzMjQ3&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d31496db4f4f3b652ab685d382bd7677c834cc1a62e3988484c61c583958bbcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0791596f-38e1-6eca-07f3-4e8e39e76fd9&amp;u=a1aHR0cHM6Ly9hdGhsb25zcG9ydHMuY29tL2tpY2tzL2V4Y2x1c2l2ZS1haXItam9yZGFuLTQtbm9ydGgtY2Fyb2xpbmEtdW5pdmVyc2l0eS1yZWxlYXNlLWRhdGU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c890b745cf939e2dec026c7f883fde514879124e93f25af9b3babe889b11875JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0791596f-38e1-6eca-07f3-4e8e39e76fd9&amp;u=a1aHR0cHM6Ly93d3cuZWJheS5jb20vc2hvcC9qb3JkYW4tNC11bmMtcGU_X25rdz1qb3JkYW4rNCt1bmMrcGUmbXNvY2tpZD0wNzkxNTk2ZjM4ZTE2ZWNhMDdmMzRlOGUzOWU3NmZkOQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=79585ea05692d8bbe35872f0c57e3539e55fc0e3a8bdce57b2de6009a49f41fdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0791596f-38e1-6eca-07f3-4e8e39e76fd9&amp;u=a1aHR0cHM6Ly9zbmVha2VybmV3cy5jb20vMjAyNS8wMS8xNS9haXItam9yZGFuLTQtdW5jLXBlLTIwMjUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1dbd27e8919cc1284bcf28304cff101485cc80656ff43660afa611b1aa176ebdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0791596f-38e1-6eca-07f3-4e8e39e76fd9&amp;u=a1aHR0cHM6Ly93d3cuZWJheS5jb20vc2NoL2kuaHRtbD9fbmt3PXVuYys0Jl9zb3A9MTImbXNvY2tpZD0wNzkxNTk2ZjM4ZTE2ZWNhMDdmMzRlOGUzOWU3NmZkOQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ac4775df92a8e2b79f5bc91859931021a2f71db9e2263a8c26b5d8aa4b7860eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0791596f-38e1-6eca-07f3-4e8e39e76fd9&amp;u=a1aHR0cHM6Ly9ub3ZlbHNoaXAuY29tL2Fpci1qb3JkYW4tNC1yZXRyby11bmMtcGU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2343457c2e13184440995e2702202d8742414df610f2a4aff2c23d26f0e412cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22bd2b8a-c275-6dac-189f-3c6bc35a6cc5&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10c9c59dc09a4ccd7276942eead629cd4b5417ffe149296864321215540aee50JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22bd2b8a-c275-6dac-189f-3c6bc35a6cc5&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS9hcHA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=769c602e65abea21a4c7308b28be6fc477d74b7cb44a1ba33d04d8c0d3d2bb78JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22bd2b8a-c275-6dac-189f-3c6bc35a6cc5&amp;u=a1aHR0cHM6Ly9kZDUzanl4bWdjaHU4LmNsb3VkZnJvbnQubmV0Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e8fe40fa727a99db5f523b69eaf3014eff3243ce5e88cb1fa7bd9a9608a619bcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22bd2b8a-c275-6dac-189f-3c6bc35a6cc5&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9EdWNrRHVja0dv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=123b1905dab5c5014639d2786c8b76384b2c81372909b0c191f9ec2067c8c65aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22bd2b8a-c275-6dac-189f-3c6bc35a6cc5&amp;u=a1aHR0cHM6Ly9ub2FpLmR1Y2tkdWNrZ28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be616a8a2a49cfeb7063d2b99695068f0ba187841fcc64c846b745dbe74bf17fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22bd2b8a-c275-6dac-189f-3c6bc35a6cc5&amp;u=a1aHR0cHM6Ly9zdGFydC5kdWNrZHVja2dvLmNvbS9kdWNrZHVja2dvLWhlbHAtcGFnZXMvZ2V0LWR1Y2tkdWNrZ28&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e0834da5591b30ae00ddc602e450f30f8d0ab6e77ea4d21c2095615c470d6a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22bd2b8a-c275-6dac-189f-3c6bc35a6cc5&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS93aW5kb3dz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=76fb5759e3e01fa2a0af9b5ba7a87ef1394f9defa1d7ba85a845661bb78303dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22bd2b8a-c275-6dac-189f-3c6bc35a6cc5&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS9wcm8vbG9naW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=35af3c4d46fe1b00324e8e4e781b2d5b69a4a924aae101ddf2b9549525479afbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22bd2b8a-c275-6dac-189f-3c6bc35a6cc5&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS9hYm91dA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7139f580a1c0f93d9dc5c95e3a1f55ad2c59271e4cc67772c4c6b6c8e7117bedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22bd2b8a-c275-6dac-189f-3c6bc35a6cc5&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS9wcm8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a3868fb8325f0f93c89981f781c1e96bbf8192467187a444a43499d2572138cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8a0dfb-ae0f-62b7-031b-1a1aaf4f63d9&amp;u=a1aHR0cHM6Ly91c2V3ZXN0bW9udGguY29tL3Byb2R1Y3RzLzEwMDBnc20tbHV4dXJ5LWV4dHJhLXRoaWNrLW1hdHRyZXNzLXBhZC1wcmVtaXVtLXF1aWx0ZWQtdG9wcGVyLXdpdGgtYnJlYXRoYWJsZS1mbHVmZnktc29mdA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb1245766016c6e2c7d845aaa700a14bd3419b4cdb1686b3bf8d06ad62324db4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8a0dfb-ae0f-62b7-031b-1a1aaf4f63d9&amp;u=a1aHR0cHM6Ly9tYWx3YXJldGlwcy5jb20vYmxvZ3Mvd2VzdC1tb250aC1tYXR0cmVzcy10b3BwZXItc2NhbS1vci1sZWdpdC1mdWxsLXJldmlldy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc17bc110eb1dabbbfee4c669260d8ed7d74b76eb2cb678f5a08662d051f2aaeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8a0dfb-ae0f-62b7-031b-1a1aaf4f63d9&amp;u=a1aHR0cHM6Ly91c3dlc3Rtb250aC5jb20vcHJvZHVjdHMvMTAwMGdzbS1sdXh1cnktZXh0cmEtdGhpY2stbWF0dHJlc3MtcGFkLXByZW1pdW0tcXVpbHRlZC10b3BwZXItd2l0aC1icmVhdGhhYmxlLWZsdWZmeS1zb2Z0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=414240b5c5e1b47be52f6b5e2ce161d25f6fd0d1a6105b1a8c26df049bc44a5dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8a0dfb-ae0f-62b7-031b-1a1aaf4f63d9&amp;u=a1aHR0cHM6Ly91c2V3ZXN0bW9udGguY29tL3Byb2R1Y3RzL2x1eHVyeS1iYW1ib28tMTAwMGdzbS1leHRyYS10aGljay1tYXR0cmVzcy10b3BwZXItdWx0cmEtcGx1c2gtY29vbGluZy1icmVhdGhhYmxl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0dafda59ed4010ef86c39f35bba5739f19934aafdd4fefbf219c7ee84e2160c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8a0dfb-ae0f-62b7-031b-1a1aaf4f63d9&amp;u=a1aHR0cHM6Ly93d3cuYW1hem9uLmNvbS9XZXN0LU1vbnRoLU1hdHRyZXNzLVRvcHBlci1NYXR0cmVzc2VzL2RwL0IwR1lOMzFOUTk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98ffe37e1f63164bac37b220471e9ade40f63cfb0b1a71189c3bf6f32ef0772dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8a0dfb-ae0f-62b7-031b-1a1aaf4f63d9&amp;u=a1aHR0cHM6Ly93d3cuYW1hem9uLmNvbS9XZXN0TW9udGgtUHJlbWl1bS1RdWlsdGVkLTEwMDBHU00tTWF0dHJlc3MvZHAvQjBIMlFCTTRDTA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=889b4ec81707333fb3b91519ddff207e2caf02b2028c8374dcb89a0db97fce9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8a0dfb-ae0f-62b7-031b-1a1aaf4f63d9&amp;u=a1aHR0cHM6Ly93d3cuYW1hem9uLmNhL1dlc3QtTW9udGgtTWF0dHJlc3MtVG9wcGVyLU1hdHRyZXNzZXMvZHAvQjBHWU1XV1g1UA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a98718d1a7ad6cfb6ef4d5316ab3fcdf9aeac5b6572d16661403e4fc83c1e0edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8a0dfb-ae0f-62b7-031b-1a1aaf4f63d9&amp;u=a1aHR0cHM6Ly91c3dlc3Rtb250aC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07e3b209cb3ce0a6279e042e3c6d6bceeeeebc31756bc658e2668d241964005aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8a0dfb-ae0f-62b7-031b-1a1aaf4f63d9&amp;u=a1aHR0cHM6Ly93d3cudHJ1c3RwaWxvdC5jb20vcmV2aWV3L3VzZXdlc3Rtb250aC5jb20&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0228de20935261d2be21b68436fd7bc772eed44472eb97a33b2b4de1076ef8cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8a0dfb-ae0f-62b7-031b-1a1aaf4f63d9&amp;u=a1aHR0cHM6Ly9tYXR0cmVzc21pcmFjbGUuY2EvYmxvZ3MvbWF0dHJlc3MtbWlyYWNsZS1ibG9nL2NhbmFkaWFuLW1hZGUtbWF0dHJlc3MtdG9wcGVyLWJyYW5kcw&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -1579,7 +1921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H196"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1613,19 +1955,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C2" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>205</v>
+        <v>262</v>
       </c>
       <c r="G2" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H2" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1633,19 +1975,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="G3" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H3" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1653,19 +1995,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C4" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>207</v>
+        <v>264</v>
       </c>
       <c r="G4" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H4" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1673,19 +2015,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>208</v>
+        <v>265</v>
       </c>
       <c r="G5" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H5" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1693,19 +2035,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C6" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>209</v>
+        <v>266</v>
       </c>
       <c r="G6" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H6" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1713,19 +2055,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C7" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>210</v>
+        <v>267</v>
       </c>
       <c r="G7" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H7" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1733,19 +2075,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C8" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>211</v>
+        <v>268</v>
       </c>
       <c r="G8" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H8" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1753,19 +2095,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C9" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="G9" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H9" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1773,19 +2115,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C10" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>213</v>
+        <v>270</v>
       </c>
       <c r="G10" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H10" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1793,19 +2135,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C11" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="G11" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H11" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1813,19 +2155,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C12" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>215</v>
+        <v>272</v>
       </c>
       <c r="G12" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H12" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1833,19 +2175,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C13" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>216</v>
+        <v>273</v>
       </c>
       <c r="G13" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H13" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1853,19 +2195,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C14" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>217</v>
+        <v>274</v>
       </c>
       <c r="G14" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H14" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1873,19 +2215,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C15" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>218</v>
+        <v>275</v>
       </c>
       <c r="G15" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H15" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1893,19 +2235,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C16" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>219</v>
+        <v>276</v>
       </c>
       <c r="G16" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H16" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1913,19 +2255,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C17" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>220</v>
+        <v>277</v>
       </c>
       <c r="G17" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H17" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1933,19 +2275,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C18" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>221</v>
+        <v>278</v>
       </c>
       <c r="G18" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H18" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1953,19 +2295,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C19" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>222</v>
+        <v>279</v>
       </c>
       <c r="G19" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H19" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1973,19 +2315,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C20" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
       <c r="G20" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H20" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1993,19 +2335,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C21" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="G21" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H21" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2013,19 +2355,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C22" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="G22" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H22" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2033,19 +2375,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C23" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>226</v>
+        <v>283</v>
       </c>
       <c r="G23" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H23" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2053,19 +2395,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C24" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>227</v>
+        <v>284</v>
       </c>
       <c r="G24" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H24" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2073,19 +2415,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C25" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>228</v>
+        <v>285</v>
       </c>
       <c r="G25" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H25" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2093,19 +2435,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C26" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>229</v>
+        <v>286</v>
       </c>
       <c r="G26" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H26" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2113,19 +2455,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C27" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="G27" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H27" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -2133,19 +2475,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C28" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>231</v>
+        <v>288</v>
       </c>
       <c r="G28" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H28" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2153,19 +2495,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C29" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>232</v>
+        <v>289</v>
       </c>
       <c r="G29" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H29" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2173,19 +2515,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C30" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>233</v>
+        <v>290</v>
       </c>
       <c r="G30" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H30" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2193,19 +2535,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C31" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>234</v>
+        <v>291</v>
       </c>
       <c r="G31" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H31" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2213,19 +2555,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C32" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="G32" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H32" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2233,19 +2575,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C33" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>236</v>
+        <v>293</v>
       </c>
       <c r="G33" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H33" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2253,19 +2595,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C34" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>237</v>
+        <v>294</v>
       </c>
       <c r="G34" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H34" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2273,19 +2615,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C35" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>238</v>
+        <v>295</v>
       </c>
       <c r="G35" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H35" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2293,19 +2635,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C36" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>239</v>
+        <v>296</v>
       </c>
       <c r="G36" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H36" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2313,19 +2655,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C37" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="G37" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H37" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2333,19 +2675,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C38" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>241</v>
+        <v>298</v>
       </c>
       <c r="G38" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H38" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2353,19 +2695,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C39" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>242</v>
+        <v>299</v>
       </c>
       <c r="G39" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H39" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -2373,19 +2715,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C40" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>243</v>
+        <v>300</v>
       </c>
       <c r="G40" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H40" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2393,19 +2735,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C41" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>244</v>
+        <v>301</v>
       </c>
       <c r="G41" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H41" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2413,19 +2755,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C42" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>245</v>
+        <v>302</v>
       </c>
       <c r="G42" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H42" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2433,19 +2775,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C43" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>246</v>
+        <v>303</v>
       </c>
       <c r="G43" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H43" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2453,19 +2795,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C44" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>247</v>
+        <v>304</v>
       </c>
       <c r="G44" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H44" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2473,19 +2815,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C45" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>248</v>
+        <v>305</v>
       </c>
       <c r="G45" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H45" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2493,19 +2835,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C46" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="G46" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H46" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2513,19 +2855,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C47" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>250</v>
+        <v>307</v>
       </c>
       <c r="G47" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H47" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2533,19 +2875,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C48" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>251</v>
+        <v>308</v>
       </c>
       <c r="G48" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H48" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2553,19 +2895,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C49" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>252</v>
+        <v>309</v>
       </c>
       <c r="G49" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H49" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2573,19 +2915,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C50" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="G50" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H50" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2593,19 +2935,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C51" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>254</v>
+        <v>311</v>
       </c>
       <c r="G51" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H51" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2613,19 +2955,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C52" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="G52" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H52" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2633,19 +2975,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C53" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>256</v>
+        <v>313</v>
       </c>
       <c r="G53" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H53" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2653,19 +2995,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C54" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="G54" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H54" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2673,19 +3015,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C55" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>258</v>
+        <v>315</v>
       </c>
       <c r="G55" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H55" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2693,19 +3035,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C56" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>259</v>
+        <v>316</v>
       </c>
       <c r="G56" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H56" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2713,19 +3055,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C57" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>260</v>
+        <v>317</v>
       </c>
       <c r="G57" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H57" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2733,19 +3075,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C58" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="G58" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H58" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2753,19 +3095,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C59" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>262</v>
+        <v>319</v>
       </c>
       <c r="G59" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H59" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2773,19 +3115,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C60" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="G60" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H60" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2793,19 +3135,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C61" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>264</v>
+        <v>321</v>
       </c>
       <c r="G61" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H61" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2813,19 +3155,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C62" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>265</v>
+        <v>322</v>
       </c>
       <c r="G62" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H62" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2833,19 +3175,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C63" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>266</v>
+        <v>323</v>
       </c>
       <c r="G63" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H63" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2853,19 +3195,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C64" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>267</v>
+        <v>324</v>
       </c>
       <c r="G64" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H64" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2873,19 +3215,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C65" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>268</v>
+        <v>325</v>
       </c>
       <c r="G65" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H65" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2893,19 +3235,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C66" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>269</v>
+        <v>326</v>
       </c>
       <c r="G66" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H66" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2913,19 +3255,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C67" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="G67" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H67" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2933,19 +3275,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C68" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>271</v>
+        <v>328</v>
       </c>
       <c r="G68" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H68" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2953,19 +3295,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C69" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>272</v>
+        <v>329</v>
       </c>
       <c r="G69" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H69" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2973,19 +3315,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C70" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>273</v>
+        <v>330</v>
       </c>
       <c r="G70" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H70" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2993,19 +3335,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C71" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="G71" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H71" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -3013,19 +3355,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C72" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>275</v>
+        <v>332</v>
       </c>
       <c r="G72" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H72" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -3033,19 +3375,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C73" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>276</v>
+        <v>333</v>
       </c>
       <c r="G73" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H73" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -3053,19 +3395,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C74" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>277</v>
+        <v>334</v>
       </c>
       <c r="G74" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H74" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -3073,19 +3415,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C75" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="G75" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H75" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -3093,19 +3435,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C76" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
       <c r="G76" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H76" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -3113,19 +3455,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="G77" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="H77" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -3133,19 +3475,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>281</v>
+        <v>338</v>
       </c>
       <c r="G78" t="s">
-        <v>400</v>
+        <v>515</v>
       </c>
       <c r="H78" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -3153,19 +3495,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>282</v>
+        <v>339</v>
       </c>
       <c r="G79" t="s">
-        <v>400</v>
+        <v>515</v>
       </c>
       <c r="H79" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -3173,19 +3515,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>283</v>
+        <v>340</v>
       </c>
       <c r="G80" t="s">
-        <v>400</v>
+        <v>515</v>
       </c>
       <c r="H80" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -3193,19 +3535,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>284</v>
+        <v>341</v>
       </c>
       <c r="G81" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H81" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -3213,19 +3555,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>285</v>
+        <v>342</v>
       </c>
       <c r="G82" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H82" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -3233,19 +3575,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C83" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="G83" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H83" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -3253,19 +3595,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C84" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
       <c r="G84" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H84" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -3273,19 +3615,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C85" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>288</v>
+        <v>345</v>
       </c>
       <c r="G85" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H85" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -3293,19 +3635,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C86" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>289</v>
+        <v>346</v>
       </c>
       <c r="G86" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H86" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -3313,19 +3655,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C87" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>290</v>
+        <v>347</v>
       </c>
       <c r="G87" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H87" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -3333,19 +3675,19 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C88" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>291</v>
+        <v>348</v>
       </c>
       <c r="G88" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H88" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -3353,19 +3695,19 @@
         <v>95</v>
       </c>
       <c r="B89" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C89" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>292</v>
+        <v>349</v>
       </c>
       <c r="G89" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H89" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -3373,19 +3715,19 @@
         <v>96</v>
       </c>
       <c r="B90" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C90" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="G90" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H90" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -3393,19 +3735,19 @@
         <v>97</v>
       </c>
       <c r="B91" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C91" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>294</v>
+        <v>351</v>
       </c>
       <c r="G91" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H91" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -3413,19 +3755,19 @@
         <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C92" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>295</v>
+        <v>352</v>
       </c>
       <c r="G92" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H92" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -3433,19 +3775,19 @@
         <v>99</v>
       </c>
       <c r="B93" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C93" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>296</v>
+        <v>353</v>
       </c>
       <c r="G93" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H93" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3453,19 +3795,19 @@
         <v>100</v>
       </c>
       <c r="B94" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C94" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>297</v>
+        <v>354</v>
       </c>
       <c r="G94" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H94" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3473,19 +3815,19 @@
         <v>101</v>
       </c>
       <c r="B95" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C95" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>298</v>
+        <v>355</v>
       </c>
       <c r="G95" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H95" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3493,19 +3835,19 @@
         <v>102</v>
       </c>
       <c r="B96" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C96" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>299</v>
+        <v>356</v>
       </c>
       <c r="G96" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H96" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3513,19 +3855,19 @@
         <v>103</v>
       </c>
       <c r="B97" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>300</v>
+        <v>357</v>
       </c>
       <c r="G97" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H97" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3533,19 +3875,19 @@
         <v>104</v>
       </c>
       <c r="B98" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C98" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="G98" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H98" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3553,19 +3895,19 @@
         <v>105</v>
       </c>
       <c r="B99" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C99" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>302</v>
+        <v>359</v>
       </c>
       <c r="G99" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="H99" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3573,19 +3915,19 @@
         <v>106</v>
       </c>
       <c r="B100" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C100" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>303</v>
+        <v>360</v>
       </c>
       <c r="G100" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H100" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3593,19 +3935,19 @@
         <v>107</v>
       </c>
       <c r="B101" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C101" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>304</v>
+        <v>361</v>
       </c>
       <c r="G101" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H101" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3613,19 +3955,19 @@
         <v>108</v>
       </c>
       <c r="B102" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C102" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>305</v>
+        <v>362</v>
       </c>
       <c r="G102" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H102" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3633,19 +3975,19 @@
         <v>109</v>
       </c>
       <c r="B103" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C103" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>306</v>
+        <v>363</v>
       </c>
       <c r="G103" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H103" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -3653,19 +3995,19 @@
         <v>110</v>
       </c>
       <c r="B104" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C104" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>307</v>
+        <v>364</v>
       </c>
       <c r="G104" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H104" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -3673,19 +4015,19 @@
         <v>111</v>
       </c>
       <c r="B105" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C105" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>308</v>
+        <v>365</v>
       </c>
       <c r="G105" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H105" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -3693,19 +4035,19 @@
         <v>112</v>
       </c>
       <c r="B106" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C106" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>309</v>
+        <v>366</v>
       </c>
       <c r="G106" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H106" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -3713,19 +4055,19 @@
         <v>113</v>
       </c>
       <c r="B107" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C107" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>310</v>
+        <v>367</v>
       </c>
       <c r="G107" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H107" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -3733,19 +4075,19 @@
         <v>114</v>
       </c>
       <c r="B108" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C108" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>311</v>
+        <v>368</v>
       </c>
       <c r="G108" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H108" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -3753,19 +4095,19 @@
         <v>115</v>
       </c>
       <c r="B109" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C109" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>312</v>
+        <v>369</v>
       </c>
       <c r="G109" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H109" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -3773,19 +4115,19 @@
         <v>116</v>
       </c>
       <c r="B110" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C110" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>313</v>
+        <v>370</v>
       </c>
       <c r="G110" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H110" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -3793,19 +4135,19 @@
         <v>117</v>
       </c>
       <c r="B111" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C111" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>314</v>
+        <v>371</v>
       </c>
       <c r="G111" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H111" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -3813,19 +4155,19 @@
         <v>118</v>
       </c>
       <c r="B112" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C112" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>315</v>
+        <v>372</v>
       </c>
       <c r="G112" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H112" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -3833,19 +4175,19 @@
         <v>119</v>
       </c>
       <c r="B113" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C113" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>316</v>
+        <v>373</v>
       </c>
       <c r="G113" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H113" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -3853,19 +4195,19 @@
         <v>120</v>
       </c>
       <c r="B114" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C114" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>317</v>
+        <v>374</v>
       </c>
       <c r="G114" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H114" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -3873,19 +4215,19 @@
         <v>121</v>
       </c>
       <c r="B115" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C115" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="G115" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H115" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -3893,19 +4235,19 @@
         <v>122</v>
       </c>
       <c r="B116" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C116" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>319</v>
+        <v>376</v>
       </c>
       <c r="G116" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H116" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -3913,19 +4255,19 @@
         <v>123</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C117" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>320</v>
+        <v>377</v>
       </c>
       <c r="G117" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="H117" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -3933,19 +4275,19 @@
         <v>124</v>
       </c>
       <c r="B118" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C118" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>321</v>
+        <v>378</v>
       </c>
       <c r="G118" t="s">
-        <v>402</v>
+        <v>516</v>
       </c>
       <c r="H118" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -3953,19 +4295,19 @@
         <v>125</v>
       </c>
       <c r="B119" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C119" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>322</v>
+        <v>379</v>
       </c>
       <c r="G119" t="s">
-        <v>402</v>
+        <v>516</v>
       </c>
       <c r="H119" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -3973,19 +4315,19 @@
         <v>126</v>
       </c>
       <c r="B120" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C120" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>323</v>
+        <v>380</v>
       </c>
       <c r="G120" t="s">
-        <v>402</v>
+        <v>516</v>
       </c>
       <c r="H120" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -3993,19 +4335,19 @@
         <v>127</v>
       </c>
       <c r="B121" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C121" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>324</v>
+        <v>381</v>
       </c>
       <c r="G121" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H121" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -4013,19 +4355,19 @@
         <v>128</v>
       </c>
       <c r="B122" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C122" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>325</v>
+        <v>382</v>
       </c>
       <c r="G122" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H122" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -4033,19 +4375,19 @@
         <v>129</v>
       </c>
       <c r="B123" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C123" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="G123" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H123" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -4053,19 +4395,19 @@
         <v>130</v>
       </c>
       <c r="B124" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C124" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="G124" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H124" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -4073,19 +4415,19 @@
         <v>131</v>
       </c>
       <c r="B125" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C125" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>328</v>
+        <v>385</v>
       </c>
       <c r="G125" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H125" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -4093,19 +4435,19 @@
         <v>132</v>
       </c>
       <c r="B126" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C126" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>329</v>
+        <v>386</v>
       </c>
       <c r="G126" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H126" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -4113,19 +4455,19 @@
         <v>133</v>
       </c>
       <c r="B127" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C127" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>330</v>
+        <v>387</v>
       </c>
       <c r="G127" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H127" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -4133,19 +4475,19 @@
         <v>134</v>
       </c>
       <c r="B128" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C128" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>331</v>
+        <v>388</v>
       </c>
       <c r="G128" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H128" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -4153,19 +4495,19 @@
         <v>135</v>
       </c>
       <c r="B129" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C129" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>332</v>
+        <v>389</v>
       </c>
       <c r="G129" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H129" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -4173,19 +4515,19 @@
         <v>136</v>
       </c>
       <c r="B130" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C130" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>333</v>
+        <v>390</v>
       </c>
       <c r="G130" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H130" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -4193,19 +4535,19 @@
         <v>137</v>
       </c>
       <c r="B131" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C131" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>334</v>
+        <v>391</v>
       </c>
       <c r="G131" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H131" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4213,19 +4555,19 @@
         <v>138</v>
       </c>
       <c r="B132" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C132" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>335</v>
+        <v>392</v>
       </c>
       <c r="G132" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H132" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -4233,19 +4575,19 @@
         <v>139</v>
       </c>
       <c r="B133" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C133" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>336</v>
+        <v>393</v>
       </c>
       <c r="G133" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H133" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -4253,19 +4595,19 @@
         <v>140</v>
       </c>
       <c r="B134" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C134" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
       <c r="G134" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H134" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -4273,19 +4615,19 @@
         <v>141</v>
       </c>
       <c r="B135" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C135" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>338</v>
+        <v>395</v>
       </c>
       <c r="G135" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H135" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -4293,19 +4635,19 @@
         <v>142</v>
       </c>
       <c r="B136" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C136" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>339</v>
+        <v>396</v>
       </c>
       <c r="G136" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H136" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -4313,19 +4655,19 @@
         <v>143</v>
       </c>
       <c r="B137" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C137" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>340</v>
+        <v>397</v>
       </c>
       <c r="G137" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H137" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -4333,19 +4675,19 @@
         <v>144</v>
       </c>
       <c r="B138" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C138" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="G138" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H138" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -4353,19 +4695,19 @@
         <v>145</v>
       </c>
       <c r="B139" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C139" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>342</v>
+        <v>399</v>
       </c>
       <c r="G139" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H139" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -4373,19 +4715,19 @@
         <v>146</v>
       </c>
       <c r="B140" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C140" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>343</v>
+        <v>400</v>
       </c>
       <c r="G140" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H140" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -4393,19 +4735,19 @@
         <v>147</v>
       </c>
       <c r="B141" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C141" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>344</v>
+        <v>401</v>
       </c>
       <c r="G141" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H141" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -4413,19 +4755,19 @@
         <v>148</v>
       </c>
       <c r="B142" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C142" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>345</v>
+        <v>402</v>
       </c>
       <c r="G142" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H142" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -4433,19 +4775,19 @@
         <v>149</v>
       </c>
       <c r="B143" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C143" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>346</v>
+        <v>403</v>
       </c>
       <c r="G143" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H143" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -4453,19 +4795,19 @@
         <v>150</v>
       </c>
       <c r="B144" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>347</v>
+        <v>404</v>
       </c>
       <c r="G144" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H144" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -4473,19 +4815,19 @@
         <v>151</v>
       </c>
       <c r="B145" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>348</v>
+        <v>405</v>
       </c>
       <c r="G145" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H145" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -4493,19 +4835,19 @@
         <v>152</v>
       </c>
       <c r="B146" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="G146" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H146" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -4513,19 +4855,19 @@
         <v>153</v>
       </c>
       <c r="B147" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>350</v>
+        <v>407</v>
       </c>
       <c r="G147" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H147" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -4533,19 +4875,19 @@
         <v>154</v>
       </c>
       <c r="B148" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C148" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>351</v>
+        <v>408</v>
       </c>
       <c r="G148" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H148" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -4553,19 +4895,19 @@
         <v>155</v>
       </c>
       <c r="B149" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C149" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>352</v>
+        <v>409</v>
       </c>
       <c r="G149" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H149" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -4573,19 +4915,19 @@
         <v>156</v>
       </c>
       <c r="B150" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C150" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>353</v>
+        <v>410</v>
       </c>
       <c r="G150" t="s">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H150" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -4593,19 +4935,19 @@
         <v>157</v>
       </c>
       <c r="B151" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C151" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="G151" t="s">
-        <v>404</v>
+        <v>516</v>
       </c>
       <c r="H151" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -4613,19 +4955,19 @@
         <v>158</v>
       </c>
       <c r="B152" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C152" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="G152" t="s">
-        <v>404</v>
+        <v>516</v>
       </c>
       <c r="H152" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -4633,19 +4975,19 @@
         <v>159</v>
       </c>
       <c r="B153" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C153" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
       <c r="G153" t="s">
-        <v>404</v>
+        <v>516</v>
       </c>
       <c r="H153" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -4653,19 +4995,19 @@
         <v>160</v>
       </c>
       <c r="B154" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C154" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
       <c r="G154" t="s">
-        <v>404</v>
+        <v>516</v>
       </c>
       <c r="H154" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -4673,19 +5015,19 @@
         <v>161</v>
       </c>
       <c r="B155" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C155" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
       <c r="G155" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="H155" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -4693,19 +5035,19 @@
         <v>162</v>
       </c>
       <c r="B156" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C156" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
       <c r="G156" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="H156" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -4713,19 +5055,19 @@
         <v>163</v>
       </c>
       <c r="B157" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C157" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="G157" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="H157" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -4733,19 +5075,19 @@
         <v>164</v>
       </c>
       <c r="B158" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C158" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="G158" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="H158" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -4753,19 +5095,19 @@
         <v>165</v>
       </c>
       <c r="B159" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C159" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="G159" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="H159" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -4773,19 +5115,19 @@
         <v>166</v>
       </c>
       <c r="B160" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C160" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>363</v>
+        <v>420</v>
       </c>
       <c r="G160" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="H160" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -4793,19 +5135,19 @@
         <v>167</v>
       </c>
       <c r="B161" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C161" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>364</v>
+        <v>421</v>
       </c>
       <c r="G161" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="H161" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -4813,19 +5155,19 @@
         <v>168</v>
       </c>
       <c r="B162" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C162" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="G162" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="H162" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -4833,19 +5175,19 @@
         <v>169</v>
       </c>
       <c r="B163" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C163" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="G163" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="H163" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -4853,19 +5195,19 @@
         <v>170</v>
       </c>
       <c r="B164" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C164" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="G164" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="H164" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -4873,19 +5215,19 @@
         <v>171</v>
       </c>
       <c r="B165" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C165" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="G165" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="H165" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -4893,19 +5235,19 @@
         <v>172</v>
       </c>
       <c r="B166" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C166" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
       <c r="G166" t="s">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="H166" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -4913,19 +5255,19 @@
         <v>173</v>
       </c>
       <c r="B167" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C167" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>370</v>
+        <v>427</v>
       </c>
       <c r="G167" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H167" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -4933,19 +5275,19 @@
         <v>174</v>
       </c>
       <c r="B168" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C168" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="G168" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H168" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -4953,19 +5295,19 @@
         <v>175</v>
       </c>
       <c r="B169" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C169" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="G169" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H169" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -4973,19 +5315,19 @@
         <v>176</v>
       </c>
       <c r="B170" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C170" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="G170" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H170" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -4993,19 +5335,19 @@
         <v>177</v>
       </c>
       <c r="B171" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C171" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>374</v>
+        <v>431</v>
       </c>
       <c r="G171" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H171" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -5013,19 +5355,19 @@
         <v>178</v>
       </c>
       <c r="B172" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C172" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="G172" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H172" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -5033,19 +5375,19 @@
         <v>179</v>
       </c>
       <c r="B173" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C173" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="G173" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H173" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -5053,19 +5395,19 @@
         <v>180</v>
       </c>
       <c r="B174" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C174" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="G174" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H174" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -5073,19 +5415,19 @@
         <v>181</v>
       </c>
       <c r="B175" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C175" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="G175" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H175" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -5093,19 +5435,19 @@
         <v>182</v>
       </c>
       <c r="B176" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C176" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="G176" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H176" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -5113,19 +5455,19 @@
         <v>183</v>
       </c>
       <c r="B177" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C177" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="G177" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H177" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -5133,19 +5475,19 @@
         <v>184</v>
       </c>
       <c r="B178" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C178" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="G178" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H178" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -5153,19 +5495,19 @@
         <v>185</v>
       </c>
       <c r="B179" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C179" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
       <c r="G179" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H179" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -5173,19 +5515,19 @@
         <v>186</v>
       </c>
       <c r="B180" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C180" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>383</v>
+        <v>440</v>
       </c>
       <c r="G180" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H180" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -5193,19 +5535,19 @@
         <v>187</v>
       </c>
       <c r="B181" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C181" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="G181" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H181" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -5213,19 +5555,19 @@
         <v>188</v>
       </c>
       <c r="B182" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C182" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>385</v>
+        <v>442</v>
       </c>
       <c r="G182" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H182" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -5233,19 +5575,19 @@
         <v>189</v>
       </c>
       <c r="B183" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C183" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="G183" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H183" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -5253,19 +5595,19 @@
         <v>190</v>
       </c>
       <c r="B184" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C184" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>387</v>
+        <v>444</v>
       </c>
       <c r="G184" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H184" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -5273,19 +5615,19 @@
         <v>191</v>
       </c>
       <c r="B185" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C185" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="G185" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="H185" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -5293,19 +5635,19 @@
         <v>192</v>
       </c>
       <c r="B186" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C186" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="G186" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="H186" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -5313,19 +5655,19 @@
         <v>193</v>
       </c>
       <c r="B187" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C187" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>390</v>
+        <v>447</v>
       </c>
       <c r="G187" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="H187" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -5333,19 +5675,19 @@
         <v>194</v>
       </c>
       <c r="B188" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C188" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>391</v>
+        <v>448</v>
       </c>
       <c r="G188" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="H188" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -5353,19 +5695,19 @@
         <v>195</v>
       </c>
       <c r="B189" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C189" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>392</v>
+        <v>449</v>
       </c>
       <c r="G189" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="H189" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -5373,19 +5715,19 @@
         <v>196</v>
       </c>
       <c r="B190" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C190" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>393</v>
+        <v>450</v>
       </c>
       <c r="G190" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="H190" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -5393,19 +5735,19 @@
         <v>197</v>
       </c>
       <c r="B191" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C191" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>394</v>
+        <v>451</v>
       </c>
       <c r="G191" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="H191" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -5413,19 +5755,19 @@
         <v>198</v>
       </c>
       <c r="B192" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C192" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
       <c r="G192" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="H192" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -5433,19 +5775,19 @@
         <v>199</v>
       </c>
       <c r="B193" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C193" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>396</v>
+        <v>453</v>
       </c>
       <c r="G193" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="H193" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -5453,19 +5795,19 @@
         <v>200</v>
       </c>
       <c r="B194" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C194" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>397</v>
+        <v>454</v>
       </c>
       <c r="G194" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="H194" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -5473,19 +5815,19 @@
         <v>201</v>
       </c>
       <c r="B195" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="C195" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>398</v>
+        <v>455</v>
       </c>
       <c r="G195" t="s">
-        <v>405</v>
+        <v>518</v>
       </c>
       <c r="H195" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -5493,19 +5835,1159 @@
         <v>202</v>
       </c>
       <c r="B196" t="s">
+        <v>260</v>
+      </c>
+      <c r="C196" t="s">
+        <v>261</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="G196" t="s">
+        <v>518</v>
+      </c>
+      <c r="H196" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" t="s">
         <v>203</v>
       </c>
-      <c r="C196" t="s">
+      <c r="B197" t="s">
+        <v>260</v>
+      </c>
+      <c r="C197" t="s">
+        <v>261</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G197" t="s">
+        <v>518</v>
+      </c>
+      <c r="H197" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198" t="s">
         <v>204</v>
       </c>
-      <c r="F196" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="G196" t="s">
-        <v>405</v>
-      </c>
-      <c r="H196" t="s">
-        <v>406</v>
+      <c r="B198" t="s">
+        <v>260</v>
+      </c>
+      <c r="C198" t="s">
+        <v>261</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="G198" t="s">
+        <v>518</v>
+      </c>
+      <c r="H198" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199" t="s">
+        <v>205</v>
+      </c>
+      <c r="B199" t="s">
+        <v>260</v>
+      </c>
+      <c r="C199" t="s">
+        <v>261</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G199" t="s">
+        <v>518</v>
+      </c>
+      <c r="H199" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" t="s">
+        <v>206</v>
+      </c>
+      <c r="B200" t="s">
+        <v>260</v>
+      </c>
+      <c r="C200" t="s">
+        <v>261</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="G200" t="s">
+        <v>518</v>
+      </c>
+      <c r="H200" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" t="s">
+        <v>207</v>
+      </c>
+      <c r="B201" t="s">
+        <v>260</v>
+      </c>
+      <c r="C201" t="s">
+        <v>261</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="G201" t="s">
+        <v>518</v>
+      </c>
+      <c r="H201" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" t="s">
+        <v>208</v>
+      </c>
+      <c r="B202" t="s">
+        <v>260</v>
+      </c>
+      <c r="C202" t="s">
+        <v>261</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="G202" t="s">
+        <v>518</v>
+      </c>
+      <c r="H202" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" t="s">
+        <v>209</v>
+      </c>
+      <c r="B203" t="s">
+        <v>260</v>
+      </c>
+      <c r="C203" t="s">
+        <v>261</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="G203" t="s">
+        <v>518</v>
+      </c>
+      <c r="H203" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" t="s">
+        <v>210</v>
+      </c>
+      <c r="B204" t="s">
+        <v>260</v>
+      </c>
+      <c r="C204" t="s">
+        <v>261</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G204" t="s">
+        <v>518</v>
+      </c>
+      <c r="H204" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="A205" t="s">
+        <v>211</v>
+      </c>
+      <c r="B205" t="s">
+        <v>260</v>
+      </c>
+      <c r="C205" t="s">
+        <v>261</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="G205" t="s">
+        <v>518</v>
+      </c>
+      <c r="H205" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="A206" t="s">
+        <v>212</v>
+      </c>
+      <c r="B206" t="s">
+        <v>260</v>
+      </c>
+      <c r="C206" t="s">
+        <v>261</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G206" t="s">
+        <v>518</v>
+      </c>
+      <c r="H206" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" t="s">
+        <v>213</v>
+      </c>
+      <c r="B207" t="s">
+        <v>260</v>
+      </c>
+      <c r="C207" t="s">
+        <v>261</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="G207" t="s">
+        <v>518</v>
+      </c>
+      <c r="H207" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" t="s">
+        <v>214</v>
+      </c>
+      <c r="B208" t="s">
+        <v>260</v>
+      </c>
+      <c r="C208" t="s">
+        <v>261</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="G208" t="s">
+        <v>518</v>
+      </c>
+      <c r="H208" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" t="s">
+        <v>215</v>
+      </c>
+      <c r="B209" t="s">
+        <v>260</v>
+      </c>
+      <c r="C209" t="s">
+        <v>261</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="G209" t="s">
+        <v>518</v>
+      </c>
+      <c r="H209" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" t="s">
+        <v>216</v>
+      </c>
+      <c r="B210" t="s">
+        <v>260</v>
+      </c>
+      <c r="C210" t="s">
+        <v>261</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="G210" t="s">
+        <v>518</v>
+      </c>
+      <c r="H210" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211" t="s">
+        <v>217</v>
+      </c>
+      <c r="B211" t="s">
+        <v>260</v>
+      </c>
+      <c r="C211" t="s">
+        <v>261</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="G211" t="s">
+        <v>518</v>
+      </c>
+      <c r="H211" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" t="s">
+        <v>218</v>
+      </c>
+      <c r="B212" t="s">
+        <v>260</v>
+      </c>
+      <c r="C212" t="s">
+        <v>261</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="G212" t="s">
+        <v>518</v>
+      </c>
+      <c r="H212" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213" t="s">
+        <v>219</v>
+      </c>
+      <c r="B213" t="s">
+        <v>260</v>
+      </c>
+      <c r="C213" t="s">
+        <v>261</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="G213" t="s">
+        <v>518</v>
+      </c>
+      <c r="H213" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" t="s">
+        <v>220</v>
+      </c>
+      <c r="B214" t="s">
+        <v>260</v>
+      </c>
+      <c r="C214" t="s">
+        <v>261</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="G214" t="s">
+        <v>518</v>
+      </c>
+      <c r="H214" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215" t="s">
+        <v>221</v>
+      </c>
+      <c r="B215" t="s">
+        <v>260</v>
+      </c>
+      <c r="C215" t="s">
+        <v>261</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="G215" t="s">
+        <v>518</v>
+      </c>
+      <c r="H215" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" t="s">
+        <v>222</v>
+      </c>
+      <c r="B216" t="s">
+        <v>260</v>
+      </c>
+      <c r="C216" t="s">
+        <v>261</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="G216" t="s">
+        <v>518</v>
+      </c>
+      <c r="H216" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" t="s">
+        <v>223</v>
+      </c>
+      <c r="B217" t="s">
+        <v>260</v>
+      </c>
+      <c r="C217" t="s">
+        <v>261</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="G217" t="s">
+        <v>519</v>
+      </c>
+      <c r="H217" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" t="s">
+        <v>224</v>
+      </c>
+      <c r="B218" t="s">
+        <v>260</v>
+      </c>
+      <c r="C218" t="s">
+        <v>261</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="G218" t="s">
+        <v>519</v>
+      </c>
+      <c r="H218" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" t="s">
+        <v>225</v>
+      </c>
+      <c r="B219" t="s">
+        <v>260</v>
+      </c>
+      <c r="C219" t="s">
+        <v>261</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="G219" t="s">
+        <v>519</v>
+      </c>
+      <c r="H219" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" t="s">
+        <v>226</v>
+      </c>
+      <c r="B220" t="s">
+        <v>260</v>
+      </c>
+      <c r="C220" t="s">
+        <v>261</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="G220" t="s">
+        <v>519</v>
+      </c>
+      <c r="H220" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221" t="s">
+        <v>227</v>
+      </c>
+      <c r="B221" t="s">
+        <v>260</v>
+      </c>
+      <c r="C221" t="s">
+        <v>261</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="G221" t="s">
+        <v>519</v>
+      </c>
+      <c r="H221" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222" t="s">
+        <v>228</v>
+      </c>
+      <c r="B222" t="s">
+        <v>260</v>
+      </c>
+      <c r="C222" t="s">
+        <v>261</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="G222" t="s">
+        <v>519</v>
+      </c>
+      <c r="H222" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="A223" t="s">
+        <v>229</v>
+      </c>
+      <c r="B223" t="s">
+        <v>260</v>
+      </c>
+      <c r="C223" t="s">
+        <v>261</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="G223" t="s">
+        <v>519</v>
+      </c>
+      <c r="H223" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" t="s">
+        <v>230</v>
+      </c>
+      <c r="B224" t="s">
+        <v>260</v>
+      </c>
+      <c r="C224" t="s">
+        <v>261</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="G224" t="s">
+        <v>519</v>
+      </c>
+      <c r="H224" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8">
+      <c r="A225" t="s">
+        <v>231</v>
+      </c>
+      <c r="B225" t="s">
+        <v>260</v>
+      </c>
+      <c r="C225" t="s">
+        <v>261</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G225" t="s">
+        <v>519</v>
+      </c>
+      <c r="H225" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8">
+      <c r="A226" t="s">
+        <v>232</v>
+      </c>
+      <c r="B226" t="s">
+        <v>260</v>
+      </c>
+      <c r="C226" t="s">
+        <v>261</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="G226" t="s">
+        <v>519</v>
+      </c>
+      <c r="H226" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227" t="s">
+        <v>233</v>
+      </c>
+      <c r="B227" t="s">
+        <v>260</v>
+      </c>
+      <c r="C227" t="s">
+        <v>261</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="G227" t="s">
+        <v>519</v>
+      </c>
+      <c r="H227" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228" t="s">
+        <v>234</v>
+      </c>
+      <c r="B228" t="s">
+        <v>260</v>
+      </c>
+      <c r="C228" t="s">
+        <v>261</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="G228" t="s">
+        <v>519</v>
+      </c>
+      <c r="H228" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229" t="s">
+        <v>235</v>
+      </c>
+      <c r="B229" t="s">
+        <v>260</v>
+      </c>
+      <c r="C229" t="s">
+        <v>261</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="G229" t="s">
+        <v>519</v>
+      </c>
+      <c r="H229" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="A230" t="s">
+        <v>236</v>
+      </c>
+      <c r="B230" t="s">
+        <v>260</v>
+      </c>
+      <c r="C230" t="s">
+        <v>261</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="G230" t="s">
+        <v>519</v>
+      </c>
+      <c r="H230" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8">
+      <c r="A231" t="s">
+        <v>237</v>
+      </c>
+      <c r="B231" t="s">
+        <v>260</v>
+      </c>
+      <c r="C231" t="s">
+        <v>261</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="G231" t="s">
+        <v>519</v>
+      </c>
+      <c r="H231" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8">
+      <c r="A232" t="s">
+        <v>238</v>
+      </c>
+      <c r="B232" t="s">
+        <v>260</v>
+      </c>
+      <c r="C232" t="s">
+        <v>261</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="G232" t="s">
+        <v>519</v>
+      </c>
+      <c r="H232" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8">
+      <c r="A233" t="s">
+        <v>239</v>
+      </c>
+      <c r="B233" t="s">
+        <v>260</v>
+      </c>
+      <c r="C233" t="s">
+        <v>261</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="G233" t="s">
+        <v>519</v>
+      </c>
+      <c r="H233" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234" t="s">
+        <v>240</v>
+      </c>
+      <c r="B234" t="s">
+        <v>260</v>
+      </c>
+      <c r="C234" t="s">
+        <v>261</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="G234" t="s">
+        <v>519</v>
+      </c>
+      <c r="H234" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235" t="s">
+        <v>241</v>
+      </c>
+      <c r="B235" t="s">
+        <v>260</v>
+      </c>
+      <c r="C235" t="s">
+        <v>261</v>
+      </c>
+      <c r="F235" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="G235" t="s">
+        <v>519</v>
+      </c>
+      <c r="H235" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236" t="s">
+        <v>242</v>
+      </c>
+      <c r="B236" t="s">
+        <v>260</v>
+      </c>
+      <c r="C236" t="s">
+        <v>261</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="G236" t="s">
+        <v>519</v>
+      </c>
+      <c r="H236" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8">
+      <c r="A237" t="s">
+        <v>243</v>
+      </c>
+      <c r="B237" t="s">
+        <v>260</v>
+      </c>
+      <c r="C237" t="s">
+        <v>261</v>
+      </c>
+      <c r="F237" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="G237" t="s">
+        <v>519</v>
+      </c>
+      <c r="H237" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8">
+      <c r="A238" t="s">
+        <v>244</v>
+      </c>
+      <c r="B238" t="s">
+        <v>260</v>
+      </c>
+      <c r="C238" t="s">
+        <v>261</v>
+      </c>
+      <c r="F238" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="G238" t="s">
+        <v>519</v>
+      </c>
+      <c r="H238" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239" t="s">
+        <v>245</v>
+      </c>
+      <c r="B239" t="s">
+        <v>260</v>
+      </c>
+      <c r="C239" t="s">
+        <v>261</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G239" t="s">
+        <v>519</v>
+      </c>
+      <c r="H239" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240" t="s">
+        <v>246</v>
+      </c>
+      <c r="B240" t="s">
+        <v>260</v>
+      </c>
+      <c r="C240" t="s">
+        <v>261</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="G240" t="s">
+        <v>519</v>
+      </c>
+      <c r="H240" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8">
+      <c r="A241" t="s">
+        <v>247</v>
+      </c>
+      <c r="B241" t="s">
+        <v>260</v>
+      </c>
+      <c r="C241" t="s">
+        <v>261</v>
+      </c>
+      <c r="F241" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="G241" t="s">
+        <v>519</v>
+      </c>
+      <c r="H241" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8">
+      <c r="A242" t="s">
+        <v>248</v>
+      </c>
+      <c r="B242" t="s">
+        <v>260</v>
+      </c>
+      <c r="C242" t="s">
+        <v>261</v>
+      </c>
+      <c r="F242" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="G242" t="s">
+        <v>519</v>
+      </c>
+      <c r="H242" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243" t="s">
+        <v>249</v>
+      </c>
+      <c r="B243" t="s">
+        <v>260</v>
+      </c>
+      <c r="C243" t="s">
+        <v>261</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="G243" t="s">
+        <v>519</v>
+      </c>
+      <c r="H243" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244" t="s">
+        <v>250</v>
+      </c>
+      <c r="B244" t="s">
+        <v>260</v>
+      </c>
+      <c r="C244" t="s">
+        <v>261</v>
+      </c>
+      <c r="F244" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="G244" t="s">
+        <v>519</v>
+      </c>
+      <c r="H244" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8">
+      <c r="A245" t="s">
+        <v>251</v>
+      </c>
+      <c r="B245" t="s">
+        <v>260</v>
+      </c>
+      <c r="C245" t="s">
+        <v>261</v>
+      </c>
+      <c r="F245" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G245" t="s">
+        <v>519</v>
+      </c>
+      <c r="H245" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8">
+      <c r="A246" t="s">
+        <v>252</v>
+      </c>
+      <c r="B246" t="s">
+        <v>260</v>
+      </c>
+      <c r="C246" t="s">
+        <v>261</v>
+      </c>
+      <c r="F246" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="G246" t="s">
+        <v>519</v>
+      </c>
+      <c r="H246" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8">
+      <c r="A247" t="s">
+        <v>253</v>
+      </c>
+      <c r="B247" t="s">
+        <v>260</v>
+      </c>
+      <c r="C247" t="s">
+        <v>261</v>
+      </c>
+      <c r="F247" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="G247" t="s">
+        <v>519</v>
+      </c>
+      <c r="H247" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8">
+      <c r="A248" t="s">
+        <v>254</v>
+      </c>
+      <c r="B248" t="s">
+        <v>260</v>
+      </c>
+      <c r="C248" t="s">
+        <v>261</v>
+      </c>
+      <c r="F248" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="G248" t="s">
+        <v>519</v>
+      </c>
+      <c r="H248" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8">
+      <c r="A249" t="s">
+        <v>255</v>
+      </c>
+      <c r="B249" t="s">
+        <v>260</v>
+      </c>
+      <c r="C249" t="s">
+        <v>261</v>
+      </c>
+      <c r="F249" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="G249" t="s">
+        <v>519</v>
+      </c>
+      <c r="H249" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8">
+      <c r="A250" t="s">
+        <v>256</v>
+      </c>
+      <c r="B250" t="s">
+        <v>260</v>
+      </c>
+      <c r="C250" t="s">
+        <v>261</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="G250" t="s">
+        <v>519</v>
+      </c>
+      <c r="H250" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8">
+      <c r="A251" t="s">
+        <v>257</v>
+      </c>
+      <c r="B251" t="s">
+        <v>260</v>
+      </c>
+      <c r="C251" t="s">
+        <v>261</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="G251" t="s">
+        <v>519</v>
+      </c>
+      <c r="H251" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
+      <c r="A252" t="s">
+        <v>258</v>
+      </c>
+      <c r="B252" t="s">
+        <v>260</v>
+      </c>
+      <c r="C252" t="s">
+        <v>261</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="G252" t="s">
+        <v>519</v>
+      </c>
+      <c r="H252" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" t="s">
+        <v>259</v>
+      </c>
+      <c r="B253" t="s">
+        <v>260</v>
+      </c>
+      <c r="C253" t="s">
+        <v>261</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="G253" t="s">
+        <v>519</v>
+      </c>
+      <c r="H253" t="s">
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -5705,6 +7187,63 @@
     <hyperlink ref="F194" r:id="rId193"/>
     <hyperlink ref="F195" r:id="rId194"/>
     <hyperlink ref="F196" r:id="rId195"/>
+    <hyperlink ref="F197" r:id="rId196"/>
+    <hyperlink ref="F198" r:id="rId197"/>
+    <hyperlink ref="F199" r:id="rId198"/>
+    <hyperlink ref="F200" r:id="rId199"/>
+    <hyperlink ref="F201" r:id="rId200"/>
+    <hyperlink ref="F202" r:id="rId201"/>
+    <hyperlink ref="F203" r:id="rId202"/>
+    <hyperlink ref="F204" r:id="rId203"/>
+    <hyperlink ref="F205" r:id="rId204"/>
+    <hyperlink ref="F206" r:id="rId205"/>
+    <hyperlink ref="F207" r:id="rId206"/>
+    <hyperlink ref="F208" r:id="rId207"/>
+    <hyperlink ref="F209" r:id="rId208"/>
+    <hyperlink ref="F210" r:id="rId209"/>
+    <hyperlink ref="F211" r:id="rId210"/>
+    <hyperlink ref="F212" r:id="rId211"/>
+    <hyperlink ref="F213" r:id="rId212"/>
+    <hyperlink ref="F214" r:id="rId213"/>
+    <hyperlink ref="F215" r:id="rId214"/>
+    <hyperlink ref="F216" r:id="rId215"/>
+    <hyperlink ref="F217" r:id="rId216"/>
+    <hyperlink ref="F218" r:id="rId217"/>
+    <hyperlink ref="F219" r:id="rId218"/>
+    <hyperlink ref="F220" r:id="rId219"/>
+    <hyperlink ref="F221" r:id="rId220"/>
+    <hyperlink ref="F222" r:id="rId221"/>
+    <hyperlink ref="F223" r:id="rId222"/>
+    <hyperlink ref="F224" r:id="rId223"/>
+    <hyperlink ref="F225" r:id="rId224"/>
+    <hyperlink ref="F226" r:id="rId225"/>
+    <hyperlink ref="F227" r:id="rId226"/>
+    <hyperlink ref="F228" r:id="rId227"/>
+    <hyperlink ref="F229" r:id="rId228"/>
+    <hyperlink ref="F230" r:id="rId229"/>
+    <hyperlink ref="F231" r:id="rId230"/>
+    <hyperlink ref="F232" r:id="rId231"/>
+    <hyperlink ref="F233" r:id="rId232"/>
+    <hyperlink ref="F234" r:id="rId233"/>
+    <hyperlink ref="F235" r:id="rId234"/>
+    <hyperlink ref="F236" r:id="rId235"/>
+    <hyperlink ref="F237" r:id="rId236"/>
+    <hyperlink ref="F238" r:id="rId237"/>
+    <hyperlink ref="F239" r:id="rId238"/>
+    <hyperlink ref="F240" r:id="rId239"/>
+    <hyperlink ref="F241" r:id="rId240"/>
+    <hyperlink ref="F242" r:id="rId241"/>
+    <hyperlink ref="F243" r:id="rId242"/>
+    <hyperlink ref="F244" r:id="rId243"/>
+    <hyperlink ref="F245" r:id="rId244"/>
+    <hyperlink ref="F246" r:id="rId245"/>
+    <hyperlink ref="F247" r:id="rId246"/>
+    <hyperlink ref="F248" r:id="rId247"/>
+    <hyperlink ref="F249" r:id="rId248"/>
+    <hyperlink ref="F250" r:id="rId249"/>
+    <hyperlink ref="F251" r:id="rId250"/>
+    <hyperlink ref="F252" r:id="rId251"/>
+    <hyperlink ref="F253" r:id="rId252"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Senior_Care.xlsx
+++ b/results/scraped_Cape_Town_Senior_Care.xlsx
@@ -58,168 +58,168 @@
     <t>Old| Rotten Tomatoes</t>
   </si>
   <si>
+    <t>Old- YouTube</t>
+  </si>
+  <si>
     <t>OLD| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>Old- YouTube</t>
-  </si>
-  <si>
-    <t>Old(2021) - Full cast &amp; crew - IMDb</t>
-  </si>
-  <si>
     <t>WatchOld| Netflix</t>
   </si>
   <si>
+    <t>Old| Universal Pictures At Home</t>
+  </si>
+  <si>
     <t>Retirement benefits| SSA</t>
   </si>
   <si>
+    <t>RetirementOnline - Office of the New York State Comptroller</t>
+  </si>
+  <si>
+    <t>Retirement| Office of the New York State Comptroller</t>
+  </si>
+  <si>
     <t>Retirement- News, Advice &amp; Resources fromAARP</t>
   </si>
   <si>
+    <t>Retirement- Wikipedia</t>
+  </si>
+  <si>
     <t>RetirementCalculator - NerdWallet</t>
   </si>
   <si>
-    <t>Retirement- Wikipedia</t>
+    <t>10 Steps to Take as You Get Ready to Retire - AARP</t>
+  </si>
+  <si>
+    <t>Retirementplanning tools - USAGov</t>
   </si>
   <si>
     <t>Retirement Calculator</t>
   </si>
   <si>
-    <t>10 Steps to Take as You Get Ready to Retire - AARP</t>
-  </si>
-  <si>
-    <t>Retirementplanning tools - USAGov</t>
-  </si>
-  <si>
     <t>Plan forRetirement| SSA</t>
   </si>
   <si>
-    <t>Log Into Your Account |Transamerica</t>
-  </si>
-  <si>
-    <t>Account Login</t>
-  </si>
-  <si>
-    <t>Home -SeniorResources</t>
-  </si>
-  <si>
-    <t>Senior Services- City ofMilwaukee</t>
-  </si>
-  <si>
-    <t>Home - TrinitySeniorServices</t>
-  </si>
-  <si>
-    <t>SeniorCenters &amp; Dining | Department on Aging |MilwaukeeCounty</t>
-  </si>
-  <si>
-    <t>SeniorDining Menus | Department on Aging |MilwaukeeCounty</t>
-  </si>
-  <si>
-    <t>SeniorLivingWisconsin| HeritageSeniorLiving</t>
-  </si>
-  <si>
-    <t>SeniorExpress - Transportation for Seniors -Milwaukee Wi</t>
-  </si>
-  <si>
-    <t>Wisconsin Senior Employment Program(WISE)</t>
-  </si>
-  <si>
-    <t>148SeniorLiving Communities inMilwaukee,Wisconsin</t>
-  </si>
-  <si>
-    <t>Senior Centers– Serving Older Adults</t>
+    <t>91SeniorLiving Communities inWashington,District Of Columbia</t>
+  </si>
+  <si>
+    <t>55+ Communities &amp;SeniorLiving inDistrict of Columbia| After55</t>
+  </si>
+  <si>
+    <t>| dacl</t>
+  </si>
+  <si>
+    <t>SeniorCenters | dacl</t>
+  </si>
+  <si>
+    <t>DCVillages - Home Page -DCVillages</t>
+  </si>
+  <si>
+    <t>SeniorSmart Trip - WMATA</t>
+  </si>
+  <si>
+    <t>Home - VidaSeniorCenters</t>
+  </si>
+  <si>
+    <t>Senior Washington Apartments for Rent|Washington,DC</t>
+  </si>
+  <si>
+    <t>Seniors | dpr</t>
+  </si>
+  <si>
+    <t>Senior- Wikipedia</t>
   </si>
   <si>
     <t>ELDERLYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>What Age Is ConsideredElderly? - MedicareAdvantage.com</t>
+  </si>
+  <si>
     <t>Old age -Wikipedia</t>
   </si>
   <si>
-    <t>What Age Is ConsideredElderly? - MedicareAdvantage.com</t>
-  </si>
-  <si>
     <t>THEELDERLYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>ELDERLY| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
     <t>Elderly Instruments| New, Used &amp; Vintage Musical Instruments</t>
   </si>
   <si>
-    <t>ELDERLY| English meaning - Cambridge Dictionary</t>
+    <t>Expanded In-home Services for theElderly(EISEP)</t>
+  </si>
+  <si>
+    <t>What IsElderly? Understanding the Age Group</t>
+  </si>
+  <si>
+    <t>ELDERLY| definition in the Cambridge English Dictionary</t>
   </si>
   <si>
     <t>At What Age Are You Officially ConsideredElderly?</t>
   </si>
   <si>
-    <t>What IsElderly? Understanding the Age Group</t>
-  </si>
-  <si>
-    <t>What Age Is Legally Considered Elderly? - Informed Senior Living</t>
-  </si>
-  <si>
-    <t>ELDERLY| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
     <t>FRAILDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>FRAILSynonyms: 223 Similar and Opposite Words -Merriam-Webster</t>
+  </si>
+  <si>
     <t>FRAIL| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>FRAILSynonyms: 223 Similar and Opposite Words -Merriam-Webster</t>
-  </si>
-  <si>
     <t>FRAILDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
+    <t>Frail- definition offrailby The Free Dictionary</t>
+  </si>
+  <si>
     <t>Frail- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
   </si>
   <si>
-    <t>Frail- definition offrailby The Free Dictionary</t>
+    <t>frail- Wiktionary, the free dictionary</t>
+  </si>
+  <si>
+    <t>FRAIL definitionand meaning | Collins English Dictionary</t>
+  </si>
+  <si>
+    <t>Frailty: Definition &amp; Scores -Cleveland Clinic</t>
   </si>
   <si>
     <t>FRAIL| definition in the Cambridge English Dictionary</t>
   </si>
   <si>
-    <t>frail- Wiktionary, the free dictionary</t>
-  </si>
-  <si>
-    <t>FRAIL definitionand meaning | Collins English Dictionary</t>
-  </si>
-  <si>
-    <t>What DoesfrailMean? Definition &amp; Examples | Dictionary.net</t>
-  </si>
-  <si>
     <t>AGEDDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>AGED| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>AGEDDefinition &amp; Meaning |Dictionary.com</t>
+  </si>
+  <si>
+    <t>Aged(2023) - IMDb</t>
+  </si>
+  <si>
     <t>AGEDTrust Home -AgedTrust | Non-Profit</t>
   </si>
   <si>
-    <t>AGED| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>AGEDDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
-    <t>Aged(2023) - IMDb</t>
-  </si>
-  <si>
     <t>Aged- definition ofagedby The Free Dictionary</t>
   </si>
   <si>
     <t>AGED| definition in the Cambridge English Dictionary</t>
   </si>
   <si>
+    <t>Agedvs. Age - Which is Correct?</t>
+  </si>
+  <si>
+    <t>(aged.) Online Menu | Best Bistro in Forest Hills</t>
+  </si>
+  <si>
     <t>aged- Wiktionary, the free dictionary</t>
   </si>
   <si>
-    <t>Agedvs. Age - Which is Correct?</t>
-  </si>
-  <si>
-    <t>THEAGEDDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
     <t>67Easy Dinner IdeasWe Love - Taste of Home</t>
   </si>
   <si>
@@ -241,229 +241,229 @@
     <t>100Easy DinnerRecipes for Busy Weeknights - The Pioneer Woman</t>
   </si>
   <si>
-    <t>22 Easy Dinner Recipes to Make With 5 Ingredients (Or Fewer!)</t>
-  </si>
-  <si>
-    <t>Recipes, Dinners and Easy Meal Ideas | Food Network</t>
-  </si>
-  <si>
     <t>HelloFresh® Meal Kits | Free Breakfast for Life + 10 FreeMeals</t>
   </si>
   <si>
+    <t>Easy Dinner Recipes| Good Food</t>
+  </si>
+  <si>
+    <t>52Easy Dinner Recipes&amp; Ideas | Food Network</t>
+  </si>
+  <si>
     <t>Senior Care</t>
   </si>
   <si>
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae4fffc3cf21e0b29453e6dcdcf6adc0b2b839cf9cf24574cde429c4ca9c3834JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35283939-35b6-6fb2-2c7d-2ed834f76e36&amp;u=a1aHR0cHM6Ly9vbGRuYXZ5LmdhcC5jb20vP21zb2NraWQ9MzUyODM5MzkzNWI2NmZiMjJjN2QyZWQ4MzRmNzZlMzY&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aab8d2396787c215da235a787744f1822457e1cc6a03314452a33ee0340ab4a8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35283939-35b6-6fb2-2c7d-2ed834f76e36&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9PbGRfKGZpbG0p&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2aa9243f769253334d027bedcfe250875bba910f371fbe24ff681aaac8ac8664JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35283939-35b6-6fb2-2c7d-2ed834f76e36&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTA5NTQ2NTIv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=257bc2a3207f8e8275d5986836473802da27fde13d8e08d5ff0eb12f2b986ac3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35283939-35b6-6fb2-2c7d-2ed834f76e36&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L29sZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c32a53177881cfc37f94d6d89e7d2253b8376fd7e12f111561905b3a92a92efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35283939-35b6-6fb2-2c7d-2ed834f76e36&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9QTRVMnBNUlY5X2s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fac111d94df5337a9705c6208bc5e8184da2832540c77bd7125d5bc80da1fedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35283939-35b6-6fb2-2c7d-2ed834f76e36&amp;u=a1aHR0cHM6Ly93d3cucm90dGVudG9tYXRvZXMuY29tL20vb2xk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5e0ddf8acd5c374b87e5d12015960d19eb8034626d81400c7b6233fc962a2ee1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35283939-35b6-6fb2-2c7d-2ed834f76e36&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL29sZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a0bab05742c03fbff2a4c15396d4c2e17726d53e648fa523fc0b25cf27221b2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35283939-35b6-6fb2-2c7d-2ed834f76e36&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9ODR4QUQ0ci05a0U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bea285abd23708f2929a37eb0de35d87bf409e685cb784ba2fd816ecc0db809bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35283939-35b6-6fb2-2c7d-2ed834f76e36&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTA5NTQ2NTIvZnVsbGNyZWRpdHMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0778e35b3fa36c71c2f2382c92f1fa931dadf6d31533a1b99b3c296238d6010fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35283939-35b6-6fb2-2c7d-2ed834f76e36&amp;u=a1aHR0cHM6Ly93d3cubmV0ZmxpeC5jb20vdGl0bGUvODE0MTAzODY&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8968dea07a160083cde11b79171e577a9c67bb65ed3e8b3eb1f77e434857af5dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35bca7eb-32a9-6b12-26ae-b00a33bb6a1e&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e18e7797d84870a5a92884307b9cbd2c9576423bb7d44ea4a0e197e00915448bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35bca7eb-32a9-6b12-26ae-b00a33bb6a1e&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC8_bXNvY2tpZD0zNWJjYTdlYjMyYTk2YjEyMjZhZWIwMGEzM2JiNmExZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b55b9b08fa064ff6ff4110bb95864bb0ba7a515bc14168bb54ac180227961da3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35bca7eb-32a9-6b12-26ae-b00a33bb6a1e&amp;u=a1aHR0cHM6Ly93d3cubmVyZHdhbGxldC5jb20vaW52ZXN0aW5nL2NhbGN1bGF0b3JzL3JldGlyZW1lbnQtY2FsY3VsYXRvcj9tc29ja2lkPTM1YmNhN2ViMzJhOTZiMTIyNmFlYjAwYTMzYmI2YTFl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91e4bcf842db7a88fb892bd6531e1499e4d8abc3448eb511641489ffa63c0626JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35bca7eb-32a9-6b12-26ae-b00a33bb6a1e&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9SZXRpcmVtZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6530d6d71d6a0bfa25b7b04d723a510875ec3702c9432921b5c427ff839e8274JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35bca7eb-32a9-6b12-26ae-b00a33bb6a1e&amp;u=a1aHR0cHM6Ly93d3cuY2FsY3VsYXRvci5uZXQvcmV0aXJlbWVudC1jYWxjdWxhdG9yLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f256432e4351673cf1fd7b8dd9d05e6bec5e5da5fafaaa5c6583431dc5479397JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35bca7eb-32a9-6b12-26ae-b00a33bb6a1e&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC9zdGVwcy10by10YWtlLWJlZm9yZS15b3UtcmV0aXJlLz9tc29ja2lkPTM1YmNhN2ViMzJhOTZiMTIyNmFlYjAwYTMzYmI2YTFl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0e4fde0b6d575a6bcea0b211f82dc221351462e2e89e256730870034e4e0462JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35bca7eb-32a9-6b12-26ae-b00a33bb6a1e&amp;u=a1aHR0cHM6Ly93d3cudXNhLmdvdi9yZXRpcmVtZW50LXBsYW5uaW5nLXRvb2xz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b25a818c1140e647bbd889f35a1fc02d5ece6e460dde4a2e5d6105579076059cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35bca7eb-32a9-6b12-26ae-b00a33bb6a1e&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50L3BsYW4tZm9yLXJldGlyZW1lbnQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c743fd8e89a190a5ca524310ea386e30fea6a44a1914a674d89e51358d8be218JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35bca7eb-32a9-6b12-26ae-b00a33bb6a1e&amp;u=a1aHR0cHM6Ly93d3cudHJhbnNhbWVyaWNhLmNvbS9sb2dpbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3efc4e7dcc73523295f39859fe340a4b8282f9028bfe49ba2d380a3f287b6ed3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35bca7eb-32a9-6b12-26ae-b00a33bb6a1e&amp;u=a1aHR0cHM6Ly9sb2dpbi52b3lhLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5942162318f9d4770865004bf20d2cc29b1030d5aa9f59b4f65501ab69db72e9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3af62a3d-dcd6-61f6-33bd-3ddcdd4a607c&amp;u=a1aHR0cHM6Ly9zZW5pb3JyZXNvdXJjZXNvbmxpbmUuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a8c9bf0d156f5e0340d7d64c5915ee6a6a32fa83429536ab66ddb454b6cdc4bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3af62a3d-dcd6-61f6-33bd-3ddcdd4a607c&amp;u=a1aHR0cHM6Ly9jaXR5Lm1pbHdhdWtlZS5nb3YvY29tbW9uY291bmNpbC9EaXN0cmljdDYvU2VuaW9yU2VydmljZXMuaHRt&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=85e078807ef733fe396e3e729231578c34a3ffe28885ef0d72964b97cdbd3d0aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3af62a3d-dcd6-61f6-33bd-3ddcdd4a607c&amp;u=a1aHR0cHM6Ly90cmluaXR5c2VuaW9yc2VydmljZXMub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9537f208744cdc0a7231b4e317773c70f47e807dde2d54773429858e8021c47JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3af62a3d-dcd6-61f6-33bd-3ddcdd4a607c&amp;u=a1aHR0cHM6Ly9jb3VudHkubWlsd2F1a2VlLmdvdi9FTi9ESEhTL09sZGVyLUFkdWx0cy1TZXJ2aWNlcy9TZW5pb3ItQ2VudGVycy0tRGluaW5n&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91ae56708e769b2469d5a1a893dbf9fb4f448495453b26721895e139faf17bc6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3af62a3d-dcd6-61f6-33bd-3ddcdd4a607c&amp;u=a1aHR0cHM6Ly9jb3VudHkubWlsd2F1a2VlLmdvdi9FTi9ESEhTL09sZGVyLUFkdWx0cy1TZXJ2aWNlcy9TZW5pb3ItQ2VudGVycy0tRGluaW5nL1Nlbmlvci1EaW5pbmctTWVudXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5c4551da828ec7bc432e789d84c7afbde18b57ef5677075bba1db9c7dca9fa9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3af62a3d-dcd6-61f6-33bd-3ddcdd4a607c&amp;u=a1aHR0cHM6Ly9oZXJpdGFnZXNlbmlvci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b20c47eb0d7dfa6429c2bd75c7abcf61ec3d0b89d704c9dac753c2732bb4c72cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3af62a3d-dcd6-61f6-33bd-3ddcdd4a607c&amp;u=a1aHR0cHM6Ly9zZW5pb3JleHByZXNzd2kuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1f5af2521d16d7d58646ac47fb74d84431dd36c7bf85956df5e8833a1434fe6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3af62a3d-dcd6-61f6-33bd-3ddcdd4a607c&amp;u=a1aHR0cHM6Ly93d3cuZGhzLndpc2NvbnNpbi5nb3Yvd2lzZS9pbmRleC5odG0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f381b8b0f464c1fb54678d72f73eef61f7f65a53fecad27e0e33393459e911cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3af62a3d-dcd6-61f6-33bd-3ddcdd4a607c&amp;u=a1aHR0cHM6Ly93d3cuYWZ0ZXI1NS5jb20vc2VhcmNoL3dpL21pbHdhdWtlZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b9ecb754cd74f74279493bd3277dc3dc54aa7349cce9c2b7e22b64bfbf62b06fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3af62a3d-dcd6-61f6-33bd-3ddcdd4a607c&amp;u=a1aHR0cHM6Ly9zZXJ2aW5nb2xkZXJhZHVsdHMub3JnL3Nlbmlvci1jZW50ZXJzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8cf5bfb78b732962ea272bcc12697627e474f5ed63ba7194e770b3fe54c08b1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05122c73-198e-68f0-21f8-3b92184b6972&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2289f3d6334d327f218192b4956d0385342fa992323d0c0f9724bb0dd99a2cbcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05122c73-198e-68f0-21f8-3b92184b6972&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT2xkX2FnZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f35d2cd5fb7748ecf550dc4c4834939871fdfb79923ccfdc3f1c96ac63c7033JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05122c73-198e-68f0-21f8-3b92184b6972&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhcmVhZHZhbnRhZ2UuY29tL2NvbW1vbi1xdWVzdGlvbnMvd2hhdC1hZ2UtaXMtY29uc2lkZXJlZC1lbGRlcmx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d77daeee9338ec1b2704bf115d6b08ef9c61d474a56b7f61646fd4d3f5afb21JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05122c73-198e-68f0-21f8-3b92184b6972&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3RoZSUyMGVsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=122310dc5df0927eee6473d04c3a6928b27a8ec43aecf8113f654074ccd63800JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05122c73-198e-68f0-21f8-3b92184b6972&amp;u=a1aHR0cHM6Ly93d3cuZWxkZXJseS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12250a471b0803ec2c1ec04d7d0cf68868cb39107fa8b7af397b0cbf5b4ea06dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05122c73-198e-68f0-21f8-3b92184b6972&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b634079ea914425229acdcf1abe3bba269db4c5464c5a895afa7d1c9d39dbe59JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05122c73-198e-68f0-21f8-3b92184b6972&amp;u=a1aHR0cHM6Ly93d3cuc2VuaW9yc3Ryb25nLm9yZy9hdC13aGF0LWFnZS1hcmUteW91LWNvbnNpZGVyZWQtZWxkZXJseS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2f1df915623a7a9a0db805ffb112ba9308740718af4908c3427ebd8520348dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05122c73-198e-68f0-21f8-3b92184b6972&amp;u=a1aHR0cHM6Ly93d3cudGhlZWxkZXJseXdlbGxuZXNzLmNvbS9ibG9ncy93aGF0LWlzLWVsZGVybHkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=43162cc034cce6366fb329d5ae4f2a1fbc96e9c2bd2a0ef2ac5fbbe197872c4eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05122c73-198e-68f0-21f8-3b92184b6972&amp;u=a1aHR0cHM6Ly9pbmZvcm1lZHNlbmlvcmxpdmluZy5jb20vd2hhdC1hZ2UtaXMtbGVnYWxseS1jb25zaWRlcmVkLWVsZGVybHkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ca9e3a626c61ad1c80e738223362a49d4e78b989c9983342713d91b5093f2bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05122c73-198e-68f0-21f8-3b92184b6972&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2VsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9d23dfa5e8901440d7a7d818bec7968a21bad58c77d8daa954c108c95b23dd9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14e59f23-3b7a-68fa-1ab2-88c23a9269e3&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20304c3f1273a930b640e407673ebad66807f1b02ed36450a1efff772868a61dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14e59f23-3b7a-68fa-1ab2-88c23a9269e3&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d044c9032c767289fb5010d14d4370a364c2e14cd72497c4188786b05c2513eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14e59f23-3b7a-68fa-1ab2-88c23a9269e3&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvZnJhaWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f378aa285befad505f66407751c4a78aa2c95fc44b5fee9da68f2fd91a3fc39aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14e59f23-3b7a-68fa-1ab2-88c23a9269e3&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce8ef9e0074baf32aa2d07cb7178c9568403ce7f7060c2c262aec466be02f488JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14e59f23-3b7a-68fa-1ab2-88c23a9269e3&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61cceb7a9b6f31c19fd61f95ca9b14697985ffd1b906e35a9f4ff9f42d36ae73JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14e59f23-3b7a-68fa-1ab2-88c23a9269e3&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cad8a474343185733d4b914b50dff7a684bb4d6b2d13ccf4516505cbbfcb988dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14e59f23-3b7a-68fa-1ab2-88c23a9269e3&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2237ccabfc48c128dab5ba67a950d2f138ae7ffbadc4a2d899e363a0f4dc3e3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14e59f23-3b7a-68fa-1ab2-88c23a9269e3&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45373f409973e39ff3c1237ae2a4d13a6df02cb91d257c66414fc61513c5a323JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14e59f23-3b7a-68fa-1ab2-88c23a9269e3&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL2RpY3Rpb25hcnkvZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=484be241c03fdbb420da2bb6406ebd47bcb832b10fe8cb15fbde8553ada58193JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14e59f23-3b7a-68fa-1ab2-88c23a9269e3&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5uZXQvZGljdGlvbmFyeS9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bde13339eca066d3192c8c5baad390a49f862777869896e5d0b4ef26f7ef8c80JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34e15d4c-6f82-6816-012a-4aad6ef0698f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3894b6ceb05f55122391a94954edc6b9c5a0f002a7853f340aa95e0289c9cdd7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34e15d4c-6f82-6816-012a-4aad6ef0698f&amp;u=a1aHR0cHM6Ly90cnVzdGFnZWQub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ac4390460aee207f6ea0efc582266fa43534c7b4b9967ad283d64d726b97527JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34e15d4c-6f82-6816-012a-4aad6ef0698f&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=349d2bf17edb2b43d8579061751ed3a343597dbf7b044d50d93e8da35b09639eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34e15d4c-6f82-6816-012a-4aad6ef0698f&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f554079f7f3b28aef29c3efeeffcc5ac7055420fa1cc20fdfd5fe17b8a88d98fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34e15d4c-6f82-6816-012a-4aad6ef0698f&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNzA0NDAyMA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=006ffd590b172db9a87cd9abf0d9c15aa2a085eab9ec3b4a0d382ccb7e48ebf8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34e15d4c-6f82-6816-012a-4aad6ef0698f&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4321418dab6dae195450636ce754e278399cc40ca3a1c6f512ae5d6cc665d8cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34e15d4c-6f82-6816-012a-4aad6ef0698f&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=414e4b60e2f4a922d9404c1a2bc2731b67b23899d16c8462ec4cae55f064ef42JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34e15d4c-6f82-6816-012a-4aad6ef0698f&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=886643a64ae0deb107f9ea0cb37dba01982c67be19a0d35d38fb03f13f7df6b2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34e15d4c-6f82-6816-012a-4aad6ef0698f&amp;u=a1aHR0cHM6Ly9jb3JyZWN0d29yZGluZy5jb20vYWdlZC1vci1hZ2Uv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3970768758c1206af93140ab4af2f8040b067d34bdfa926a7d0cd7ff1d4dde63JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34e15d4c-6f82-6816-012a-4aad6ef0698f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3RoZSUyMGFnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91ae560aa63f7529110b8e3c6be68f66a99b537ffcf687383c094efda5fffbffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e8e237e-9d20-6b74-3581-349f9ce06aa9&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZWFzeS1kaW5uZXItaWRlYXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d05058f65762454d7a985073b0894fbc8a865fe75f1bdde7a6999a106f6bf85JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e8e237e-9d20-6b74-3581-349f9ce06aa9&amp;u=a1aHR0cHM6Ly93d3cuYWxscmVjaXBlcy5jb20vMTAwLWVhc3ktbWVhbHMtMTE2OTUyMjc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a12a33fe9006a2f777c54b17f9fd282d766d88406e849f5f87bc96850a773c65JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e8e237e-9d20-6b74-3581-349f9ce06aa9&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzY4OTA2OTk3L2Jlc3QtZWFzeS1kaW5uZXItcmVjaXBlcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=954744b45414cf8374d7a7ecfe884554e9b94ed3f4485b07cfc24d6f4c17ebdfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e8e237e-9d20-6b74-3581-349f9ce06aa9&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=643b151f9202cfbc87db770a1af6b9db9fb7381ee664c66c6a30ad8b848febeaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e8e237e-9d20-6b74-3581-349f9ce06aa9&amp;u=a1aHR0cHM6Ly90aGVyZWFsZm9vZGRpZXRpdGlhbnMuY29tL2Vhc3ktZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a03d360a0cd860de65c27a18416bab4e4fc7310639347ab5cde2ca8a9b51b878JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e8e237e-9d20-6b74-3581-349f9ce06aa9&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zLzMwLW1pbnV0ZS1kaW5uZXItcmVjaXBlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d20e559b0cca09fcf91e9323be84a2a2388e72de33ec450efee16490af94c61cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e8e237e-9d20-6b74-3581-349f9ce06aa9&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzMyMjY0Mjg0L2Vhc3ktZGlubmVyLXJlY2lwZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3eb993bb6283a88f135724f5548635dfd47644c6632f9d3d807dbc67ae773038JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e8e237e-9d20-6b74-3581-349f9ce06aa9&amp;u=a1aHR0cHM6Ly93d3cuYWxscmVjaXBlcy5jb20vNS1pbmdyZWRpZW50LWRpbm5lci1yZWNpcGVzLTExODQxODYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe24a2d587d3019c119b99949d9d330593bacff4bf66737d6222ef6db3d045d1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e8e237e-9d20-6b74-3581-349f9ce06aa9&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=588024c52f982c4814209acdedaba577cfc663d1128a30ed8b8bab4305b18373JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e8e237e-9d20-6b74-3581-349f9ce06aa9&amp;u=a1aHR0cHM6Ly93d3cuaGVsbG9mcmVzaC5jb20v&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2167a3a847354e566b137ea4bb963d82d3fcd167b19c86048a14552ca5372249JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly9vbGRuYXZ5LmdhcC5jb20vP21zb2NraWQ9MzhiYjhlOWFhMTk3NmVjZTNjYWI5OTdiYTA4ODZmNzI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0579c1e7060e6aa534d5ed910fd9413eb362f0cbb7ca413c9574900652b391bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9PbGRfKGZpbG0p&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ac81849a0b8d9248ed5d4711b8430fb385c738fc648600ecabf813aaeb8ebdcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTA5NTQ2NTIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5cdee5b504926cc5e1f4bf81114765ea7dcc7c1e0defa446dcd2bde579d42ce3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L29sZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91226115219946c2550f2c14e8e8272115b52a7fcce748d2f946b52cec6fcf90JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9QTRVMnBNUlY5X2s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd3c334e771da4253e8d7ac918c8828e62aa97440f1b9070756122df97058dd1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly93d3cucm90dGVudG9tYXRvZXMuY29tL20vb2xk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffceb824d3df922428669ba16ba2440b51122f16c7c8ae389212088c7a15e1e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9ODR4QUQ0ci05a0U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1725a1ecb723082519abb3665c06bc8f71ff2571622d815964faacd2ca6039bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL29sZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2dc5bca6ce3b6e27d5a9f12319faaf8dd8349c02c373356859dab09ad0edc835JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly93d3cubmV0ZmxpeC5jb20vdGl0bGUvODE0MTAzODY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d90e39609765e55a8734d5ba8c0d67aab42a94a270ca96462a699d92a5525a15JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly93d3cudW5pdmVyc2FscGljdHVyZXNhdGhvbWUuY29tL21vdmllcy9vbGQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f11b6197d2d65b9e3d83d05f64d7caf903e8d0a3bef57f1f50fbeeb8771f213JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d4049ce11d622bd5e1ba10929d884cb59b89a4c92536c5134cbaa88845935ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93ZWIub3NjLnN0YXRlLm55LnVzL3JldGlyZS9yZXRpcmVtZW50X29ubGluZS9jdXN0b21lcnMucGhwP3JlZGlyZWN0PWxlZ2FjeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=90c1756fa856b4997a3150fa89b586f442f1bf741a4af4e8f61bd585ad23dceeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cub3NjLm55Lmdvdi9yZXRpcmVtZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=051e221000bf80278132cb1eac0b54a72727764f402d2350308485ea8970564fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC8_bXNvY2tpZD0yMTk4MzYyZjJjY2U2ZjA4MjgwZTIxY2UyZDRkNmVhMw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ff77cdfea890be9ae75821221546db52406d2c5f4d8bececdd33d9364c599a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUmV0aXJlbWVudA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2dde7c8b65df4a21e7bd45c9365d65a2cfd6e29b7deba8eefb7dff2ca23ee8deJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cubmVyZHdhbGxldC5jb20vaW52ZXN0aW5nL2NhbGN1bGF0b3JzL3JldGlyZW1lbnQtY2FsY3VsYXRvcj9tc29ja2lkPTIxOTgzNjJmMmNjZTZmMDgyODBlMjFjZTJkNGQ2ZWEz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45b8c2c6edd946c46969f1b48aacf1c4f43d51c493d03f527596f357ee1094bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC9zdGVwcy10by10YWtlLWJlZm9yZS15b3UtcmV0aXJlLz9tc29ja2lkPTIxOTgzNjJmMmNjZTZmMDgyODBlMjFjZTJkNGQ2ZWEz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=431200c7ecdb588072436ecacd334c8821733b81742eb578a0e4c6b10a47f9d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cudXNhLmdvdi9yZXRpcmVtZW50LXBsYW5uaW5nLXRvb2xz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a72f1bf9d9632216137fe748eb4824af2f729f332367a5546bd4407570617877JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cuY2FsY3VsYXRvci5uZXQvcmV0aXJlbWVudC1jYWxjdWxhdG9yLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb8a46fc38b7387a943883d4f712e41efb3080ea83d2e973130a0f800fbd346bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50L3BsYW4tZm9yLXJldGlyZW1lbnQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e4e735e58a9152e9b93ec19c7de2cb7371b72f5c2bb08c8fd184c13dc70441c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly93d3cuYWZ0ZXI1NS5jb20vc2VhcmNoL2RjL3dhc2hpbmd0b24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=39b9de3ec56b84797d83f5353353ebb9a90577660fe27e9b19e68245d514ce50JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly93d3cuYWZ0ZXI1NS5jb20vc2VhcmNoL2Rj&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8891b3d6978f1aebd1c1005cd7179122a161b8cd4ee52719f62d1e7617018e66JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly9kYWNsLmRjLmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96026f27b119b15c5e88873ed01651d2fe04f735f9a012f20bf65c0d374a0cc5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly9kYWNsLmRjLmdvdi9zZXJ2aWNlL3Nlbmlvci1jZW50ZXJz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a614110e486f34d7c943bb0fb7d263ca24ff87f85baf426939a86e7f522f8579JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly9kY3ZpbGxhZ2VzLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86aa7f2d72c0f24a41c6a8749f6184c7e98b77658eb77a8e285098be19899ab3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly93d3cud21hdGEuY29tL3BheS9mYXJlLXByb2dyYW1zL3Nlbmlvci1zbWFydC10cmlwLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11ef3ac0148c597ebb13816bbe37321816329659c2095c3e776c19bcdabbfb16JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly93d3cudmlkYXNlbmlvcmNlbnRlci5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8bcc56e722a38246d0d82619db35cc25a38557e0c20341d34dccba04269d86c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly93d3cuYXBhcnRtZW50aG9tZWxpdmluZy5jb20vd2FzaGluZ3Rvbi1kYy9hcGFydG1lbnRzLWZvci1yZW50L3Nlbmlvcj9tc29ja2lkPTM5NzBjNjdjYjlmNzY3NGYxZjQwZDE5ZGI4ODk2NjUw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=607169a3622bca8c19fa94e1c9732adcbbfe8bbe01ec1d3ae943d62f032367d0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly9kcHIuZGMuZ292L3BhZ2Uvc2VuaW9ycw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9bf21fd30d4227b0a3e5b900f39effac07fe8624618235d656c1c2f66dae585JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2VuaW9y&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1859246502cadc78243b4cc953116f0f7a7074d1217d0c0f9c2a27be0805ab7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VsZGVybHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b6fd4d02beb3d2747987cd65546cd8de44dccd5fc997c43ebca723c1384caafJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhcmVhZHZhbnRhZ2UuY29tL2NvbW1vbi1xdWVzdGlvbnMvd2hhdC1hZ2UtaXMtY29uc2lkZXJlZC1lbGRlcmx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dda9064a44da202afa4fc99434845341bf8cce4219e1e40a59da104f79dd919cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT2xkX2FnZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=238de197fed6d5b64e05eb074a862346e02a2ecaf9066edb11d25a0401420203JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3RoZSUyMGVsZGVybHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2fe4f8f47ebf6b11b67ae14da0e0993248487b7a380d3f8ab1d6693f132c7562JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VsZGVybHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0364fd0f9df17bff6a594651462f6f102cab5a070656dbe5ad27088bd54b7d88JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly93d3cuZWxkZXJseS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40a90cf77c9450023ef693ac71c68064d757dbc3eb2563c8f9276a6ea9bd073dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly9hZ2luZy5ueS5nb3YvZXhwYW5kZWQtaG9tZS1zZXJ2aWNlcy1lbGRlcmx5LWVpc2Vw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00e3670878a89bebca72f218d98dee38439477cda6bd1f3038291aad901e8051JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly93d3cudGhlZWxkZXJseXdlbGxuZXNzLmNvbS9ibG9ncy93aGF0LWlzLWVsZGVybHkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=680f6d0271f86daf074f9d0d90e87ba1ca27699ed977f2c74558d57ef1a2bbe5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2VsZGVybHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=998a35d2e4c0693548a2487dd1caa1ab37e482b033e63e443b89d20a4eff450aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly93d3cuc2VuaW9yc3Ryb25nLm9yZy9hdC13aGF0LWFnZS1hcmUteW91LWNvbnNpZGVyZWQtZWxkZXJseS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=92268235fd8f3327f9625e13e82f2ae5427fcb5fbc51117955b34102101706cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27c1180a080b3ea22d3926b986fd9d85c44130f5d92ef086c929355056d82377JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvZnJhaWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8786ffe0cb3f4c0ee90bb61fa8127c4e3259ecb81c7b80afa04d6a34255475eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0d86c08649edec224ac4e7b80d9fd27c0da8c423e8e4e219a13de661481cdf6cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5257731a33a48128f9c84e2156744bd72eee7f4e0884e09e98b3fd5252b9076JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f7294a5928d168831cd8b076e03207bdf247ef1949178aad0faf96015ad96210JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9mcmFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a596c50cc08442c8caa38565f4a75da3c5022bac31914c855132a8fb3e57a7eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly9lbi5tLndpa3Rpb25hcnkub3JnL3dpa2kvZnJhaWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ec574743125b088444da9b6f41f782f6ecb14b62548ea1744ccb08fdae76e749JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL2RpY3Rpb25hcnkvZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04202b9820b6c06ea0dad8e170a6ccfaeb4ebc2ecb488808b32fba941750052aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9kaXNlYXNlcy9mcmFpbHR5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=864d83121470159efb0a666053bfddf8c3a6e3259fb5a60bcbf3c90832174359JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba074f3cf59410bf7b8c07c16e741d282a806c4b516b02481be291aaf5d3b6f6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FnZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0dc9c939e1047452a872a8a15029c990b82d503fc1b3f938d51e42cd7ba806bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FnZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4368c4a408e1357dfc3a6129f3f71ac7c2e3ba2037c6ec26f1e8e4e74c2c684bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FnZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e64d9b28838d1e6e7127816a25ee77c57b56d7d056965d6654a38ee63491ced4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNzA0NDAyMA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=750ad9c24b928bb0c0a73aac55986c61719d6ffd5a34a7e291aaa296b017787cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly90cnVzdGFnZWQub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9f2104b9a214ed3142138f84c119964ddf1818284e1ca6729f7f8c31c7e02569JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FnZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cac5ac8b677d50da7bff48de79d68f9bfe049d89f3bdfef3eed01aae6e99d690JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2FnZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4446c4a8e5e2f4a04d94938cbb68a0815d6ab7b266dc4fff4e8720dacc9b185fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly9jb3JyZWN0d29yZGluZy5jb20vYWdlZC1vci1hZ2Uv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=457af204292340be59d8a68351e81ab85b74f333ba857a50211a2e6cc4c83ab3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly9hZ2VkbnljLmNvbS9tZW51&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b8f4d7b8d248713b135a82f7187b278dc365e3375e7852b6578ddf8b558aff5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2FnZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e6daa5e73382d743c48564504029e9bf72f59fb3453e9bf9b7ba8e74f12807fcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZWFzeS1kaW5uZXItaWRlYXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3eb44853c0c360f333e99bbb66f8b287695fee59a5f10cbe790d35d0681891a9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cuYWxscmVjaXBlcy5jb20vMTAwLWVhc3ktbWVhbHMtMTE2OTUyMjc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=990ee36492c0b614c18b50dbb7ee8395d8638212e7ba4b6fa4cb00c0eb7bdfc6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzY4OTA2OTk3L2Jlc3QtZWFzeS1kaW5uZXItcmVjaXBlcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f61ae393922ec88ca88cb2fd82e8c7ba0cb2b8c39fa89ac7ea91ca0abe318dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f055129b0572bfc31d57289086bfbcf45f243f7cd17b0c855d138e52457785e5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly90aGVyZWFsZm9vZGRpZXRpdGlhbnMuY29tL2Vhc3ktZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=abacce5398bb28931c11fcc51b4caec49506b470f93adca7219e61a558d5ad00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zLzMwLW1pbnV0ZS1kaW5uZXItcmVjaXBlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=acbb470e6ae379e08dcf58a820d80b8b7ac7be1e4e2e6868e0178677699ff270JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzMyMjY0Mjg0L2Vhc3ktZGlubmVyLXJlY2lwZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c68aeca96e4c2552818a3e90de53b5ad2fb2e56c47b5d5708117879ae8a3bdfdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cuaGVsbG9mcmVzaC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3fb176aaa9c7378d23b05099b5612079be3c29dbff7bdc72bc277d5ead74f58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cuYmJjZ29vZGZvb2QuY29tL3JlY2lwZXMvY29sbGVjdGlvbi9lYXN5LWRpbm5lci1yZWNpcGVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3014ef8555bb28bfdabcaeb7a139ad6f00b1524a661df5d8a1b68083a9e7dab8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zL2Vhc3ktZGlubmVyLXJlY2lwZXM&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>

--- a/results/scraped_Cape_Town_Senior_Care.xlsx
+++ b/results/scraped_Cape_Town_Senior_Care.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="341">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -73,12 +73,6 @@
     <t>Retirement benefits| SSA</t>
   </si>
   <si>
-    <t>RetirementOnline - Office of the New York State Comptroller</t>
-  </si>
-  <si>
-    <t>Retirement| Office of the New York State Comptroller</t>
-  </si>
-  <si>
     <t>Retirement- News, Advice &amp; Resources fromAARP</t>
   </si>
   <si>
@@ -88,51 +82,60 @@
     <t>RetirementCalculator - NerdWallet</t>
   </si>
   <si>
+    <t>California Public Employees'RetirementSystem</t>
+  </si>
+  <si>
     <t>10 Steps to Take as You Get Ready to Retire - AARP</t>
   </si>
   <si>
+    <t>Plan forRetirement| SSA</t>
+  </si>
+  <si>
+    <t>Retirement Calculator</t>
+  </si>
+  <si>
     <t>Retirementplanning tools - USAGov</t>
   </si>
   <si>
-    <t>Retirement Calculator</t>
-  </si>
-  <si>
-    <t>Plan forRetirement| SSA</t>
-  </si>
-  <si>
-    <t>91SeniorLiving Communities inWashington,District Of Columbia</t>
-  </si>
-  <si>
-    <t>55+ Communities &amp;SeniorLiving inDistrict of Columbia| After55</t>
-  </si>
-  <si>
-    <t>| dacl</t>
-  </si>
-  <si>
-    <t>SeniorCenters | dacl</t>
-  </si>
-  <si>
-    <t>DCVillages - Home Page -DCVillages</t>
-  </si>
-  <si>
-    <t>SeniorSmart Trip - WMATA</t>
-  </si>
-  <si>
-    <t>Home - VidaSeniorCenters</t>
-  </si>
-  <si>
-    <t>Senior Washington Apartments for Rent|Washington,DC</t>
-  </si>
-  <si>
-    <t>Seniors | dpr</t>
-  </si>
-  <si>
-    <t>Senior- Wikipedia</t>
+    <t>RetirementPlanning | Preparing ForRetirement| Fidelity Investments</t>
+  </si>
+  <si>
+    <t>IslandSeniorResources – Serving Whidbey and Camano Islands …</t>
+  </si>
+  <si>
+    <t>SeniorServices |Oak Harbor,WA</t>
+  </si>
+  <si>
+    <t>TheCenter In Oak Harbor: Activities &amp; Resources For50+</t>
+  </si>
+  <si>
+    <t>4SeniorLiving Communities inOak Harbor,Washington</t>
+  </si>
+  <si>
+    <t>Home | Ohscfoundation</t>
+  </si>
+  <si>
+    <t>SeniorLiving Communitiesin Oak Harbor,Washington</t>
+  </si>
+  <si>
+    <t>SeniorHome Care inOak Harbor| Family Resource Home Care</t>
+  </si>
+  <si>
+    <t>Facilities • The Center -Oak Harbor,WA</t>
+  </si>
+  <si>
+    <t>Oak Harbor,WA SeniorLiving |Regency on Whidbey</t>
+  </si>
+  <si>
+    <t>SENIORDefinition &amp; Meaning - Merriam-Webster</t>
   </si>
   <si>
     <t>ELDERLYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>Elderly Instruments| New, Used &amp; Vintage Musical Instruments</t>
+  </si>
+  <si>
     <t>What Age Is ConsideredElderly? - MedicareAdvantage.com</t>
   </si>
   <si>
@@ -145,37 +148,37 @@
     <t>ELDERLY| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>Elderly Instruments| New, Used &amp; Vintage Musical Instruments</t>
-  </si>
-  <si>
-    <t>Expanded In-home Services for theElderly(EISEP)</t>
+    <t>At What Age Are You Officially ConsideredElderly?</t>
   </si>
   <si>
     <t>What IsElderly? Understanding the Age Group</t>
   </si>
   <si>
-    <t>ELDERLY| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>At What Age Are You Officially ConsideredElderly?</t>
+    <t>What Age Is Legally Considered Elderly? - Informed Senior Living</t>
+  </si>
+  <si>
+    <t>ELDERLYDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
     <t>FRAILDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>FRAIL| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
     <t>FRAILSynonyms: 223 Similar and Opposite Words -Merriam-Webster</t>
   </si>
   <si>
-    <t>FRAIL| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
     <t>FRAILDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
+    <t>Frail- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
+  </si>
+  <si>
     <t>Frail- definition offrailby The Free Dictionary</t>
   </si>
   <si>
-    <t>Frail- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
+    <t>FRAIL| definition in the Cambridge English Dictionary</t>
   </si>
   <si>
     <t>frail- Wiktionary, the free dictionary</t>
@@ -187,67 +190,340 @@
     <t>Frailty: Definition &amp; Scores -Cleveland Clinic</t>
   </si>
   <si>
-    <t>FRAIL| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>AGEDDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>AGED| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>AGEDDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
-    <t>Aged(2023) - IMDb</t>
-  </si>
-  <si>
-    <t>AGEDTrust Home -AgedTrust | Non-Profit</t>
-  </si>
-  <si>
-    <t>Aged- definition ofagedby The Free Dictionary</t>
-  </si>
-  <si>
-    <t>AGED| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>Agedvs. Age - Which is Correct?</t>
-  </si>
-  <si>
-    <t>(aged.) Online Menu | Best Bistro in Forest Hills</t>
-  </si>
-  <si>
-    <t>aged- Wiktionary, the free dictionary</t>
-  </si>
-  <si>
-    <t>67Easy Dinner IdeasWe Love - Taste of Home</t>
-  </si>
-  <si>
-    <t>100 of the EasiestMealsWe’ve Ever Made - Allrecipes</t>
-  </si>
-  <si>
-    <t>50 Easy Dinner Recipes for Busy Weeknights - The Pioneer Woman</t>
-  </si>
-  <si>
-    <t>92 Dinner Ideas You Can Make in a Flash | Taste of Home</t>
-  </si>
-  <si>
-    <t>70 Easy Dinner Ideas</t>
-  </si>
-  <si>
-    <t>104 Quick Dinner Ideas in 30 Minutes or Less | Food Network</t>
-  </si>
-  <si>
-    <t>100Easy DinnerRecipes for Busy Weeknights - The Pioneer Woman</t>
-  </si>
-  <si>
-    <t>HelloFresh® Meal Kits | Free Breakfast for Life + 10 FreeMeals</t>
-  </si>
-  <si>
-    <t>Easy Dinner Recipes| Good Food</t>
-  </si>
-  <si>
-    <t>52Easy Dinner Recipes&amp; Ideas | Food Network</t>
+    <t>Baggageinformation, restrictions - Travel info -WestJet</t>
+  </si>
+  <si>
+    <t>Travel help and support |WestJet</t>
+  </si>
+  <si>
+    <t>WestJetBaggage, Cancellation &amp; Seat Policy: Complete Guide</t>
+  </si>
+  <si>
+    <t>WestJetTravel Guide -Check-in, Baggage &amp;Flights</t>
+  </si>
+  <si>
+    <t>WestJet Baggage Fees, Policy, and Terms [Updated 2026]</t>
+  </si>
+  <si>
+    <t>WestJet| Manage Booking</t>
+  </si>
+  <si>
+    <t>Check in|WestJet</t>
+  </si>
+  <si>
+    <t>Free Porn Videos &amp; Sex Movies - Porno, XXX, Porn Tube |Pornhub</t>
+  </si>
+  <si>
+    <t>PornhubPorn Videos</t>
+  </si>
+  <si>
+    <t>Pornhub| Free Porn Videos &amp; Sex Movies - Porno, XXX Tube</t>
+  </si>
+  <si>
+    <t>Pornhub- Free HD Porn Videos &amp; Online Sex Movies</t>
+  </si>
+  <si>
+    <t>PornhubVideos &amp; Streaming Content |Pornhub</t>
+  </si>
+  <si>
+    <t>pornhubvideos -XVIDEOS.COM</t>
+  </si>
+  <si>
+    <t>Pornhub Categories: Find Your Favorite Free Hardcore Porn Videos</t>
+  </si>
+  <si>
+    <t>Free XXX PornVideos: Hardcore Adult Sex Movies, Porno Hub Tube</t>
+  </si>
+  <si>
+    <t>FreeRecommendedPorn: Hot Hardcore Sex Videos |Pornhub</t>
+  </si>
+  <si>
+    <t>Videos Porno y Películas De Sexo Gratis - Porno, XXX, Porno Tube |Pornhub</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>GoogleAI - How we're making AI helpful for everyone</t>
+  </si>
+  <si>
+    <t>AboutGoogle: Our products, technology and company ...</t>
+  </si>
+  <si>
+    <t>Google- Facebook</t>
+  </si>
+  <si>
+    <t>AboutGoogle: History, office locations, commitments ...</t>
+  </si>
+  <si>
+    <t>GoogleSearch - A new kind of help</t>
+  </si>
+  <si>
+    <t>The 10 bestmotels in Las Vegas, US |Booking.com</t>
+  </si>
+  <si>
+    <t>MotelsinLas Vegasfrom $28/night -KAYAK</t>
+  </si>
+  <si>
+    <t>THE 10 BESTCheap MotelsinLas Vegas-Tripadvisor</t>
+  </si>
+  <si>
+    <t>10 BestMotels in Las Vegas: Find CheapMotels in Las Vegas... -Expedia</t>
+  </si>
+  <si>
+    <t>THE 10BEST Las Vegas Motels2026 (with Prices) -Tripadvisor</t>
+  </si>
+  <si>
+    <t>Top 10 BestMotelsAnd InnsNear Las Vegas, Nevada (Updated …</t>
+  </si>
+  <si>
+    <t>Top 10 Bestmotels Near Las Vegas, Nevada (Updated 2026)</t>
+  </si>
+  <si>
+    <t>TopMotels in Las Vegas, NV |Hotels.com</t>
+  </si>
+  <si>
+    <t>FindLas Vegas motelsdeals from $55+ | momondo</t>
+  </si>
+  <si>
+    <t>BookmotelsinLas Vegasfrom $52+ | HotelsCombined</t>
+  </si>
+  <si>
+    <t>2026 NFL Division Standings</t>
+  </si>
+  <si>
+    <t>NFL Schedules: Games, Times, Matchups &amp; Tickets</t>
+  </si>
+  <si>
+    <t>NGS | NFL Next Gen Stats</t>
+  </si>
+  <si>
+    <t>2025 OFFICIAL PLAYING RULES OF THE NATIONAL …</t>
+  </si>
+  <si>
+    <t>NFL Rulebook – NFL</t>
+  </si>
+  <si>
+    <t>National Football League - NFL Pick'em</t>
+  </si>
+  <si>
+    <t>Contact Us – NFL</t>
+  </si>
+  <si>
+    <t>Pepsi Rookie of the Week - Week 2 Winner Announced</t>
+  </si>
+  <si>
+    <t>National Football League Game Summary</t>
+  </si>
+  <si>
+    <t>02 - Rulebook Tab</t>
+  </si>
+  <si>
+    <t>Contact Us - Microsoft Support</t>
+  </si>
+  <si>
+    <t>Anmelden bei Hotmail | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Microsoft Copilot Blog | Microsoft Community Hub</t>
+  </si>
+  <si>
+    <t>Exchange Online EWS, Your Time is Almost Up | Microsoft …</t>
+  </si>
+  <si>
+    <t>Getting ready for the Windows 11 upgrade | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Mettre à jour les pilotes via Gestionnaire de périphériques dans ...</t>
+  </si>
+  <si>
+    <t>Aktualisieren von Treibern über Geräte-Manager in Windows</t>
+  </si>
+  <si>
+    <t>Getting the latest Microsoft Edge update just got easier</t>
+  </si>
+  <si>
+    <t>Share your calendar in Outlook | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Sign in to Microsoft Forms</t>
+  </si>
+  <si>
+    <t>Microsoft– AI, Cloud, Productivity, Computing, Gaming &amp; Apps</t>
+  </si>
+  <si>
+    <t>Microsoftaccount | Sign In or Create Your Account Today –Microsoft</t>
+  </si>
+  <si>
+    <t>Sign in to your account</t>
+  </si>
+  <si>
+    <t>Microsoft- Wikipedia</t>
+  </si>
+  <si>
+    <t>Microsoft365 for Individuals: Subscription for Productivity Apps</t>
+  </si>
+  <si>
+    <t>Sign in to your account - myaccount.microsoft.com</t>
+  </si>
+  <si>
+    <t>Home |MicrosoftCareers</t>
+  </si>
+  <si>
+    <t>Create yourMicrosoftaccount</t>
+  </si>
+  <si>
+    <t>MicrosoftStore - Download apps,games&amp; more for your Windows PC</t>
+  </si>
+  <si>
+    <t>Microsoft365 - Sign into Copilot</t>
+  </si>
+  <si>
+    <t>BestWishes - All TheBestQuotes and Messages | WishesMsg</t>
+  </si>
+  <si>
+    <t>112 HeartfeltBestWishes Messages for Every Occasion</t>
+  </si>
+  <si>
+    <t>BestSampleMessage| List of Wishes and Text Messages</t>
+  </si>
+  <si>
+    <t>Our 8 FavoriteMobile Messaging Appsof 2026 - Lifewire</t>
+  </si>
+  <si>
+    <t>130+BestWishesMessagefor Every Occasion</t>
+  </si>
+  <si>
+    <t>200+ Short Positive Messages for Friends that Show Support</t>
+  </si>
+  <si>
+    <t>70 Positive Encouragement Quotes and Messages For All Occasions</t>
+  </si>
+  <si>
+    <t>150+ Deep Love Messages for Her That Will Melt Her Heart …</t>
+  </si>
+  <si>
+    <t>138Best Wishes and Good Luck Messagesfor All Occasions</t>
+  </si>
+  <si>
+    <t>Short Messages for Every Occasion (300+ Examples)</t>
+  </si>
+  <si>
+    <t>Google Finance - Stock Market Prices, Real-time Quotes &amp; Business …</t>
+  </si>
+  <si>
+    <t>NIFTY 50 Price, Real-time Quote &amp; News - Google Finance</t>
+  </si>
+  <si>
+    <t>Freecast Inc (CAST) Stock Price &amp; News - Google Finance</t>
+  </si>
+  <si>
+    <t>SoFi Technologies Inc (SOFI) Stock Price &amp; News - Google Finance</t>
+  </si>
+  <si>
+    <t>IQIYI Inc - ADR (IQ) Stock Price &amp; News - Google Finance</t>
+  </si>
+  <si>
+    <t>Boeing Co (BA) Stock Price &amp; News - Google Finance</t>
+  </si>
+  <si>
+    <t>McDonald's Corp (MCD) Stock Price &amp; News - Google Finance</t>
+  </si>
+  <si>
+    <t>Robinhood Markets Inc (HOOD) Stock Price &amp; News - Google Finance</t>
+  </si>
+  <si>
+    <t>SSR Mining Inc (SSRM) Stock Price &amp; News - Google Finance</t>
+  </si>
+  <si>
+    <t>Tilray Brands Inc (TLRY) Stock Price &amp; News - Google Finance</t>
+  </si>
+  <si>
+    <t>WalgreensPharmacies &amp; Stores NearChicago, IL</t>
+  </si>
+  <si>
+    <t>WalgreensPharmacy -151 N STATE ST, Chicago, IL 60601</t>
+  </si>
+  <si>
+    <t>Walgreens- 4801 N LINCOLN AVE,ChicagoHours &amp; Location</t>
+  </si>
+  <si>
+    <t>Walgreens- 3201 Broadway,Chicago, IL - Hours &amp; Weekly Ad</t>
+  </si>
+  <si>
+    <t>Walgreens- 342 E ILLINOIS ST,ChicagoHours &amp; Location</t>
+  </si>
+  <si>
+    <t>Walgreens Chicago, Cook County, IL - Store Locator &amp; Hours</t>
+  </si>
+  <si>
+    <t>Walgreenslocations inChicago- See hours, directions, tips, and photos.</t>
+  </si>
+  <si>
+    <t>WalgreensinChicago, 4710 S Western Ave. Location, phone, …</t>
+  </si>
+  <si>
+    <t>WalgreensLocations &amp; Hours inChicago, Illinois -MyStore411</t>
+  </si>
+  <si>
+    <t>Walgreens- 4700 S HALSTED ST,CHICAGO, IL 60609 - Inside Rx</t>
+  </si>
+  <si>
+    <t>Latest news, sport and opinion from the Guardian</t>
+  </si>
+  <si>
+    <t>A lesson in hate - The Guardian</t>
+  </si>
+  <si>
+    <t>Guardian Jobs</t>
+  </si>
+  <si>
+    <t>holidays.theguardian.com</t>
+  </si>
+  <si>
+    <t>My brother, the Unabomber | US news | The Guardian</t>
+  </si>
+  <si>
+    <t>Join the mass killers' appreciation society - The Guardian</t>
+  </si>
+  <si>
+    <t>‘Unabomber’ Ted Kaczynski died by suicide in prison – report</t>
+  </si>
+  <si>
+    <t>Brother who turned in the Unabomber: 'I want him to know that the …</t>
+  </si>
+  <si>
+    <t>Ted K review – queasy inner life of the monkish, unhappy Unabomber</t>
+  </si>
+  <si>
+    <t>Tundra- Wikipedia</t>
+  </si>
+  <si>
+    <t>Tundra| Definition, Climate, Animals, &amp; Facts | Britannica</t>
+  </si>
+  <si>
+    <t>2026Tundra- Toyota.com</t>
+  </si>
+  <si>
+    <t>TundraBiome: Types, Location, Climate, &amp; Animals</t>
+  </si>
+  <si>
+    <t>TundraBiome - Education</t>
+  </si>
+  <si>
+    <t>Biome:Tundra- NASA Science</t>
+  </si>
+  <si>
+    <t>TundraBiome - Characteristics, Flora, Fauna</t>
+  </si>
+  <si>
+    <t>Tundra- Arctic, Permafrost, Climate | Britannica</t>
+  </si>
+  <si>
+    <t>What Is TheTundra? - WorldAtlas</t>
+  </si>
+  <si>
+    <t>Tundras Explained - National Geographic Society</t>
   </si>
   <si>
     <t>Senior Care</t>
@@ -256,217 +532,508 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2167a3a847354e566b137ea4bb963d82d3fcd167b19c86048a14552ca5372249JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly9vbGRuYXZ5LmdhcC5jb20vP21zb2NraWQ9MzhiYjhlOWFhMTk3NmVjZTNjYWI5OTdiYTA4ODZmNzI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0579c1e7060e6aa534d5ed910fd9413eb362f0cbb7ca413c9574900652b391bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9PbGRfKGZpbG0p&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ac81849a0b8d9248ed5d4711b8430fb385c738fc648600ecabf813aaeb8ebdcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTA5NTQ2NTIv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5cdee5b504926cc5e1f4bf81114765ea7dcc7c1e0defa446dcd2bde579d42ce3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L29sZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91226115219946c2550f2c14e8e8272115b52a7fcce748d2f946b52cec6fcf90JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9QTRVMnBNUlY5X2s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd3c334e771da4253e8d7ac918c8828e62aa97440f1b9070756122df97058dd1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly93d3cucm90dGVudG9tYXRvZXMuY29tL20vb2xk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffceb824d3df922428669ba16ba2440b51122f16c7c8ae389212088c7a15e1e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9ODR4QUQ0ci05a0U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1725a1ecb723082519abb3665c06bc8f71ff2571622d815964faacd2ca6039bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL29sZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2dc5bca6ce3b6e27d5a9f12319faaf8dd8349c02c373356859dab09ad0edc835JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly93d3cubmV0ZmxpeC5jb20vdGl0bGUvODE0MTAzODY&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d90e39609765e55a8734d5ba8c0d67aab42a94a270ca96462a699d92a5525a15JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38bb8e9a-a197-6ece-3cab-997ba0886f72&amp;u=a1aHR0cHM6Ly93d3cudW5pdmVyc2FscGljdHVyZXNhdGhvbWUuY29tL21vdmllcy9vbGQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f11b6197d2d65b9e3d83d05f64d7caf903e8d0a3bef57f1f50fbeeb8771f213JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d4049ce11d622bd5e1ba10929d884cb59b89a4c92536c5134cbaa88845935ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93ZWIub3NjLnN0YXRlLm55LnVzL3JldGlyZS9yZXRpcmVtZW50X29ubGluZS9jdXN0b21lcnMucGhwP3JlZGlyZWN0PWxlZ2FjeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=90c1756fa856b4997a3150fa89b586f442f1bf741a4af4e8f61bd585ad23dceeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cub3NjLm55Lmdvdi9yZXRpcmVtZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=051e221000bf80278132cb1eac0b54a72727764f402d2350308485ea8970564fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC8_bXNvY2tpZD0yMTk4MzYyZjJjY2U2ZjA4MjgwZTIxY2UyZDRkNmVhMw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ff77cdfea890be9ae75821221546db52406d2c5f4d8bececdd33d9364c599a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUmV0aXJlbWVudA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2dde7c8b65df4a21e7bd45c9365d65a2cfd6e29b7deba8eefb7dff2ca23ee8deJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cubmVyZHdhbGxldC5jb20vaW52ZXN0aW5nL2NhbGN1bGF0b3JzL3JldGlyZW1lbnQtY2FsY3VsYXRvcj9tc29ja2lkPTIxOTgzNjJmMmNjZTZmMDgyODBlMjFjZTJkNGQ2ZWEz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45b8c2c6edd946c46969f1b48aacf1c4f43d51c493d03f527596f357ee1094bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC9zdGVwcy10by10YWtlLWJlZm9yZS15b3UtcmV0aXJlLz9tc29ja2lkPTIxOTgzNjJmMmNjZTZmMDgyODBlMjFjZTJkNGQ2ZWEz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=431200c7ecdb588072436ecacd334c8821733b81742eb578a0e4c6b10a47f9d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cudXNhLmdvdi9yZXRpcmVtZW50LXBsYW5uaW5nLXRvb2xz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a72f1bf9d9632216137fe748eb4824af2f729f332367a5546bd4407570617877JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cuY2FsY3VsYXRvci5uZXQvcmV0aXJlbWVudC1jYWxjdWxhdG9yLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb8a46fc38b7387a943883d4f712e41efb3080ea83d2e973130a0f800fbd346bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2198362f-2cce-6f08-280e-21ce2d4d6ea3&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50L3BsYW4tZm9yLXJldGlyZW1lbnQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e4e735e58a9152e9b93ec19c7de2cb7371b72f5c2bb08c8fd184c13dc70441c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly93d3cuYWZ0ZXI1NS5jb20vc2VhcmNoL2RjL3dhc2hpbmd0b24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=39b9de3ec56b84797d83f5353353ebb9a90577660fe27e9b19e68245d514ce50JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly93d3cuYWZ0ZXI1NS5jb20vc2VhcmNoL2Rj&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8891b3d6978f1aebd1c1005cd7179122a161b8cd4ee52719f62d1e7617018e66JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly9kYWNsLmRjLmdvdi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96026f27b119b15c5e88873ed01651d2fe04f735f9a012f20bf65c0d374a0cc5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly9kYWNsLmRjLmdvdi9zZXJ2aWNlL3Nlbmlvci1jZW50ZXJz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a614110e486f34d7c943bb0fb7d263ca24ff87f85baf426939a86e7f522f8579JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly9kY3ZpbGxhZ2VzLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86aa7f2d72c0f24a41c6a8749f6184c7e98b77658eb77a8e285098be19899ab3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly93d3cud21hdGEuY29tL3BheS9mYXJlLXByb2dyYW1zL3Nlbmlvci1zbWFydC10cmlwLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11ef3ac0148c597ebb13816bbe37321816329659c2095c3e776c19bcdabbfb16JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly93d3cudmlkYXNlbmlvcmNlbnRlci5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8bcc56e722a38246d0d82619db35cc25a38557e0c20341d34dccba04269d86c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly93d3cuYXBhcnRtZW50aG9tZWxpdmluZy5jb20vd2FzaGluZ3Rvbi1kYy9hcGFydG1lbnRzLWZvci1yZW50L3Nlbmlvcj9tc29ja2lkPTM5NzBjNjdjYjlmNzY3NGYxZjQwZDE5ZGI4ODk2NjUw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=607169a3622bca8c19fa94e1c9732adcbbfe8bbe01ec1d3ae943d62f032367d0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly9kcHIuZGMuZ292L3BhZ2Uvc2VuaW9ycw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9bf21fd30d4227b0a3e5b900f39effac07fe8624618235d656c1c2f66dae585JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3970c67c-b9f7-674f-1f40-d19db8896650&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2VuaW9y&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1859246502cadc78243b4cc953116f0f7a7074d1217d0c0f9c2a27be0805ab7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b6fd4d02beb3d2747987cd65546cd8de44dccd5fc997c43ebca723c1384caafJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhcmVhZHZhbnRhZ2UuY29tL2NvbW1vbi1xdWVzdGlvbnMvd2hhdC1hZ2UtaXMtY29uc2lkZXJlZC1lbGRlcmx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dda9064a44da202afa4fc99434845341bf8cce4219e1e40a59da104f79dd919cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT2xkX2FnZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=238de197fed6d5b64e05eb074a862346e02a2ecaf9066edb11d25a0401420203JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3RoZSUyMGVsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2fe4f8f47ebf6b11b67ae14da0e0993248487b7a380d3f8ab1d6693f132c7562JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0364fd0f9df17bff6a594651462f6f102cab5a070656dbe5ad27088bd54b7d88JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly93d3cuZWxkZXJseS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40a90cf77c9450023ef693ac71c68064d757dbc3eb2563c8f9276a6ea9bd073dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly9hZ2luZy5ueS5nb3YvZXhwYW5kZWQtaG9tZS1zZXJ2aWNlcy1lbGRlcmx5LWVpc2Vw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00e3670878a89bebca72f218d98dee38439477cda6bd1f3038291aad901e8051JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly93d3cudGhlZWxkZXJseXdlbGxuZXNzLmNvbS9ibG9ncy93aGF0LWlzLWVsZGVybHkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=680f6d0271f86daf074f9d0d90e87ba1ca27699ed977f2c74558d57ef1a2bbe5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2VsZGVybHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=998a35d2e4c0693548a2487dd1caa1ab37e482b033e63e443b89d20a4eff450aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f6cf28f-b1f7-65bd-2256-e56eb01e648d&amp;u=a1aHR0cHM6Ly93d3cuc2VuaW9yc3Ryb25nLm9yZy9hdC13aGF0LWFnZS1hcmUteW91LWNvbnNpZGVyZWQtZWxkZXJseS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=92268235fd8f3327f9625e13e82f2ae5427fcb5fbc51117955b34102101706cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27c1180a080b3ea22d3926b986fd9d85c44130f5d92ef086c929355056d82377JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvZnJhaWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8786ffe0cb3f4c0ee90bb61fa8127c4e3259ecb81c7b80afa04d6a34255475eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0d86c08649edec224ac4e7b80d9fd27c0da8c423e8e4e219a13de661481cdf6cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5257731a33a48128f9c84e2156744bd72eee7f4e0884e09e98b3fd5252b9076JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f7294a5928d168831cd8b076e03207bdf247ef1949178aad0faf96015ad96210JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a596c50cc08442c8caa38565f4a75da3c5022bac31914c855132a8fb3e57a7eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly9lbi5tLndpa3Rpb25hcnkub3JnL3dpa2kvZnJhaWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ec574743125b088444da9b6f41f782f6ecb14b62548ea1744ccb08fdae76e749JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL2RpY3Rpb25hcnkvZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04202b9820b6c06ea0dad8e170a6ccfaeb4ebc2ecb488808b32fba941750052aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9kaXNlYXNlcy9mcmFpbHR5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=864d83121470159efb0a666053bfddf8c3a6e3259fb5a60bcbf3c90832174359JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=113694a3-0e23-6c61-168e-83420f426df7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba074f3cf59410bf7b8c07c16e741d282a806c4b516b02481be291aaf5d3b6f6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0dc9c939e1047452a872a8a15029c990b82d503fc1b3f938d51e42cd7ba806bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4368c4a408e1357dfc3a6129f3f71ac7c2e3ba2037c6ec26f1e8e4e74c2c684bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e64d9b28838d1e6e7127816a25ee77c57b56d7d056965d6654a38ee63491ced4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNzA0NDAyMA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=750ad9c24b928bb0c0a73aac55986c61719d6ffd5a34a7e291aaa296b017787cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly90cnVzdGFnZWQub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9f2104b9a214ed3142138f84c119964ddf1818284e1ca6729f7f8c31c7e02569JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cac5ac8b677d50da7bff48de79d68f9bfe049d89f3bdfef3eed01aae6e99d690JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4446c4a8e5e2f4a04d94938cbb68a0815d6ab7b266dc4fff4e8720dacc9b185fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly9jb3JyZWN0d29yZGluZy5jb20vYWdlZC1vci1hZ2Uv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=457af204292340be59d8a68351e81ab85b74f333ba857a50211a2e6cc4c83ab3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly9hZ2VkbnljLmNvbS9tZW51&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b8f4d7b8d248713b135a82f7187b278dc365e3375e7852b6578ddf8b558aff5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e68ed76-12ab-6f6d-3a3c-fa97135e6e84&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2FnZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e6daa5e73382d743c48564504029e9bf72f59fb3453e9bf9b7ba8e74f12807fcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZWFzeS1kaW5uZXItaWRlYXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3eb44853c0c360f333e99bbb66f8b287695fee59a5f10cbe790d35d0681891a9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cuYWxscmVjaXBlcy5jb20vMTAwLWVhc3ktbWVhbHMtMTE2OTUyMjc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=990ee36492c0b614c18b50dbb7ee8395d8638212e7ba4b6fa4cb00c0eb7bdfc6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzY4OTA2OTk3L2Jlc3QtZWFzeS1kaW5uZXItcmVjaXBlcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f61ae393922ec88ca88cb2fd82e8c7ba0cb2b8c39fa89ac7ea91ca0abe318dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cudGFzdGVvZmhvbWUuY29tL2NvbGxlY3Rpb24vZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f055129b0572bfc31d57289086bfbcf45f243f7cd17b0c855d138e52457785e5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly90aGVyZWFsZm9vZGRpZXRpdGlhbnMuY29tL2Vhc3ktZGlubmVyLWlkZWFzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=abacce5398bb28931c11fcc51b4caec49506b470f93adca7219e61a558d5ad00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zLzMwLW1pbnV0ZS1kaW5uZXItcmVjaXBlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=acbb470e6ae379e08dcf58a820d80b8b7ac7be1e4e2e6868e0178677699ff270JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cudGhlcGlvbmVlcndvbWFuLmNvbS9mb29kLWNvb2tpbmcvbWVhbHMtbWVudXMvZzMyMjY0Mjg0L2Vhc3ktZGlubmVyLXJlY2lwZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c68aeca96e4c2552818a3e90de53b5ad2fb2e56c47b5d5708117879ae8a3bdfdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cuaGVsbG9mcmVzaC5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3fb176aaa9c7378d23b05099b5612079be3c29dbff7bdc72bc277d5ead74f58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cuYmJjZ29vZGZvb2QuY29tL3JlY2lwZXMvY29sbGVjdGlvbi9lYXN5LWRpbm5lci1yZWNpcGVz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3014ef8555bb28bfdabcaeb7a139ad6f00b1524a661df5d8a1b68083a9e7dab8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1413a021-551d-6e43-342a-b7c0541e6f22&amp;u=a1aHR0cHM6Ly93d3cuZm9vZG5ldHdvcmsuY29tL3JlY2lwZXMvcGhvdG9zL2Vhc3ktZGlubmVyLXJlY2lwZXM&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=095e0d2b5332a4f57a2678746b8768703a44fdd946666bdc53c6bb56110ba6feJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a9a628b-c6a3-695f-145e-756ac76668fc&amp;u=a1aHR0cHM6Ly9vbGRuYXZ5LmdhcC5jb20vP21zb2NraWQ9MmE5YTYyOGJjNmEzNjk1ZjE0NWU3NTZhYzc2NjY4ZmM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9bc691245cc2ac8719d7a807345367ec698e6a35442fd4e76a23fe71ea212d76JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a9a628b-c6a3-695f-145e-756ac76668fc&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9PbGRfKGZpbG0p&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e60906270172a5802ee470720b9253e6ebc3fe2a4471845f2cffe3ddb6bb9ce4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a9a628b-c6a3-695f-145e-756ac76668fc&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTA5NTQ2NTIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b9821f90d01a26fd67dac6018a62e78d6d1b0053e4e67b7aa26f679cad30b0c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a9a628b-c6a3-695f-145e-756ac76668fc&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L29sZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86097159a49d3cbe6c1a217174000edf2a0ea33a23222ab609b0c16b7651bbd4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a9a628b-c6a3-695f-145e-756ac76668fc&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9QTRVMnBNUlY5X2s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4545d36b1e9c66f68163ddc952f959875b5f9f6225036c62b4a14de6012a588JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a9a628b-c6a3-695f-145e-756ac76668fc&amp;u=a1aHR0cHM6Ly93d3cucm90dGVudG9tYXRvZXMuY29tL20vb2xk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f30becdf3b813ff07cbc4ad78642a8d980f5815510914d42f6bee38cd558ec13JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a9a628b-c6a3-695f-145e-756ac76668fc&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9ODR4QUQ0ci05a0U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=205ac37fba2afb35b5dde151cc64c60dedb743cfe67092277d738fae1fdb1ceaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a9a628b-c6a3-695f-145e-756ac76668fc&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL29sZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4362e3e9b36cd3db7ad4f707c4bad77e8e9ffbe8dd24b006fc2f885b9761fa6dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a9a628b-c6a3-695f-145e-756ac76668fc&amp;u=a1aHR0cHM6Ly93d3cubmV0ZmxpeC5jb20vdGl0bGUvODE0MTAzODY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=006dd50af083cc9862d82ef1b76965e3ebdc9904891abcb70f44f36a41742d3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a9a628b-c6a3-695f-145e-756ac76668fc&amp;u=a1aHR0cHM6Ly93d3cudW5pdmVyc2FscGljdHVyZXNhdGhvbWUuY29tL21vdmllcy9vbGQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5592c46f59b78968df2a07ba1f2c75b31e241992872c9c9263aefc8672454b7cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a9e3f57-c9ba-60ad-1d15-28b6c82061a9&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dcff4195388dc923188eae184af0944edc8617882aa2c11d8291c7e630e28a99JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a9e3f57-c9ba-60ad-1d15-28b6c82061a9&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC8_bXNvY2tpZD0wYTllM2Y1N2M5YmE2MGFkMWQxNTI4YjZjODIwNjFhOQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87863cef5fae403121275c3243f15d3af3c02d41168897198380193d0f826616JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a9e3f57-c9ba-60ad-1d15-28b6c82061a9&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9SZXRpcmVtZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89578474d1916448971311b16136db3fd64110ddec00e847cb08a4068634e1cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a9e3f57-c9ba-60ad-1d15-28b6c82061a9&amp;u=a1aHR0cHM6Ly93d3cubmVyZHdhbGxldC5jb20vaW52ZXN0aW5nL2NhbGN1bGF0b3JzL3JldGlyZW1lbnQtY2FsY3VsYXRvcj9tc29ja2lkPTBhOWUzZjU3YzliYTYwYWQxZDE1MjhiNmM4MjA2MWE5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20b2b52b90b56eb9a1e4a860e8dae2843056f6ad5257e6ae3f4180dc22e1cc23JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a9e3f57-c9ba-60ad-1d15-28b6c82061a9&amp;u=a1aHR0cHM6Ly93d3cuY2FscGVycy5jYS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=69185dac0287070ee232619c96ec25a4399bad2d7bc1fc4ea9252b119a5939d2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a9e3f57-c9ba-60ad-1d15-28b6c82061a9&amp;u=a1aHR0cHM6Ly93d3cuYWFycC5vcmcvbW9uZXkvcmV0aXJlbWVudC9zdGVwcy10by10YWtlLWJlZm9yZS15b3UtcmV0aXJlLz9tc29ja2lkPTBhOWUzZjU3YzliYTYwYWQxZDE1MjhiNmM4MjA2MWE5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41db865b62c1ff81bf49f35731ed4ab322756fd8e3247c356fa0e427b1d989f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a9e3f57-c9ba-60ad-1d15-28b6c82061a9&amp;u=a1aHR0cHM6Ly93d3cuc3NhLmdvdi9yZXRpcmVtZW50L3BsYW4tZm9yLXJldGlyZW1lbnQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=864e4c9c48d2eaa3cd547e39171848f474436034f8391fcfb7e287ad63c5debfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a9e3f57-c9ba-60ad-1d15-28b6c82061a9&amp;u=a1aHR0cHM6Ly93d3cuY2FsY3VsYXRvci5uZXQvcmV0aXJlbWVudC1jYWxjdWxhdG9yLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=36a24d7e8a7db60508b5bfd6a1530bd8542f3d3009f209f44bab679dd557e99cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a9e3f57-c9ba-60ad-1d15-28b6c82061a9&amp;u=a1aHR0cHM6Ly93d3cudXNhLmdvdi9yZXRpcmVtZW50LXBsYW5uaW5nLXRvb2xz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f628a53cb348af2b4daf2304e53d12030f7f930cfb1ed4050f3ce1b69358511JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a9e3f57-c9ba-60ad-1d15-28b6c82061a9&amp;u=a1aHR0cHM6Ly93d3cuZmlkZWxpdHkuY29tL3JldGlyZW1lbnQvcmV0aXJlbWVudC1wbGFubmluZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b59fe55a4acb579ac5c09556e0cb90cbb48710762a21e8df3c5d55bc1135e261JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186dd91e-5fb6-6cf6-2d25-ceff5e6d6db3&amp;u=a1aHR0cHM6Ly9zZW5pb3ItcmVzb3VyY2VzLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71935ed96831ddea3a048b37aaaf0c1b8b794809fb91f340628f0a1f979f4734JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186dd91e-5fb6-6cf6-2d25-ceff5e6d6db3&amp;u=a1aHR0cHM6Ly9vYWtoYXJib3IuZ292LzM2MS9TZW5pb3ItU2VydmljZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=23cc29c3ccfeb975910fe9e5fec227e6e5fe73bc832580f43e82480ee838d735JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186dd91e-5fb6-6cf6-2d25-ceff5e6d6db3&amp;u=a1aHR0cHM6Ly9zZW5pb3JjZW50ZXIudXMvc2Mvb2FrX2hhcmJvcl9zZW5pb3JfY2VudGVyX29ha19oYXJib3Jfd2E&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b03f5e60539c7d6b11fadb7e25475a2da3586001a333f4e1940277ebf2f82b42JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186dd91e-5fb6-6cf6-2d25-ceff5e6d6db3&amp;u=a1aHR0cHM6Ly93d3cuYWZ0ZXI1NS5jb20vc2VhcmNoL3dhL29hay1oYXJib3I&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80c8cd4fe6e83fee4d93b2891f91bcf89327845589495c5e240734cf6182d73cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186dd91e-5fb6-6cf6-2d25-ceff5e6d6db3&amp;u=a1aHR0cHM6Ly93d3cub2hzY2ZvdW5kYXRpb24ub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e26e66d9970a0639cd03f51c1584980303ad8192589649a3ebbb682d3687af39JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186dd91e-5fb6-6cf6-2d25-ceff5e6d6db3&amp;u=a1aHR0cHM6Ly93d3cuc2VuaW9yZ3VpZGFuY2Uub3JnL3Nlbmlvci1ob3VzaW5nL3dhc2hpbmd0b24vb2FrLWhhcmJvci5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6a5a7b500f78e3c8583ccee758b6d55862332541b46d696771ff8cd080ff2a8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186dd91e-5fb6-6cf6-2d25-ceff5e6d6db3&amp;u=a1aHR0cHM6Ly93d3cuZmFtaWx5cmVzb3VyY2Vob21lY2FyZS5jb20vbG9jYXRpb25zL29hay1oYXJib3Iv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=318a35f67f2bfb4f0fc5d3f031cbfd2be96c9157fb0107344afb9d95f1e0d876JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186dd91e-5fb6-6cf6-2d25-ceff5e6d6db3&amp;u=a1aHR0cHM6Ly9vYWtoYXJib3IuZ292L0ZhY2lsaXRpZXMvRmFjaWxpdHkvRGV0YWlscy9UaGUtQ2VudGVyLTEy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66800d4aa6a76a1acf06e9f37a0c02ab1a9622e34114de2c118b1c55e79a8944JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186dd91e-5fb6-6cf6-2d25-ceff5e6d6db3&amp;u=a1aHR0cHM6Ly93d3cucmVnZW5jeS1wYWNpZmljLmNvbS9zZW5pb3ItbGl2aW5nL3dhL29hay1oYXJib3IvcmVnZW5jeS1vbi13aGlkYmV5Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1416e1af2e035e2635385682896e0049e4cd641cbead7d5f97d109dac3db31c0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186dd91e-5fb6-6cf6-2d25-ceff5e6d6db3&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Nlbmlvcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a814694cbb7ae48e5a3f7028c571df23065fbeab77f6cd2a8c46f695fd47ea02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b372b3-adff-6bc3-0fb2-6552acc26a3a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VsZGVybHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=783ae94bbba28646a898321159ac2900d26a37daf8a62c803b8c3c8a1007a016JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b372b3-adff-6bc3-0fb2-6552acc26a3a&amp;u=a1aHR0cHM6Ly93d3cuZWxkZXJseS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8c072138a28d0ee9bdfc51dc95c5abfd8b3aa854ce8a57e20f75b2f28065558bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b372b3-adff-6bc3-0fb2-6552acc26a3a&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhcmVhZHZhbnRhZ2UuY29tL2NvbW1vbi1xdWVzdGlvbnMvd2hhdC1hZ2UtaXMtY29uc2lkZXJlZC1lbGRlcmx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=073899a7f1b99fec128e87e61d515c18b35e41b72f979a293fcb8c622e1b7b9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b372b3-adff-6bc3-0fb2-6552acc26a3a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT2xkX2FnZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47dfc9a2968104eb81eef800fa405e34394ae1d3babf1cd79b435b8640d3e774JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b372b3-adff-6bc3-0fb2-6552acc26a3a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3RoZSUyMGVsZGVybHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dfff601b60ee73a560a5ed96c6047760971312b49a62eccb816c02003e7c0992JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b372b3-adff-6bc3-0fb2-6552acc26a3a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VsZGVybHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7c40da0e64be4c5622198e7e4abb5132b0c4dc5abba423f519594d3fff7b13dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b372b3-adff-6bc3-0fb2-6552acc26a3a&amp;u=a1aHR0cHM6Ly93d3cuc2VuaW9yc3Ryb25nLm9yZy9hdC13aGF0LWFnZS1hcmUteW91LWNvbnNpZGVyZWQtZWxkZXJseS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=90fb75c1701465e592cbc8604013443a1f10b6735fa38bb705b1298c3a3455feJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b372b3-adff-6bc3-0fb2-6552acc26a3a&amp;u=a1aHR0cHM6Ly93d3cudGhlZWxkZXJseXdlbGxuZXNzLmNvbS9ibG9ncy93aGF0LWlzLWVsZGVybHkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ec396d7b34068518f01af29421f16424e806b1b6d2d371d7f0aa16d434d6b7fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b372b3-adff-6bc3-0fb2-6552acc26a3a&amp;u=a1aHR0cHM6Ly9pbmZvcm1lZHNlbmlvcmxpdmluZy5jb20vd2hhdC1hZ2UtaXMtbGVnYWxseS1jb25zaWRlcmVkLWVsZGVybHkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e8588f4f36bc2f96c3cff2e99876388d87c944a342a7516a61950f1a4dc88f0eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b372b3-adff-6bc3-0fb2-6552acc26a3a&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2VsZGVybHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb9c8f7f67ba8864ca41abf94d68d4dab951dd5d2bf4101aaf3570c3b51e9de9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2350df54-d5b4-6f10-0ab1-c8b5d4146e42&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4f41ff86c03ea69a1ba4d9cb07f3fc2a7941d1c2b34050c3d48223a772f742b9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2350df54-d5b4-6f10-0ab1-c8b5d4146e42&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cce606c8fd4997c8f9f1bc535f36413c359684fe266ebbae265e00e979361f28JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2350df54-d5b4-6f10-0ab1-c8b5d4146e42&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvZnJhaWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16afb814033852b1b28d1ca833cb52b0ca4c1783fdd13b388a7429d4e2ef2596JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2350df54-d5b4-6f10-0ab1-c8b5d4146e42&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2349383942b21137d1dea4669d9ece3f4667b6f4d6bdda39fbdac15cd9cf838JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2350df54-d5b4-6f10-0ab1-c8b5d4146e42&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9mcmFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e56ec0991fb9dbf2e1d1aa51e84c31635c90170ff22b274cd404946e5ec061cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2350df54-d5b4-6f10-0ab1-c8b5d4146e42&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5db3823de29773471bba03b92693c79620e1ae2502840da0ddcf65c0b08e3e5dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2350df54-d5b4-6f10-0ab1-c8b5d4146e42&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b35bfb4afb85e0ff8c67ff58924500ef6fd833b647f2fc3e95a534a395c77dccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2350df54-d5b4-6f10-0ab1-c8b5d4146e42&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2ZyYWls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f180d02e4591733d2fd282132f3a99fbbda309aa6dcd9b3639e4f7661552319JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2350df54-d5b4-6f10-0ab1-c8b5d4146e42&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL2RpY3Rpb25hcnkvZW5nbGlzaC9mcmFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=39f5098329087bc88b50d9d6694c2d550570ebbe3532e2708e5c5eec13177404JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2350df54-d5b4-6f10-0ab1-c8b5d4146e42&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9kaXNlYXNlcy9mcmFpbHR5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11747874f864db8107e4047b93a88ea9fd95a5f376f09464c64b8d2e7c5baf54JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2aa86db9-4190-6a3f-0d92-7a5840096b59&amp;u=a1aHR0cHM6Ly93d3cud2VzdGpldC5jb20vZW4tdXMvYmFnZ2FnZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=39d7db59a19b9dacda62530fc6f406901975713c02b10211e3ec660191f9c89eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2aa86db9-4190-6a3f-0d92-7a5840096b59&amp;u=a1aHR0cHM6Ly93d3cud2VzdGpldC5jb20vZW4tY2EvaGVscA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b349e83fe04a8bbe87d3200fe6149ef697862c370081f0231d8fca837a2b40e9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2aa86db9-4190-6a3f-0d92-7a5840096b59&amp;u=a1aHR0cHM6Ly93d3cuYWlydHJhdmVscXVlc3Rpb25zLmNvbS9haXJsaW5lLXBvbGljaWVzL3dlc3RqZXQtcG9saWNpZXMtZ3VpZGU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=746fc8ca9d27a646ce6538e8052be39128c05decb39651fb9914c99d6903ec37JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2aa86db9-4190-6a3f-0d92-7a5840096b59&amp;u=a1aHR0cHM6Ly93d3cud2VzdGpldHZhY2F0aW9ucy5jb20vZW4vYWlybGluZS1pbmZvcm1hdGlvbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=997490fe7c60d3aa8ca92bae04ac698b9ba0f46a70cdb357f78b20844c90f8c7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2aa86db9-4190-6a3f-0d92-7a5840096b59&amp;u=a1aHR0cHM6Ly91cGdyYWRlZHBvaW50cy5jb20vdHJhdmVsL2FpcmxpbmVzL3dlc3RqZXQtYmFnZ2FnZS1mZWVzLWFuZC1wb2xpY3kv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96418bbe5a58423b4e170b25b5741d1a888558074a597ca8780ffd8e8bce7989JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2aa86db9-4190-6a3f-0d92-7a5840096b59&amp;u=a1aHR0cHM6Ly9hdXRvcy53ZXN0amV0LmNvbS9lbi11cy9tYW5hZ2UtYm9va2luZz9nb3RvPWZhcXMvdG9waWNzL0NIQU5HRV9PUl9DQU5DRUxfWU9VUl9CT09LSU5HL3F1ZXN0aW9ucy9IT1dfRE9fSV9DQU5DRUxfTVlfQk9PS0lORw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=65643cef0fdb7b071219f173c8cc157ef9d77117375e50cb3bb9583e7f659279JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2aa86db9-4190-6a3f-0d92-7a5840096b59&amp;u=a1aHR0cHM6Ly93d3cud2VzdGpldC5jb20vZW4tdXMvbWFuYWdlL2NoZWNrLWlu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=93db50849e5712a96c6b538ddbb8e9382548257affd413cf50d99a279972d12eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186bd619-b2ac-6b46-28df-c1f8b3c06a8d&amp;u=a1aHR0cHM6Ly93d3cucG9ybmh1Yi5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=83f9132f65e90918c4f61be5592852c04007882930b74d68a8008be114fa6c07JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186bd619-b2ac-6b46-28df-c1f8b3c06a8d&amp;u=a1aHR0cHM6Ly93d3cucG9ybmh1Yi5jb20vdmlkZW8vc2VhcmNoP3NlYXJjaD1wb3JuaHVi&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3db3cb8372aa9343c2210b518cc4ba42cfc96a7de7ac752d2e4537ca16bb03d2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186bd619-b2ac-6b46-28df-c1f8b3c06a8d&amp;u=a1aHR0cHM6Ly9tLXBvcm5odWIuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c99626a955bfc672658c75ac2e5f776a617a3a5979a3677186cd0d83b340d3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186bd619-b2ac-6b46-28df-c1f8b3c06a8d&amp;u=a1aHR0cHM6Ly9lbi1wb3JuaHViLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5743db028306159cc24093a8bb97077baa9e537d16d5d0c51227b38920cf3d89JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186bd619-b2ac-6b46-28df-c1f8b3c06a8d&amp;u=a1aHR0cHM6Ly9lbi1wb3JuaHViLmNvbS9zaXRlcy9wb3JuaHViLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8bc735c008c64a8dc250f07b3515f7140da4335e772300cbcfbb152be085399fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186bd619-b2ac-6b46-28df-c1f8b3c06a8d&amp;u=a1aHR0cHM6Ly93d3cueHZpZGVvcy5jb20vdGFncy9wb3JuaHVi&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd2f4198dcce255ffea3aa70fe992b870f21aaef6d7337ed389c1fc6016d8a71JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186bd619-b2ac-6b46-28df-c1f8b3c06a8d&amp;u=a1aHR0cHM6Ly93d3cucG9ybmh1Yi5jb20vY2F0ZWdvcmllcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b9eacd7062f3f37a61f4d1d3c807adfa002f4d6b05644fc5f7b0d5851882a16JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186bd619-b2ac-6b46-28df-c1f8b3c06a8d&amp;u=a1aHR0cHM6Ly93d3cucG9ybmh1Yi5jb20vdmlkZW8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e5394685d31fd494bfe38f46321ee1dfce3c0782985649f0182fa35ee62c3bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186bd619-b2ac-6b46-28df-c1f8b3c06a8d&amp;u=a1aHR0cHM6Ly93d3cucG9ybmh1Yi5jb20vcmVjb21tZW5kZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b58e0adac6230ff4e20d32ef640e75adcf3df2211d2d45bfb3ce90a7b45cab3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=186bd619-b2ac-6b46-28df-c1f8b3c06a8d&amp;u=a1aHR0cHM6Ly9lcy5wb3JuaHViLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72afa5a9896198a6b05ffab2d7cec301fa0dc56ecd29a40a96278d90c7b635e5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=164b6245-2b70-6c06-1221-75a42a696d90&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=354240e9f5dc001521e35a10ec79ae6d3595990b6e2d1e64baa6bf14648337beJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=164b6245-2b70-6c06-1221-75a42a696d90&amp;u=a1aHR0cHM6Ly9haS5nb29nbGUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7019f1e518ea4eac8a71b57559f4f4a6f9c8608b94ed7815af7dda7d8b180644JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=164b6245-2b70-6c06-1221-75a42a696d90&amp;u=a1aHR0cHM6Ly9hYm91dC5nb29nbGUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6fcdf931c84b70c74d413a80ae31b8b8c2cd251493f040a4a58a08edcf6fa1bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=164b6245-2b70-6c06-1221-75a42a696d90&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL0dvb2dsZS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=705f6e928738e2a4ab10ccfc7b7aa771f2ec907a8b11c16ec85806d32369381aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=164b6245-2b70-6c06-1221-75a42a696d90&amp;u=a1aHR0cHM6Ly9hYm91dC5nb29nbGUvY29tcGFueS1pbmZvLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=585301cb1ee853d743f2066595b007c5ad552ad15ce1d5047dd2807a9c17b603JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=164b6245-2b70-6c06-1221-75a42a696d90&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=004d41592edfcc8c0b17895cfd29b4e43f9fc0b0a725fea25a40e1ad2745fde1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b3b2f6b-760d-687e-290e-388a77d5690c&amp;u=a1aHR0cHM6Ly93d3cuYm9va2luZy5jb20vbW90ZWxzL2NpdHkvdXMvbGFzLXZlZ2FzLmh0bWw_bXNvY2tpZD0yYjNiMmY2Yjc2MGQ2ODdlMjkwZTM4OGE3N2Q1NjkwYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=247b596cfca8b376a0e175620478b70dc9e828543f6663ace7a96ea6bcdf4915JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b3b2f6b-760d-687e-290e-388a77d5690c&amp;u=a1aHR0cHM6Ly93d3cua2F5YWsuY29tL0xhcy1WZWdhcy1Ib3RlbHNfTW90ZWwuVG1vdGVsLjM1MTA3LmhvdGVsLmtzcD9tc29ja2lkPTJiM2IyZjZiNzYwZDY4N2UyOTBlMzg4YTc3ZDU2OTBj&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d459d6b84dbb3a57f16a5a613aa2768d4cb542eccf23771cad9d0acc8f09b4c1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b3b2f6b-760d-687e-290e-388a77d5690c&amp;u=a1aHR0cHM6Ly93d3cudHJpcGFkdmlzb3IuY29tL0hvdGVsc0xpc3QtTGFzX1ZlZ2FzLUNoZWFwLU1vdGVscy16ZnAyMTEwOS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc4d4c4951e16aa93356db25b5d7166ad23cecebda82da14a4a5a7a4f43460bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b3b2f6b-760d-687e-290e-388a77d5690c&amp;u=a1aHR0cHM6Ly93d3cuZXhwZWRpYS5jb20vTGFzLVZlZ2FzLU1vdGVscy5kMTc4Mjc2LWFhTW90ZWxzLlRyYXZlbC1HdWlkZS1BY2NvbW1vZGF0aW9uP21zb2NraWQ9MmIzYjJmNmI3NjBkNjg3ZTI5MGUzODhhNzdkNTY5MGM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a811de0ae607416110a0a6512e34f5c82e1751b4d30db30e0c44a1df3d390e4aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b3b2f6b-760d-687e-290e-388a77d5690c&amp;u=a1aHR0cHM6Ly93d3cudHJpcGFkdmlzb3IuY29tL0hvdGVscy1nNDU5NjMtemZkMi1MYXNfVmVnYXNfTmV2YWRhLUhvdGVscy5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9f263d3b1e28cb6ea0f0b56709ceae04b673b18948b1e777365c503743578219JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b3b2f6b-760d-687e-290e-388a77d5690c&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1Nb3RlbHMrQW5kK0lubnMmZmluZF9sb2M9TGFzK1ZlZ2FzJTJDK05WJm1zb2NraWQ9MmIzYjJmNmI3NjBkNjg3ZTI5MGUzODhhNzdkNTY5MGM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e01518cc25d4d6a3a53350a99570d0214435053e0fbcd250bf034745347f0ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b3b2f6b-760d-687e-290e-388a77d5690c&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1tb3RlbHMmZmluZF9sb2M9TGFzK1ZlZ2FzJTJDK05WJm1zb2NraWQ9MmIzYjJmNmI3NjBkNjg3ZTI5MGUzODhhNzdkNTY5MGM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5de7968eb3a7fa5956fc7b3a868a5ef2e8971b4e04e0ae2ef478d3a4fb99c416JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b3b2f6b-760d-687e-290e-388a77d5690c&amp;u=a1aHR0cHM6Ly93d3cuaG90ZWxzLmNvbS9kZTE1MDQwMzMtYXQ3L21vdGVscy1ob3RlbHMtbGFzLXZlZ2FzLW5ldmFkYS8_bXNvY2tpZD0yYjNiMmY2Yjc2MGQ2ODdlMjkwZTM4OGE3N2Q1NjkwYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb7681a0a445084cb32c46896e2be314d16cb441efe38c47ebce536a85236924JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b3b2f6b-760d-687e-290e-388a77d5690c&amp;u=a1aHR0cHM6Ly93d3cubW9tb25kby5jb20vaG90ZWxzL01vdGVscy1pbi1MYXMtVmVnYXMtMzUxMDcubW90ZWwua3Nw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9de971294570c553af39bb091e89e74c3f604cb97120f10911eddc685b9c5d6bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b3b2f6b-760d-687e-290e-388a77d5690c&amp;u=a1aHR0cHM6Ly93d3cuaG90ZWxzY29tYmluZWQuY29tL1BsYWNlL0xhcy1WZWdhcy1Nb3RlbC5tb3RlbC4zNTEwNy5rc3A&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=547c64137eaaba72a29dbc40c493f3a37a8f105027108a4b6df5de5c0616658cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235ada5a-da8d-6501-3963-cdbbdb2f646c&amp;u=a1aHR0cHM6Ly93d3cubmZsLmNvbS9zdGFuZGluZ3Mv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4396c17cdd207570dd90163bd0b71558c244fb89fbb5dcd662bdfd746e17bb4cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235ada5a-da8d-6501-3963-cdbbdb2f646c&amp;u=a1aHR0cHM6Ly93d3cubmZsLmNvbS9zY2hlZHVsZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b684e1b05074cd982f20516ffe39334aad414afeb24078d58a8ad56b9049cd27JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235ada5a-da8d-6501-3963-cdbbdb2f646c&amp;u=a1aHR0cHM6Ly9uZXh0Z2Vuc3RhdHMubmZsLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=419677e6086073b250d8436c0c51feee00e2a8826f74018f05eb4f3e5a7489bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235ada5a-da8d-6501-3963-cdbbdb2f646c&amp;u=a1aHR0cHM6Ly9tZWRpYS5uZmwuY29tL2NvbnRlbnQvZGFtL2NvbW11bmljYXRpb25zL09mZmljaWFsJTIwUGxheWluZyUyMFJ1bGVzLzIwMjUlMjBPZmZpY2lhbCUyMFBsYXlpbmclMjBSdWxlcy5wZGY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0b1ce0ef558b9c80f149746603d3cb04af08262655add95ace510d4013089625JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235ada5a-da8d-6501-3963-cdbbdb2f646c&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm5mbC5jb20vaGMvZW4tdXMvYXJ0aWNsZXMvMzU4Njk3NzM0ODc3NjQtTkZMLVJ1bGVib29r&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0410ed314638ffcdf587051486677ab29e692ddd87be19032d1e43eee92febcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235ada5a-da8d-6501-3963-cdbbdb2f646c&amp;u=a1aHR0cHM6Ly9jYW5hZGEucGlja2VtLm5mbC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=62e5aaf11410fc35ad73f53f1498816ca7f51a6a3e4f8ce097f7fd6cb1c21b0fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235ada5a-da8d-6501-3963-cdbbdb2f646c&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm5mbC5jb20vaGMvZW4tdXMvYXJ0aWNsZXMvMzk0MTQ0OTgzNDc3OTYtQ29udGFjdC1Vcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f781aad475b9d1328cc9570c5373ef3ddf8594464e31dff8c8d590cc88619530JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235ada5a-da8d-6501-3963-cdbbdb2f646c&amp;u=a1aHR0cHM6Ly9tZWRpYS5uZmwuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=528541b0a367d9fb907eda335a23946d5995becf05a7ec9b2660b5a9ddf59c06JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235ada5a-da8d-6501-3963-cdbbdb2f646c&amp;u=a1aHR0cHM6Ly9zdGF0aWMud3d3Lm5mbC5jb20vZ2FtZWNlbnRlci80NWMxNmYxNi0xMzEzLTExZWYtYWZkMS02NDYwMDlmMThiMmUucGRm&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd75a03b1437a0706ad58699c6a07faa9ba251cb905c99485137dc796bcf89f5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=235ada5a-da8d-6501-3963-cdbbdb2f646c&amp;u=a1aHR0cHM6Ly9zdGF0aWMud3d3Lm5mbC5jb20vaW1hZ2UvdXBsb2FkL2ZsX2F0dGFjaG1lbnQvbGVhZ3VlL3RxaXZka3p0OW11NndkZ3NoMWt1LnBkZg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=49d2e3e5f289b740f1fdb5514e193774e091875493976f9b86e87f8cccab3025JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3abad4f9-b419-6f25-27a4-c318b5f56e66&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tZ2IvY29udGFjdHVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe78d7081c7a891893cd8f88ef2b5c209ce1e69660272ffa1bf9d755611b48c1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3abad4f9-b419-6f25-27a4-c318b5f56e66&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvYWNjb3VudHMtYmlsbGluZy9tYW5hZ2UvaG93LXRvLXNpZ24taW4tdG8taG90bWFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc9816c48e83eaf31ca77d643e8e20bf47d715ce1448dd8b4fb6de86fbd63e80JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3abad4f9-b419-6f25-27a4-c318b5f56e66&amp;u=a1aHR0cHM6Ly90ZWNoY29tbXVuaXR5Lm1pY3Jvc29mdC5jb20vY2F0ZWdvcnkvbWljcm9zb2Z0LWNvcGlsb3QvYmxvZy9taWNyb3NvZnQtY29waWxvdC1ibG9n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df785daa4b8b054b7fc88890dfe07a903f9ccb98705f7d6e19809734420086b8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3abad4f9-b419-6f25-27a4-c318b5f56e66&amp;u=a1aHR0cHM6Ly90ZWNoY29tbXVuaXR5Lm1pY3Jvc29mdC5jb20vYmxvZy9leGNoYW5nZS9leGNoYW5nZS1vbmxpbmUtZXdzLXlvdXItdGltZS1pcy1hbG1vc3QtdXAvNDQ5MjM2MQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd805493ccdee18a4a0b5c90039d7ad817f25d4f0ba07ab4d6b6eb73d6f77122JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3abad4f9-b419-6f25-27a4-c318b5f56e66&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9kZXBsb3ltZW50L2luc3RhbGwtdXBncmFkZS9nZXR0aW5nLXJlYWR5LWZvci10aGUtd2luZG93cy0xMS11cGdyYWRl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=080eb0bb25f3d9413e8d7796ab01db9f3999d15f3c81fa11766138e9b24c1c6dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3abad4f9-b419-6f25-27a4-c318b5f56e66&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZnItZnIvd2luZG93cy9tZXR0cmUtJUMzJUEwLWpvdXItbGVzLXBpbG90ZXMtdmlhLWdlc3Rpb25uYWlyZS1kZS1wJUMzJUE5cmlwaCVDMyVBOXJpcXVlcy1kYW5zLXdpbmRvd3MtZWM2MmY0NmMtZmYxNC1jOTFkLWVlYWQtZDcxMjZkYzFmN2I2&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d24b07395af739cdcbb0ad66e6084b8c9300dd58b5ff92567da97c8fcbca4a04JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3abad4f9-b419-6f25-27a4-c318b5f56e66&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvd2luZG93cy9ha3R1YWxpc2llcmVuLXZvbi10cmVpYmVybi0lQzMlQkNiZXItZ2VyJUMzJUE0dGUtbWFuYWdlci1pbi13aW5kb3dzLWVjNjJmNDZjLWZmMTQtYzkxZC1lZWFkLWQ3MTI2ZGMxZjdiNg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=552d6ffa520a4bb159cc2faa1a6dc5d2822b1207c1fdee2d1f1ad03b30401f31JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3abad4f9-b419-6f25-27a4-c318b5f56e66&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvZWRnZS9nZXR0aW5nLXRoZS1sYXRlc3QtbWljcm9zb2Z0LWVkZ2UtdXBkYXRlLWp1c3QtZ290LWVhc2llcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a31aa486abdb2ecdd02d23611238c53e95530f36acd710f093168100e0e108aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3abad4f9-b419-6f25-27a4-c318b5f56e66&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvb3V0bG9vay90cmFpbmluZy9zaGFyZS15b3VyLWNhbGVuZGFyLWluLW91dGxvb2s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b53c446b1eaf1c67b2d8e980c16311502ce76475f212e32755a9a1f84c042b79JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3abad4f9-b419-6f25-27a4-c318b5f56e66&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvZm9ybXMvc2lnbi1pbi10by1taWNyb3NvZnQtZm9ybXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74e434cb25bc330f8f5d09a6f15e9cddbe40c8db1705c1de890ecd732327085fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37a6be61-6c42-6869-3dec-a9806d2e695c&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cz9tc29ja2lkPTM3YTZiZTYxNmM0MjY4NjkzZGVjYTk4MDZkMmU2OTVj&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6f3dbbeafb3ba103b1317969e6d377f65a15cb7dc3ee88b8eb6b39da9b53eae4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37a6be61-6c42-6869-3dec-a9806d2e695c&amp;u=a1aHR0cHM6Ly9hY2NvdW50Lm1pY3Jvc29mdC5jb20vYWNjb3VudA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1814f9e58b902a30b964291749ca26da61f2e346f801ccc487ed3d7d3fe6a1feJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37a6be61-6c42-6869-3dec-a9806d2e695c&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a13733471103feaaa5d6329bf0ef900475f1edf6cf91a08fc7d53306e0f8a3b3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37a6be61-6c42-6869-3dec-a9806d2e695c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWljcm9zb2Z0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d24d9b2679fd5e35c3c0994d0d75acf3cb06ca2d5c6ce7b8225d722559fdcfdeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37a6be61-6c42-6869-3dec-a9806d2e695c&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cy9taWNyb3NvZnQtMzY1P21zb2NraWQ9MzdhNmJlNjE2YzQyNjg2OTNkZWNhOTgwNmQyZTY5NWM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2bfbc9aba13657049b95093066c92cc88295c8cc86205e8d1c14e2c18b93a759JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37a6be61-6c42-6869-3dec-a9806d2e695c&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS9sb2dpbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2cac85e87516a8921b3fe76acd8cae24e4171309c882cd51e58791ab1d57f0c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37a6be61-6c42-6869-3dec-a9806d2e695c&amp;u=a1aHR0cHM6Ly9jYXJlZXJzLm1pY3Jvc29mdC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7544ae1ddab1f9244a75a2af7253f75363daa0347c199f250dac816a4459563JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37a6be61-6c42-6869-3dec-a9806d2e695c&amp;u=a1aHR0cHM6Ly9zaWdudXAubGl2ZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52225f47d99c5e9ac6998c0eb14e1df934d155568470310c9e4cf2d4086c0fe0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37a6be61-6c42-6869-3dec-a9806d2e695c&amp;u=a1aHR0cHM6Ly9hcHBzLm1pY3Jvc29mdC5jb20vaG9tZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3edecc98310be729b0950b0a177240c048e6c0e9685d3e233832178bdae9d817JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37a6be61-6c42-6869-3dec-a9806d2e695c&amp;u=a1aHR0cHM6Ly9tMzY1LmNsb3VkLm1pY3Jvc29mdC8_b3JpZ2luZG9tYWluPW1pY3Jvc29mdDM2NQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56f9442e738fa7af9a6f608253731f37648a5a5c987790f2755b25f996e3de22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19c44e29-941f-60a4-24e5-59c895f661e8&amp;u=a1aHR0cHM6Ly93d3cud2lzaGVzbXNnLmNvbS9iZXN0LXdpc2hlcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41252f1430e43492c6288ba8a8687f3d45d6d6050f5aded9dcaa4a8a30308548JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19c44e29-941f-60a4-24e5-59c895f661e8&amp;u=a1aHR0cHM6Ly9jb3p5d2lzaGVyLmNvbS9hbGwtdGhlLWJlc3QtbWVzc2FnZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f13bf8c2ec932a174ddbbb18c99339fb46a78f3e2012cb2862b81295116414c1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19c44e29-941f-60a4-24e5-59c895f661e8&amp;u=a1aHR0cHM6Ly93d3cuYmVzdG1lc3NhZ2Uub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de597e6efc78c618d6c208eda0eaefa86070e44c4b4e0ea6c7c09020ba0c0a52JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19c44e29-941f-60a4-24e5-59c895f661e8&amp;u=a1aHR0cHM6Ly93d3cubGlmZXdpcmUuY29tL2Jlc3QtbW9iaWxlLW1lc3NhZ2luZy1hcHBzLTI2NTQ4Mzk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b6373f501df70488a020b1b2c6df9a75c27fe5348d1ace0736d20030d2da5efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19c44e29-941f-60a4-24e5-59c895f661e8&amp;u=a1aHR0cHM6Ly9ncmVldGluZ2lzLmNvbS9iZXN0LXdpc2hlcy1tZXNzYWdlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=407ff68e93a93f1b1173c265b335deeb21de5728ce4c144fe95b01c0e83e0ef9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19c44e29-941f-60a4-24e5-59c895f661e8&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vU2hvcnQtUG9zaXRpdmUtTWVzc2FnZXMtZm9yLUZyaWVuZHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=26e5e34f1205cf308e178741c4af0ee121795e85f76bfeaae3df2ebc7961b6ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19c44e29-941f-60a4-24e5-59c895f661e8&amp;u=a1aHR0cHM6Ly9yZWFkaW5nc3dpdGhob3BlLmNvbS9lbmNvdXJhZ2VtZW50LW1lc3NhZ2VzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8548f6be83f2d1a40a371916ef6d9ec7f265c95b2fc05fa027c81d3dbe340fdfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19c44e29-941f-60a4-24e5-59c895f661e8&amp;u=a1aHR0cHM6Ly9tc2d0aG91Z2h0cy5jb20vZGVlcC1sb3ZlLW1lc3NhZ2VzLWZvci1oZXIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1eda09c0595d85ae53958a232ea1d48a41e1c503eea1bc35b60941a8a5274c22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19c44e29-941f-60a4-24e5-59c895f661e8&amp;u=a1aHR0cHM6Ly93d3cuaGFuZHdyeXR0ZW4uY29tL3Jlc291cmNlcy9iZXN0LXdpc2hlcy1nb29kLWx1Y2stbWVzc2FnZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89108d2ff83fc1a4fd80ddd5fe86ef8992147af7b7ed0b61feda6bf7b4a4e7ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19c44e29-941f-60a4-24e5-59c895f661e8&amp;u=a1aHR0cHM6Ly93d3cuZ3JlZXRpbmdjYXJkcG9ldC5jb20vc2hvcnQtbWVzc2FnZXMtZm9yLWV2ZXJ5LW9jY2FzaW9uLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=877b7757fe2592e9bd4646724c36ff4f4af4e60091de450054e2b08a3f86ad46JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1eada1b7-aba2-6c4c-3ea3-b656aaaf6d11&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS9maW5hbmNlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ef38c86574f5735de270de8908fabe2cc01992a06a7e3b6e615581f9cb9a0f5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1eada1b7-aba2-6c4c-3ea3-b656aaaf6d11&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS9maW5hbmNlL3F1b3RlL05JRlRZXzUwOklOREVYTlNF&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71c185324d1b89d961aa7175d1fcae0ea77ec31dbee93a2234434d23345ba18aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1eada1b7-aba2-6c4c-3ea3-b656aaaf6d11&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS9maW5hbmNlL3F1b3RlL0NBU1Q6TkFTREFR&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f3ef27a875fb68677764acb241ed0283b6c7e89ea98c9577e0c7f467fdfd9afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1eada1b7-aba2-6c4c-3ea3-b656aaaf6d11&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS9maW5hbmNlL3F1b3RlL1NPRkk6TkFTREFR&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87e51f5f39c57c05f2225e83b0bb710e0f1f54a983cfae3581200eef6fb43033JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1eada1b7-aba2-6c4c-3ea3-b656aaaf6d11&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS9maW5hbmNlL3F1b3RlL0lROk5BU0RBUQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd1500cd99e664ccb7b7ea8f2845f253f9fb523cdae90fdb26adfc70178c2c7dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1eada1b7-aba2-6c4c-3ea3-b656aaaf6d11&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS9maW5hbmNlL3F1b3RlL0JBOk5ZU0U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e523b95f9b0f820d77a91a71c02caaf820fec36262efb451da2cba687cef54aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1eada1b7-aba2-6c4c-3ea3-b656aaaf6d11&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS9maW5hbmNlL3F1b3RlL01DRDpOWVNF&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a45069f151db372ff5a20a2c16c130782f22cf2bcc1599ee8a1965646ceff25bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1eada1b7-aba2-6c4c-3ea3-b656aaaf6d11&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS9maW5hbmNlL3F1b3RlL0hPT0Q6TkFTREFR&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=db71fbb952a9516cbc647f77479d931a81e11f40ef1be4594996f4f213e0f4e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1eada1b7-aba2-6c4c-3ea3-b656aaaf6d11&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS9maW5hbmNlL2JldGEvcXVvdGUvU1NSTTpOQVNEQVE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b0f2abf5845d392ac8e141d897443bbcac99f220181c567acf6334ca6a1a623bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1eada1b7-aba2-6c4c-3ea3-b656aaaf6d11&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS9maW5hbmNlL3F1b3RlL1RMUlk6TkFTREFR&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73fc7ac29dccdcc65653132d6bbefdd67b315542f2e13598b6f3ec76d394fa12JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=108874ed-5713-6744-236c-630c56046672&amp;u=a1aHR0cHM6Ly93d3cud2FsZ3JlZW5zLmNvbS9zdG9yZWxvY2F0b3IvcGhhcm1hY3kvY2hpY2Fnby1pbD9tc29ja2lkPTEwODg3NGVkNTcxMzY3NDQyMzZjNjMwYzU2MDQ2Njcy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9c1a3f4d6ef7e428752d957b6bbb5b0faaaa8fa99c2cdce3d5a14c799025fb7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=108874ed-5713-6744-236c-630c56046672&amp;u=a1aHR0cHM6Ly93d3cud2FsZ3JlZW5zLmNvbS9sb2NhdG9yL3dhbGdyZWVucy0xNTErbitzdGF0ZStzdC1jaGljYWdvLWlsLTYwNjAxL2lkPTE1MTk2P21zb2NraWQ9MTA4ODc0ZWQ1NzEzNjc0NDIzNmM2MzBjNTYwNDY2NzI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=571022f5937a564b49018e63da57cef0010faa67ad8c37c491ecca82ea147a41JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=108874ed-5713-6744-236c-630c56046672&amp;u=a1aHR0cHM6Ly93d3cuc3RvcmVzaW5mby5jb20vd2FsZ3JlZW5zL2lsbGlub2lzL2NoaWNhZ28vNDgwMS1saW5jb2xuLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1dbeec7cf02f86f4768693b951e0b119a4c324bf77ea823bef72781272d4fe50JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=108874ed-5713-6744-236c-630c56046672&amp;u=a1aHR0cHM6Ly93d3cuc3RvcmVvcGVuaW5naG91cnMuY29tL3dhbGdyZWVucy0zMjAxLWJyb2Fkd2F5LWNoaWNhZ28taWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e276a38fab7ae9a46c6182c31ec6e8228164e46566678f6a36d78f9e48cc6f9aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=108874ed-5713-6744-236c-630c56046672&amp;u=a1aHR0cHM6Ly93d3cuc3RvcmVzaW5mby5jb20vd2FsZ3JlZW5zL2lsbGlub2lzL2NoaWNhZ28vMzQyLWUtaWxsaW5vaXMtc3QuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c55368d278dad817144d146f7b2ee1eafbc1d201d56105b92547c2595e8d7e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=108874ed-5713-6744-236c-630c56046672&amp;u=a1aHR0cHM6Ly93d3cuc3RvcmVvcGVuaW5naG91cnMuY29tL3JldGFpbGVycy93YWxncmVlbnMvY2hpY2Fnby1pbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=84f504d3261ed509735bb676d7cc1d5411cbdcca8db81f5c8434d222fa42e5adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=108874ed-5713-6744-236c-630c56046672&amp;u=a1aHR0cHM6Ly9hcHAuZm91cnNxdWFyZS5jb20vbG9jYXRpb25zL3dhbGdyZWVucy9jaGljYWdv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f2c4e9740ad2fff25216f7e190af4bb53899b1a122e32da207acea22a265efeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=108874ed-5713-6744-236c-630c56046672&amp;u=a1aHR0cHM6Ly93d3cuc3RvcmVzaG91cnMuY29tL3dhbGdyZWVucy9pbGxpbm9pcy9jaGljYWdvL3N3ZXN0ZXJuYXZl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=43685ca0c07ca96de43d5613caf57b824b88fa637fa1331209cf19bd41e4328aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=108874ed-5713-6744-236c-630c56046672&amp;u=a1aHR0cHM6Ly93d3cubXlzdG9yZTQxMS5jb20vc3RvcmUvbGlzdF9jaXR5LzIxL0lsbGlub2lzL0NoaWNhZ28vV2FsZ3JlZW5zLXN0b3JlLWxvY2F0aW9ucz9wYWdlPTE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0d16e45a4608b02d57966e46aa94e354205b47fabf75bdf1ff1c008e3dd9da58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=108874ed-5713-6744-236c-630c56046672&amp;u=a1aHR0cHM6Ly9pbnNpZGVyeC5jb20vcGhhcm1hY3ktbmVhci1tZS93YWxncmVlbnMvaWwvY2hpY2Fnby80NzAwLXMtaGFsc3RlZC1zdC8xOTkyNzEyOTg4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c7d41246f43570f3bfdfba97074dcf1ca61e7e9b3e09ca2c59e795f1dadf5b1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14dec174-b91c-68b4-0440-d695b83e6956&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL3Vr&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=93f9fe810d00e05ab77f9640aa7ae41aa579b8ad6349455e7408c30fe0f2e7d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14dec174-b91c-68b4-0440-d695b83e6956&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL3RoZWd1YXJkaWFuLzIwMDAvanVuLzIyL2ZlYXR1cmVzMTEuZzI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4441a3593c6c856d7bc71c6bae360452a21266cf6fe70750697f9c400416748aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14dec174-b91c-68b4-0440-d695b83e6956&amp;u=a1aHR0cHM6Ly9qb2JzLnRoZWd1YXJkaWFuLmNvbS9nZXRhc3NldC8yYTgzYmE2Ni1jZjVhLTRjYzctYjE5NC1iNjkxYmRmZWE3NjAvO3c9MjAw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=840db1a4ab4f2d4f1c48713c3541d141f6f46f7c2f4994d6438aa7ce4c3b835bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14dec174-b91c-68b4-0440-d695b83e6956&amp;u=a1aHR0cHM6Ly9ob2xpZGF5cy50aGVndWFyZGlhbi5jb20vaW1hZ2VzL3BlcnVfbGxhbWFzXzE0NjB4NjIwL3RyYXZlbGZpbmRlcnNz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df4918f4765c4878917eaf3b4ea4295912d5e621feb33de122ca641e0d145fabJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14dec174-b91c-68b4-0440-d695b83e6956&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL3dvcmxkLzIwMDkvc2VwLzE1L215LWJyb3RoZXItdGhlLXVuYWJvbWJlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a6027ba077372562f22f13bd9e32203a1653d834331c2161a284aece4a65b20JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14dec174-b91c-68b4-0440-d695b83e6956&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL3dvcmxkLzE5OTkvbWFyLzE0L21jdmVpZ2gudXNh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0d2b3aab9f5741392c8509f27ea04a1832c9200147afbdf2ca4c34a5f53b5b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14dec174-b91c-68b4-0440-d695b83e6956&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL3VzLW5ld3MvMjAyMy9qdW4vMTEvdW5hYm9tYmVyLXRlZC1rYWN6eW5za2ktZGllZC1ieS1zdWljaWRlLXJlcG9ydA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c97c1e9033665b77cbf93d72dd1e8f44033b152f9a3e8676c4dee47d12605e0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14dec174-b91c-68b4-0440-d695b83e6956&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL2Jvb2tzLzIwMTYvZmViLzA3L3VuYWJvbWJlci10ZWQta2Fjenluc2tpLWJyb3RoZXItZGF2aWQta2Fjenluc2tpLWV2ZXJ5LWxhc3QtdGllLWJvb2s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=88c9d2cfb42d5ac9cf1387aa1bb2e2aadf45188b500dc35352f06392f6b24bcbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14dec174-b91c-68b4-0440-d695b83e6956&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL2ZpbG0vMjAyMS9tYXIvMDEvdGVkLWstcmV2aWV3LXF1ZWFzeS1pbm5lci1saWZlLW9mLXRoZS11bmFib21iZXItYmVybGluLWZpbG0tZmVzdGl2YWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97a8ba7aa94925ddd79447d866437146b180d08eb85ce882c5dfa00fcaf88581JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d07588e-f67a-6081-2e6e-4f6ff79b6133&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9UdW5kcmE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=28fd3645a73298241ca797b447d99d784c72e935f684ac163dfd81f496d0f834JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d07588e-f67a-6081-2e6e-4f6ff79b6133&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS90dW5kcmE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0d740d193607852ce9f5cf90be3adc60fc1d2b204be9441fc1bd3b43273011ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d07588e-f67a-6081-2e6e-4f6ff79b6133&amp;u=a1aHR0cHM6Ly93d3cudG95b3RhLmNvbS90dW5kcmEvP21zb2NraWQ9MmQwNzU4OGVmNjdhNjA4MTJlNmU0ZjZmZjc5YjYxMzM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5866a02b6d8d0cde3e9339a38a665eb63c408d122c7c9afdeb11155aa9453d19JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d07588e-f67a-6081-2e6e-4f6ff79b6133&amp;u=a1aHR0cHM6Ly93d3cuZ2xvYmFsYmlvZW5lcmd5Lm9yZy90dW5kcmEtYmlvbWUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b3f7e8e9548edb640acdbcc4927e5292d891a1eedd2706da624da187bc20c2baJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d07588e-f67a-6081-2e6e-4f6ff79b6133&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS90dW5kcmEtYmlvbWUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=faee2f7b67758df9557f8a893f4d2ee0dfb82fa21c6a1cdcbe9d3618f5b2c8ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d07588e-f67a-6081-2e6e-4f6ff79b6133&amp;u=a1aHR0cHM6Ly9zY2llbmNlLm5hc2EuZ292L2tpZHMvZWFydGgvbWlzc2lvbi1iaW9tZXMvYmlvdHVuZHJhLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e9a0c3b2219910ac0e115f1c8441dd49880ea8ccd55ebffada2dc0307feab8cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d07588e-f67a-6081-2e6e-4f6ff79b6133&amp;u=a1aHR0cHM6Ly9zY2llbmNlbm90ZXMub3JnL3R1bmRyYS1iaW9tZS1jaGFyYWN0ZXJpc3RpY3MtZmxvcmEtZmF1bmEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8bb16cf082dc842a8b5c8790cde7f52e87581b565ee5d6279958204cf5d50417JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d07588e-f67a-6081-2e6e-4f6ff79b6133&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS90dW5kcmEvRW52aXJvbm1lbnRhbC1jb25kaXRpb25z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b476a1e23e38547584d5a432d6df90fed7832918f9a0dc241eb023290ace4a5eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d07588e-f67a-6081-2e6e-4f6ff79b6133&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vZ2VvZ3JhcGh5L3doYXQtaXMtdGhlLXR1bmRyYS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8aafb2f534006469308de528346521535ede8afde8e5adaf74e5761690b08d1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d07588e-f67a-6081-2e6e-4f6ff79b6133&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS90dW5kcmFzLWV4cGxhaW5lZC8&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
+  </si>
+  <si>
+    <t>Sea Point</t>
+  </si>
+  <si>
+    <t>Green Point</t>
+  </si>
+  <si>
+    <t>Woodstock</t>
+  </si>
+  <si>
+    <t>Observatory</t>
+  </si>
+  <si>
+    <t>Salt River</t>
   </si>
   <si>
     <t>Bing</t>
@@ -814,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -848,19 +1415,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="G2" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H2" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -868,19 +1435,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="G3" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H3" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -888,19 +1455,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="G4" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H4" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -908,19 +1475,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>83</v>
+        <v>175</v>
       </c>
       <c r="G5" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H5" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -928,19 +1495,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="G6" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H6" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -948,19 +1515,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="G7" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H7" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -968,19 +1535,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="G8" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H8" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -988,19 +1555,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="G9" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H9" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1008,19 +1575,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>88</v>
+        <v>180</v>
       </c>
       <c r="G10" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H10" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1028,19 +1595,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>89</v>
+        <v>181</v>
       </c>
       <c r="G11" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H11" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1048,19 +1615,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>90</v>
+        <v>182</v>
       </c>
       <c r="G12" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H12" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1068,19 +1635,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>91</v>
+        <v>183</v>
       </c>
       <c r="G13" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H13" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1088,19 +1655,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="G14" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H14" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1108,19 +1675,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>93</v>
+        <v>185</v>
       </c>
       <c r="G15" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H15" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1128,19 +1695,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>94</v>
+        <v>186</v>
       </c>
       <c r="G16" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H16" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1148,19 +1715,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>95</v>
+        <v>187</v>
       </c>
       <c r="G17" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H17" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1168,19 +1735,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>96</v>
+        <v>188</v>
       </c>
       <c r="G18" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H18" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1188,19 +1755,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="G19" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H19" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1208,19 +1775,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="G20" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H20" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1228,19 +1795,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>99</v>
+        <v>191</v>
       </c>
       <c r="G21" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H21" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1248,19 +1815,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="G22" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H22" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1268,19 +1835,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>101</v>
+        <v>193</v>
       </c>
       <c r="G23" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H23" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1288,19 +1855,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>102</v>
+        <v>194</v>
       </c>
       <c r="G24" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H24" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1308,19 +1875,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>103</v>
+        <v>195</v>
       </c>
       <c r="G25" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H25" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1328,19 +1895,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>104</v>
+        <v>196</v>
       </c>
       <c r="G26" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H26" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1348,19 +1915,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="G27" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H27" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1368,19 +1935,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>106</v>
+        <v>198</v>
       </c>
       <c r="G28" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H28" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1388,19 +1955,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>107</v>
+        <v>199</v>
       </c>
       <c r="G29" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H29" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1408,19 +1975,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="G30" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H30" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1428,19 +1995,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>109</v>
+        <v>201</v>
       </c>
       <c r="G31" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H31" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1448,19 +2015,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="G32" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H32" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1468,19 +2035,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="G33" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H33" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1488,19 +2055,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>112</v>
+        <v>204</v>
       </c>
       <c r="G34" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H34" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1508,19 +2075,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>113</v>
+        <v>205</v>
       </c>
       <c r="G35" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H35" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1528,19 +2095,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>114</v>
+        <v>206</v>
       </c>
       <c r="G36" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H36" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1548,19 +2115,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>115</v>
+        <v>207</v>
       </c>
       <c r="G37" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H37" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1568,19 +2135,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>116</v>
+        <v>208</v>
       </c>
       <c r="G38" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H38" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1588,19 +2155,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>117</v>
+        <v>209</v>
       </c>
       <c r="G39" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H39" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1608,19 +2175,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>118</v>
+        <v>210</v>
       </c>
       <c r="G40" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H40" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1628,19 +2195,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C41" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>119</v>
+        <v>211</v>
       </c>
       <c r="G41" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H41" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1648,19 +2215,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C42" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>120</v>
+        <v>212</v>
       </c>
       <c r="G42" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H42" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1668,19 +2235,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>121</v>
+        <v>213</v>
       </c>
       <c r="G43" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H43" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1688,19 +2255,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C44" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>122</v>
+        <v>214</v>
       </c>
       <c r="G44" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H44" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1708,19 +2275,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>123</v>
+        <v>215</v>
       </c>
       <c r="G45" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H45" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1728,19 +2295,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C46" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="G46" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H46" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1748,19 +2315,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C47" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>125</v>
+        <v>217</v>
       </c>
       <c r="G47" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H47" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1768,19 +2335,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>126</v>
+        <v>218</v>
       </c>
       <c r="G48" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H48" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1788,19 +2355,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>127</v>
+        <v>219</v>
       </c>
       <c r="G49" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H49" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1808,19 +2375,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C50" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="G50" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H50" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1828,19 +2395,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C51" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>129</v>
+        <v>221</v>
       </c>
       <c r="G51" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H51" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1848,19 +2415,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>130</v>
+        <v>222</v>
       </c>
       <c r="G52" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H52" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1868,19 +2435,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C53" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="G53" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H53" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1888,19 +2455,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C54" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>132</v>
+        <v>224</v>
       </c>
       <c r="G54" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H54" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -1908,19 +2475,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C55" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>133</v>
+        <v>225</v>
       </c>
       <c r="G55" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H55" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -1928,19 +2495,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C56" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>134</v>
+        <v>226</v>
       </c>
       <c r="G56" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H56" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -1948,19 +2515,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C57" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="G57" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H57" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -1968,19 +2535,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C58" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="G58" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H58" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -1988,19 +2555,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C59" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>137</v>
+        <v>229</v>
       </c>
       <c r="G59" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H59" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2008,19 +2575,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>138</v>
+        <v>230</v>
       </c>
       <c r="G60" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H60" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2028,19 +2595,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C61" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>139</v>
+        <v>231</v>
       </c>
       <c r="G61" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H61" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2048,19 +2615,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C62" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>140</v>
+        <v>232</v>
       </c>
       <c r="G62" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H62" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2068,19 +2635,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C63" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>141</v>
+        <v>233</v>
       </c>
       <c r="G63" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H63" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2088,19 +2655,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C64" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>142</v>
+        <v>234</v>
       </c>
       <c r="G64" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H64" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2108,19 +2675,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>143</v>
+        <v>235</v>
       </c>
       <c r="G65" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H65" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2128,19 +2695,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C66" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>144</v>
+        <v>236</v>
       </c>
       <c r="G66" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H66" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2148,19 +2715,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C67" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>145</v>
+        <v>237</v>
       </c>
       <c r="G67" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H67" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2168,19 +2735,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C68" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>146</v>
+        <v>238</v>
       </c>
       <c r="G68" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="H68" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2188,19 +2755,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C69" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="G69" t="s">
-        <v>150</v>
+        <v>335</v>
       </c>
       <c r="H69" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2208,19 +2775,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C70" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>148</v>
+        <v>240</v>
       </c>
       <c r="G70" t="s">
-        <v>150</v>
+        <v>335</v>
       </c>
       <c r="H70" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2228,19 +2795,1859 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
+        <v>170</v>
+      </c>
+      <c r="C71" t="s">
+        <v>171</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G71" t="s">
+        <v>335</v>
+      </c>
+      <c r="H71" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
         <v>78</v>
       </c>
-      <c r="C71" t="s">
+      <c r="B72" t="s">
+        <v>170</v>
+      </c>
+      <c r="C72" t="s">
+        <v>171</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G72" t="s">
+        <v>335</v>
+      </c>
+      <c r="H72" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
         <v>79</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="B73" t="s">
+        <v>170</v>
+      </c>
+      <c r="C73" t="s">
+        <v>171</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G73" t="s">
+        <v>335</v>
+      </c>
+      <c r="H73" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" t="s">
+        <v>170</v>
+      </c>
+      <c r="C74" t="s">
+        <v>171</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G74" t="s">
+        <v>335</v>
+      </c>
+      <c r="H74" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" t="s">
+        <v>170</v>
+      </c>
+      <c r="C75" t="s">
+        <v>171</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G75" t="s">
+        <v>335</v>
+      </c>
+      <c r="H75" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" t="s">
+        <v>170</v>
+      </c>
+      <c r="C76" t="s">
+        <v>171</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G76" t="s">
+        <v>335</v>
+      </c>
+      <c r="H76" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" t="s">
+        <v>170</v>
+      </c>
+      <c r="C77" t="s">
+        <v>171</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G77" t="s">
+        <v>335</v>
+      </c>
+      <c r="H77" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" t="s">
+        <v>170</v>
+      </c>
+      <c r="C78" t="s">
+        <v>171</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G78" t="s">
+        <v>335</v>
+      </c>
+      <c r="H78" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" t="s">
+        <v>170</v>
+      </c>
+      <c r="C79" t="s">
+        <v>171</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G79" t="s">
+        <v>335</v>
+      </c>
+      <c r="H79" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" t="s">
+        <v>170</v>
+      </c>
+      <c r="C80" t="s">
+        <v>171</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G80" t="s">
+        <v>335</v>
+      </c>
+      <c r="H80" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" t="s">
+        <v>170</v>
+      </c>
+      <c r="C81" t="s">
+        <v>171</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G81" t="s">
+        <v>335</v>
+      </c>
+      <c r="H81" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" t="s">
+        <v>170</v>
+      </c>
+      <c r="C82" t="s">
+        <v>171</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G82" t="s">
+        <v>335</v>
+      </c>
+      <c r="H82" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" t="s">
+        <v>170</v>
+      </c>
+      <c r="C83" t="s">
+        <v>171</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G83" t="s">
+        <v>335</v>
+      </c>
+      <c r="H83" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" t="s">
+        <v>171</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G84" t="s">
+        <v>335</v>
+      </c>
+      <c r="H84" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" t="s">
+        <v>170</v>
+      </c>
+      <c r="C85" t="s">
+        <v>171</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G85" t="s">
+        <v>336</v>
+      </c>
+      <c r="H85" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86" t="s">
+        <v>171</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G86" t="s">
+        <v>336</v>
+      </c>
+      <c r="H86" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" t="s">
+        <v>170</v>
+      </c>
+      <c r="C87" t="s">
+        <v>171</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G87" t="s">
+        <v>336</v>
+      </c>
+      <c r="H87" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" t="s">
+        <v>170</v>
+      </c>
+      <c r="C88" t="s">
+        <v>171</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G88" t="s">
+        <v>336</v>
+      </c>
+      <c r="H88" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" t="s">
+        <v>170</v>
+      </c>
+      <c r="C89" t="s">
+        <v>171</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G89" t="s">
+        <v>336</v>
+      </c>
+      <c r="H89" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" t="s">
+        <v>170</v>
+      </c>
+      <c r="C90" t="s">
+        <v>171</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G90" t="s">
+        <v>336</v>
+      </c>
+      <c r="H90" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" t="s">
+        <v>170</v>
+      </c>
+      <c r="C91" t="s">
+        <v>171</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G91" t="s">
+        <v>336</v>
+      </c>
+      <c r="H91" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" t="s">
+        <v>170</v>
+      </c>
+      <c r="C92" t="s">
+        <v>171</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G92" t="s">
+        <v>336</v>
+      </c>
+      <c r="H92" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" t="s">
+        <v>170</v>
+      </c>
+      <c r="C93" t="s">
+        <v>171</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G93" t="s">
+        <v>336</v>
+      </c>
+      <c r="H93" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" t="s">
+        <v>170</v>
+      </c>
+      <c r="C94" t="s">
+        <v>171</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G94" t="s">
+        <v>336</v>
+      </c>
+      <c r="H94" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" t="s">
+        <v>170</v>
+      </c>
+      <c r="C95" t="s">
+        <v>171</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G95" t="s">
+        <v>336</v>
+      </c>
+      <c r="H95" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" t="s">
+        <v>171</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G96" t="s">
+        <v>336</v>
+      </c>
+      <c r="H96" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" t="s">
+        <v>170</v>
+      </c>
+      <c r="C97" t="s">
+        <v>171</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G97" t="s">
+        <v>336</v>
+      </c>
+      <c r="H97" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" t="s">
+        <v>170</v>
+      </c>
+      <c r="C98" t="s">
+        <v>171</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G98" t="s">
+        <v>336</v>
+      </c>
+      <c r="H98" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" t="s">
+        <v>170</v>
+      </c>
+      <c r="C99" t="s">
+        <v>171</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="G99" t="s">
+        <v>336</v>
+      </c>
+      <c r="H99" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" t="s">
+        <v>170</v>
+      </c>
+      <c r="C100" t="s">
+        <v>171</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G100" t="s">
+        <v>336</v>
+      </c>
+      <c r="H100" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" t="s">
+        <v>170</v>
+      </c>
+      <c r="C101" t="s">
+        <v>171</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G101" t="s">
+        <v>336</v>
+      </c>
+      <c r="H101" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" t="s">
+        <v>170</v>
+      </c>
+      <c r="C102" t="s">
+        <v>171</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G102" t="s">
+        <v>336</v>
+      </c>
+      <c r="H102" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" t="s">
+        <v>170</v>
+      </c>
+      <c r="C103" t="s">
+        <v>171</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G103" t="s">
+        <v>336</v>
+      </c>
+      <c r="H103" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" t="s">
+        <v>170</v>
+      </c>
+      <c r="C104" t="s">
+        <v>171</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G104" t="s">
+        <v>336</v>
+      </c>
+      <c r="H104" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" t="s">
+        <v>170</v>
+      </c>
+      <c r="C105" t="s">
+        <v>171</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G105" t="s">
+        <v>337</v>
+      </c>
+      <c r="H105" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" t="s">
+        <v>170</v>
+      </c>
+      <c r="C106" t="s">
+        <v>171</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G106" t="s">
+        <v>337</v>
+      </c>
+      <c r="H106" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" t="s">
+        <v>170</v>
+      </c>
+      <c r="C107" t="s">
+        <v>171</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G107" t="s">
+        <v>337</v>
+      </c>
+      <c r="H107" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" t="s">
+        <v>170</v>
+      </c>
+      <c r="C108" t="s">
+        <v>171</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G108" t="s">
+        <v>337</v>
+      </c>
+      <c r="H108" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" t="s">
+        <v>170</v>
+      </c>
+      <c r="C109" t="s">
+        <v>171</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G109" t="s">
+        <v>337</v>
+      </c>
+      <c r="H109" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" t="s">
+        <v>170</v>
+      </c>
+      <c r="C110" t="s">
+        <v>171</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G110" t="s">
+        <v>337</v>
+      </c>
+      <c r="H110" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" t="s">
+        <v>170</v>
+      </c>
+      <c r="C111" t="s">
+        <v>171</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G111" t="s">
+        <v>337</v>
+      </c>
+      <c r="H111" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" t="s">
+        <v>170</v>
+      </c>
+      <c r="C112" t="s">
+        <v>171</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G112" t="s">
+        <v>337</v>
+      </c>
+      <c r="H112" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" t="s">
+        <v>170</v>
+      </c>
+      <c r="C113" t="s">
+        <v>171</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G113" t="s">
+        <v>337</v>
+      </c>
+      <c r="H113" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" t="s">
+        <v>170</v>
+      </c>
+      <c r="C114" t="s">
+        <v>171</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G114" t="s">
+        <v>337</v>
+      </c>
+      <c r="H114" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" t="s">
+        <v>170</v>
+      </c>
+      <c r="C115" t="s">
+        <v>171</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G115" t="s">
+        <v>337</v>
+      </c>
+      <c r="H115" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" t="s">
+        <v>170</v>
+      </c>
+      <c r="C116" t="s">
+        <v>171</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G116" t="s">
+        <v>337</v>
+      </c>
+      <c r="H116" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>123</v>
+      </c>
+      <c r="B117" t="s">
+        <v>170</v>
+      </c>
+      <c r="C117" t="s">
+        <v>171</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G117" t="s">
+        <v>337</v>
+      </c>
+      <c r="H117" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" t="s">
+        <v>170</v>
+      </c>
+      <c r="C118" t="s">
+        <v>171</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G118" t="s">
+        <v>337</v>
+      </c>
+      <c r="H118" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" t="s">
+        <v>170</v>
+      </c>
+      <c r="C119" t="s">
+        <v>171</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G119" t="s">
+        <v>337</v>
+      </c>
+      <c r="H119" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>126</v>
+      </c>
+      <c r="B120" t="s">
+        <v>170</v>
+      </c>
+      <c r="C120" t="s">
+        <v>171</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G120" t="s">
+        <v>337</v>
+      </c>
+      <c r="H120" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>127</v>
+      </c>
+      <c r="B121" t="s">
+        <v>170</v>
+      </c>
+      <c r="C121" t="s">
+        <v>171</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G121" t="s">
+        <v>337</v>
+      </c>
+      <c r="H121" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" t="s">
+        <v>170</v>
+      </c>
+      <c r="C122" t="s">
+        <v>171</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G122" t="s">
+        <v>337</v>
+      </c>
+      <c r="H122" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>129</v>
+      </c>
+      <c r="B123" t="s">
+        <v>170</v>
+      </c>
+      <c r="C123" t="s">
+        <v>171</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G123" t="s">
+        <v>337</v>
+      </c>
+      <c r="H123" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" t="s">
+        <v>170</v>
+      </c>
+      <c r="C124" t="s">
+        <v>171</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G124" t="s">
+        <v>337</v>
+      </c>
+      <c r="H124" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>131</v>
+      </c>
+      <c r="B125" t="s">
+        <v>170</v>
+      </c>
+      <c r="C125" t="s">
+        <v>171</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G125" t="s">
+        <v>338</v>
+      </c>
+      <c r="H125" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" t="s">
+        <v>170</v>
+      </c>
+      <c r="C126" t="s">
+        <v>171</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G126" t="s">
+        <v>338</v>
+      </c>
+      <c r="H126" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" t="s">
+        <v>170</v>
+      </c>
+      <c r="C127" t="s">
+        <v>171</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G127" t="s">
+        <v>338</v>
+      </c>
+      <c r="H127" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" t="s">
+        <v>170</v>
+      </c>
+      <c r="C128" t="s">
+        <v>171</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G128" t="s">
+        <v>338</v>
+      </c>
+      <c r="H128" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" t="s">
+        <v>170</v>
+      </c>
+      <c r="C129" t="s">
+        <v>171</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G129" t="s">
+        <v>338</v>
+      </c>
+      <c r="H129" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
+        <v>136</v>
+      </c>
+      <c r="B130" t="s">
+        <v>170</v>
+      </c>
+      <c r="C130" t="s">
+        <v>171</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="G130" t="s">
+        <v>338</v>
+      </c>
+      <c r="H130" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" t="s">
+        <v>137</v>
+      </c>
+      <c r="B131" t="s">
+        <v>170</v>
+      </c>
+      <c r="C131" t="s">
+        <v>171</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="G131" t="s">
+        <v>338</v>
+      </c>
+      <c r="H131" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" t="s">
+        <v>138</v>
+      </c>
+      <c r="B132" t="s">
+        <v>170</v>
+      </c>
+      <c r="C132" t="s">
+        <v>171</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G132" t="s">
+        <v>338</v>
+      </c>
+      <c r="H132" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>139</v>
+      </c>
+      <c r="B133" t="s">
+        <v>170</v>
+      </c>
+      <c r="C133" t="s">
+        <v>171</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G133" t="s">
+        <v>338</v>
+      </c>
+      <c r="H133" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>140</v>
+      </c>
+      <c r="B134" t="s">
+        <v>170</v>
+      </c>
+      <c r="C134" t="s">
+        <v>171</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G134" t="s">
+        <v>338</v>
+      </c>
+      <c r="H134" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" t="s">
+        <v>141</v>
+      </c>
+      <c r="B135" t="s">
+        <v>170</v>
+      </c>
+      <c r="C135" t="s">
+        <v>171</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G135" t="s">
+        <v>338</v>
+      </c>
+      <c r="H135" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>142</v>
+      </c>
+      <c r="B136" t="s">
+        <v>170</v>
+      </c>
+      <c r="C136" t="s">
+        <v>171</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G136" t="s">
+        <v>338</v>
+      </c>
+      <c r="H136" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="s">
+        <v>143</v>
+      </c>
+      <c r="B137" t="s">
+        <v>170</v>
+      </c>
+      <c r="C137" t="s">
+        <v>171</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G137" t="s">
+        <v>338</v>
+      </c>
+      <c r="H137" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="s">
+        <v>144</v>
+      </c>
+      <c r="B138" t="s">
+        <v>170</v>
+      </c>
+      <c r="C138" t="s">
+        <v>171</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G138" t="s">
+        <v>338</v>
+      </c>
+      <c r="H138" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="s">
+        <v>145</v>
+      </c>
+      <c r="B139" t="s">
+        <v>170</v>
+      </c>
+      <c r="C139" t="s">
+        <v>171</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="G139" t="s">
+        <v>338</v>
+      </c>
+      <c r="H139" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="s">
+        <v>146</v>
+      </c>
+      <c r="B140" t="s">
+        <v>170</v>
+      </c>
+      <c r="C140" t="s">
+        <v>171</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G140" t="s">
+        <v>338</v>
+      </c>
+      <c r="H140" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="s">
+        <v>147</v>
+      </c>
+      <c r="B141" t="s">
+        <v>170</v>
+      </c>
+      <c r="C141" t="s">
+        <v>171</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G141" t="s">
+        <v>338</v>
+      </c>
+      <c r="H141" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" t="s">
+        <v>148</v>
+      </c>
+      <c r="B142" t="s">
+        <v>170</v>
+      </c>
+      <c r="C142" t="s">
+        <v>171</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G142" t="s">
+        <v>338</v>
+      </c>
+      <c r="H142" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" t="s">
         <v>149</v>
       </c>
-      <c r="G71" t="s">
+      <c r="B143" t="s">
+        <v>170</v>
+      </c>
+      <c r="C143" t="s">
+        <v>171</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="G143" t="s">
+        <v>338</v>
+      </c>
+      <c r="H143" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" t="s">
         <v>150</v>
       </c>
-      <c r="H71" t="s">
+      <c r="B144" t="s">
+        <v>170</v>
+      </c>
+      <c r="C144" t="s">
+        <v>171</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G144" t="s">
+        <v>338</v>
+      </c>
+      <c r="H144" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" t="s">
         <v>151</v>
+      </c>
+      <c r="B145" t="s">
+        <v>170</v>
+      </c>
+      <c r="C145" t="s">
+        <v>171</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G145" t="s">
+        <v>339</v>
+      </c>
+      <c r="H145" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" t="s">
+        <v>152</v>
+      </c>
+      <c r="B146" t="s">
+        <v>170</v>
+      </c>
+      <c r="C146" t="s">
+        <v>171</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G146" t="s">
+        <v>339</v>
+      </c>
+      <c r="H146" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" t="s">
+        <v>153</v>
+      </c>
+      <c r="B147" t="s">
+        <v>170</v>
+      </c>
+      <c r="C147" t="s">
+        <v>171</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G147" t="s">
+        <v>339</v>
+      </c>
+      <c r="H147" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>154</v>
+      </c>
+      <c r="B148" t="s">
+        <v>170</v>
+      </c>
+      <c r="C148" t="s">
+        <v>171</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G148" t="s">
+        <v>339</v>
+      </c>
+      <c r="H148" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" t="s">
+        <v>155</v>
+      </c>
+      <c r="B149" t="s">
+        <v>170</v>
+      </c>
+      <c r="C149" t="s">
+        <v>171</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="G149" t="s">
+        <v>339</v>
+      </c>
+      <c r="H149" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" t="s">
+        <v>156</v>
+      </c>
+      <c r="B150" t="s">
+        <v>170</v>
+      </c>
+      <c r="C150" t="s">
+        <v>171</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G150" t="s">
+        <v>339</v>
+      </c>
+      <c r="H150" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" t="s">
+        <v>157</v>
+      </c>
+      <c r="B151" t="s">
+        <v>170</v>
+      </c>
+      <c r="C151" t="s">
+        <v>171</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G151" t="s">
+        <v>339</v>
+      </c>
+      <c r="H151" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" t="s">
+        <v>158</v>
+      </c>
+      <c r="B152" t="s">
+        <v>170</v>
+      </c>
+      <c r="C152" t="s">
+        <v>171</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G152" t="s">
+        <v>339</v>
+      </c>
+      <c r="H152" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" t="s">
+        <v>159</v>
+      </c>
+      <c r="B153" t="s">
+        <v>170</v>
+      </c>
+      <c r="C153" t="s">
+        <v>171</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G153" t="s">
+        <v>339</v>
+      </c>
+      <c r="H153" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" t="s">
+        <v>160</v>
+      </c>
+      <c r="B154" t="s">
+        <v>170</v>
+      </c>
+      <c r="C154" t="s">
+        <v>171</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G154" t="s">
+        <v>339</v>
+      </c>
+      <c r="H154" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" t="s">
+        <v>161</v>
+      </c>
+      <c r="B155" t="s">
+        <v>170</v>
+      </c>
+      <c r="C155" t="s">
+        <v>171</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G155" t="s">
+        <v>339</v>
+      </c>
+      <c r="H155" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" t="s">
+        <v>162</v>
+      </c>
+      <c r="B156" t="s">
+        <v>170</v>
+      </c>
+      <c r="C156" t="s">
+        <v>171</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G156" t="s">
+        <v>339</v>
+      </c>
+      <c r="H156" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" t="s">
+        <v>163</v>
+      </c>
+      <c r="B157" t="s">
+        <v>170</v>
+      </c>
+      <c r="C157" t="s">
+        <v>171</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G157" t="s">
+        <v>339</v>
+      </c>
+      <c r="H157" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" t="s">
+        <v>164</v>
+      </c>
+      <c r="B158" t="s">
+        <v>170</v>
+      </c>
+      <c r="C158" t="s">
+        <v>171</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G158" t="s">
+        <v>339</v>
+      </c>
+      <c r="H158" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" t="s">
+        <v>165</v>
+      </c>
+      <c r="B159" t="s">
+        <v>170</v>
+      </c>
+      <c r="C159" t="s">
+        <v>171</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="G159" t="s">
+        <v>339</v>
+      </c>
+      <c r="H159" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" t="s">
+        <v>166</v>
+      </c>
+      <c r="B160" t="s">
+        <v>170</v>
+      </c>
+      <c r="C160" t="s">
+        <v>171</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G160" t="s">
+        <v>339</v>
+      </c>
+      <c r="H160" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" t="s">
+        <v>167</v>
+      </c>
+      <c r="B161" t="s">
+        <v>170</v>
+      </c>
+      <c r="C161" t="s">
+        <v>171</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G161" t="s">
+        <v>339</v>
+      </c>
+      <c r="H161" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" t="s">
+        <v>168</v>
+      </c>
+      <c r="B162" t="s">
+        <v>170</v>
+      </c>
+      <c r="C162" t="s">
+        <v>171</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G162" t="s">
+        <v>339</v>
+      </c>
+      <c r="H162" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" t="s">
+        <v>169</v>
+      </c>
+      <c r="B163" t="s">
+        <v>170</v>
+      </c>
+      <c r="C163" t="s">
+        <v>171</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G163" t="s">
+        <v>339</v>
+      </c>
+      <c r="H163" t="s">
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -2315,6 +4722,98 @@
     <hyperlink ref="F69" r:id="rId68"/>
     <hyperlink ref="F70" r:id="rId69"/>
     <hyperlink ref="F71" r:id="rId70"/>
+    <hyperlink ref="F72" r:id="rId71"/>
+    <hyperlink ref="F73" r:id="rId72"/>
+    <hyperlink ref="F74" r:id="rId73"/>
+    <hyperlink ref="F75" r:id="rId74"/>
+    <hyperlink ref="F76" r:id="rId75"/>
+    <hyperlink ref="F77" r:id="rId76"/>
+    <hyperlink ref="F78" r:id="rId77"/>
+    <hyperlink ref="F79" r:id="rId78"/>
+    <hyperlink ref="F80" r:id="rId79"/>
+    <hyperlink ref="F81" r:id="rId80"/>
+    <hyperlink ref="F82" r:id="rId81"/>
+    <hyperlink ref="F83" r:id="rId82"/>
+    <hyperlink ref="F84" r:id="rId83"/>
+    <hyperlink ref="F85" r:id="rId84"/>
+    <hyperlink ref="F86" r:id="rId85"/>
+    <hyperlink ref="F87" r:id="rId86"/>
+    <hyperlink ref="F88" r:id="rId87"/>
+    <hyperlink ref="F89" r:id="rId88"/>
+    <hyperlink ref="F90" r:id="rId89"/>
+    <hyperlink ref="F91" r:id="rId90"/>
+    <hyperlink ref="F92" r:id="rId91"/>
+    <hyperlink ref="F93" r:id="rId92"/>
+    <hyperlink ref="F94" r:id="rId93"/>
+    <hyperlink ref="F95" r:id="rId94"/>
+    <hyperlink ref="F96" r:id="rId95"/>
+    <hyperlink ref="F97" r:id="rId96"/>
+    <hyperlink ref="F98" r:id="rId97"/>
+    <hyperlink ref="F99" r:id="rId98"/>
+    <hyperlink ref="F100" r:id="rId99"/>
+    <hyperlink ref="F101" r:id="rId100"/>
+    <hyperlink ref="F102" r:id="rId101"/>
+    <hyperlink ref="F103" r:id="rId102"/>
+    <hyperlink ref="F104" r:id="rId103"/>
+    <hyperlink ref="F105" r:id="rId104"/>
+    <hyperlink ref="F106" r:id="rId105"/>
+    <hyperlink ref="F107" r:id="rId106"/>
+    <hyperlink ref="F108" r:id="rId107"/>
+    <hyperlink ref="F109" r:id="rId108"/>
+    <hyperlink ref="F110" r:id="rId109"/>
+    <hyperlink ref="F111" r:id="rId110"/>
+    <hyperlink ref="F112" r:id="rId111"/>
+    <hyperlink ref="F113" r:id="rId112"/>
+    <hyperlink ref="F114" r:id="rId113"/>
+    <hyperlink ref="F115" r:id="rId114"/>
+    <hyperlink ref="F116" r:id="rId115"/>
+    <hyperlink ref="F117" r:id="rId116"/>
+    <hyperlink ref="F118" r:id="rId117"/>
+    <hyperlink ref="F119" r:id="rId118"/>
+    <hyperlink ref="F120" r:id="rId119"/>
+    <hyperlink ref="F121" r:id="rId120"/>
+    <hyperlink ref="F122" r:id="rId121"/>
+    <hyperlink ref="F123" r:id="rId122"/>
+    <hyperlink ref="F124" r:id="rId123"/>
+    <hyperlink ref="F125" r:id="rId124"/>
+    <hyperlink ref="F126" r:id="rId125"/>
+    <hyperlink ref="F127" r:id="rId126"/>
+    <hyperlink ref="F128" r:id="rId127"/>
+    <hyperlink ref="F129" r:id="rId128"/>
+    <hyperlink ref="F130" r:id="rId129"/>
+    <hyperlink ref="F131" r:id="rId130"/>
+    <hyperlink ref="F132" r:id="rId131"/>
+    <hyperlink ref="F133" r:id="rId132"/>
+    <hyperlink ref="F134" r:id="rId133"/>
+    <hyperlink ref="F135" r:id="rId134"/>
+    <hyperlink ref="F136" r:id="rId135"/>
+    <hyperlink ref="F137" r:id="rId136"/>
+    <hyperlink ref="F138" r:id="rId137"/>
+    <hyperlink ref="F139" r:id="rId138"/>
+    <hyperlink ref="F140" r:id="rId139"/>
+    <hyperlink ref="F141" r:id="rId140"/>
+    <hyperlink ref="F142" r:id="rId141"/>
+    <hyperlink ref="F143" r:id="rId142"/>
+    <hyperlink ref="F144" r:id="rId143"/>
+    <hyperlink ref="F145" r:id="rId144"/>
+    <hyperlink ref="F146" r:id="rId145"/>
+    <hyperlink ref="F147" r:id="rId146"/>
+    <hyperlink ref="F148" r:id="rId147"/>
+    <hyperlink ref="F149" r:id="rId148"/>
+    <hyperlink ref="F150" r:id="rId149"/>
+    <hyperlink ref="F151" r:id="rId150"/>
+    <hyperlink ref="F152" r:id="rId151"/>
+    <hyperlink ref="F153" r:id="rId152"/>
+    <hyperlink ref="F154" r:id="rId153"/>
+    <hyperlink ref="F155" r:id="rId154"/>
+    <hyperlink ref="F156" r:id="rId155"/>
+    <hyperlink ref="F157" r:id="rId156"/>
+    <hyperlink ref="F158" r:id="rId157"/>
+    <hyperlink ref="F159" r:id="rId158"/>
+    <hyperlink ref="F160" r:id="rId159"/>
+    <hyperlink ref="F161" r:id="rId160"/>
+    <hyperlink ref="F162" r:id="rId161"/>
+    <hyperlink ref="F163" r:id="rId162"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
